--- a/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
+++ b/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabir\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f25347fadc9be86b/Documents/MaintApp/MaintApp/maintainance ^0 expenditure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E53382-A171-4EBB-97C4-844A4882A8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{84E53382-A171-4EBB-97C4-844A4882A8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF71D720-7178-4AA6-9BB0-67446FD6A607}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Details MC " sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Details MC '!$A$1:$AC$81</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">EXPENSES!$A$1:$BA$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">EXPENSES!$A$1:$BA$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Month wise MC'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="241">
   <si>
     <t>Dr. Narendranath Pal</t>
   </si>
@@ -610,9 +610,6 @@
   </si>
   <si>
     <t>Stationery Items for Official Purpose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over All </t>
   </si>
   <si>
     <t xml:space="preserve">Sl No </t>
@@ -868,7 +865,7 @@
     <numFmt numFmtId="166" formatCode="\₹\ 0.00"/>
     <numFmt numFmtId="167" formatCode="\₹\ #,##0.00;[Red]\₹\ #,##0.00"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="35">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1026,12 +1023,6 @@
       <name val="Arial MT"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
@@ -1043,18 +1034,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -1211,7 +1190,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1458,17 +1437,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1476,19 +1444,6 @@
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1542,7 +1497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1822,10 +1777,10 @@
     <xf numFmtId="167" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1837,9 +1792,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1861,9 +1813,6 @@
     <xf numFmtId="16" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1876,7 +1825,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="17" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1906,13 +1855,13 @@
     <xf numFmtId="16" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1927,7 +1876,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="35" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="32" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1936,13 +1885,127 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="17" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="10" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1954,212 +2017,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="15" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="15" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="16" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="22" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="10" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="10" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2492,117 +2423,117 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AM81"/>
-  <sheetFormatPr defaultColWidth="9.296875" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" customWidth="1"/>
-    <col min="2" max="2" width="49.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="20" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="22.5" style="3" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="16.19921875" style="3" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="16.69921875" style="3" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.796875" style="3" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.83203125" style="3" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="18" style="3" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.69921875" style="3" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="20.19921875" style="3" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.8984375" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="21.296875" style="3" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" style="3" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" style="3" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="21.33203125" style="3" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="18.5" style="3" hidden="1" customWidth="1"/>
     <col min="16" max="17" width="18" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="17.69921875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="21.296875" customWidth="1"/>
-    <col min="20" max="21" width="16.796875" hidden="1" customWidth="1"/>
-    <col min="22" max="23" width="17.296875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="17.6640625" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="21.33203125" customWidth="1"/>
+    <col min="20" max="21" width="16.83203125" hidden="1" customWidth="1"/>
+    <col min="22" max="23" width="17.33203125" hidden="1" customWidth="1"/>
     <col min="24" max="25" width="18.5" hidden="1" customWidth="1"/>
     <col min="26" max="33" width="18.5" customWidth="1"/>
-    <col min="34" max="34" width="91.796875" customWidth="1"/>
+    <col min="34" max="34" width="91.83203125" customWidth="1"/>
     <col min="35" max="35" width="18.5" customWidth="1"/>
-    <col min="36" max="36" width="19.19921875" customWidth="1"/>
-    <col min="37" max="38" width="18.69921875" customWidth="1"/>
-    <col min="39" max="39" width="18.796875" customWidth="1"/>
+    <col min="36" max="36" width="19.1640625" customWidth="1"/>
+    <col min="37" max="38" width="18.6640625" customWidth="1"/>
+    <col min="39" max="39" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="20.149999999999999" customHeight="1">
-      <c r="A1" s="197" t="s">
+    <row r="1" spans="1:39" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
-      <c r="V1" s="197"/>
-      <c r="W1" s="197"/>
-      <c r="X1" s="197"/>
-      <c r="Y1" s="197"/>
-      <c r="Z1" s="197"/>
-      <c r="AA1" s="197"/>
-    </row>
-    <row r="2" spans="1:39" ht="20.149999999999999" customHeight="1">
-      <c r="A2" s="197"/>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
-      <c r="M2" s="197"/>
-      <c r="N2" s="197"/>
-      <c r="O2" s="197"/>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="197"/>
-      <c r="R2" s="197"/>
-      <c r="S2" s="197"/>
-      <c r="T2" s="197"/>
-      <c r="U2" s="197"/>
-      <c r="V2" s="197"/>
-      <c r="W2" s="197"/>
-      <c r="X2" s="197"/>
-      <c r="Y2" s="197"/>
-      <c r="Z2" s="197"/>
-      <c r="AA2" s="197"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
+      <c r="Y1" s="138"/>
+      <c r="Z1" s="138"/>
+      <c r="AA1" s="138"/>
+    </row>
+    <row r="2" spans="1:39" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="138"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
+      <c r="U2" s="138"/>
+      <c r="V2" s="138"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="138"/>
+      <c r="Z2" s="138"/>
+      <c r="AA2" s="138"/>
     </row>
     <row r="3" spans="1:39" ht="65.25" customHeight="1">
-      <c r="F3" s="190" t="s">
+      <c r="F3" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="190"/>
+      <c r="G3" s="149"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="190" t="s">
+      <c r="J3" s="149" t="s">
         <v>130</v>
       </c>
-      <c r="K3" s="190"/>
+      <c r="K3" s="149"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="190" t="s">
+      <c r="R3" s="149" t="s">
         <v>127</v>
       </c>
-      <c r="S3" s="190"/>
+      <c r="S3" s="149"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
@@ -2624,70 +2555,70 @@
       <c r="AL3" s="6"/>
       <c r="AM3" s="7"/>
     </row>
-    <row r="4" spans="1:39" ht="44.5" customHeight="1">
-      <c r="A4" s="182" t="s">
+    <row r="4" spans="1:39" ht="44.45" customHeight="1">
+      <c r="A4" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="176">
+      <c r="B4" s="140"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="147">
         <v>45748</v>
       </c>
-      <c r="G4" s="177"/>
-      <c r="H4" s="178">
+      <c r="G4" s="148"/>
+      <c r="H4" s="145">
         <v>45778</v>
       </c>
-      <c r="I4" s="179"/>
-      <c r="J4" s="176">
+      <c r="I4" s="146"/>
+      <c r="J4" s="147">
         <v>45809</v>
       </c>
-      <c r="K4" s="177"/>
-      <c r="L4" s="178">
+      <c r="K4" s="148"/>
+      <c r="L4" s="145">
         <v>45839</v>
       </c>
-      <c r="M4" s="179"/>
-      <c r="N4" s="176">
+      <c r="M4" s="146"/>
+      <c r="N4" s="147">
         <v>45870</v>
       </c>
-      <c r="O4" s="177"/>
-      <c r="P4" s="178">
+      <c r="O4" s="148"/>
+      <c r="P4" s="145">
         <v>45901</v>
       </c>
-      <c r="Q4" s="179"/>
-      <c r="R4" s="176">
+      <c r="Q4" s="146"/>
+      <c r="R4" s="147">
         <v>45931</v>
       </c>
-      <c r="S4" s="177"/>
-      <c r="T4" s="178">
+      <c r="S4" s="148"/>
+      <c r="T4" s="145">
         <v>45962</v>
       </c>
-      <c r="U4" s="179"/>
-      <c r="V4" s="173">
+      <c r="U4" s="146"/>
+      <c r="V4" s="136">
         <v>45992</v>
       </c>
-      <c r="W4" s="174"/>
-      <c r="X4" s="173">
+      <c r="W4" s="137"/>
+      <c r="X4" s="136">
         <v>46023</v>
       </c>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="173">
+      <c r="Y4" s="137"/>
+      <c r="Z4" s="136">
         <v>46054</v>
       </c>
-      <c r="AA4" s="174"/>
-      <c r="AB4" s="173">
+      <c r="AA4" s="137"/>
+      <c r="AB4" s="136">
         <v>46082</v>
       </c>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="173">
+      <c r="AC4" s="137"/>
+      <c r="AD4" s="136">
         <v>46113</v>
       </c>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="173">
+      <c r="AE4" s="137"/>
+      <c r="AF4" s="136">
         <v>46143</v>
       </c>
-      <c r="AG4" s="174"/>
+      <c r="AG4" s="137"/>
       <c r="AH4" s="10"/>
     </row>
     <row r="5" spans="1:39" s="5" customFormat="1" ht="31.5" customHeight="1">
@@ -3021,19 +2952,19 @@
       <c r="R8" s="73">
         <v>1200</v>
       </c>
-      <c r="S8" s="119"/>
+      <c r="S8" s="117"/>
       <c r="T8" s="73">
         <v>1200</v>
       </c>
-      <c r="U8" s="119"/>
+      <c r="U8" s="117"/>
       <c r="V8" s="73">
         <v>1200</v>
       </c>
-      <c r="W8" s="119"/>
+      <c r="W8" s="117"/>
       <c r="X8" s="73">
         <v>1200</v>
       </c>
-      <c r="Y8" s="119"/>
+      <c r="Y8" s="117"/>
       <c r="Z8" s="73">
         <v>1200</v>
       </c>
@@ -3115,7 +3046,7 @@
       <c r="W9" s="1"/>
       <c r="X9" s="28"/>
       <c r="Y9" s="1"/>
-      <c r="Z9" s="117"/>
+      <c r="Z9" s="115"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="57"/>
       <c r="AC9" s="1"/>
@@ -3392,40 +3323,40 @@
       <c r="AH12" s="1"/>
     </row>
     <row r="13" spans="1:39" ht="26.25" customHeight="1">
-      <c r="A13" s="185" t="s">
+      <c r="A13" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="186"/>
-      <c r="C13" s="186"/>
-      <c r="D13" s="186"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="101"/>
-      <c r="M13" s="100"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="103"/>
-      <c r="V13" s="103"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="103"/>
-      <c r="Y13" s="103"/>
-      <c r="Z13" s="103"/>
-      <c r="AA13" s="103"/>
-      <c r="AB13" s="103"/>
+      <c r="B13" s="158"/>
+      <c r="C13" s="158"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="102"/>
+      <c r="R13" s="102"/>
+      <c r="S13" s="102"/>
+      <c r="T13" s="102"/>
+      <c r="U13" s="102"/>
+      <c r="V13" s="102"/>
+      <c r="W13" s="102"/>
+      <c r="X13" s="102"/>
+      <c r="Y13" s="102"/>
+      <c r="Z13" s="102"/>
+      <c r="AA13" s="102"/>
+      <c r="AB13" s="102"/>
       <c r="AC13" s="1"/>
-      <c r="AD13" s="103"/>
+      <c r="AD13" s="102"/>
       <c r="AE13" s="1"/>
-      <c r="AF13" s="103"/>
+      <c r="AF13" s="102"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
     </row>
@@ -3952,33 +3883,33 @@
       <c r="AH20" s="41"/>
     </row>
     <row r="21" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A21" s="182" t="s">
+      <c r="A21" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="183"/>
-      <c r="C21" s="183"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="182"/>
-      <c r="G21" s="183"/>
-      <c r="H21" s="183"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="184"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="183"/>
-      <c r="M21" s="183"/>
-      <c r="N21" s="183"/>
-      <c r="O21" s="184"/>
-      <c r="P21" s="182"/>
-      <c r="Q21" s="183"/>
-      <c r="R21" s="183"/>
-      <c r="S21" s="183"/>
-      <c r="T21" s="184"/>
-      <c r="U21" s="182"/>
-      <c r="V21" s="183"/>
-      <c r="W21" s="183"/>
-      <c r="X21" s="183"/>
-      <c r="Y21" s="184"/>
+      <c r="B21" s="140"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="139"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="140"/>
+      <c r="N21" s="140"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="140"/>
+      <c r="R21" s="140"/>
+      <c r="S21" s="140"/>
+      <c r="T21" s="141"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="140"/>
+      <c r="W21" s="140"/>
+      <c r="X21" s="140"/>
+      <c r="Y21" s="141"/>
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
@@ -4586,33 +4517,33 @@
       <c r="AH29" s="1"/>
     </row>
     <row r="30" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A30" s="182" t="s">
+      <c r="A30" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="183"/>
-      <c r="C30" s="183"/>
-      <c r="D30" s="183"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="182"/>
-      <c r="G30" s="183"/>
-      <c r="H30" s="183"/>
-      <c r="I30" s="183"/>
-      <c r="J30" s="184"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="183"/>
-      <c r="M30" s="183"/>
-      <c r="N30" s="183"/>
-      <c r="O30" s="184"/>
-      <c r="P30" s="182"/>
-      <c r="Q30" s="183"/>
-      <c r="R30" s="183"/>
-      <c r="S30" s="183"/>
-      <c r="T30" s="184"/>
-      <c r="U30" s="182"/>
-      <c r="V30" s="183"/>
-      <c r="W30" s="183"/>
-      <c r="X30" s="183"/>
-      <c r="Y30" s="184"/>
+      <c r="B30" s="140"/>
+      <c r="C30" s="140"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
+      <c r="H30" s="140"/>
+      <c r="I30" s="140"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="140"/>
+      <c r="M30" s="140"/>
+      <c r="N30" s="140"/>
+      <c r="O30" s="141"/>
+      <c r="P30" s="139"/>
+      <c r="Q30" s="140"/>
+      <c r="R30" s="140"/>
+      <c r="S30" s="140"/>
+      <c r="T30" s="141"/>
+      <c r="U30" s="139"/>
+      <c r="V30" s="140"/>
+      <c r="W30" s="140"/>
+      <c r="X30" s="140"/>
+      <c r="Y30" s="141"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
@@ -5266,33 +5197,33 @@
       <c r="AH38" s="1"/>
     </row>
     <row r="39" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A39" s="182" t="s">
+      <c r="A39" s="139" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="183"/>
-      <c r="C39" s="183"/>
-      <c r="D39" s="183"/>
-      <c r="E39" s="184"/>
-      <c r="F39" s="182"/>
-      <c r="G39" s="183"/>
-      <c r="H39" s="183"/>
-      <c r="I39" s="183"/>
-      <c r="J39" s="184"/>
-      <c r="K39" s="182"/>
-      <c r="L39" s="183"/>
-      <c r="M39" s="183"/>
-      <c r="N39" s="183"/>
-      <c r="O39" s="184"/>
-      <c r="P39" s="182"/>
-      <c r="Q39" s="183"/>
-      <c r="R39" s="183"/>
-      <c r="S39" s="183"/>
-      <c r="T39" s="184"/>
-      <c r="U39" s="182"/>
-      <c r="V39" s="183"/>
-      <c r="W39" s="183"/>
-      <c r="X39" s="183"/>
-      <c r="Y39" s="184"/>
+      <c r="B39" s="140"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="140"/>
+      <c r="H39" s="140"/>
+      <c r="I39" s="140"/>
+      <c r="J39" s="141"/>
+      <c r="K39" s="139"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="140"/>
+      <c r="N39" s="140"/>
+      <c r="O39" s="141"/>
+      <c r="P39" s="139"/>
+      <c r="Q39" s="140"/>
+      <c r="R39" s="140"/>
+      <c r="S39" s="140"/>
+      <c r="T39" s="141"/>
+      <c r="U39" s="139"/>
+      <c r="V39" s="140"/>
+      <c r="W39" s="140"/>
+      <c r="X39" s="140"/>
+      <c r="Y39" s="141"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
@@ -5405,16 +5336,16 @@
       <c r="E41" s="38">
         <v>8820411025</v>
       </c>
-      <c r="F41" s="194" t="s">
+      <c r="F41" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="G41" s="195"/>
-      <c r="H41" s="195"/>
-      <c r="I41" s="195"/>
-      <c r="J41" s="195"/>
-      <c r="K41" s="195"/>
-      <c r="L41" s="195"/>
-      <c r="M41" s="196"/>
+      <c r="G41" s="143"/>
+      <c r="H41" s="143"/>
+      <c r="I41" s="143"/>
+      <c r="J41" s="143"/>
+      <c r="K41" s="143"/>
+      <c r="L41" s="143"/>
+      <c r="M41" s="144"/>
       <c r="N41" s="51">
         <v>1300</v>
       </c>
@@ -5888,35 +5819,35 @@
       <c r="AH46" s="1"/>
     </row>
     <row r="47" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A47" s="182" t="s">
+      <c r="A47" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="183"/>
-      <c r="C47" s="183"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="184"/>
-      <c r="F47" s="182"/>
-      <c r="G47" s="183"/>
-      <c r="H47" s="183"/>
-      <c r="I47" s="183"/>
-      <c r="J47" s="184"/>
-      <c r="K47" s="182"/>
-      <c r="L47" s="183"/>
-      <c r="M47" s="183">
+      <c r="B47" s="140"/>
+      <c r="C47" s="140"/>
+      <c r="D47" s="140"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
+      <c r="H47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="141"/>
+      <c r="K47" s="139"/>
+      <c r="L47" s="140"/>
+      <c r="M47" s="140">
         <v>45884</v>
       </c>
-      <c r="N47" s="183"/>
-      <c r="O47" s="184"/>
-      <c r="P47" s="182"/>
-      <c r="Q47" s="183"/>
-      <c r="R47" s="183"/>
-      <c r="S47" s="183"/>
-      <c r="T47" s="184"/>
-      <c r="U47" s="182"/>
-      <c r="V47" s="183"/>
-      <c r="W47" s="183"/>
-      <c r="X47" s="183"/>
-      <c r="Y47" s="184"/>
+      <c r="N47" s="140"/>
+      <c r="O47" s="141"/>
+      <c r="P47" s="139"/>
+      <c r="Q47" s="140"/>
+      <c r="R47" s="140"/>
+      <c r="S47" s="140"/>
+      <c r="T47" s="141"/>
+      <c r="U47" s="139"/>
+      <c r="V47" s="140"/>
+      <c r="W47" s="140"/>
+      <c r="X47" s="140"/>
+      <c r="Y47" s="141"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
@@ -5982,19 +5913,19 @@
       <c r="R48" s="28">
         <v>1500</v>
       </c>
-      <c r="S48" s="118"/>
+      <c r="S48" s="116"/>
       <c r="T48" s="28">
         <v>1500</v>
       </c>
-      <c r="U48" s="118"/>
+      <c r="U48" s="116"/>
       <c r="V48" s="28">
         <v>1500</v>
       </c>
-      <c r="W48" s="118"/>
+      <c r="W48" s="116"/>
       <c r="X48" s="28">
         <v>1500</v>
       </c>
-      <c r="Y48" s="118"/>
+      <c r="Y48" s="116"/>
       <c r="Z48" s="28">
         <v>1500</v>
       </c>
@@ -6327,16 +6258,16 @@
       <c r="E53" s="38">
         <v>7044376634</v>
       </c>
-      <c r="F53" s="194" t="s">
+      <c r="F53" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="G53" s="195"/>
-      <c r="H53" s="195"/>
-      <c r="I53" s="195"/>
-      <c r="J53" s="195"/>
-      <c r="K53" s="195"/>
-      <c r="L53" s="195"/>
-      <c r="M53" s="196"/>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="143"/>
+      <c r="J53" s="143"/>
+      <c r="K53" s="143"/>
+      <c r="L53" s="143"/>
+      <c r="M53" s="144"/>
       <c r="N53" s="52">
         <v>1300</v>
       </c>
@@ -6405,51 +6336,51 @@
       <c r="E54" s="38">
         <v>7908550094</v>
       </c>
-      <c r="F54" s="194" t="s">
+      <c r="F54" s="142" t="s">
         <v>138</v>
       </c>
-      <c r="G54" s="195"/>
-      <c r="H54" s="195"/>
-      <c r="I54" s="195"/>
-      <c r="J54" s="195"/>
-      <c r="K54" s="195"/>
-      <c r="L54" s="195"/>
-      <c r="M54" s="196"/>
+      <c r="G54" s="143"/>
+      <c r="H54" s="143"/>
+      <c r="I54" s="143"/>
+      <c r="J54" s="143"/>
+      <c r="K54" s="143"/>
+      <c r="L54" s="143"/>
+      <c r="M54" s="144"/>
       <c r="N54" s="51">
         <v>1000</v>
       </c>
       <c r="O54" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P54" s="51">
         <v>1000</v>
       </c>
       <c r="Q54" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R54" s="73">
         <v>1200</v>
       </c>
-      <c r="S54" s="120" t="s">
-        <v>190</v>
+      <c r="S54" s="118" t="s">
+        <v>189</v>
       </c>
       <c r="T54" s="73">
         <v>1200</v>
       </c>
-      <c r="U54" s="120" t="s">
-        <v>190</v>
+      <c r="U54" s="118" t="s">
+        <v>189</v>
       </c>
       <c r="V54" s="73">
         <v>1200</v>
       </c>
-      <c r="W54" s="120" t="s">
-        <v>190</v>
+      <c r="W54" s="118" t="s">
+        <v>189</v>
       </c>
       <c r="X54" s="73">
         <v>1200</v>
       </c>
-      <c r="Y54" s="120" t="s">
-        <v>190</v>
+      <c r="Y54" s="118" t="s">
+        <v>189</v>
       </c>
       <c r="Z54" s="73">
         <v>1200</v>
@@ -6512,33 +6443,33 @@
       <c r="AH55" s="41"/>
     </row>
     <row r="56" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A56" s="182" t="s">
+      <c r="A56" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="183"/>
-      <c r="C56" s="183"/>
-      <c r="D56" s="183"/>
-      <c r="E56" s="184"/>
-      <c r="F56" s="182"/>
-      <c r="G56" s="183"/>
-      <c r="H56" s="183"/>
-      <c r="I56" s="183"/>
-      <c r="J56" s="184"/>
-      <c r="K56" s="182"/>
-      <c r="L56" s="183"/>
-      <c r="M56" s="183"/>
-      <c r="N56" s="183"/>
-      <c r="O56" s="184"/>
-      <c r="P56" s="182"/>
-      <c r="Q56" s="183"/>
-      <c r="R56" s="183"/>
-      <c r="S56" s="183"/>
-      <c r="T56" s="184"/>
-      <c r="U56" s="182"/>
-      <c r="V56" s="183"/>
-      <c r="W56" s="183"/>
-      <c r="X56" s="183"/>
-      <c r="Y56" s="184"/>
+      <c r="B56" s="140"/>
+      <c r="C56" s="140"/>
+      <c r="D56" s="140"/>
+      <c r="E56" s="141"/>
+      <c r="F56" s="139"/>
+      <c r="G56" s="140"/>
+      <c r="H56" s="140"/>
+      <c r="I56" s="140"/>
+      <c r="J56" s="141"/>
+      <c r="K56" s="139"/>
+      <c r="L56" s="140"/>
+      <c r="M56" s="140"/>
+      <c r="N56" s="140"/>
+      <c r="O56" s="141"/>
+      <c r="P56" s="139"/>
+      <c r="Q56" s="140"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="140"/>
+      <c r="T56" s="141"/>
+      <c r="U56" s="139"/>
+      <c r="V56" s="140"/>
+      <c r="W56" s="140"/>
+      <c r="X56" s="140"/>
+      <c r="Y56" s="141"/>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
@@ -6610,7 +6541,7 @@
       <c r="T57" s="73">
         <v>1500</v>
       </c>
-      <c r="U57" s="119"/>
+      <c r="U57" s="117"/>
       <c r="V57" s="73">
         <v>1500</v>
       </c>
@@ -6725,18 +6656,18 @@
       <c r="E59" s="38">
         <v>9831313288</v>
       </c>
-      <c r="F59" s="191" t="s">
+      <c r="F59" s="151" t="s">
         <v>139</v>
       </c>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="192"/>
-      <c r="L59" s="192"/>
-      <c r="M59" s="192"/>
-      <c r="N59" s="192"/>
-      <c r="O59" s="193"/>
+      <c r="G59" s="152"/>
+      <c r="H59" s="152"/>
+      <c r="I59" s="152"/>
+      <c r="J59" s="152"/>
+      <c r="K59" s="152"/>
+      <c r="L59" s="152"/>
+      <c r="M59" s="152"/>
+      <c r="N59" s="152"/>
+      <c r="O59" s="153"/>
       <c r="P59" s="52"/>
       <c r="Q59" s="41"/>
       <c r="R59" s="28">
@@ -7112,33 +7043,33 @@
       <c r="AH64" s="41"/>
     </row>
     <row r="65" spans="1:34" ht="26.25" customHeight="1">
-      <c r="A65" s="182" t="s">
+      <c r="A65" s="139" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="183"/>
-      <c r="C65" s="183"/>
-      <c r="D65" s="183"/>
-      <c r="E65" s="184"/>
-      <c r="F65" s="182"/>
-      <c r="G65" s="183"/>
-      <c r="H65" s="183"/>
-      <c r="I65" s="183"/>
-      <c r="J65" s="184"/>
-      <c r="K65" s="182"/>
-      <c r="L65" s="183"/>
-      <c r="M65" s="183"/>
-      <c r="N65" s="183"/>
-      <c r="O65" s="184"/>
-      <c r="P65" s="182"/>
-      <c r="Q65" s="183"/>
-      <c r="R65" s="183"/>
-      <c r="S65" s="183"/>
-      <c r="T65" s="184"/>
-      <c r="U65" s="182"/>
-      <c r="V65" s="183"/>
-      <c r="W65" s="183"/>
-      <c r="X65" s="183"/>
-      <c r="Y65" s="184"/>
+      <c r="B65" s="140"/>
+      <c r="C65" s="140"/>
+      <c r="D65" s="140"/>
+      <c r="E65" s="141"/>
+      <c r="F65" s="139"/>
+      <c r="G65" s="140"/>
+      <c r="H65" s="140"/>
+      <c r="I65" s="140"/>
+      <c r="J65" s="141"/>
+      <c r="K65" s="139"/>
+      <c r="L65" s="140"/>
+      <c r="M65" s="140"/>
+      <c r="N65" s="140"/>
+      <c r="O65" s="141"/>
+      <c r="P65" s="139"/>
+      <c r="Q65" s="140"/>
+      <c r="R65" s="140"/>
+      <c r="S65" s="140"/>
+      <c r="T65" s="141"/>
+      <c r="U65" s="139"/>
+      <c r="V65" s="140"/>
+      <c r="W65" s="140"/>
+      <c r="X65" s="140"/>
+      <c r="Y65" s="141"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
@@ -7366,11 +7297,11 @@
       <c r="T70" s="73">
         <v>1500</v>
       </c>
-      <c r="U70" s="119"/>
+      <c r="U70" s="117"/>
       <c r="V70" s="73">
         <v>1500</v>
       </c>
-      <c r="W70" s="119"/>
+      <c r="W70" s="117"/>
       <c r="X70" s="73">
         <v>1500</v>
       </c>
@@ -7450,11 +7381,11 @@
       <c r="T71" s="73">
         <v>1500</v>
       </c>
-      <c r="U71" s="119"/>
+      <c r="U71" s="117"/>
       <c r="V71" s="73">
         <v>1500</v>
       </c>
-      <c r="W71" s="119"/>
+      <c r="W71" s="117"/>
       <c r="X71" s="73">
         <v>1500</v>
       </c>
@@ -7534,11 +7465,11 @@
       <c r="T72" s="73">
         <v>1200</v>
       </c>
-      <c r="U72" s="119"/>
+      <c r="U72" s="117"/>
       <c r="V72" s="73">
         <v>1200</v>
       </c>
-      <c r="W72" s="119"/>
+      <c r="W72" s="117"/>
       <c r="X72" s="73">
         <v>1200</v>
       </c>
@@ -7690,7 +7621,7 @@
         <v>64</v>
       </c>
       <c r="B76" s="61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C76" s="62"/>
       <c r="D76" s="63"/>
@@ -7731,12 +7662,12 @@
       <c r="AG76" s="70"/>
       <c r="AH76" s="41"/>
     </row>
-    <row r="77" spans="1:34" ht="26.5" customHeight="1">
+    <row r="77" spans="1:34" ht="26.45" customHeight="1">
       <c r="A77" s="22"/>
-      <c r="B77" s="180" t="s">
+      <c r="B77" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="C77" s="181"/>
+      <c r="C77" s="156"/>
       <c r="D77" s="23"/>
       <c r="E77" s="24"/>
       <c r="F77" s="25"/>
@@ -7770,13 +7701,13 @@
       <c r="AH77" s="1"/>
     </row>
     <row r="78" spans="1:34" ht="27" customHeight="1">
-      <c r="A78" s="189" t="s">
+      <c r="A78" s="150" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="189"/>
-      <c r="C78" s="189"/>
-      <c r="D78" s="189"/>
-      <c r="E78" s="189"/>
+      <c r="B78" s="150"/>
+      <c r="C78" s="150"/>
+      <c r="D78" s="150"/>
+      <c r="E78" s="150"/>
       <c r="F78" s="28">
         <f>SUM(F6:F77)</f>
         <v>55200</v>
@@ -7864,90 +7795,146 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="25">
-      <c r="F80" s="176">
+    <row r="80" spans="1:34" ht="25.5">
+      <c r="F80" s="147">
         <v>45748</v>
       </c>
-      <c r="G80" s="177"/>
-      <c r="H80" s="178">
+      <c r="G80" s="148"/>
+      <c r="H80" s="145">
         <v>45778</v>
       </c>
-      <c r="I80" s="179"/>
-      <c r="J80" s="176">
+      <c r="I80" s="146"/>
+      <c r="J80" s="147">
         <v>45809</v>
       </c>
-      <c r="K80" s="177"/>
-      <c r="L80" s="178">
+      <c r="K80" s="148"/>
+      <c r="L80" s="145">
         <v>45839</v>
       </c>
-      <c r="M80" s="179"/>
-      <c r="N80" s="176">
+      <c r="M80" s="146"/>
+      <c r="N80" s="147">
         <v>45870</v>
       </c>
-      <c r="O80" s="177"/>
-      <c r="P80" s="178">
+      <c r="O80" s="148"/>
+      <c r="P80" s="145">
         <v>45901</v>
       </c>
-      <c r="Q80" s="179"/>
-      <c r="R80" s="176">
+      <c r="Q80" s="146"/>
+      <c r="R80" s="147">
         <v>45931</v>
       </c>
-      <c r="S80" s="177"/>
-      <c r="T80" s="178">
+      <c r="S80" s="148"/>
+      <c r="T80" s="145">
         <v>45962</v>
       </c>
-      <c r="U80" s="179"/>
-      <c r="V80" s="173">
+      <c r="U80" s="146"/>
+      <c r="V80" s="136">
         <v>45992</v>
       </c>
-      <c r="W80" s="174"/>
-      <c r="X80" s="173">
+      <c r="W80" s="137"/>
+      <c r="X80" s="136">
         <v>46023</v>
       </c>
-      <c r="Y80" s="174"/>
-      <c r="Z80" s="173">
+      <c r="Y80" s="137"/>
+      <c r="Z80" s="136">
         <v>46054</v>
       </c>
-      <c r="AA80" s="174"/>
-      <c r="AB80" s="173">
+      <c r="AA80" s="137"/>
+      <c r="AB80" s="136">
         <v>46082</v>
       </c>
-      <c r="AC80" s="174"/>
-      <c r="AD80" s="173">
+      <c r="AC80" s="137"/>
+      <c r="AD80" s="136">
         <v>46113</v>
       </c>
-      <c r="AE80" s="174"/>
-      <c r="AF80" s="173">
+      <c r="AE80" s="137"/>
+      <c r="AF80" s="136">
         <v>46143</v>
       </c>
-      <c r="AG80" s="174"/>
-    </row>
-    <row r="81" spans="1:17" ht="32.5" customHeight="1">
-      <c r="A81" s="175" t="s">
+      <c r="AG80" s="137"/>
+    </row>
+    <row r="81" spans="1:17" ht="32.450000000000003" customHeight="1">
+      <c r="A81" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="B81" s="175"/>
-      <c r="C81" s="175"/>
-      <c r="D81" s="175"/>
-      <c r="E81" s="175"/>
-      <c r="F81" s="188">
+      <c r="B81" s="154"/>
+      <c r="C81" s="154"/>
+      <c r="D81" s="154"/>
+      <c r="E81" s="154"/>
+      <c r="F81" s="160">
         <f>SUM(F78:AC78)</f>
         <v>767400</v>
       </c>
-      <c r="G81" s="188"/>
-      <c r="H81" s="188"/>
-      <c r="I81" s="188"/>
-      <c r="J81" s="188"/>
-      <c r="K81" s="188"/>
-      <c r="L81" s="188"/>
-      <c r="M81" s="188"/>
-      <c r="N81" s="188"/>
-      <c r="O81" s="188"/>
-      <c r="P81" s="188"/>
-      <c r="Q81" s="188"/>
+      <c r="G81" s="160"/>
+      <c r="H81" s="160"/>
+      <c r="I81" s="160"/>
+      <c r="J81" s="160"/>
+      <c r="K81" s="160"/>
+      <c r="L81" s="160"/>
+      <c r="M81" s="160"/>
+      <c r="N81" s="160"/>
+      <c r="O81" s="160"/>
+      <c r="P81" s="160"/>
+      <c r="Q81" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="AB80:AC80"/>
+    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F81:Q81"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="P21:T21"/>
+    <mergeCell ref="U21:Y21"/>
+    <mergeCell ref="F30:J30"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="U30:Y30"/>
+    <mergeCell ref="F39:J39"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="F59:O59"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="U56:Y56"/>
+    <mergeCell ref="P30:T30"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:O21"/>
+    <mergeCell ref="U39:Y39"/>
+    <mergeCell ref="F41:M41"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="K56:O56"/>
+    <mergeCell ref="P56:T56"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="P39:T39"/>
+    <mergeCell ref="Z80:AA80"/>
+    <mergeCell ref="T80:U80"/>
+    <mergeCell ref="V80:W80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="X80:Y80"/>
     <mergeCell ref="AD4:AE4"/>
     <mergeCell ref="AD80:AE80"/>
     <mergeCell ref="AF4:AG4"/>
@@ -7964,62 +7951,6 @@
     <mergeCell ref="P47:T47"/>
     <mergeCell ref="U47:Y47"/>
     <mergeCell ref="F56:J56"/>
-    <mergeCell ref="K56:O56"/>
-    <mergeCell ref="P56:T56"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="P39:T39"/>
-    <mergeCell ref="Z80:AA80"/>
-    <mergeCell ref="T80:U80"/>
-    <mergeCell ref="V80:W80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="X80:Y80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="U56:Y56"/>
-    <mergeCell ref="P30:T30"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:O21"/>
-    <mergeCell ref="U39:Y39"/>
-    <mergeCell ref="F41:M41"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="P21:T21"/>
-    <mergeCell ref="U21:Y21"/>
-    <mergeCell ref="F30:J30"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="U30:Y30"/>
-    <mergeCell ref="F39:J39"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="F59:O59"/>
-    <mergeCell ref="AB80:AC80"/>
-    <mergeCell ref="A81:E81"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F81:Q81"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="AB4:AC4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8034,21 +7965,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388B0986-349B-4B1A-860F-2315B64A4EE8}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="31.296875" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="52.5" customHeight="1">
-      <c r="A1" s="198" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-    </row>
-    <row r="3" spans="1:4" ht="26.5" customHeight="1">
+      <c r="A1" s="161" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+    </row>
+    <row r="3" spans="1:4" ht="26.45" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>129</v>
       </c>
@@ -8059,7 +7990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="4" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A4" s="48">
         <v>1</v>
       </c>
@@ -8071,7 +8002,7 @@
         <v>55200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="5" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A5" s="48">
         <v>2</v>
       </c>
@@ -8083,7 +8014,7 @@
         <v>55200</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="6" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A6" s="48">
         <v>3</v>
       </c>
@@ -8095,7 +8026,7 @@
         <v>54100</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="7" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A7" s="48">
         <v>4</v>
       </c>
@@ -8107,7 +8038,7 @@
         <v>71300</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="8" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A8" s="48">
         <v>5</v>
       </c>
@@ -8119,7 +8050,7 @@
         <v>57700</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="9" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A9" s="48">
         <v>6</v>
       </c>
@@ -8131,7 +8062,7 @@
         <v>57700</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="10" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A10" s="48">
         <v>7</v>
       </c>
@@ -8142,11 +8073,11 @@
         <f>'Details MC '!R78</f>
         <v>78900</v>
       </c>
-      <c r="D10" s="122" t="s">
+      <c r="D10" s="120" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="11" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A11" s="48">
         <v>8</v>
       </c>
@@ -8158,7 +8089,7 @@
         <v>68500</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18.649999999999999" customHeight="1">
+    <row r="12" spans="1:4" ht="18.600000000000001" customHeight="1">
       <c r="A12" s="48">
         <v>9</v>
       </c>
@@ -8170,7 +8101,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.5">
+    <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="48">
         <v>10</v>
       </c>
@@ -8182,7 +8113,7 @@
         <v>65800</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.5">
+    <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="48">
         <v>11</v>
       </c>
@@ -8194,8 +8125,8 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.5">
-      <c r="A15" s="200">
+    <row r="15" spans="1:4" ht="15.75">
+      <c r="A15" s="129">
         <v>12</v>
       </c>
       <c r="B15" s="47">
@@ -8206,8 +8137,8 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.5">
-      <c r="A16" s="200">
+    <row r="16" spans="1:4" ht="15.75">
+      <c r="A16" s="129">
         <v>13</v>
       </c>
       <c r="B16" s="47">
@@ -8218,8 +8149,8 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.5">
-      <c r="A17" s="200">
+    <row r="17" spans="1:3" ht="15.75">
+      <c r="A17" s="129">
         <v>14</v>
       </c>
       <c r="B17" s="47">
@@ -8241,146 +8172,146 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810C1D33-6CDF-4F26-B97B-E4FC71263824}">
-  <dimension ref="A1:BA141"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="A1:BA137"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" customWidth="1"/>
-    <col min="2" max="2" width="58.19921875" customWidth="1"/>
-    <col min="3" max="3" width="12.19921875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.09765625" hidden="1" customWidth="1"/>
-    <col min="5" max="16" width="14.5" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="26" max="28" width="14.5" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="30" max="32" width="14.5" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="34" max="36" width="14.5" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="38" max="40" width="14.5" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="18.796875" hidden="1" customWidth="1"/>
-    <col min="42" max="44" width="14.5" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="18.796875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="58.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="16" width="14.5" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="20" width="14.5" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="24" width="14.5" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="26" max="28" width="14.5" customWidth="1"/>
+    <col min="29" max="29" width="18.83203125" customWidth="1"/>
+    <col min="30" max="32" width="14.5" customWidth="1"/>
+    <col min="33" max="33" width="18.83203125" customWidth="1"/>
+    <col min="34" max="36" width="14.5" customWidth="1"/>
+    <col min="37" max="37" width="18.83203125" customWidth="1"/>
+    <col min="38" max="40" width="14.5" customWidth="1"/>
+    <col min="41" max="41" width="18.83203125" customWidth="1"/>
+    <col min="42" max="44" width="14.5" customWidth="1"/>
+    <col min="45" max="45" width="18.83203125" customWidth="1"/>
     <col min="46" max="48" width="14.5" customWidth="1"/>
-    <col min="49" max="49" width="18.796875" customWidth="1"/>
+    <col min="49" max="49" width="18.83203125" customWidth="1"/>
     <col min="50" max="52" width="14.5" customWidth="1"/>
-    <col min="53" max="53" width="22.19921875" customWidth="1"/>
+    <col min="53" max="53" width="22.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="29.15" customHeight="1">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:53" ht="29.1" customHeight="1">
+      <c r="A1" s="170" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
     </row>
     <row r="2" spans="1:53" ht="31.5" customHeight="1">
-      <c r="A2" s="136" t="s">
+      <c r="A2" s="172" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="174" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="160" t="s">
+      <c r="C2" s="166" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="161"/>
-      <c r="E2" s="162" t="s">
+      <c r="D2" s="167"/>
+      <c r="E2" s="164" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="163"/>
-      <c r="G2" s="164"/>
-      <c r="H2" s="160" t="s">
+      <c r="F2" s="165"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="166" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="161"/>
-      <c r="J2" s="165"/>
-      <c r="K2" s="162" t="s">
+      <c r="I2" s="167"/>
+      <c r="J2" s="168"/>
+      <c r="K2" s="164" t="s">
         <v>146</v>
       </c>
-      <c r="L2" s="163"/>
-      <c r="M2" s="164"/>
-      <c r="N2" s="160" t="s">
+      <c r="L2" s="165"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="166" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="161"/>
-      <c r="P2" s="161"/>
-      <c r="Q2" s="165"/>
-      <c r="R2" s="162" t="s">
-        <v>169</v>
-      </c>
-      <c r="S2" s="163"/>
-      <c r="T2" s="163"/>
-      <c r="U2" s="163"/>
-      <c r="V2" s="131" t="s">
-        <v>183</v>
-      </c>
-      <c r="W2" s="132"/>
-      <c r="X2" s="132"/>
-      <c r="Y2" s="132"/>
-      <c r="Z2" s="131" t="s">
+      <c r="O2" s="167"/>
+      <c r="P2" s="167"/>
+      <c r="Q2" s="168"/>
+      <c r="R2" s="164" t="s">
+        <v>168</v>
+      </c>
+      <c r="S2" s="165"/>
+      <c r="T2" s="165"/>
+      <c r="U2" s="165"/>
+      <c r="V2" s="162" t="s">
+        <v>182</v>
+      </c>
+      <c r="W2" s="163"/>
+      <c r="X2" s="163"/>
+      <c r="Y2" s="163"/>
+      <c r="Z2" s="162" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA2" s="163"/>
+      <c r="AB2" s="163"/>
+      <c r="AC2" s="163"/>
+      <c r="AD2" s="162" t="s">
         <v>188</v>
       </c>
-      <c r="AA2" s="132"/>
-      <c r="AB2" s="132"/>
-      <c r="AC2" s="132"/>
-      <c r="AD2" s="131" t="s">
-        <v>189</v>
-      </c>
-      <c r="AE2" s="132"/>
-      <c r="AF2" s="132"/>
-      <c r="AG2" s="132"/>
-      <c r="AH2" s="131" t="s">
-        <v>191</v>
-      </c>
-      <c r="AI2" s="132"/>
-      <c r="AJ2" s="132"/>
-      <c r="AK2" s="132"/>
-      <c r="AL2" s="131" t="s">
+      <c r="AE2" s="163"/>
+      <c r="AF2" s="163"/>
+      <c r="AG2" s="163"/>
+      <c r="AH2" s="162" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI2" s="163"/>
+      <c r="AJ2" s="163"/>
+      <c r="AK2" s="163"/>
+      <c r="AL2" s="162" t="s">
+        <v>215</v>
+      </c>
+      <c r="AM2" s="163"/>
+      <c r="AN2" s="163"/>
+      <c r="AO2" s="163"/>
+      <c r="AP2" s="162" t="s">
         <v>216</v>
       </c>
-      <c r="AM2" s="132"/>
-      <c r="AN2" s="132"/>
-      <c r="AO2" s="132"/>
-      <c r="AP2" s="131" t="s">
-        <v>217</v>
-      </c>
-      <c r="AQ2" s="132"/>
-      <c r="AR2" s="132"/>
-      <c r="AS2" s="132"/>
-      <c r="AT2" s="131" t="s">
+      <c r="AQ2" s="163"/>
+      <c r="AR2" s="163"/>
+      <c r="AS2" s="163"/>
+      <c r="AT2" s="162" t="s">
+        <v>226</v>
+      </c>
+      <c r="AU2" s="163"/>
+      <c r="AV2" s="163"/>
+      <c r="AW2" s="163"/>
+      <c r="AX2" s="162" t="s">
         <v>227</v>
       </c>
-      <c r="AU2" s="132"/>
-      <c r="AV2" s="132"/>
-      <c r="AW2" s="132"/>
-      <c r="AX2" s="131" t="s">
-        <v>228</v>
-      </c>
-      <c r="AY2" s="132"/>
-      <c r="AZ2" s="132"/>
-      <c r="BA2" s="132"/>
+      <c r="AY2" s="163"/>
+      <c r="AZ2" s="163"/>
+      <c r="BA2" s="163"/>
     </row>
     <row r="3" spans="1:53" ht="45.75" customHeight="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="138"/>
+      <c r="A3" s="173"/>
+      <c r="B3" s="174"/>
       <c r="C3" s="76" t="s">
         <v>149</v>
       </c>
@@ -8394,7 +8325,7 @@
         <v>150</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H3" s="76" t="s">
         <v>149</v>
@@ -8412,7 +8343,7 @@
         <v>150</v>
       </c>
       <c r="M3" s="76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N3" s="76" t="s">
         <v>149</v>
@@ -8421,9 +8352,9 @@
         <v>150</v>
       </c>
       <c r="P3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="R3" s="76" t="s">
@@ -8433,9 +8364,9 @@
         <v>150</v>
       </c>
       <c r="T3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="U3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="U3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="V3" s="76" t="s">
@@ -8445,9 +8376,9 @@
         <v>150</v>
       </c>
       <c r="X3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="Z3" s="76" t="s">
@@ -8457,9 +8388,9 @@
         <v>150</v>
       </c>
       <c r="AB3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AC3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AC3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AD3" s="76" t="s">
@@ -8469,9 +8400,9 @@
         <v>150</v>
       </c>
       <c r="AF3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AG3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AH3" s="76" t="s">
@@ -8481,9 +8412,9 @@
         <v>150</v>
       </c>
       <c r="AJ3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AL3" s="76" t="s">
@@ -8493,9 +8424,9 @@
         <v>150</v>
       </c>
       <c r="AN3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AO3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AO3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AP3" s="76" t="s">
@@ -8505,9 +8436,9 @@
         <v>150</v>
       </c>
       <c r="AR3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AS3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AS3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AT3" s="76" t="s">
@@ -8517,9 +8448,9 @@
         <v>150</v>
       </c>
       <c r="AV3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="AW3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="AW3" s="103" t="s">
         <v>148</v>
       </c>
       <c r="AX3" s="76" t="s">
@@ -8529,13 +8460,13 @@
         <v>150</v>
       </c>
       <c r="AZ3" s="76" t="s">
-        <v>171</v>
-      </c>
-      <c r="BA3" s="104" t="s">
+        <v>170</v>
+      </c>
+      <c r="BA3" s="103" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="44.5" customHeight="1">
+    <row r="4" spans="1:53" ht="44.45" customHeight="1">
       <c r="A4" s="78">
         <v>1</v>
       </c>
@@ -8553,99 +8484,99 @@
       <c r="K4" s="84">
         <v>5500</v>
       </c>
-      <c r="L4" s="105">
+      <c r="L4" s="104">
         <v>45843</v>
       </c>
-      <c r="M4" s="105"/>
-      <c r="N4" s="114">
+      <c r="M4" s="104"/>
+      <c r="N4" s="112">
         <v>5500</v>
       </c>
-      <c r="O4" s="105">
+      <c r="O4" s="104">
         <v>45874</v>
       </c>
-      <c r="P4" s="105"/>
+      <c r="P4" s="104"/>
       <c r="Q4" s="85"/>
-      <c r="R4" s="115">
+      <c r="R4" s="113">
         <v>5500</v>
       </c>
-      <c r="S4" s="105">
+      <c r="S4" s="104">
         <v>45905</v>
       </c>
-      <c r="T4" s="105"/>
+      <c r="T4" s="104"/>
       <c r="U4" s="85"/>
-      <c r="V4" s="115">
+      <c r="V4" s="113">
         <v>4950</v>
       </c>
-      <c r="W4" s="105">
+      <c r="W4" s="104">
         <v>45938</v>
       </c>
-      <c r="X4" s="105"/>
+      <c r="X4" s="104"/>
       <c r="Y4" s="85"/>
-      <c r="Z4" s="115">
+      <c r="Z4" s="113">
         <v>5340</v>
       </c>
-      <c r="AA4" s="105" t="s">
+      <c r="AA4" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB4" s="104"/>
+      <c r="AC4" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="AB4" s="105"/>
-      <c r="AC4" s="85" t="s">
-        <v>193</v>
-      </c>
-      <c r="AD4" s="115">
+      <c r="AD4" s="113">
         <v>5500</v>
       </c>
-      <c r="AE4" s="105" t="s">
-        <v>201</v>
-      </c>
-      <c r="AF4" s="105"/>
+      <c r="AE4" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="AF4" s="104"/>
       <c r="AG4" s="85"/>
-      <c r="AH4" s="115">
+      <c r="AH4" s="113">
         <v>5323</v>
       </c>
-      <c r="AI4" s="105" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ4" s="105"/>
+      <c r="AI4" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ4" s="104"/>
       <c r="AK4" s="85"/>
-      <c r="AL4" s="115">
+      <c r="AL4" s="113">
         <v>8430</v>
       </c>
-      <c r="AM4" s="105">
+      <c r="AM4" s="104">
         <v>46063</v>
       </c>
-      <c r="AN4" s="105"/>
+      <c r="AN4" s="104"/>
       <c r="AO4" s="85"/>
-      <c r="AP4" s="115">
+      <c r="AP4" s="113">
         <v>10180</v>
       </c>
-      <c r="AQ4" s="105">
+      <c r="AQ4" s="104">
         <v>46100</v>
       </c>
-      <c r="AR4" s="105"/>
+      <c r="AR4" s="104"/>
       <c r="AS4" s="85"/>
-      <c r="AT4" s="115">
+      <c r="AT4" s="113">
         <v>11000</v>
       </c>
-      <c r="AU4" s="105">
+      <c r="AU4" s="104">
         <v>46130</v>
       </c>
-      <c r="AV4" s="105"/>
+      <c r="AV4" s="104"/>
       <c r="AW4" s="85"/>
-      <c r="AX4" s="115">
+      <c r="AX4" s="113">
         <v>10267</v>
       </c>
-      <c r="AY4" s="105">
+      <c r="AY4" s="104">
         <v>46157</v>
       </c>
-      <c r="AZ4" s="105"/>
+      <c r="AZ4" s="104"/>
       <c r="BA4" s="85"/>
     </row>
-    <row r="5" spans="1:53" ht="44.5" customHeight="1">
+    <row r="5" spans="1:53" ht="44.45" customHeight="1">
       <c r="A5" s="86">
         <v>2</v>
       </c>
       <c r="B5" s="87" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C5" s="80"/>
       <c r="D5" s="81"/>
@@ -8658,98 +8589,98 @@
       <c r="K5" s="84">
         <v>5000</v>
       </c>
-      <c r="L5" s="105">
+      <c r="L5" s="104">
         <v>45843</v>
       </c>
-      <c r="M5" s="105"/>
-      <c r="N5" s="114">
+      <c r="M5" s="104"/>
+      <c r="N5" s="112">
         <v>10000</v>
       </c>
-      <c r="O5" s="105">
+      <c r="O5" s="104">
         <v>45874</v>
       </c>
-      <c r="P5" s="105"/>
+      <c r="P5" s="104"/>
       <c r="Q5" s="85"/>
-      <c r="R5" s="114">
+      <c r="R5" s="112">
         <v>9190</v>
       </c>
-      <c r="S5" s="105">
+      <c r="S5" s="104">
         <v>45905</v>
       </c>
-      <c r="T5" s="105"/>
+      <c r="T5" s="104"/>
       <c r="U5" s="85"/>
-      <c r="V5" s="114">
+      <c r="V5" s="112">
         <v>9300</v>
       </c>
-      <c r="W5" s="105">
+      <c r="W5" s="104">
         <v>45938</v>
       </c>
-      <c r="X5" s="105"/>
+      <c r="X5" s="104"/>
       <c r="Y5" s="85"/>
-      <c r="Z5" s="114">
+      <c r="Z5" s="112">
         <v>10000</v>
       </c>
-      <c r="AA5" s="105" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB5" s="105"/>
+      <c r="AA5" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB5" s="104"/>
       <c r="AC5" s="85"/>
-      <c r="AD5" s="114">
+      <c r="AD5" s="112">
         <v>15000</v>
       </c>
-      <c r="AE5" s="105" t="s">
+      <c r="AE5" s="104" t="s">
+        <v>198</v>
+      </c>
+      <c r="AF5" s="104"/>
+      <c r="AG5" s="85" t="s">
         <v>199</v>
       </c>
-      <c r="AF5" s="105"/>
-      <c r="AG5" s="85" t="s">
-        <v>200</v>
-      </c>
-      <c r="AH5" s="114">
+      <c r="AH5" s="112">
         <v>15000</v>
       </c>
-      <c r="AI5" s="105" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ5" s="105"/>
+      <c r="AI5" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="AJ5" s="104"/>
       <c r="AK5" s="85"/>
-      <c r="AL5" s="114">
+      <c r="AL5" s="112">
         <v>15000</v>
       </c>
-      <c r="AM5" s="105">
+      <c r="AM5" s="104">
         <v>46063</v>
       </c>
-      <c r="AN5" s="105"/>
+      <c r="AN5" s="104"/>
       <c r="AO5" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="AP5" s="112">
+        <v>15000</v>
+      </c>
+      <c r="AQ5" s="104">
+        <v>46100</v>
+      </c>
+      <c r="AR5" s="104"/>
+      <c r="AS5" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="AP5" s="114">
+      <c r="AT5" s="112">
         <v>15000</v>
       </c>
-      <c r="AQ5" s="105">
-        <v>46100</v>
-      </c>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="85" t="s">
-        <v>230</v>
-      </c>
-      <c r="AT5" s="114">
+      <c r="AU5" s="104">
+        <v>46130</v>
+      </c>
+      <c r="AV5" s="104"/>
+      <c r="AW5" s="85"/>
+      <c r="AX5" s="112">
         <v>15000</v>
       </c>
-      <c r="AU5" s="105">
-        <v>46130</v>
-      </c>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="85"/>
-      <c r="AX5" s="114">
-        <v>15000</v>
-      </c>
-      <c r="AY5" s="105">
+      <c r="AY5" s="104">
         <v>46157</v>
       </c>
-      <c r="AZ5" s="105"/>
+      <c r="AZ5" s="104"/>
       <c r="BA5" s="85"/>
     </row>
-    <row r="6" spans="1:53" ht="44.5" customHeight="1">
+    <row r="6" spans="1:53" ht="44.45" customHeight="1">
       <c r="A6" s="86">
         <v>3</v>
       </c>
@@ -8764,106 +8695,106 @@
       <c r="H6" s="82">
         <v>1500</v>
       </c>
-      <c r="I6" s="105">
+      <c r="I6" s="104">
         <v>45810</v>
       </c>
-      <c r="J6" s="105"/>
+      <c r="J6" s="104"/>
       <c r="K6" s="82">
         <v>1500</v>
       </c>
-      <c r="L6" s="105">
+      <c r="L6" s="104">
         <v>45842</v>
       </c>
-      <c r="M6" s="105"/>
-      <c r="N6" s="114">
-        <v>1500</v>
-      </c>
-      <c r="O6" s="105">
+      <c r="M6" s="104"/>
+      <c r="N6" s="112">
+        <v>1500</v>
+      </c>
+      <c r="O6" s="104">
         <v>45872</v>
       </c>
-      <c r="P6" s="105"/>
+      <c r="P6" s="104"/>
       <c r="Q6" s="85"/>
-      <c r="R6" s="114">
-        <v>1500</v>
-      </c>
-      <c r="S6" s="105">
+      <c r="R6" s="112">
+        <v>1500</v>
+      </c>
+      <c r="S6" s="104">
         <v>45903</v>
       </c>
-      <c r="T6" s="105"/>
+      <c r="T6" s="104"/>
       <c r="U6" s="85"/>
-      <c r="V6" s="114">
-        <v>1500</v>
-      </c>
-      <c r="W6" s="105">
+      <c r="V6" s="112">
+        <v>1500</v>
+      </c>
+      <c r="W6" s="104">
         <v>45931</v>
       </c>
-      <c r="X6" s="105"/>
+      <c r="X6" s="104"/>
       <c r="Y6" s="85"/>
-      <c r="Z6" s="114">
+      <c r="Z6" s="112">
         <v>2000</v>
       </c>
-      <c r="AA6" s="105" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB6" s="105"/>
+      <c r="AA6" s="104" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB6" s="104"/>
       <c r="AC6" s="85"/>
-      <c r="AD6" s="114">
+      <c r="AD6" s="112">
         <v>2000</v>
       </c>
-      <c r="AE6" s="105" t="s">
-        <v>202</v>
-      </c>
-      <c r="AF6" s="105"/>
+      <c r="AE6" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="AF6" s="104"/>
       <c r="AG6" s="85"/>
-      <c r="AH6" s="114">
+      <c r="AH6" s="112">
         <v>2000</v>
       </c>
-      <c r="AI6" s="105">
+      <c r="AI6" s="104">
         <v>46025</v>
       </c>
-      <c r="AJ6" s="105"/>
+      <c r="AJ6" s="104"/>
       <c r="AK6" s="85"/>
-      <c r="AL6" s="114">
+      <c r="AL6" s="112">
         <v>2000</v>
       </c>
-      <c r="AM6" s="105">
+      <c r="AM6" s="104">
         <v>46055</v>
       </c>
-      <c r="AN6" s="105"/>
+      <c r="AN6" s="104"/>
       <c r="AO6" s="85"/>
-      <c r="AP6" s="114">
+      <c r="AP6" s="112">
         <v>2500</v>
       </c>
-      <c r="AQ6" s="105">
+      <c r="AQ6" s="104">
         <v>46082</v>
       </c>
-      <c r="AR6" s="105"/>
+      <c r="AR6" s="104"/>
       <c r="AS6" s="90" t="s">
-        <v>224</v>
-      </c>
-      <c r="AT6" s="114">
+        <v>223</v>
+      </c>
+      <c r="AT6" s="112">
         <f>1500+1000</f>
         <v>2500</v>
       </c>
-      <c r="AU6" s="105">
+      <c r="AU6" s="104">
         <v>46113</v>
       </c>
-      <c r="AV6" s="105"/>
+      <c r="AV6" s="104"/>
       <c r="AW6" s="90" t="s">
-        <v>237</v>
-      </c>
-      <c r="AX6" s="114">
+        <v>236</v>
+      </c>
+      <c r="AX6" s="112">
         <v>3000</v>
       </c>
-      <c r="AY6" s="105">
+      <c r="AY6" s="104">
         <v>46146</v>
       </c>
-      <c r="AZ6" s="105"/>
+      <c r="AZ6" s="104"/>
       <c r="BA6" s="90" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:53" ht="56.15" customHeight="1">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" ht="56.1" customHeight="1">
       <c r="A7" s="86">
         <v>4</v>
       </c>
@@ -8875,10 +8806,10 @@
       <c r="E7" s="82">
         <v>15940</v>
       </c>
-      <c r="F7" s="105">
+      <c r="F7" s="104">
         <v>45790</v>
       </c>
-      <c r="G7" s="105"/>
+      <c r="G7" s="104"/>
       <c r="H7" s="82">
         <f>18393+226</f>
         <v>18619</v>
@@ -8892,92 +8823,92 @@
       <c r="K7" s="84">
         <v>12293</v>
       </c>
-      <c r="L7" s="105">
+      <c r="L7" s="104">
         <v>45847</v>
       </c>
-      <c r="M7" s="105"/>
-      <c r="N7" s="115">
+      <c r="M7" s="104"/>
+      <c r="N7" s="113">
         <v>10010</v>
       </c>
-      <c r="O7" s="105">
+      <c r="O7" s="104">
         <v>45871</v>
       </c>
-      <c r="P7" s="105"/>
+      <c r="P7" s="104"/>
       <c r="Q7" s="90"/>
-      <c r="R7" s="115">
+      <c r="R7" s="113">
         <v>20526</v>
       </c>
-      <c r="S7" s="105">
+      <c r="S7" s="104">
         <v>45902</v>
       </c>
-      <c r="T7" s="105"/>
+      <c r="T7" s="104"/>
       <c r="U7" s="90"/>
-      <c r="V7" s="115">
+      <c r="V7" s="113">
         <v>19242</v>
       </c>
-      <c r="W7" s="105">
+      <c r="W7" s="104">
         <v>45936</v>
       </c>
-      <c r="X7" s="105"/>
+      <c r="X7" s="104"/>
       <c r="Y7" s="90"/>
-      <c r="Z7" s="115">
+      <c r="Z7" s="113">
         <v>15366</v>
       </c>
-      <c r="AA7" s="105" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB7" s="105"/>
+      <c r="AA7" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="AB7" s="104"/>
       <c r="AC7" s="90"/>
-      <c r="AD7" s="115">
+      <c r="AD7" s="113">
         <v>22913</v>
       </c>
-      <c r="AE7" s="105" t="s">
-        <v>203</v>
-      </c>
-      <c r="AF7" s="105"/>
+      <c r="AE7" s="104" t="s">
+        <v>202</v>
+      </c>
+      <c r="AF7" s="104"/>
       <c r="AG7" s="90"/>
-      <c r="AH7" s="115">
+      <c r="AH7" s="113">
         <v>18237</v>
       </c>
-      <c r="AI7" s="105">
+      <c r="AI7" s="104">
         <v>46048</v>
       </c>
-      <c r="AJ7" s="105"/>
+      <c r="AJ7" s="104"/>
       <c r="AK7" s="90"/>
-      <c r="AL7" s="115">
+      <c r="AL7" s="113">
         <v>15635</v>
       </c>
-      <c r="AM7" s="105">
+      <c r="AM7" s="104">
         <v>46069</v>
       </c>
-      <c r="AN7" s="105"/>
+      <c r="AN7" s="104"/>
       <c r="AO7" s="90"/>
-      <c r="AP7" s="115">
+      <c r="AP7" s="113">
         <v>17286</v>
       </c>
-      <c r="AQ7" s="128">
+      <c r="AQ7" s="126">
         <v>46082</v>
       </c>
-      <c r="AR7" s="105"/>
+      <c r="AR7" s="104"/>
       <c r="AS7" s="90"/>
-      <c r="AT7" s="115">
+      <c r="AT7" s="113">
         <v>12248</v>
       </c>
-      <c r="AU7" s="204">
+      <c r="AU7" s="133">
         <v>46132</v>
       </c>
-      <c r="AV7" s="105"/>
+      <c r="AV7" s="104"/>
       <c r="AW7" s="90"/>
-      <c r="AX7" s="115">
+      <c r="AX7" s="113">
         <v>19906</v>
       </c>
-      <c r="AY7" s="204">
+      <c r="AY7" s="133">
         <v>46154</v>
       </c>
-      <c r="AZ7" s="105"/>
+      <c r="AZ7" s="104"/>
       <c r="BA7" s="90"/>
     </row>
-    <row r="8" spans="1:53" ht="44.5" customHeight="1">
+    <row r="8" spans="1:53" ht="44.45" customHeight="1">
       <c r="A8" s="86">
         <v>5</v>
       </c>
@@ -8989,430 +8920,436 @@
       <c r="E8" s="82">
         <v>5000</v>
       </c>
-      <c r="F8" s="105">
+      <c r="F8" s="104">
         <v>45796</v>
       </c>
-      <c r="G8" s="105"/>
+      <c r="G8" s="104"/>
       <c r="H8" s="82"/>
       <c r="I8" s="83"/>
       <c r="J8" s="83"/>
       <c r="K8" s="92">
         <v>4570</v>
       </c>
-      <c r="L8" s="105">
+      <c r="L8" s="104">
         <v>45843</v>
       </c>
-      <c r="M8" s="105"/>
+      <c r="M8" s="104"/>
       <c r="N8" s="82"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="105"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="104"/>
       <c r="Q8" s="85"/>
-      <c r="R8" s="114">
+      <c r="R8" s="112">
         <v>5731</v>
       </c>
-      <c r="S8" s="105">
+      <c r="S8" s="104">
         <v>45903</v>
       </c>
-      <c r="T8" s="105"/>
+      <c r="T8" s="104"/>
       <c r="U8" s="85"/>
-      <c r="V8" s="114"/>
-      <c r="W8" s="105"/>
-      <c r="X8" s="105"/>
+      <c r="V8" s="112"/>
+      <c r="W8" s="104"/>
+      <c r="X8" s="104"/>
       <c r="Y8" s="85"/>
-      <c r="Z8" s="114"/>
-      <c r="AA8" s="105"/>
-      <c r="AB8" s="105"/>
+      <c r="Z8" s="112"/>
+      <c r="AA8" s="104"/>
+      <c r="AB8" s="104"/>
       <c r="AC8" s="85"/>
-      <c r="AD8" s="114">
+      <c r="AD8" s="112">
         <f>1800+5194</f>
         <v>6994</v>
       </c>
-      <c r="AE8" s="116" t="s">
-        <v>205</v>
-      </c>
-      <c r="AF8" s="105"/>
+      <c r="AE8" s="114" t="s">
+        <v>204</v>
+      </c>
+      <c r="AF8" s="104"/>
       <c r="AG8" s="85" t="s">
-        <v>204</v>
-      </c>
-      <c r="AH8" s="114">
+        <v>203</v>
+      </c>
+      <c r="AH8" s="112">
         <v>15574</v>
       </c>
-      <c r="AI8" s="105">
+      <c r="AI8" s="104">
         <v>46035</v>
       </c>
-      <c r="AJ8" s="105"/>
+      <c r="AJ8" s="104"/>
       <c r="AK8" s="85" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL8" s="114"/>
-      <c r="AM8" s="105"/>
-      <c r="AN8" s="105"/>
+        <v>209</v>
+      </c>
+      <c r="AL8" s="112"/>
+      <c r="AM8" s="104"/>
+      <c r="AN8" s="104"/>
       <c r="AO8" s="85"/>
-      <c r="AP8" s="114">
+      <c r="AP8" s="112">
         <v>7384</v>
       </c>
-      <c r="AQ8" s="128">
+      <c r="AQ8" s="126">
         <v>46091</v>
       </c>
-      <c r="AR8" s="105"/>
-      <c r="AS8" s="127" t="s">
-        <v>225</v>
-      </c>
-      <c r="AT8" s="114"/>
-      <c r="AU8" s="128"/>
-      <c r="AV8" s="105"/>
-      <c r="AW8" s="127"/>
-      <c r="AX8" s="114"/>
-      <c r="AY8" s="128"/>
-      <c r="AZ8" s="105"/>
-      <c r="BA8" s="127"/>
+      <c r="AR8" s="104"/>
+      <c r="AS8" s="125" t="s">
+        <v>224</v>
+      </c>
+      <c r="AT8" s="112"/>
+      <c r="AU8" s="126"/>
+      <c r="AV8" s="104"/>
+      <c r="AW8" s="125"/>
+      <c r="AX8" s="112"/>
+      <c r="AY8" s="126"/>
+      <c r="AZ8" s="104"/>
+      <c r="BA8" s="125"/>
     </row>
     <row r="9" spans="1:53" ht="33" customHeight="1">
-      <c r="A9" s="139">
+      <c r="A9" s="177">
         <v>6</v>
       </c>
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="176" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="145"/>
-      <c r="D9" s="148"/>
-      <c r="E9" s="151">
+      <c r="C9" s="180"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="186">
         <v>2593</v>
       </c>
-      <c r="F9" s="154">
+      <c r="F9" s="189">
         <v>45808</v>
       </c>
-      <c r="G9" s="154"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="157"/>
-      <c r="J9" s="157"/>
-      <c r="K9" s="151">
+      <c r="G9" s="189"/>
+      <c r="H9" s="186"/>
+      <c r="I9" s="195"/>
+      <c r="J9" s="195"/>
+      <c r="K9" s="186">
         <v>223</v>
       </c>
-      <c r="L9" s="167">
+      <c r="L9" s="192">
         <v>45857</v>
       </c>
-      <c r="M9" s="167"/>
-      <c r="N9" s="151">
+      <c r="M9" s="192"/>
+      <c r="N9" s="186">
         <v>155</v>
       </c>
-      <c r="O9" s="167">
+      <c r="O9" s="192">
         <v>45882</v>
       </c>
-      <c r="P9" s="105"/>
+      <c r="P9" s="104"/>
       <c r="Q9" s="90"/>
-      <c r="R9" s="114">
+      <c r="R9" s="112">
         <v>140</v>
       </c>
-      <c r="S9" s="105">
+      <c r="S9" s="104">
         <v>45908</v>
       </c>
-      <c r="T9" s="105"/>
+      <c r="T9" s="104"/>
       <c r="U9" s="90" t="s">
-        <v>173</v>
-      </c>
-      <c r="V9" s="114">
+        <v>172</v>
+      </c>
+      <c r="V9" s="112">
         <v>540</v>
       </c>
-      <c r="W9" s="105">
+      <c r="W9" s="104">
         <v>45937</v>
       </c>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z9" s="114"/>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="105"/>
-      <c r="AC9" s="105"/>
-      <c r="AD9" s="114">
+      <c r="X9" s="104"/>
+      <c r="Y9" s="104" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z9" s="112"/>
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104"/>
+      <c r="AC9" s="104"/>
+      <c r="AD9" s="112">
         <f>1716+565</f>
         <v>2281</v>
       </c>
-      <c r="AE9" s="116" t="s">
+      <c r="AE9" s="114" t="s">
+        <v>205</v>
+      </c>
+      <c r="AF9" s="104"/>
+      <c r="AG9" s="85" t="s">
         <v>206</v>
       </c>
-      <c r="AF9" s="105"/>
-      <c r="AG9" s="85" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH9" s="114">
+      <c r="AH9" s="112">
         <v>1128</v>
       </c>
-      <c r="AI9" s="105">
+      <c r="AI9" s="104">
         <v>46053</v>
       </c>
-      <c r="AJ9" s="105"/>
-      <c r="AK9" s="105"/>
-      <c r="AL9" s="114"/>
-      <c r="AM9" s="105"/>
-      <c r="AN9" s="105"/>
-      <c r="AO9" s="105"/>
-      <c r="AP9" s="114">
+      <c r="AJ9" s="104"/>
+      <c r="AK9" s="104"/>
+      <c r="AL9" s="112"/>
+      <c r="AM9" s="104"/>
+      <c r="AN9" s="104"/>
+      <c r="AO9" s="104"/>
+      <c r="AP9" s="112">
         <f>496+523</f>
         <v>1019</v>
       </c>
-      <c r="AQ9" s="105">
+      <c r="AQ9" s="104">
         <v>46093</v>
       </c>
-      <c r="AR9" s="105"/>
-      <c r="AS9" s="105" t="s">
-        <v>235</v>
-      </c>
-      <c r="AT9" s="114">
+      <c r="AR9" s="104"/>
+      <c r="AS9" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="AT9" s="112">
         <f>100+350</f>
         <v>450</v>
       </c>
-      <c r="AU9" s="105">
+      <c r="AU9" s="104">
         <v>46103</v>
       </c>
-      <c r="AV9" s="105"/>
+      <c r="AV9" s="104"/>
       <c r="AW9" s="90" t="s">
-        <v>238</v>
-      </c>
-      <c r="AX9" s="114">
+        <v>237</v>
+      </c>
+      <c r="AX9" s="112">
         <v>194</v>
       </c>
-      <c r="AY9" s="105">
+      <c r="AY9" s="104">
         <v>46153</v>
       </c>
-      <c r="AZ9" s="105"/>
-      <c r="BA9" s="105" t="s">
-        <v>234</v>
+      <c r="AZ9" s="104"/>
+      <c r="BA9" s="104" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:53" ht="58.5" customHeight="1">
-      <c r="A10" s="140"/>
-      <c r="B10" s="143"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="152"/>
-      <c r="F10" s="155"/>
-      <c r="G10" s="155"/>
-      <c r="H10" s="152"/>
-      <c r="I10" s="158"/>
-      <c r="J10" s="158"/>
-      <c r="K10" s="152"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="153"/>
-      <c r="O10" s="168"/>
-      <c r="P10" s="105"/>
+      <c r="A10" s="178"/>
+      <c r="B10" s="176" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="181"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="190"/>
+      <c r="G10" s="190"/>
+      <c r="H10" s="187"/>
+      <c r="I10" s="196"/>
+      <c r="J10" s="196"/>
+      <c r="K10" s="187"/>
+      <c r="L10" s="193"/>
+      <c r="M10" s="193"/>
+      <c r="N10" s="188"/>
+      <c r="O10" s="194"/>
+      <c r="P10" s="104"/>
       <c r="Q10" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="112">
         <v>936</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="104">
         <v>45925</v>
       </c>
-      <c r="T10" s="105"/>
+      <c r="T10" s="104"/>
       <c r="U10" s="90" t="s">
-        <v>174</v>
-      </c>
-      <c r="V10" s="114">
+        <v>173</v>
+      </c>
+      <c r="V10" s="112">
         <v>210</v>
       </c>
-      <c r="W10" s="105">
+      <c r="W10" s="104">
         <v>45938</v>
       </c>
-      <c r="X10" s="105"/>
-      <c r="Y10" s="105" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z10" s="114"/>
-      <c r="AA10" s="105"/>
-      <c r="AB10" s="105"/>
-      <c r="AC10" s="105"/>
-      <c r="AD10" s="114">
+      <c r="X10" s="104"/>
+      <c r="Y10" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z10" s="112"/>
+      <c r="AA10" s="104"/>
+      <c r="AB10" s="104"/>
+      <c r="AC10" s="104"/>
+      <c r="AD10" s="112">
         <v>55</v>
       </c>
-      <c r="AE10" s="105" t="s">
-        <v>208</v>
-      </c>
-      <c r="AF10" s="105"/>
-      <c r="AG10" s="105" t="s">
-        <v>185</v>
-      </c>
-      <c r="AH10" s="114">
+      <c r="AE10" s="104" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF10" s="104"/>
+      <c r="AG10" s="104" t="s">
+        <v>184</v>
+      </c>
+      <c r="AH10" s="112">
         <v>220</v>
       </c>
-      <c r="AI10" s="105">
+      <c r="AI10" s="104">
         <v>46038</v>
       </c>
-      <c r="AJ10" s="105"/>
-      <c r="AK10" s="116" t="s">
-        <v>211</v>
-      </c>
-      <c r="AL10" s="114">
+      <c r="AJ10" s="104"/>
+      <c r="AK10" s="114" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL10" s="112">
         <v>405</v>
       </c>
-      <c r="AM10" s="105">
+      <c r="AM10" s="104">
         <v>46076</v>
       </c>
-      <c r="AN10" s="105"/>
-      <c r="AO10" s="116" t="s">
-        <v>222</v>
-      </c>
-      <c r="AP10" s="114"/>
-      <c r="AQ10" s="105"/>
-      <c r="AR10" s="105"/>
-      <c r="AS10" s="116"/>
-      <c r="AT10" s="114"/>
-      <c r="AU10" s="105"/>
-      <c r="AV10" s="105"/>
-      <c r="AW10" s="116"/>
-      <c r="AX10" s="114"/>
-      <c r="AY10" s="105"/>
-      <c r="AZ10" s="105"/>
-      <c r="BA10" s="116"/>
+      <c r="AN10" s="104"/>
+      <c r="AO10" s="114" t="s">
+        <v>221</v>
+      </c>
+      <c r="AP10" s="112"/>
+      <c r="AQ10" s="104"/>
+      <c r="AR10" s="104"/>
+      <c r="AS10" s="114"/>
+      <c r="AT10" s="112"/>
+      <c r="AU10" s="104"/>
+      <c r="AV10" s="104"/>
+      <c r="AW10" s="114"/>
+      <c r="AX10" s="112"/>
+      <c r="AY10" s="104"/>
+      <c r="AZ10" s="104"/>
+      <c r="BA10" s="114"/>
     </row>
     <row r="11" spans="1:53" ht="73.5" customHeight="1">
-      <c r="A11" s="140"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="146"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="155"/>
-      <c r="G11" s="155"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="158"/>
-      <c r="J11" s="158"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="172"/>
-      <c r="M11" s="172"/>
+      <c r="A11" s="178"/>
+      <c r="B11" s="176" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="181"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="187"/>
+      <c r="F11" s="190"/>
+      <c r="G11" s="190"/>
+      <c r="H11" s="187"/>
+      <c r="I11" s="196"/>
+      <c r="J11" s="196"/>
+      <c r="K11" s="187"/>
+      <c r="L11" s="193"/>
+      <c r="M11" s="193"/>
       <c r="N11" s="82">
         <v>525</v>
       </c>
-      <c r="O11" s="105">
+      <c r="O11" s="104">
         <v>45883</v>
       </c>
-      <c r="P11" s="105"/>
+      <c r="P11" s="104"/>
       <c r="Q11" s="90" t="s">
         <v>158</v>
       </c>
       <c r="R11" s="82"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="105"/>
+      <c r="S11" s="104"/>
+      <c r="T11" s="104"/>
       <c r="U11" s="90"/>
       <c r="V11" s="82">
         <v>5700</v>
       </c>
-      <c r="W11" s="105"/>
-      <c r="X11" s="105"/>
-      <c r="Y11" s="116" t="s">
-        <v>187</v>
+      <c r="W11" s="104"/>
+      <c r="X11" s="104"/>
+      <c r="Y11" s="114" t="s">
+        <v>186</v>
       </c>
       <c r="Z11" s="82"/>
-      <c r="AA11" s="105"/>
-      <c r="AB11" s="105"/>
-      <c r="AC11" s="116"/>
+      <c r="AA11" s="104"/>
+      <c r="AB11" s="104"/>
+      <c r="AC11" s="114"/>
       <c r="AD11" s="82"/>
-      <c r="AE11" s="105"/>
-      <c r="AF11" s="105"/>
-      <c r="AG11" s="116"/>
+      <c r="AE11" s="104"/>
+      <c r="AF11" s="104"/>
+      <c r="AG11" s="114"/>
       <c r="AH11" s="82">
         <v>200</v>
       </c>
-      <c r="AI11" s="105">
+      <c r="AI11" s="104">
         <v>46039</v>
       </c>
-      <c r="AJ11" s="105"/>
-      <c r="AK11" s="116" t="s">
-        <v>212</v>
+      <c r="AJ11" s="104"/>
+      <c r="AK11" s="114" t="s">
+        <v>211</v>
       </c>
       <c r="AL11" s="82">
         <v>767</v>
       </c>
-      <c r="AM11" s="105">
+      <c r="AM11" s="104">
         <v>46075</v>
       </c>
-      <c r="AN11" s="105"/>
-      <c r="AO11" s="116" t="s">
-        <v>223</v>
+      <c r="AN11" s="104"/>
+      <c r="AO11" s="114" t="s">
+        <v>222</v>
       </c>
       <c r="AP11" s="82"/>
-      <c r="AQ11" s="105"/>
-      <c r="AR11" s="105"/>
-      <c r="AS11" s="116"/>
-      <c r="AT11" s="114"/>
-      <c r="AU11" s="105"/>
-      <c r="AV11" s="105"/>
-      <c r="AW11" s="116"/>
+      <c r="AQ11" s="104"/>
+      <c r="AR11" s="104"/>
+      <c r="AS11" s="114"/>
+      <c r="AT11" s="112"/>
+      <c r="AU11" s="104"/>
+      <c r="AV11" s="104"/>
+      <c r="AW11" s="114"/>
       <c r="AX11" s="82"/>
-      <c r="AY11" s="105"/>
-      <c r="AZ11" s="105"/>
-      <c r="BA11" s="116"/>
-    </row>
-    <row r="12" spans="1:53" ht="44.5" customHeight="1">
-      <c r="A12" s="141"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="159"/>
-      <c r="J12" s="159"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="168"/>
-      <c r="M12" s="168"/>
+      <c r="AY11" s="104"/>
+      <c r="AZ11" s="104"/>
+      <c r="BA11" s="114"/>
+    </row>
+    <row r="12" spans="1:53" ht="44.45" customHeight="1">
+      <c r="A12" s="179"/>
+      <c r="B12" s="176" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="182"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="188"/>
+      <c r="F12" s="191"/>
+      <c r="G12" s="191"/>
+      <c r="H12" s="188"/>
+      <c r="I12" s="197"/>
+      <c r="J12" s="197"/>
+      <c r="K12" s="188"/>
+      <c r="L12" s="194"/>
+      <c r="M12" s="194"/>
       <c r="N12" s="82">
         <v>376</v>
       </c>
-      <c r="O12" s="105">
+      <c r="O12" s="104">
         <v>45885</v>
       </c>
-      <c r="P12" s="105"/>
+      <c r="P12" s="104"/>
       <c r="Q12" s="90" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="R12" s="82"/>
-      <c r="S12" s="105"/>
-      <c r="T12" s="105"/>
+      <c r="S12" s="104"/>
+      <c r="T12" s="104"/>
       <c r="U12" s="90"/>
       <c r="V12" s="82"/>
-      <c r="W12" s="105"/>
-      <c r="X12" s="105"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="104"/>
       <c r="Y12" s="90"/>
       <c r="Z12" s="82"/>
-      <c r="AA12" s="105"/>
-      <c r="AB12" s="105"/>
+      <c r="AA12" s="104"/>
+      <c r="AB12" s="104"/>
       <c r="AC12" s="90"/>
       <c r="AD12" s="82"/>
-      <c r="AE12" s="105"/>
-      <c r="AF12" s="105"/>
+      <c r="AE12" s="104"/>
+      <c r="AF12" s="104"/>
       <c r="AG12" s="90"/>
       <c r="AH12" s="82">
         <v>200</v>
       </c>
-      <c r="AI12" s="105" t="s">
+      <c r="AI12" s="104" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ12" s="104"/>
+      <c r="AK12" s="114" t="s">
         <v>213</v>
       </c>
-      <c r="AJ12" s="105"/>
-      <c r="AK12" s="116" t="s">
-        <v>214</v>
-      </c>
       <c r="AL12" s="82"/>
-      <c r="AM12" s="105"/>
-      <c r="AN12" s="105"/>
-      <c r="AO12" s="116"/>
+      <c r="AM12" s="104"/>
+      <c r="AN12" s="104"/>
+      <c r="AO12" s="114"/>
       <c r="AP12" s="82"/>
-      <c r="AQ12" s="105"/>
-      <c r="AR12" s="105"/>
-      <c r="AS12" s="116"/>
-      <c r="AT12" s="114"/>
-      <c r="AU12" s="105"/>
-      <c r="AV12" s="105"/>
-      <c r="AW12" s="116"/>
+      <c r="AQ12" s="104"/>
+      <c r="AR12" s="104"/>
+      <c r="AS12" s="114"/>
+      <c r="AT12" s="112"/>
+      <c r="AU12" s="104"/>
+      <c r="AV12" s="104"/>
+      <c r="AW12" s="114"/>
       <c r="AX12" s="82"/>
-      <c r="AY12" s="105"/>
-      <c r="AZ12" s="105"/>
-      <c r="BA12" s="116"/>
-    </row>
-    <row r="13" spans="1:53" ht="32" customHeight="1">
+      <c r="AY12" s="104"/>
+      <c r="AZ12" s="104"/>
+      <c r="BA12" s="114"/>
+    </row>
+    <row r="13" spans="1:53" ht="32.1" customHeight="1">
       <c r="A13" s="93">
         <v>7</v>
       </c>
@@ -9430,52 +9367,52 @@
       <c r="K13" s="82">
         <v>1349</v>
       </c>
-      <c r="L13" s="105">
+      <c r="L13" s="104">
         <v>45852</v>
       </c>
-      <c r="M13" s="105"/>
+      <c r="M13" s="104"/>
       <c r="N13" s="82"/>
-      <c r="O13" s="105"/>
-      <c r="P13" s="105"/>
+      <c r="O13" s="104"/>
+      <c r="P13" s="104"/>
       <c r="Q13" s="90"/>
       <c r="R13" s="82"/>
-      <c r="S13" s="105"/>
-      <c r="T13" s="105"/>
+      <c r="S13" s="104"/>
+      <c r="T13" s="104"/>
       <c r="U13" s="90"/>
       <c r="V13" s="82"/>
-      <c r="W13" s="105"/>
-      <c r="X13" s="105"/>
+      <c r="W13" s="104"/>
+      <c r="X13" s="104"/>
       <c r="Y13" s="90"/>
       <c r="Z13" s="82"/>
-      <c r="AA13" s="105"/>
-      <c r="AB13" s="105"/>
+      <c r="AA13" s="104"/>
+      <c r="AB13" s="104"/>
       <c r="AC13" s="90"/>
       <c r="AD13" s="82"/>
-      <c r="AE13" s="105"/>
-      <c r="AF13" s="105"/>
+      <c r="AE13" s="104"/>
+      <c r="AF13" s="104"/>
       <c r="AG13" s="90"/>
       <c r="AH13" s="82"/>
-      <c r="AI13" s="105"/>
-      <c r="AJ13" s="105"/>
+      <c r="AI13" s="104"/>
+      <c r="AJ13" s="104"/>
       <c r="AK13" s="90"/>
       <c r="AL13" s="82"/>
-      <c r="AM13" s="105"/>
-      <c r="AN13" s="105"/>
+      <c r="AM13" s="104"/>
+      <c r="AN13" s="104"/>
       <c r="AO13" s="90"/>
       <c r="AP13" s="82"/>
-      <c r="AQ13" s="105"/>
-      <c r="AR13" s="105"/>
+      <c r="AQ13" s="104"/>
+      <c r="AR13" s="104"/>
       <c r="AS13" s="90"/>
-      <c r="AT13" s="114"/>
-      <c r="AU13" s="105"/>
-      <c r="AV13" s="105"/>
+      <c r="AT13" s="112"/>
+      <c r="AU13" s="104"/>
+      <c r="AV13" s="104"/>
       <c r="AW13" s="90"/>
       <c r="AX13" s="82"/>
-      <c r="AY13" s="105"/>
-      <c r="AZ13" s="105"/>
+      <c r="AY13" s="104"/>
+      <c r="AZ13" s="104"/>
       <c r="BA13" s="90"/>
     </row>
-    <row r="14" spans="1:53" ht="44.5" customHeight="1">
+    <row r="14" spans="1:53" ht="44.45" customHeight="1">
       <c r="A14" s="94">
         <v>8</v>
       </c>
@@ -9495,60 +9432,60 @@
       </c>
       <c r="J14" s="89"/>
       <c r="K14" s="82"/>
-      <c r="L14" s="105"/>
-      <c r="M14" s="105"/>
+      <c r="L14" s="104"/>
+      <c r="M14" s="104"/>
       <c r="N14" s="82">
         <v>50</v>
       </c>
-      <c r="O14" s="105">
+      <c r="O14" s="104">
         <v>45879</v>
       </c>
-      <c r="P14" s="105"/>
+      <c r="P14" s="104"/>
       <c r="Q14" s="85"/>
       <c r="R14" s="82"/>
-      <c r="S14" s="105"/>
-      <c r="T14" s="105"/>
+      <c r="S14" s="104"/>
+      <c r="T14" s="104"/>
       <c r="U14" s="85"/>
       <c r="V14" s="82">
         <v>380</v>
       </c>
-      <c r="W14" s="105">
+      <c r="W14" s="104">
         <v>45942</v>
       </c>
-      <c r="X14" s="105"/>
+      <c r="X14" s="104"/>
       <c r="Y14" s="90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z14" s="82"/>
-      <c r="AA14" s="105"/>
-      <c r="AB14" s="105"/>
+      <c r="AA14" s="104"/>
+      <c r="AB14" s="104"/>
       <c r="AC14" s="90"/>
       <c r="AD14" s="82"/>
-      <c r="AE14" s="105"/>
-      <c r="AF14" s="105"/>
+      <c r="AE14" s="104"/>
+      <c r="AF14" s="104"/>
       <c r="AG14" s="90"/>
       <c r="AH14" s="82"/>
-      <c r="AI14" s="105"/>
-      <c r="AJ14" s="105"/>
+      <c r="AI14" s="104"/>
+      <c r="AJ14" s="104"/>
       <c r="AK14" s="90"/>
       <c r="AL14" s="82"/>
-      <c r="AM14" s="105"/>
-      <c r="AN14" s="105"/>
+      <c r="AM14" s="104"/>
+      <c r="AN14" s="104"/>
       <c r="AO14" s="90"/>
       <c r="AP14" s="82"/>
-      <c r="AQ14" s="105"/>
-      <c r="AR14" s="105"/>
+      <c r="AQ14" s="104"/>
+      <c r="AR14" s="104"/>
       <c r="AS14" s="90"/>
-      <c r="AT14" s="114"/>
-      <c r="AU14" s="105"/>
-      <c r="AV14" s="105"/>
+      <c r="AT14" s="112"/>
+      <c r="AU14" s="104"/>
+      <c r="AV14" s="104"/>
       <c r="AW14" s="90"/>
       <c r="AX14" s="82"/>
-      <c r="AY14" s="105"/>
-      <c r="AZ14" s="105"/>
+      <c r="AY14" s="104"/>
+      <c r="AZ14" s="104"/>
       <c r="BA14" s="90"/>
     </row>
-    <row r="15" spans="1:53" ht="44.5" customHeight="1">
+    <row r="15" spans="1:53" ht="44.45" customHeight="1">
       <c r="A15" s="94">
         <v>9</v>
       </c>
@@ -9568,50 +9505,50 @@
       </c>
       <c r="J15" s="89"/>
       <c r="K15" s="82"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
+      <c r="L15" s="104"/>
+      <c r="M15" s="104"/>
       <c r="N15" s="82"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="104"/>
       <c r="Q15" s="85"/>
       <c r="R15" s="82"/>
-      <c r="S15" s="105"/>
-      <c r="T15" s="105"/>
+      <c r="S15" s="104"/>
+      <c r="T15" s="104"/>
       <c r="U15" s="85"/>
       <c r="V15" s="82"/>
-      <c r="W15" s="105"/>
-      <c r="X15" s="105"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="104"/>
       <c r="Y15" s="85"/>
       <c r="Z15" s="82"/>
-      <c r="AA15" s="105"/>
-      <c r="AB15" s="105"/>
+      <c r="AA15" s="104"/>
+      <c r="AB15" s="104"/>
       <c r="AC15" s="85"/>
       <c r="AD15" s="82"/>
-      <c r="AE15" s="105"/>
-      <c r="AF15" s="105"/>
+      <c r="AE15" s="104"/>
+      <c r="AF15" s="104"/>
       <c r="AG15" s="85"/>
       <c r="AH15" s="82"/>
-      <c r="AI15" s="105"/>
-      <c r="AJ15" s="105"/>
+      <c r="AI15" s="104"/>
+      <c r="AJ15" s="104"/>
       <c r="AK15" s="85"/>
       <c r="AL15" s="82"/>
-      <c r="AM15" s="105"/>
-      <c r="AN15" s="105"/>
+      <c r="AM15" s="104"/>
+      <c r="AN15" s="104"/>
       <c r="AO15" s="85"/>
       <c r="AP15" s="82"/>
-      <c r="AQ15" s="105"/>
-      <c r="AR15" s="105"/>
+      <c r="AQ15" s="104"/>
+      <c r="AR15" s="104"/>
       <c r="AS15" s="85"/>
-      <c r="AT15" s="114"/>
-      <c r="AU15" s="105"/>
-      <c r="AV15" s="105"/>
+      <c r="AT15" s="112"/>
+      <c r="AU15" s="104"/>
+      <c r="AV15" s="104"/>
       <c r="AW15" s="85"/>
       <c r="AX15" s="82"/>
-      <c r="AY15" s="105"/>
-      <c r="AZ15" s="105"/>
+      <c r="AY15" s="104"/>
+      <c r="AZ15" s="104"/>
       <c r="BA15" s="85"/>
     </row>
-    <row r="16" spans="1:53" ht="44.5" customHeight="1">
+    <row r="16" spans="1:53" ht="44.45" customHeight="1">
       <c r="A16" s="96">
         <v>10</v>
       </c>
@@ -9629,62 +9566,62 @@
       <c r="K16" s="82">
         <v>1300</v>
       </c>
-      <c r="L16" s="105">
+      <c r="L16" s="104">
         <v>45850</v>
       </c>
-      <c r="M16" s="105"/>
+      <c r="M16" s="104"/>
       <c r="N16" s="82"/>
-      <c r="O16" s="105"/>
-      <c r="P16" s="105"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="104"/>
       <c r="Q16" s="85"/>
       <c r="R16" s="82"/>
-      <c r="S16" s="105"/>
-      <c r="T16" s="105"/>
+      <c r="S16" s="104"/>
+      <c r="T16" s="104"/>
       <c r="U16" s="85"/>
       <c r="V16" s="82"/>
-      <c r="W16" s="105"/>
-      <c r="X16" s="105"/>
+      <c r="W16" s="104"/>
+      <c r="X16" s="104"/>
       <c r="Y16" s="85"/>
       <c r="Z16" s="82">
         <v>130</v>
       </c>
-      <c r="AA16" s="105" t="s">
-        <v>195</v>
-      </c>
-      <c r="AB16" s="105"/>
+      <c r="AA16" s="104" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB16" s="104"/>
       <c r="AC16" s="85" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AD16" s="82"/>
-      <c r="AE16" s="105"/>
-      <c r="AF16" s="105"/>
+      <c r="AE16" s="104"/>
+      <c r="AF16" s="104"/>
       <c r="AG16" s="85"/>
       <c r="AH16" s="82"/>
-      <c r="AI16" s="105"/>
-      <c r="AJ16" s="105"/>
+      <c r="AI16" s="104"/>
+      <c r="AJ16" s="104"/>
       <c r="AK16" s="85"/>
       <c r="AL16" s="82"/>
-      <c r="AM16" s="105"/>
-      <c r="AN16" s="105"/>
+      <c r="AM16" s="104"/>
+      <c r="AN16" s="104"/>
       <c r="AO16" s="85"/>
       <c r="AP16" s="82"/>
-      <c r="AQ16" s="105"/>
-      <c r="AR16" s="105"/>
+      <c r="AQ16" s="104"/>
+      <c r="AR16" s="104"/>
       <c r="AS16" s="85"/>
-      <c r="AT16" s="114"/>
-      <c r="AU16" s="105"/>
-      <c r="AV16" s="105"/>
+      <c r="AT16" s="112"/>
+      <c r="AU16" s="104"/>
+      <c r="AV16" s="104"/>
       <c r="AW16" s="85"/>
       <c r="AX16" s="82"/>
-      <c r="AY16" s="105"/>
-      <c r="AZ16" s="105"/>
+      <c r="AY16" s="104"/>
+      <c r="AZ16" s="104"/>
       <c r="BA16" s="85"/>
     </row>
-    <row r="17" spans="1:53" ht="44.5" customHeight="1">
-      <c r="A17" s="123">
+    <row r="17" spans="1:53" ht="44.45" customHeight="1">
+      <c r="A17" s="121">
         <v>11</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="122" t="s">
         <v>163</v>
       </c>
       <c r="C17" s="80"/>
@@ -9702,74 +9639,74 @@
       <c r="K17" s="82">
         <v>650</v>
       </c>
-      <c r="L17" s="105">
+      <c r="L17" s="104">
         <v>45850</v>
       </c>
-      <c r="M17" s="105"/>
+      <c r="M17" s="104"/>
       <c r="N17" s="82"/>
-      <c r="O17" s="105"/>
-      <c r="P17" s="105"/>
+      <c r="O17" s="104"/>
+      <c r="P17" s="104"/>
       <c r="Q17" s="85"/>
       <c r="R17" s="82"/>
-      <c r="S17" s="105"/>
-      <c r="T17" s="105"/>
+      <c r="S17" s="104"/>
+      <c r="T17" s="104"/>
       <c r="U17" s="85"/>
       <c r="V17" s="82"/>
-      <c r="W17" s="105"/>
-      <c r="X17" s="105"/>
+      <c r="W17" s="104"/>
+      <c r="X17" s="104"/>
       <c r="Y17" s="85"/>
       <c r="Z17" s="82">
         <v>60</v>
       </c>
-      <c r="AA17" s="105" t="s">
+      <c r="AA17" s="104" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB17" s="104"/>
+      <c r="AC17" s="85" t="s">
         <v>195</v>
       </c>
-      <c r="AB17" s="105"/>
-      <c r="AC17" s="85" t="s">
-        <v>196</v>
-      </c>
       <c r="AD17" s="82"/>
-      <c r="AE17" s="105"/>
-      <c r="AF17" s="105"/>
+      <c r="AE17" s="104"/>
+      <c r="AF17" s="104"/>
       <c r="AG17" s="85"/>
       <c r="AH17" s="82"/>
-      <c r="AI17" s="105"/>
-      <c r="AJ17" s="105"/>
+      <c r="AI17" s="104"/>
+      <c r="AJ17" s="104"/>
       <c r="AK17" s="85"/>
       <c r="AL17" s="82"/>
-      <c r="AM17" s="105"/>
-      <c r="AN17" s="105"/>
+      <c r="AM17" s="104"/>
+      <c r="AN17" s="104"/>
       <c r="AO17" s="85"/>
       <c r="AP17" s="82">
         <f>2800+650</f>
         <v>3450</v>
       </c>
-      <c r="AQ17" s="105"/>
-      <c r="AR17" s="105"/>
-      <c r="AS17" s="201" t="s">
-        <v>231</v>
-      </c>
-      <c r="AT17" s="114">
+      <c r="AQ17" s="104"/>
+      <c r="AR17" s="104"/>
+      <c r="AS17" s="130" t="s">
+        <v>230</v>
+      </c>
+      <c r="AT17" s="112">
         <v>3300</v>
       </c>
-      <c r="AU17" s="105">
+      <c r="AU17" s="104">
         <v>46117</v>
       </c>
-      <c r="AV17" s="105"/>
-      <c r="AW17" s="202" t="s">
-        <v>236</v>
+      <c r="AV17" s="104"/>
+      <c r="AW17" s="131" t="s">
+        <v>235</v>
       </c>
       <c r="AX17" s="82"/>
-      <c r="AY17" s="105"/>
-      <c r="AZ17" s="105"/>
-      <c r="BA17" s="129"/>
+      <c r="AY17" s="104"/>
+      <c r="AZ17" s="104"/>
+      <c r="BA17" s="127"/>
     </row>
     <row r="18" spans="1:53" ht="55.5" customHeight="1">
-      <c r="A18" s="125">
+      <c r="A18" s="123">
         <v>12</v>
       </c>
-      <c r="B18" s="133" t="s">
-        <v>176</v>
+      <c r="B18" s="175" t="s">
+        <v>175</v>
       </c>
       <c r="C18" s="80"/>
       <c r="D18" s="81"/>
@@ -9780,100 +9717,102 @@
       <c r="I18" s="89"/>
       <c r="J18" s="89"/>
       <c r="K18" s="82"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="105"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="104"/>
       <c r="N18" s="82">
         <v>1537</v>
       </c>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
       <c r="Q18" s="90" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="R18" s="82">
         <v>2000</v>
       </c>
-      <c r="S18" s="105"/>
-      <c r="T18" s="105"/>
+      <c r="S18" s="104"/>
+      <c r="T18" s="104"/>
       <c r="U18" s="90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V18" s="82">
         <v>70</v>
       </c>
-      <c r="W18" s="105">
+      <c r="W18" s="104">
         <v>45947</v>
       </c>
-      <c r="X18" s="105"/>
+      <c r="X18" s="104"/>
       <c r="Y18" s="90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Z18" s="82">
         <v>8500</v>
       </c>
-      <c r="AA18" s="105" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB18" s="105"/>
+      <c r="AA18" s="104" t="s">
+        <v>193</v>
+      </c>
+      <c r="AB18" s="104"/>
       <c r="AC18" s="90" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AD18" s="82">
         <v>1720</v>
       </c>
-      <c r="AE18" s="105" t="s">
-        <v>208</v>
-      </c>
-      <c r="AF18" s="105"/>
-      <c r="AG18" s="116" t="s">
-        <v>215</v>
+      <c r="AE18" s="104" t="s">
+        <v>207</v>
+      </c>
+      <c r="AF18" s="104"/>
+      <c r="AG18" s="114" t="s">
+        <v>214</v>
       </c>
       <c r="AH18" s="82"/>
-      <c r="AI18" s="105"/>
-      <c r="AJ18" s="105"/>
+      <c r="AI18" s="104"/>
+      <c r="AJ18" s="104"/>
       <c r="AK18" s="90"/>
       <c r="AL18" s="82">
         <f>21600+8400</f>
         <v>30000</v>
       </c>
-      <c r="AM18" s="105">
+      <c r="AM18" s="104">
         <v>46075</v>
       </c>
-      <c r="AN18" s="105"/>
+      <c r="AN18" s="104"/>
       <c r="AO18" s="90" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AP18" s="82">
         <v>2070</v>
       </c>
-      <c r="AQ18" s="105">
+      <c r="AQ18" s="104">
         <v>46089</v>
       </c>
-      <c r="AR18" s="105"/>
-      <c r="AS18" s="202" t="s">
-        <v>232</v>
-      </c>
-      <c r="AT18" s="114">
+      <c r="AR18" s="104"/>
+      <c r="AS18" s="131" t="s">
+        <v>231</v>
+      </c>
+      <c r="AT18" s="112">
         <f>3000+1055</f>
         <v>4055</v>
       </c>
-      <c r="AU18" s="105">
+      <c r="AU18" s="104">
         <v>46113</v>
       </c>
-      <c r="AV18" s="105"/>
-      <c r="AW18" s="202" t="s">
-        <v>239</v>
+      <c r="AV18" s="104"/>
+      <c r="AW18" s="131" t="s">
+        <v>238</v>
       </c>
       <c r="AX18" s="82"/>
-      <c r="AY18" s="105"/>
-      <c r="AZ18" s="105"/>
-      <c r="BA18" s="129"/>
+      <c r="AY18" s="104"/>
+      <c r="AZ18" s="104"/>
+      <c r="BA18" s="127"/>
     </row>
     <row r="19" spans="1:53" ht="55.5" customHeight="1">
-      <c r="A19" s="125">
+      <c r="A19" s="123">
         <v>13</v>
       </c>
-      <c r="B19" s="133"/>
+      <c r="B19" s="175" t="s">
+        <v>175</v>
+      </c>
       <c r="C19" s="80"/>
       <c r="D19" s="81"/>
       <c r="E19" s="82"/>
@@ -9883,67 +9822,67 @@
       <c r="I19" s="89"/>
       <c r="J19" s="89"/>
       <c r="K19" s="82"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="105"/>
+      <c r="L19" s="104"/>
+      <c r="M19" s="104"/>
       <c r="N19" s="82"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="105"/>
+      <c r="O19" s="104"/>
+      <c r="P19" s="104"/>
       <c r="Q19" s="90"/>
       <c r="R19" s="82"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="105"/>
+      <c r="S19" s="104"/>
+      <c r="T19" s="104"/>
       <c r="U19" s="90"/>
       <c r="V19" s="82"/>
-      <c r="W19" s="105"/>
-      <c r="X19" s="105"/>
+      <c r="W19" s="104"/>
+      <c r="X19" s="104"/>
       <c r="Y19" s="90"/>
       <c r="Z19" s="82"/>
-      <c r="AA19" s="105"/>
-      <c r="AB19" s="105"/>
+      <c r="AA19" s="104"/>
+      <c r="AB19" s="104"/>
       <c r="AC19" s="90"/>
       <c r="AD19" s="82"/>
-      <c r="AE19" s="105"/>
-      <c r="AF19" s="105"/>
-      <c r="AG19" s="116"/>
+      <c r="AE19" s="104"/>
+      <c r="AF19" s="104"/>
+      <c r="AG19" s="114"/>
       <c r="AH19" s="82"/>
-      <c r="AI19" s="105"/>
-      <c r="AJ19" s="105"/>
+      <c r="AI19" s="104"/>
+      <c r="AJ19" s="104"/>
       <c r="AK19" s="90"/>
       <c r="AL19" s="82">
         <v>680</v>
       </c>
-      <c r="AM19" s="105">
+      <c r="AM19" s="104">
         <v>46061</v>
       </c>
-      <c r="AN19" s="105"/>
+      <c r="AN19" s="104"/>
       <c r="AO19" s="90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AP19" s="82">
         <v>800</v>
       </c>
-      <c r="AQ19" s="105">
+      <c r="AQ19" s="104">
         <v>46096</v>
       </c>
-      <c r="AR19" s="105"/>
+      <c r="AR19" s="104"/>
       <c r="AS19" s="90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AT19" s="82"/>
-      <c r="AU19" s="105"/>
-      <c r="AV19" s="105"/>
+      <c r="AU19" s="104"/>
+      <c r="AV19" s="104"/>
       <c r="AW19" s="90"/>
       <c r="AX19" s="82"/>
-      <c r="AY19" s="105"/>
-      <c r="AZ19" s="105"/>
+      <c r="AY19" s="104"/>
+      <c r="AZ19" s="104"/>
       <c r="BA19" s="90"/>
     </row>
     <row r="20" spans="1:53" ht="55.5" customHeight="1">
-      <c r="A20" s="125">
+      <c r="A20" s="123">
         <v>14</v>
       </c>
-      <c r="B20" s="126" t="s">
-        <v>220</v>
+      <c r="B20" s="124" t="s">
+        <v>219</v>
       </c>
       <c r="C20" s="80"/>
       <c r="D20" s="81"/>
@@ -9954,279 +9893,115 @@
       <c r="I20" s="89"/>
       <c r="J20" s="89"/>
       <c r="K20" s="82"/>
-      <c r="L20" s="105"/>
-      <c r="M20" s="105"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="104"/>
       <c r="N20" s="82"/>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
+      <c r="O20" s="104"/>
+      <c r="P20" s="104"/>
       <c r="Q20" s="90"/>
       <c r="R20" s="82"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="105"/>
+      <c r="S20" s="104"/>
+      <c r="T20" s="104"/>
       <c r="U20" s="90"/>
       <c r="V20" s="82"/>
-      <c r="W20" s="105"/>
-      <c r="X20" s="105"/>
+      <c r="W20" s="104"/>
+      <c r="X20" s="104"/>
       <c r="Y20" s="90"/>
       <c r="Z20" s="82"/>
-      <c r="AA20" s="105"/>
-      <c r="AB20" s="105"/>
+      <c r="AA20" s="104"/>
+      <c r="AB20" s="104"/>
       <c r="AC20" s="90"/>
       <c r="AD20" s="82"/>
-      <c r="AE20" s="105"/>
-      <c r="AF20" s="105"/>
-      <c r="AG20" s="116"/>
+      <c r="AE20" s="104"/>
+      <c r="AF20" s="104"/>
+      <c r="AG20" s="114"/>
       <c r="AH20" s="82"/>
-      <c r="AI20" s="105"/>
-      <c r="AJ20" s="105"/>
+      <c r="AI20" s="104"/>
+      <c r="AJ20" s="104"/>
       <c r="AK20" s="90"/>
       <c r="AL20" s="82">
         <f>2000+800+250+960</f>
         <v>4010</v>
       </c>
-      <c r="AM20" s="105">
+      <c r="AM20" s="104">
         <v>46081</v>
       </c>
-      <c r="AN20" s="105"/>
+      <c r="AN20" s="104"/>
       <c r="AO20" s="90" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AP20" s="82">
         <v>2277</v>
       </c>
-      <c r="AQ20" s="105">
+      <c r="AQ20" s="104">
         <v>46090</v>
       </c>
-      <c r="AR20" s="105"/>
-      <c r="AS20" s="203" t="s">
-        <v>233</v>
+      <c r="AR20" s="104"/>
+      <c r="AS20" s="132" t="s">
+        <v>232</v>
       </c>
       <c r="AT20" s="82"/>
-      <c r="AU20" s="105"/>
-      <c r="AV20" s="105"/>
-      <c r="AW20" s="130"/>
+      <c r="AU20" s="104"/>
+      <c r="AV20" s="104"/>
+      <c r="AW20" s="128"/>
       <c r="AX20" s="82">
         <f>750+90+480+30+800+1500+1950</f>
         <v>5600</v>
       </c>
-      <c r="AY20" s="105"/>
-      <c r="AZ20" s="105"/>
-      <c r="BA20" s="205" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:53" ht="44.5" customHeight="1">
-      <c r="A21" s="169" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" s="170"/>
-      <c r="C21" s="106">
-        <f>SUM(C4:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106">
-        <f>SUM(E4:E18)</f>
-        <v>23533</v>
-      </c>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106">
-        <f>SUM(H4:H18)</f>
-        <v>32714</v>
-      </c>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106">
-        <f>SUM(K4:K18)</f>
-        <v>32385</v>
-      </c>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106">
-        <f>SUM(N4:N18)</f>
-        <v>29653</v>
-      </c>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
-      <c r="Q21" s="98"/>
-      <c r="R21" s="106">
-        <f>SUM(R4:R18)</f>
-        <v>45523</v>
-      </c>
-      <c r="S21" s="106"/>
-      <c r="T21" s="106"/>
-      <c r="U21" s="98"/>
-      <c r="V21" s="106">
-        <f>SUM(V4:V18)</f>
-        <v>41892</v>
-      </c>
-      <c r="W21" s="106"/>
-      <c r="X21" s="106"/>
-      <c r="Y21" s="98"/>
-      <c r="Z21" s="106">
-        <f>SUM(Z4:Z18)</f>
-        <v>41396</v>
-      </c>
-      <c r="AA21" s="106"/>
-      <c r="AB21" s="106"/>
-      <c r="AC21" s="98"/>
-      <c r="AD21" s="106">
-        <f>SUM(AD4:AD18)</f>
-        <v>56463</v>
-      </c>
-      <c r="AE21" s="106"/>
-      <c r="AF21" s="106"/>
-      <c r="AG21" s="98"/>
-      <c r="AH21" s="106">
-        <f>SUM(AH4:AH18)</f>
-        <v>57882</v>
-      </c>
-      <c r="AI21" s="106"/>
-      <c r="AJ21" s="106"/>
-      <c r="AK21" s="98"/>
-      <c r="AL21" s="106">
-        <f>SUM(AL4:AL20)</f>
-        <v>76927</v>
-      </c>
-      <c r="AM21" s="106"/>
-      <c r="AN21" s="106"/>
-      <c r="AO21" s="98"/>
-      <c r="AP21" s="106">
-        <f>SUM(AP4:AP20)</f>
-        <v>61966</v>
-      </c>
-      <c r="AQ21" s="106"/>
-      <c r="AR21" s="106"/>
-      <c r="AS21" s="98"/>
-      <c r="AT21" s="106">
-        <f>SUM(AT4:AT20)</f>
-        <v>48553</v>
-      </c>
-      <c r="AU21" s="106"/>
-      <c r="AV21" s="106"/>
-      <c r="AW21" s="98"/>
-      <c r="AX21" s="106">
-        <f>SUM(AX4:AX20)</f>
-        <v>53967</v>
-      </c>
-      <c r="AY21" s="106"/>
-      <c r="AZ21" s="106"/>
-      <c r="BA21" s="98"/>
-    </row>
-    <row r="22" spans="1:53" ht="22.5" customHeight="1">
-      <c r="A22" s="171" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="171"/>
-      <c r="C22" s="166">
-        <f>(C21+E21+H21+K21+N21+R21)</f>
-        <v>163808</v>
-      </c>
-      <c r="D22" s="166"/>
-      <c r="E22" s="166"/>
-      <c r="F22" s="166"/>
-      <c r="G22" s="166"/>
-      <c r="H22" s="166"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="166"/>
-      <c r="K22" s="166"/>
-      <c r="L22" s="166"/>
-      <c r="M22" s="166"/>
-      <c r="N22" s="166"/>
-      <c r="O22" s="166"/>
-      <c r="P22" s="166"/>
-      <c r="Q22" s="166"/>
-      <c r="R22" s="166"/>
-    </row>
-    <row r="23" spans="1:53" ht="23.25" customHeight="1">
-      <c r="A23" s="171"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
-      <c r="H23" s="166"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="166"/>
-      <c r="L23" s="166"/>
-      <c r="M23" s="166"/>
-      <c r="N23" s="166"/>
-      <c r="O23" s="166"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="166"/>
-      <c r="R23" s="166"/>
-    </row>
-    <row r="24" spans="1:53" ht="32.5" customHeight="1"/>
-    <row r="25" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="26" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="27" spans="1:53" ht="29.9" customHeight="1"/>
-    <row r="28" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="29" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="30" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="31" spans="1:53" ht="18" customHeight="1"/>
-    <row r="32" spans="1:53" ht="28.5" customHeight="1"/>
-    <row r="33" ht="31.5" customHeight="1"/>
-    <row r="34" ht="31.5" customHeight="1"/>
-    <row r="35" ht="32.5" customHeight="1"/>
+      <c r="AY20" s="104"/>
+      <c r="AZ20" s="104"/>
+      <c r="BA20" s="134" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:53" ht="31.5" customHeight="1"/>
+    <row r="22" spans="1:53" ht="31.5" customHeight="1"/>
+    <row r="23" spans="1:53" ht="29.85" customHeight="1"/>
+    <row r="24" spans="1:53" ht="19.5" customHeight="1"/>
+    <row r="25" spans="1:53" ht="19.5" customHeight="1"/>
+    <row r="26" spans="1:53" ht="19.5" customHeight="1"/>
+    <row r="27" spans="1:53" ht="18" customHeight="1"/>
+    <row r="28" spans="1:53" ht="28.5" customHeight="1"/>
+    <row r="29" spans="1:53" ht="31.5" customHeight="1"/>
+    <row r="30" spans="1:53" ht="31.5" customHeight="1"/>
+    <row r="31" spans="1:53" ht="32.450000000000003" customHeight="1"/>
+    <row r="32" spans="1:53" ht="21" customHeight="1"/>
+    <row r="33" ht="21" customHeight="1"/>
+    <row r="34" ht="21" customHeight="1"/>
+    <row r="35" ht="21" customHeight="1"/>
     <row r="36" ht="21" customHeight="1"/>
     <row r="37" ht="21" customHeight="1"/>
     <row r="38" ht="21" customHeight="1"/>
-    <row r="39" ht="21" customHeight="1"/>
-    <row r="40" ht="21" customHeight="1"/>
-    <row r="41" ht="21" customHeight="1"/>
-    <row r="42" ht="21" customHeight="1"/>
-    <row r="43" ht="18" customHeight="1"/>
-    <row r="44" ht="30.65" customHeight="1"/>
-    <row r="56" ht="31" customHeight="1"/>
-    <row r="68" ht="28" customHeight="1"/>
-    <row r="80" ht="30" customHeight="1"/>
-    <row r="92" ht="31.5" customHeight="1"/>
-    <row r="104" ht="28" customHeight="1"/>
-    <row r="116" ht="31.5" customHeight="1"/>
-    <row r="128" ht="32.5" customHeight="1"/>
-    <row r="140" ht="28" customHeight="1"/>
-    <row r="141" ht="15" customHeight="1"/>
+    <row r="39" ht="18" customHeight="1"/>
+    <row r="40" ht="30.6" customHeight="1"/>
+    <row r="52" ht="30.95" customHeight="1"/>
+    <row r="64" ht="27.95" customHeight="1"/>
+    <row r="76" ht="30" customHeight="1"/>
+    <row r="88" ht="31.5" customHeight="1"/>
+    <row r="100" ht="27.95" customHeight="1"/>
+    <row r="112" ht="31.5" customHeight="1"/>
+    <row r="124" ht="32.450000000000003" customHeight="1"/>
+    <row r="136" ht="27.95" customHeight="1"/>
+    <row r="137" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="17">
+    <mergeCell ref="AP2:AS2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="AL2:AO2"/>
     <mergeCell ref="AT2:AW2"/>
     <mergeCell ref="AX2:BA2"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B23"/>
     <mergeCell ref="Z2:AC2"/>
     <mergeCell ref="AD2:AG2"/>
     <mergeCell ref="AH2:AK2"/>
-    <mergeCell ref="J9:J12"/>
-    <mergeCell ref="K9:K12"/>
-    <mergeCell ref="L9:L12"/>
-    <mergeCell ref="M9:M12"/>
     <mergeCell ref="R2:U2"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="V2:Y2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="C22:R23"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="AP2:AS2"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="H9:H12"/>
-    <mergeCell ref="I9:I12"/>
-    <mergeCell ref="C2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
@@ -10236,44 +10011,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65A7D1A-A130-4CF2-8F53-8DE497F18C35}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.19921875" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23">
+    <row r="1" spans="1:6" ht="23.25">
       <c r="A1" s="97" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="38.25">
+      <c r="A3" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="105" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="106" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="111" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="39">
-      <c r="A3" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="107" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="109" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="113" t="s">
-        <v>180</v>
-      </c>
-    </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="110">
+      <c r="A4" s="108">
         <v>1</v>
       </c>
-      <c r="B4" s="112">
+      <c r="B4" s="110">
         <v>45748</v>
       </c>
       <c r="C4" s="1">
@@ -10284,345 +10059,345 @@
         <f>C4</f>
         <v>55200</v>
       </c>
-      <c r="E4" s="1">
-        <f>EXPENSES!C21</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="99">
+      <c r="E4" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F4" s="98" t="e">
         <f>C4-E4</f>
-        <v>55200</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="110">
+      <c r="A5" s="108">
         <v>2</v>
       </c>
-      <c r="B5" s="112">
+      <c r="B5" s="110">
         <v>45778</v>
       </c>
       <c r="C5" s="1">
         <f>'Month wise MC'!C5</f>
         <v>55200</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="1" t="e">
         <f t="shared" ref="D5:D12" si="0">C5+F4</f>
-        <v>110400</v>
-      </c>
-      <c r="E5" s="111">
-        <f>EXPENSES!E21</f>
-        <v>23533</v>
-      </c>
-      <c r="F5" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="109" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F5" s="1" t="e">
         <f t="shared" ref="F5:F17" si="1">D5-E5</f>
-        <v>86867</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="110">
+      <c r="A6" s="108">
         <v>3</v>
       </c>
-      <c r="B6" s="112">
+      <c r="B6" s="110">
         <v>45809</v>
       </c>
       <c r="C6" s="1">
         <f>'Month wise MC'!C6</f>
         <v>54100</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>140967</v>
-      </c>
-      <c r="E6" s="111">
-        <f>EXPENSES!H21</f>
-        <v>32714</v>
-      </c>
-      <c r="F6" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E6" s="109" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F6" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>108253</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="110">
+      <c r="A7" s="108">
         <v>4</v>
       </c>
-      <c r="B7" s="112">
+      <c r="B7" s="110">
         <v>45839</v>
       </c>
       <c r="C7" s="1">
         <f>'Month wise MC'!C7</f>
         <v>71300</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>179553</v>
-      </c>
-      <c r="E7" s="111">
-        <f>EXPENSES!K21</f>
-        <v>32385</v>
-      </c>
-      <c r="F7" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E7" s="109" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F7" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>147168</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="110">
+      <c r="A8" s="108">
         <v>5</v>
       </c>
-      <c r="B8" s="112">
+      <c r="B8" s="110">
         <v>45870</v>
       </c>
       <c r="C8" s="1">
         <f>'Month wise MC'!C8</f>
         <v>57700</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>204868</v>
-      </c>
-      <c r="E8" s="111">
-        <f>EXPENSES!N21</f>
-        <v>29653</v>
-      </c>
-      <c r="F8" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E8" s="109" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F8" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>175215</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="110">
+      <c r="A9" s="108">
         <v>6</v>
       </c>
-      <c r="B9" s="112">
+      <c r="B9" s="110">
         <v>45901</v>
       </c>
       <c r="C9" s="1">
         <f>'Month wise MC'!C9</f>
         <v>57700</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>232915</v>
-      </c>
-      <c r="E9" s="1">
-        <f>EXPENSES!R21</f>
-        <v>45523</v>
-      </c>
-      <c r="F9" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E9" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F9" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>187392</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
-      <c r="A10" s="110">
+      <c r="A10" s="108">
         <v>7</v>
       </c>
-      <c r="B10" s="112">
+      <c r="B10" s="110">
         <v>45931</v>
       </c>
       <c r="C10" s="1">
         <f>'Month wise MC'!C10</f>
         <v>78900</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>266292</v>
-      </c>
-      <c r="E10" s="1">
-        <f>EXPENSES!V21</f>
-        <v>41892</v>
-      </c>
-      <c r="F10" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E10" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F10" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>224400</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1">
-      <c r="A11" s="110">
+      <c r="A11" s="108">
         <v>8</v>
       </c>
-      <c r="B11" s="112">
+      <c r="B11" s="110">
         <v>45962</v>
       </c>
       <c r="C11" s="1">
         <f>'Month wise MC'!C11</f>
         <v>68500</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>292900</v>
-      </c>
-      <c r="E11" s="1">
-        <f>EXPENSES!Z21</f>
-        <v>41396</v>
-      </c>
-      <c r="F11" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E11" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F11" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>251504</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="110">
+      <c r="A12" s="108">
         <v>9</v>
       </c>
-      <c r="B12" s="112">
+      <c r="B12" s="110">
         <v>45992</v>
       </c>
       <c r="C12" s="1">
         <f>'Month wise MC'!C12</f>
         <v>71000</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="1" t="e">
         <f t="shared" si="0"/>
-        <v>322504</v>
-      </c>
-      <c r="E12" s="1">
-        <f>EXPENSES!AD21</f>
-        <v>56463</v>
-      </c>
-      <c r="F12" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E12" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F12" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>266041</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1">
-      <c r="A13" s="110">
+      <c r="A13" s="108">
         <v>10</v>
       </c>
-      <c r="B13" s="112">
+      <c r="B13" s="110">
         <v>46023</v>
       </c>
       <c r="C13" s="1">
         <f>'Month wise MC'!C13</f>
         <v>65800</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="1" t="e">
         <f>C13+F12</f>
-        <v>331841</v>
-      </c>
-      <c r="E13" s="1">
-        <f>EXPENSES!AH21</f>
-        <v>57882</v>
-      </c>
-      <c r="F13" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E13" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F13" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>273959</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1">
-      <c r="A14" s="110">
+      <c r="A14" s="108">
         <v>11</v>
       </c>
-      <c r="B14" s="112">
+      <c r="B14" s="110">
         <v>46054</v>
       </c>
       <c r="C14" s="1">
         <f>'Month wise MC'!C14</f>
         <v>66000</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="1" t="e">
         <f>C14+F13</f>
-        <v>339959</v>
-      </c>
-      <c r="E14" s="1">
-        <f>EXPENSES!AL21</f>
-        <v>76927</v>
-      </c>
-      <c r="F14" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E14" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F14" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>263032</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1">
-      <c r="A15" s="110">
+      <c r="A15" s="108">
         <v>12</v>
       </c>
-      <c r="B15" s="112">
+      <c r="B15" s="110">
         <v>46082</v>
       </c>
       <c r="C15" s="1">
         <f>'Month wise MC'!C15</f>
         <v>66000</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="1" t="e">
         <f t="shared" ref="D15:D17" si="2">C15+F14</f>
-        <v>329032</v>
-      </c>
-      <c r="E15" s="1">
-        <f>EXPENSES!AP21</f>
-        <v>61966</v>
-      </c>
-      <c r="F15" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E15" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F15" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>267066</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1">
-      <c r="A16" s="110">
+      <c r="A16" s="108">
         <v>13</v>
       </c>
-      <c r="B16" s="112">
+      <c r="B16" s="110">
         <v>46113</v>
       </c>
       <c r="C16" s="1">
         <f>'Month wise MC'!C16</f>
         <v>66000</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="1" t="e">
         <f t="shared" si="2"/>
-        <v>333066</v>
-      </c>
-      <c r="E16" s="1">
-        <f>EXPENSES!AT21</f>
-        <v>48553</v>
-      </c>
-      <c r="F16" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E16" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F16" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>284513</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1">
-      <c r="A17" s="110">
+      <c r="A17" s="108">
         <v>14</v>
       </c>
-      <c r="B17" s="112">
+      <c r="B17" s="110">
         <v>46143</v>
       </c>
       <c r="C17" s="1">
         <f>'Month wise MC'!C17</f>
         <v>64800</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="1" t="e">
         <f t="shared" si="2"/>
-        <v>349313</v>
-      </c>
-      <c r="E17" s="1">
-        <f>EXPENSES!AX21</f>
-        <v>53967</v>
-      </c>
-      <c r="F17" s="1">
+        <v>#REF!</v>
+      </c>
+      <c r="E17" s="1" t="e">
+        <f>EXPENSES!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F17" s="1" t="e">
         <f t="shared" si="1"/>
-        <v>295346</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="13" customHeight="1">
-      <c r="A18" s="199" t="s">
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="12.95" customHeight="1">
+      <c r="A18" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="199"/>
+      <c r="B18" s="135"/>
       <c r="C18" s="45">
         <f>SUM(C4:C13)</f>
         <v>635400</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="45" t="e">
         <f>SUM(D4:D17)</f>
-        <v>3488810</v>
-      </c>
-      <c r="E18" s="45">
+        <v>#REF!</v>
+      </c>
+      <c r="E18" s="45" t="e">
         <f>SUM(E4:E17)</f>
-        <v>602854</v>
-      </c>
-      <c r="F18" s="121"/>
+        <v>#REF!</v>
+      </c>
+      <c r="F18" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
+++ b/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f25347fadc9be86b/Documents/MaintApp/MaintApp/maintainance ^0 expenditure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\developer\MaintApp\maintainance &amp; expenditure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{84E53382-A171-4EBB-97C4-844A4882A8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91A8EAA9-EB50-400E-B797-49339A8F46F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E13494E-9ED8-412A-86F8-319BB186B64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Details MC" sheetId="5" r:id="rId1"/>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="245">
   <si>
     <t>Dr. Narendranath Pal</t>
   </si>
@@ -951,7 +951,7 @@
     <numFmt numFmtId="166" formatCode="\₹\ 0.00"/>
     <numFmt numFmtId="167" formatCode="\₹\ #,##0.00;[Red]\₹\ #,##0.00"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1178,6 +1178,13 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1591,7 +1598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="321">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2505,12 +2512,30 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2526,25 +2551,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2892,17 +2905,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51717A2D-38D8-4ABE-BD5F-98B6647922FB}">
-  <dimension ref="A1:G636"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K639"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" style="185" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" style="185" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" style="185" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" style="185" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" style="185" customWidth="1"/>
     <col min="4" max="4" width="20" style="185" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="184" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="184" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="184" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="184" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="184" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="183"/>
+    <col min="8" max="16384" width="8.77734375" style="183"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30">
@@ -2925,11 +2939,11 @@
       <c r="F2" s="303"/>
       <c r="G2" s="303"/>
     </row>
-    <row r="3" spans="1:7" ht="18.75">
+    <row r="3" spans="1:7" ht="17.399999999999999">
       <c r="F3" s="302"/>
       <c r="G3" s="302"/>
     </row>
-    <row r="4" spans="1:7" ht="40.5">
+    <row r="4" spans="1:7" ht="24.6">
       <c r="A4" s="301" t="s">
         <v>5</v>
       </c>
@@ -2942,7 +2956,7 @@
       </c>
       <c r="G4" s="297"/>
     </row>
-    <row r="5" spans="1:7" ht="20.25">
+    <row r="5" spans="1:7" ht="20.399999999999999">
       <c r="A5" s="295" t="s">
         <v>12</v>
       </c>
@@ -2965,7 +2979,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="23.25">
+    <row r="6" spans="1:7" ht="22.8" hidden="1">
       <c r="A6" s="192">
         <v>1</v>
       </c>
@@ -2988,7 +3002,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="23.25">
+    <row r="7" spans="1:7" ht="22.8" hidden="1">
       <c r="A7" s="192">
         <v>2</v>
       </c>
@@ -3011,7 +3025,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="23.25">
+    <row r="8" spans="1:7" ht="22.8" hidden="1">
       <c r="A8" s="192">
         <v>3</v>
       </c>
@@ -3034,7 +3048,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="23.25">
+    <row r="9" spans="1:7" ht="22.8" hidden="1">
       <c r="A9" s="192">
         <v>4</v>
       </c>
@@ -3055,7 +3069,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="23.25">
+    <row r="10" spans="1:7" ht="22.8" hidden="1">
       <c r="A10" s="192">
         <v>5</v>
       </c>
@@ -3078,7 +3092,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="23.25">
+    <row r="11" spans="1:7" ht="22.8" hidden="1">
       <c r="A11" s="192">
         <v>6</v>
       </c>
@@ -3101,7 +3115,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="23.25">
+    <row r="12" spans="1:7" ht="22.8" hidden="1">
       <c r="A12" s="192">
         <v>7</v>
       </c>
@@ -3124,7 +3138,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="23.25">
+    <row r="13" spans="1:7" ht="22.8" hidden="1">
       <c r="A13" s="188">
         <v>8</v>
       </c>
@@ -3147,7 +3161,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="23.25">
+    <row r="14" spans="1:7" ht="22.8" hidden="1">
       <c r="A14" s="192">
         <v>9</v>
       </c>
@@ -3170,7 +3184,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="23.25">
+    <row r="15" spans="1:7" ht="22.8" hidden="1">
       <c r="A15" s="192">
         <v>11</v>
       </c>
@@ -3193,7 +3207,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="23.25">
+    <row r="16" spans="1:7" ht="22.8" hidden="1">
       <c r="A16" s="192">
         <v>12</v>
       </c>
@@ -3216,7 +3230,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="23.25">
+    <row r="17" spans="1:7" ht="22.8" hidden="1">
       <c r="A17" s="192">
         <v>13</v>
       </c>
@@ -3239,7 +3253,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="23.25">
+    <row r="18" spans="1:7" ht="22.8" hidden="1">
       <c r="A18" s="192">
         <v>15</v>
       </c>
@@ -3262,7 +3276,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="23.25">
+    <row r="19" spans="1:7" ht="22.8" hidden="1">
       <c r="A19" s="192">
         <v>16</v>
       </c>
@@ -3285,7 +3299,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="23.25">
+    <row r="20" spans="1:7" ht="22.8" hidden="1">
       <c r="A20" s="192">
         <v>17</v>
       </c>
@@ -3308,7 +3322,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="23.25">
+    <row r="21" spans="1:7" ht="22.8" hidden="1">
       <c r="A21" s="188">
         <v>20</v>
       </c>
@@ -3331,7 +3345,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="23.25">
+    <row r="22" spans="1:7" ht="22.8" hidden="1">
       <c r="A22" s="192">
         <v>21</v>
       </c>
@@ -3354,7 +3368,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="23.25">
+    <row r="23" spans="1:7" ht="22.8" hidden="1">
       <c r="A23" s="192">
         <v>22</v>
       </c>
@@ -3377,7 +3391,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="23.25">
+    <row r="24" spans="1:7" ht="22.8" hidden="1">
       <c r="A24" s="192">
         <v>23</v>
       </c>
@@ -3400,7 +3414,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="46.5">
+    <row r="25" spans="1:7" ht="45.6" hidden="1">
       <c r="A25" s="192">
         <v>24</v>
       </c>
@@ -3423,7 +3437,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="23.25">
+    <row r="26" spans="1:7" ht="22.8" hidden="1">
       <c r="A26" s="192">
         <v>25</v>
       </c>
@@ -3446,7 +3460,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="23.25">
+    <row r="27" spans="1:7" ht="22.8" hidden="1">
       <c r="A27" s="192">
         <v>27</v>
       </c>
@@ -3469,7 +3483,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="23.25">
+    <row r="28" spans="1:7" ht="22.8" hidden="1">
       <c r="A28" s="192">
         <v>28</v>
       </c>
@@ -3492,7 +3506,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="23.25">
+    <row r="29" spans="1:7" ht="22.8" hidden="1">
       <c r="A29" s="192">
         <v>29</v>
       </c>
@@ -3515,7 +3529,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="23.25">
+    <row r="30" spans="1:7" ht="22.8" hidden="1">
       <c r="A30" s="188">
         <v>30</v>
       </c>
@@ -3538,7 +3552,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="23.25">
+    <row r="31" spans="1:7" ht="22.8" hidden="1">
       <c r="A31" s="192">
         <v>31</v>
       </c>
@@ -3561,7 +3575,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="23.25">
+    <row r="32" spans="1:7" ht="22.8" hidden="1">
       <c r="A32" s="192">
         <v>33</v>
       </c>
@@ -3584,7 +3598,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="23.25">
+    <row r="33" spans="1:7" ht="22.8" hidden="1">
       <c r="A33" s="192">
         <v>34</v>
       </c>
@@ -3607,7 +3621,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="23.25">
+    <row r="34" spans="1:7" ht="22.8" hidden="1">
       <c r="A34" s="192">
         <v>35</v>
       </c>
@@ -3630,7 +3644,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="23.25">
+    <row r="35" spans="1:7" ht="22.8" hidden="1">
       <c r="A35" s="192">
         <v>36</v>
       </c>
@@ -3653,7 +3667,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="23.25">
+    <row r="36" spans="1:7" ht="22.8" hidden="1">
       <c r="A36" s="192">
         <v>37</v>
       </c>
@@ -3676,7 +3690,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="23.25">
+    <row r="37" spans="1:7" ht="22.8" hidden="1">
       <c r="A37" s="192">
         <v>38</v>
       </c>
@@ -3699,7 +3713,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="23.25">
+    <row r="38" spans="1:7" ht="22.8" hidden="1">
       <c r="A38" s="192">
         <v>39</v>
       </c>
@@ -3722,7 +3736,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="23.25">
+    <row r="39" spans="1:7" ht="22.8" hidden="1">
       <c r="A39" s="188">
         <v>40</v>
       </c>
@@ -3745,7 +3759,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="23.25">
+    <row r="40" spans="1:7" ht="22.8" hidden="1">
       <c r="A40" s="192">
         <v>42</v>
       </c>
@@ -3768,7 +3782,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="23.25">
+    <row r="41" spans="1:7" ht="22.8" hidden="1">
       <c r="A41" s="192">
         <v>46</v>
       </c>
@@ -3791,7 +3805,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="23.25">
+    <row r="42" spans="1:7" ht="22.8" hidden="1">
       <c r="A42" s="192">
         <v>47</v>
       </c>
@@ -3814,7 +3828,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="23.25">
+    <row r="43" spans="1:7" ht="22.8" hidden="1">
       <c r="A43" s="192">
         <v>50</v>
       </c>
@@ -3837,7 +3851,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="23.25">
+    <row r="44" spans="1:7" ht="22.8" hidden="1">
       <c r="A44" s="192">
         <v>51</v>
       </c>
@@ -3860,7 +3874,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="23.25">
+    <row r="45" spans="1:7" ht="22.8" hidden="1">
       <c r="A45" s="192">
         <v>52</v>
       </c>
@@ -3883,7 +3897,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="23.25">
+    <row r="46" spans="1:7" ht="22.8" hidden="1">
       <c r="A46" s="192">
         <v>58</v>
       </c>
@@ -3906,7 +3920,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="23.25">
+    <row r="47" spans="1:7" ht="22.8" hidden="1">
       <c r="A47" s="188">
         <v>59</v>
       </c>
@@ -3929,7 +3943,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="23.25">
+    <row r="48" spans="1:7" ht="22.8" hidden="1">
       <c r="A48" s="192">
         <v>60</v>
       </c>
@@ -3952,7 +3966,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="23.25">
+    <row r="49" spans="1:7" ht="22.8" hidden="1">
       <c r="A49" s="192">
         <v>1</v>
       </c>
@@ -3975,7 +3989,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="23.25">
+    <row r="50" spans="1:7" ht="22.8" hidden="1">
       <c r="A50" s="192">
         <v>2</v>
       </c>
@@ -3998,7 +4012,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="23.25">
+    <row r="51" spans="1:7" ht="22.8" hidden="1">
       <c r="A51" s="192">
         <v>3</v>
       </c>
@@ -4021,7 +4035,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="23.25">
+    <row r="52" spans="1:7" ht="22.8" hidden="1">
       <c r="A52" s="192">
         <v>4</v>
       </c>
@@ -4042,7 +4056,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="23.25">
+    <row r="53" spans="1:7" ht="22.8" hidden="1">
       <c r="A53" s="192">
         <v>5</v>
       </c>
@@ -4065,7 +4079,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="23.25">
+    <row r="54" spans="1:7" ht="22.8" hidden="1">
       <c r="A54" s="192">
         <v>6</v>
       </c>
@@ -4088,7 +4102,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="23.25">
+    <row r="55" spans="1:7" ht="22.8" hidden="1">
       <c r="A55" s="192">
         <v>7</v>
       </c>
@@ -4111,7 +4125,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="23.25">
+    <row r="56" spans="1:7" ht="22.8" hidden="1">
       <c r="A56" s="188">
         <v>8</v>
       </c>
@@ -4134,7 +4148,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="23.25">
+    <row r="57" spans="1:7" ht="22.8" hidden="1">
       <c r="A57" s="192">
         <v>9</v>
       </c>
@@ -4157,7 +4171,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="23.25">
+    <row r="58" spans="1:7" ht="22.8" hidden="1">
       <c r="A58" s="192">
         <v>11</v>
       </c>
@@ -4180,7 +4194,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="23.25">
+    <row r="59" spans="1:7" ht="22.8" hidden="1">
       <c r="A59" s="192">
         <v>12</v>
       </c>
@@ -4203,7 +4217,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="23.25">
+    <row r="60" spans="1:7" ht="22.8" hidden="1">
       <c r="A60" s="192">
         <v>13</v>
       </c>
@@ -4226,7 +4240,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="23.25">
+    <row r="61" spans="1:7" ht="22.8" hidden="1">
       <c r="A61" s="192">
         <v>15</v>
       </c>
@@ -4249,7 +4263,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="23.25">
+    <row r="62" spans="1:7" ht="22.8" hidden="1">
       <c r="A62" s="192">
         <v>16</v>
       </c>
@@ -4272,7 +4286,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="23.25">
+    <row r="63" spans="1:7" ht="22.8" hidden="1">
       <c r="A63" s="192">
         <v>17</v>
       </c>
@@ -4295,7 +4309,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="23.25">
+    <row r="64" spans="1:7" ht="22.8" hidden="1">
       <c r="A64" s="192">
         <v>20</v>
       </c>
@@ -4318,7 +4332,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="23.25">
+    <row r="65" spans="1:7" ht="22.8" hidden="1">
       <c r="A65" s="188">
         <v>21</v>
       </c>
@@ -4341,7 +4355,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="23.25">
+    <row r="66" spans="1:7" ht="22.8" hidden="1">
       <c r="A66" s="192">
         <v>22</v>
       </c>
@@ -4364,7 +4378,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="23.25">
+    <row r="67" spans="1:7" ht="22.8" hidden="1">
       <c r="A67" s="192">
         <v>23</v>
       </c>
@@ -4387,7 +4401,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="46.5">
+    <row r="68" spans="1:7" ht="45.6" hidden="1">
       <c r="A68" s="192">
         <v>24</v>
       </c>
@@ -4410,7 +4424,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="23.25">
+    <row r="69" spans="1:7" ht="22.8" hidden="1">
       <c r="A69" s="192">
         <v>25</v>
       </c>
@@ -4433,7 +4447,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="23.25">
+    <row r="70" spans="1:7" ht="22.8" hidden="1">
       <c r="A70" s="192">
         <v>27</v>
       </c>
@@ -4456,7 +4470,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="23.25">
+    <row r="71" spans="1:7" ht="22.8" hidden="1">
       <c r="A71" s="192">
         <v>28</v>
       </c>
@@ -4479,7 +4493,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="23.25">
+    <row r="72" spans="1:7" ht="22.8" hidden="1">
       <c r="A72" s="192">
         <v>29</v>
       </c>
@@ -4502,7 +4516,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="23.25">
+    <row r="73" spans="1:7" ht="22.8" hidden="1">
       <c r="A73" s="192">
         <v>30</v>
       </c>
@@ -4525,7 +4539,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="23.25">
+    <row r="74" spans="1:7" ht="22.8" hidden="1">
       <c r="A74" s="217">
         <v>31</v>
       </c>
@@ -4548,7 +4562,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="23.25">
+    <row r="75" spans="1:7" ht="22.8" hidden="1">
       <c r="A75" s="192">
         <v>33</v>
       </c>
@@ -4571,7 +4585,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="23.25">
+    <row r="76" spans="1:7" ht="22.8" hidden="1">
       <c r="A76" s="217">
         <v>34</v>
       </c>
@@ -4594,7 +4608,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="23.25">
+    <row r="77" spans="1:7" ht="22.8" hidden="1">
       <c r="A77" s="217">
         <v>35</v>
       </c>
@@ -4617,7 +4631,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="23.25">
+    <row r="78" spans="1:7" ht="22.8" hidden="1">
       <c r="A78" s="208">
         <v>36</v>
       </c>
@@ -4640,7 +4654,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="23.25">
+    <row r="79" spans="1:7" ht="22.8" hidden="1">
       <c r="A79" s="285">
         <v>37</v>
       </c>
@@ -4663,7 +4677,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="23.25">
+    <row r="80" spans="1:7" ht="22.8" hidden="1">
       <c r="A80" s="285">
         <v>38</v>
       </c>
@@ -4686,7 +4700,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="23.25">
+    <row r="81" spans="1:11" ht="22.8" hidden="1">
       <c r="A81" s="283">
         <v>39</v>
       </c>
@@ -4709,7 +4723,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="23.25">
+    <row r="82" spans="1:11" ht="22.8" hidden="1">
       <c r="A82" s="192">
         <v>40</v>
       </c>
@@ -4732,7 +4746,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="23.25">
+    <row r="83" spans="1:11" ht="22.8" hidden="1">
       <c r="A83" s="192">
         <v>42</v>
       </c>
@@ -4755,7 +4769,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="23.25">
+    <row r="84" spans="1:11" ht="22.8" hidden="1">
       <c r="A84" s="192">
         <v>46</v>
       </c>
@@ -4778,7 +4792,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="23.25">
+    <row r="85" spans="1:11" ht="22.8" hidden="1">
       <c r="A85" s="192">
         <v>47</v>
       </c>
@@ -4801,7 +4815,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="23.25">
+    <row r="86" spans="1:11" ht="22.8" hidden="1">
       <c r="A86" s="192">
         <v>50</v>
       </c>
@@ -4824,7 +4838,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="23.25">
+    <row r="87" spans="1:11" ht="22.8" hidden="1">
       <c r="A87" s="192">
         <v>51</v>
       </c>
@@ -4847,7 +4861,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="23.25">
+    <row r="88" spans="1:11" ht="22.8" hidden="1">
       <c r="A88" s="192">
         <v>52</v>
       </c>
@@ -4870,7 +4884,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="23.25">
+    <row r="89" spans="1:11" ht="22.8" hidden="1">
       <c r="A89" s="192">
         <v>58</v>
       </c>
@@ -4893,7 +4907,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="23.25">
+    <row r="90" spans="1:11" ht="22.8" hidden="1">
       <c r="A90" s="188">
         <v>59</v>
       </c>
@@ -4916,7 +4930,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="23.25">
+    <row r="91" spans="1:11" ht="22.8" hidden="1">
       <c r="A91" s="192">
         <v>60</v>
       </c>
@@ -4939,7 +4953,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="23.25">
+    <row r="92" spans="1:11" ht="22.8">
       <c r="A92" s="192">
         <v>1</v>
       </c>
@@ -4961,8 +4975,14 @@
       <c r="G92" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="23.25">
+      <c r="J92" s="183" t="s">
+        <v>27</v>
+      </c>
+      <c r="K92" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="22.8">
       <c r="A93" s="192">
         <v>2</v>
       </c>
@@ -4984,8 +5004,14 @@
       <c r="G93" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="23.25">
+      <c r="J93" s="183" t="s">
+        <v>29</v>
+      </c>
+      <c r="K93" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="22.8">
       <c r="A94" s="192">
         <v>3</v>
       </c>
@@ -5007,8 +5033,14 @@
       <c r="G94" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="23.25">
+      <c r="J94" s="183" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="22.8">
       <c r="A95" s="192">
         <v>4</v>
       </c>
@@ -5028,8 +5060,14 @@
       <c r="G95" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="23.25">
+      <c r="J95" s="183" t="s">
+        <v>32</v>
+      </c>
+      <c r="K95" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="22.8">
       <c r="A96" s="192">
         <v>5</v>
       </c>
@@ -5051,8 +5089,14 @@
       <c r="G96" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="23.25">
+      <c r="J96" s="183" t="s">
+        <v>34</v>
+      </c>
+      <c r="K96" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="22.8">
       <c r="A97" s="192">
         <v>6</v>
       </c>
@@ -5074,8 +5118,14 @@
       <c r="G97" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="23.25">
+      <c r="J97" s="183" t="s">
+        <v>243</v>
+      </c>
+      <c r="K97" s="183">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="22.8">
       <c r="A98" s="188">
         <v>7</v>
       </c>
@@ -5097,8 +5147,14 @@
       <c r="G98" s="243">
         <v>45853</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="23.25">
+      <c r="J98" s="183" t="s">
+        <v>37</v>
+      </c>
+      <c r="K98" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="22.8">
       <c r="A99" s="192">
         <v>8</v>
       </c>
@@ -5120,8 +5176,14 @@
       <c r="G99" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="23.25">
+      <c r="J99" s="183" t="s">
+        <v>242</v>
+      </c>
+      <c r="K99" s="183">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="22.8">
       <c r="A100" s="192">
         <v>9</v>
       </c>
@@ -5143,8 +5205,14 @@
       <c r="G100" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="23.25">
+      <c r="J100" s="183" t="s">
+        <v>40</v>
+      </c>
+      <c r="K100" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="22.8">
       <c r="A101" s="192">
         <v>11</v>
       </c>
@@ -5166,8 +5234,14 @@
       <c r="G101" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="23.25">
+      <c r="J101" s="183" t="s">
+        <v>43</v>
+      </c>
+      <c r="K101" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="22.8">
       <c r="A102" s="192">
         <v>12</v>
       </c>
@@ -5189,8 +5263,14 @@
       <c r="G102" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="23.25">
+      <c r="J102" s="183" t="s">
+        <v>45</v>
+      </c>
+      <c r="K102" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="22.8">
       <c r="A103" s="192">
         <v>13</v>
       </c>
@@ -5212,8 +5292,14 @@
       <c r="G103" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="23.25">
+      <c r="J103" s="183" t="s">
+        <v>47</v>
+      </c>
+      <c r="K103" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="22.8">
       <c r="A104" s="192">
         <v>15</v>
       </c>
@@ -5235,8 +5321,14 @@
       <c r="G104" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="23.25">
+      <c r="J104" s="183" t="s">
+        <v>50</v>
+      </c>
+      <c r="K104" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="22.8">
       <c r="A105" s="192">
         <v>16</v>
       </c>
@@ -5258,8 +5350,14 @@
       <c r="G105" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="23.25">
+      <c r="J105" s="183" t="s">
+        <v>52</v>
+      </c>
+      <c r="K105" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="22.8">
       <c r="A106" s="192">
         <v>17</v>
       </c>
@@ -5281,8 +5379,14 @@
       <c r="G106" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="23.25">
+      <c r="J106" s="183" t="s">
+        <v>54</v>
+      </c>
+      <c r="K106" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="22.8">
       <c r="A107" s="188">
         <v>20</v>
       </c>
@@ -5304,8 +5408,14 @@
       <c r="G107" s="243">
         <v>45853</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="23.25">
+      <c r="J107" s="183" t="s">
+        <v>58</v>
+      </c>
+      <c r="K107" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="22.8">
       <c r="A108" s="192">
         <v>21</v>
       </c>
@@ -5327,8 +5437,14 @@
       <c r="G108" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="23.25">
+      <c r="J108" s="183" t="s">
+        <v>60</v>
+      </c>
+      <c r="K108" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="22.8">
       <c r="A109" s="192">
         <v>22</v>
       </c>
@@ -5350,8 +5466,14 @@
       <c r="G109" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="23.25">
+      <c r="J109" s="183" t="s">
+        <v>62</v>
+      </c>
+      <c r="K109" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="22.8">
       <c r="A110" s="192">
         <v>23</v>
       </c>
@@ -5373,8 +5495,14 @@
       <c r="G110" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="46.5">
+      <c r="J110" s="183" t="s">
+        <v>64</v>
+      </c>
+      <c r="K110" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="45.6">
       <c r="A111" s="192">
         <v>24</v>
       </c>
@@ -5396,8 +5524,14 @@
       <c r="G111" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="23.25">
+      <c r="J111" s="183" t="s">
+        <v>66</v>
+      </c>
+      <c r="K111" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="22.8">
       <c r="A112" s="192">
         <v>25</v>
       </c>
@@ -5419,8 +5553,14 @@
       <c r="G112" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="23.25">
+      <c r="J112" s="183" t="s">
+        <v>68</v>
+      </c>
+      <c r="K112" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="22.8">
       <c r="A113" s="192">
         <v>27</v>
       </c>
@@ -5442,8 +5582,14 @@
       <c r="G113" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="23.25">
+      <c r="J113" s="183" t="s">
+        <v>71</v>
+      </c>
+      <c r="K113" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="22.8">
       <c r="A114" s="192">
         <v>28</v>
       </c>
@@ -5465,8 +5611,14 @@
       <c r="G114" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="23.25">
+      <c r="J114" s="183" t="s">
+        <v>73</v>
+      </c>
+      <c r="K114" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="22.8">
       <c r="A115" s="192">
         <v>29</v>
       </c>
@@ -5488,8 +5640,14 @@
       <c r="G115" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="23.25">
+      <c r="J115" s="183" t="s">
+        <v>75</v>
+      </c>
+      <c r="K115" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="22.8">
       <c r="A116" s="188">
         <v>30</v>
       </c>
@@ -5511,8 +5669,14 @@
       <c r="G116" s="243">
         <v>45853</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="23.25">
+      <c r="J116" s="183" t="s">
+        <v>77</v>
+      </c>
+      <c r="K116" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="22.8">
       <c r="A117" s="192">
         <v>31</v>
       </c>
@@ -5534,8 +5698,14 @@
       <c r="G117" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="23.25">
+      <c r="J117" s="183" t="s">
+        <v>79</v>
+      </c>
+      <c r="K117" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="22.8">
       <c r="A118" s="192">
         <v>33</v>
       </c>
@@ -5557,8 +5727,14 @@
       <c r="G118" s="273">
         <v>45853</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="23.25">
+      <c r="J118" s="183" t="s">
+        <v>82</v>
+      </c>
+      <c r="K118" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="22.8">
       <c r="A119" s="192">
         <v>34</v>
       </c>
@@ -5580,8 +5756,14 @@
       <c r="G119" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="23.25">
+      <c r="J119" s="183" t="s">
+        <v>84</v>
+      </c>
+      <c r="K119" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="22.8">
       <c r="A120" s="192">
         <v>35</v>
       </c>
@@ -5603,8 +5785,14 @@
       <c r="G120" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="23.25">
+      <c r="J120" s="183" t="s">
+        <v>244</v>
+      </c>
+      <c r="K120" s="183">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="22.8">
       <c r="A121" s="192">
         <v>36</v>
       </c>
@@ -5626,8 +5814,14 @@
       <c r="G121" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="23.25">
+      <c r="J121" s="183" t="s">
+        <v>88</v>
+      </c>
+      <c r="K121" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="22.8">
       <c r="A122" s="192">
         <v>37</v>
       </c>
@@ -5649,8 +5843,14 @@
       <c r="G122" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="23.25">
+      <c r="J122" s="183" t="s">
+        <v>90</v>
+      </c>
+      <c r="K122" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="22.8">
       <c r="A123" s="192">
         <v>38</v>
       </c>
@@ -5672,8 +5872,14 @@
       <c r="G123" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="23.25">
+      <c r="J123" s="183" t="s">
+        <v>92</v>
+      </c>
+      <c r="K123" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="22.8">
       <c r="A124" s="188">
         <v>39</v>
       </c>
@@ -5695,8 +5901,14 @@
       <c r="G124" s="243">
         <v>45853</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="23.25">
+      <c r="J124" s="183" t="s">
+        <v>94</v>
+      </c>
+      <c r="K124" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="22.8">
       <c r="A125" s="192">
         <v>40</v>
       </c>
@@ -5718,8 +5930,14 @@
       <c r="G125" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="23.25">
+      <c r="J125" s="183" t="s">
+        <v>96</v>
+      </c>
+      <c r="K125" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="22.8">
       <c r="A126" s="192">
         <v>42</v>
       </c>
@@ -5741,8 +5959,14 @@
       <c r="G126" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="23.25">
+      <c r="J126" s="183" t="s">
+        <v>99</v>
+      </c>
+      <c r="K126" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" ht="22.8" hidden="1">
       <c r="A127" s="192">
         <v>46</v>
       </c>
@@ -5764,8 +5988,14 @@
       <c r="G127" s="253">
         <v>45938</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="23.25">
+      <c r="J127" s="183" t="s">
+        <v>106</v>
+      </c>
+      <c r="K127" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" ht="22.8">
       <c r="A128" s="192">
         <v>47</v>
       </c>
@@ -5787,8 +6017,14 @@
       <c r="G128" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="23.25">
+      <c r="J128" s="183" t="s">
+        <v>110</v>
+      </c>
+      <c r="K128" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" ht="22.8">
       <c r="A129" s="192">
         <v>50</v>
       </c>
@@ -5810,8 +6046,14 @@
       <c r="G129" s="253">
         <v>45853</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="23.25">
+      <c r="J129" s="183" t="s">
+        <v>112</v>
+      </c>
+      <c r="K129" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="22.8">
       <c r="A130" s="192">
         <v>51</v>
       </c>
@@ -5833,8 +6075,14 @@
       <c r="G130" s="273">
         <v>45853</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="23.25">
+      <c r="J130" s="183" t="s">
+        <v>114</v>
+      </c>
+      <c r="K130" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="22.8">
       <c r="A131" s="192">
         <v>52</v>
       </c>
@@ -5856,8 +6104,14 @@
       <c r="G131" s="273">
         <v>45853</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="23.25">
+      <c r="J131" s="183" t="s">
+        <v>121</v>
+      </c>
+      <c r="K131" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" ht="22.8" hidden="1">
       <c r="A132" s="192">
         <v>58</v>
       </c>
@@ -5877,8 +6131,14 @@
         <v>1300</v>
       </c>
       <c r="G132" s="277"/>
-    </row>
-    <row r="133" spans="1:7" ht="23.25">
+      <c r="J132" s="183" t="s">
+        <v>123</v>
+      </c>
+      <c r="K132" s="183">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" ht="22.8" hidden="1">
       <c r="A133" s="188">
         <v>59</v>
       </c>
@@ -5898,8 +6158,14 @@
         <v>1300</v>
       </c>
       <c r="G133" s="278"/>
-    </row>
-    <row r="134" spans="1:7" ht="23.25">
+      <c r="J133" s="183" t="s">
+        <v>125</v>
+      </c>
+      <c r="K133" s="183">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" ht="22.8" hidden="1">
       <c r="A134" s="192">
         <v>60</v>
       </c>
@@ -5920,7 +6186,7 @@
       </c>
       <c r="G134" s="277"/>
     </row>
-    <row r="135" spans="1:7" ht="23.25">
+    <row r="135" spans="1:11" ht="22.8" hidden="1">
       <c r="A135" s="192">
         <v>1</v>
       </c>
@@ -5943,7 +6209,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="23.25">
+    <row r="136" spans="1:11" ht="22.8" hidden="1">
       <c r="A136" s="192">
         <v>2</v>
       </c>
@@ -5966,7 +6232,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="23.25">
+    <row r="137" spans="1:11" ht="22.8" hidden="1">
       <c r="A137" s="192">
         <v>3</v>
       </c>
@@ -5989,7 +6255,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="23.25">
+    <row r="138" spans="1:11" ht="22.8" hidden="1">
       <c r="A138" s="192">
         <v>4</v>
       </c>
@@ -6011,7 +6277,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="23.25">
+    <row r="139" spans="1:11" ht="22.8" hidden="1">
       <c r="A139" s="192">
         <v>5</v>
       </c>
@@ -6034,7 +6300,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="23.25">
+    <row r="140" spans="1:11" ht="22.8" hidden="1">
       <c r="A140" s="192">
         <v>6</v>
       </c>
@@ -6057,7 +6323,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="23.25">
+    <row r="141" spans="1:11" ht="22.8" hidden="1">
       <c r="A141" s="192">
         <v>7</v>
       </c>
@@ -6080,7 +6346,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="23.25">
+    <row r="142" spans="1:11" ht="22.8" hidden="1">
       <c r="A142" s="188">
         <v>8</v>
       </c>
@@ -6103,7 +6369,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="23.25">
+    <row r="143" spans="1:11" ht="22.8" hidden="1">
       <c r="A143" s="192">
         <v>9</v>
       </c>
@@ -6126,7 +6392,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="23.25">
+    <row r="144" spans="1:11" ht="22.8" hidden="1">
       <c r="A144" s="192">
         <v>11</v>
       </c>
@@ -6149,7 +6415,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="23.25">
+    <row r="145" spans="1:7" ht="22.8" hidden="1">
       <c r="A145" s="192">
         <v>12</v>
       </c>
@@ -6172,7 +6438,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="23.25">
+    <row r="146" spans="1:7" ht="22.8" hidden="1">
       <c r="A146" s="192">
         <v>13</v>
       </c>
@@ -6195,7 +6461,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="23.25">
+    <row r="147" spans="1:7" ht="22.8" hidden="1">
       <c r="A147" s="192">
         <v>15</v>
       </c>
@@ -6218,7 +6484,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="23.25">
+    <row r="148" spans="1:7" ht="22.8" hidden="1">
       <c r="A148" s="192">
         <v>16</v>
       </c>
@@ -6241,7 +6507,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="23.25">
+    <row r="149" spans="1:7" ht="22.8" hidden="1">
       <c r="A149" s="192">
         <v>17</v>
       </c>
@@ -6264,7 +6530,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="23.25">
+    <row r="150" spans="1:7" ht="22.8" hidden="1">
       <c r="A150" s="192">
         <v>20</v>
       </c>
@@ -6287,7 +6553,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="23.25">
+    <row r="151" spans="1:7" ht="22.8" hidden="1">
       <c r="A151" s="217">
         <v>21</v>
       </c>
@@ -6310,7 +6576,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="23.25">
+    <row r="152" spans="1:7" ht="22.8" hidden="1">
       <c r="A152" s="192">
         <v>22</v>
       </c>
@@ -6333,7 +6599,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="23.25">
+    <row r="153" spans="1:7" ht="22.8" hidden="1">
       <c r="A153" s="217">
         <v>23</v>
       </c>
@@ -6356,7 +6622,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="46.5">
+    <row r="154" spans="1:7" ht="45.6" hidden="1">
       <c r="A154" s="217">
         <v>24</v>
       </c>
@@ -6379,7 +6645,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="23.25">
+    <row r="155" spans="1:7" ht="22.8" hidden="1">
       <c r="A155" s="208">
         <v>25</v>
       </c>
@@ -6402,7 +6668,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="23.25">
+    <row r="156" spans="1:7" ht="22.8" hidden="1">
       <c r="A156" s="192">
         <v>27</v>
       </c>
@@ -6425,7 +6691,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="23.25">
+    <row r="157" spans="1:7" ht="22.8" hidden="1">
       <c r="A157" s="192">
         <v>28</v>
       </c>
@@ -6448,7 +6714,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="23.25">
+    <row r="158" spans="1:7" ht="22.8" hidden="1">
       <c r="A158" s="192">
         <v>29</v>
       </c>
@@ -6471,7 +6737,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="23.25">
+    <row r="159" spans="1:7" ht="22.8" hidden="1">
       <c r="A159" s="192">
         <v>30</v>
       </c>
@@ -6494,7 +6760,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="23.25">
+    <row r="160" spans="1:7" ht="22.8" hidden="1">
       <c r="A160" s="192">
         <v>31</v>
       </c>
@@ -6517,7 +6783,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="23.25">
+    <row r="161" spans="1:7" ht="22.8" hidden="1">
       <c r="A161" s="192">
         <v>33</v>
       </c>
@@ -6540,7 +6806,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="23.25">
+    <row r="162" spans="1:7" ht="22.8" hidden="1">
       <c r="A162" s="192">
         <v>34</v>
       </c>
@@ -6563,7 +6829,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="23.25">
+    <row r="163" spans="1:7" ht="22.8" hidden="1">
       <c r="A163" s="192">
         <v>35</v>
       </c>
@@ -6586,7 +6852,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="23.25">
+    <row r="164" spans="1:7" ht="22.8" hidden="1">
       <c r="A164" s="188">
         <v>36</v>
       </c>
@@ -6609,7 +6875,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="23.25">
+    <row r="165" spans="1:7" ht="22.8" hidden="1">
       <c r="A165" s="192">
         <v>37</v>
       </c>
@@ -6632,7 +6898,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="23.25">
+    <row r="166" spans="1:7" ht="22.8" hidden="1">
       <c r="A166" s="192">
         <v>38</v>
       </c>
@@ -6655,7 +6921,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="23.25">
+    <row r="167" spans="1:7" ht="22.8" hidden="1">
       <c r="A167" s="192">
         <v>39</v>
       </c>
@@ -6678,7 +6944,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="23.25">
+    <row r="168" spans="1:7" ht="22.8" hidden="1">
       <c r="A168" s="192">
         <v>40</v>
       </c>
@@ -6701,7 +6967,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="23.25">
+    <row r="169" spans="1:7" ht="22.8" hidden="1">
       <c r="A169" s="192">
         <v>42</v>
       </c>
@@ -6724,7 +6990,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="23.25">
+    <row r="170" spans="1:7" ht="22.8" hidden="1">
       <c r="A170" s="192">
         <v>46</v>
       </c>
@@ -6747,7 +7013,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="23.25">
+    <row r="171" spans="1:7" ht="22.8" hidden="1">
       <c r="A171" s="192">
         <v>47</v>
       </c>
@@ -6770,7 +7036,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="23.25">
+    <row r="172" spans="1:7" ht="22.8" hidden="1">
       <c r="A172" s="188">
         <v>50</v>
       </c>
@@ -6793,7 +7059,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="23.25">
+    <row r="173" spans="1:7" ht="22.8" hidden="1">
       <c r="A173" s="192">
         <v>51</v>
       </c>
@@ -6816,7 +7082,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="23.25">
+    <row r="174" spans="1:7" ht="22.8" hidden="1">
       <c r="A174" s="192">
         <v>52</v>
       </c>
@@ -6839,7 +7105,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="23.25">
+    <row r="175" spans="1:7" ht="22.8" hidden="1">
       <c r="A175" s="192">
         <v>58</v>
       </c>
@@ -6862,7 +7128,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="23.25">
+    <row r="176" spans="1:7" ht="22.8" hidden="1">
       <c r="A176" s="192">
         <v>59</v>
       </c>
@@ -6885,7 +7151,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="23.25">
+    <row r="177" spans="1:7" ht="22.8" hidden="1">
       <c r="A177" s="192">
         <v>60</v>
       </c>
@@ -6908,7 +7174,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="23.25">
+    <row r="178" spans="1:7" ht="22.8" hidden="1">
       <c r="A178" s="192">
         <v>1</v>
       </c>
@@ -6931,7 +7197,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="23.25">
+    <row r="179" spans="1:7" ht="22.8" hidden="1">
       <c r="A179" s="192">
         <v>2</v>
       </c>
@@ -6954,7 +7220,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="23.25">
+    <row r="180" spans="1:7" ht="22.8" hidden="1">
       <c r="A180" s="192">
         <v>3</v>
       </c>
@@ -6977,7 +7243,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="23.25">
+    <row r="181" spans="1:7" ht="22.8" hidden="1">
       <c r="A181" s="188">
         <v>4</v>
       </c>
@@ -6998,7 +7264,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="23.25">
+    <row r="182" spans="1:7" ht="22.8" hidden="1">
       <c r="A182" s="192">
         <v>5</v>
       </c>
@@ -7021,7 +7287,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="23.25">
+    <row r="183" spans="1:7" ht="22.8" hidden="1">
       <c r="A183" s="192">
         <v>6</v>
       </c>
@@ -7044,7 +7310,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="23.25">
+    <row r="184" spans="1:7" ht="22.8" hidden="1">
       <c r="A184" s="192">
         <v>7</v>
       </c>
@@ -7067,7 +7333,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="23.25">
+    <row r="185" spans="1:7" ht="22.8" hidden="1">
       <c r="A185" s="192">
         <v>8</v>
       </c>
@@ -7090,7 +7356,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="23.25">
+    <row r="186" spans="1:7" ht="22.8" hidden="1">
       <c r="A186" s="192">
         <v>9</v>
       </c>
@@ -7113,7 +7379,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="23.25">
+    <row r="187" spans="1:7" ht="22.8" hidden="1">
       <c r="A187" s="192">
         <v>11</v>
       </c>
@@ -7136,7 +7402,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="23.25">
+    <row r="188" spans="1:7" ht="22.8" hidden="1">
       <c r="A188" s="192">
         <v>12</v>
       </c>
@@ -7159,7 +7425,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="23.25">
+    <row r="189" spans="1:7" ht="22.8" hidden="1">
       <c r="A189" s="192">
         <v>13</v>
       </c>
@@ -7182,7 +7448,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="23.25">
+    <row r="190" spans="1:7" ht="22.8" hidden="1">
       <c r="A190" s="188">
         <v>15</v>
       </c>
@@ -7205,7 +7471,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="23.25">
+    <row r="191" spans="1:7" ht="22.8" hidden="1">
       <c r="A191" s="192">
         <v>16</v>
       </c>
@@ -7228,7 +7494,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="23.25">
+    <row r="192" spans="1:7" ht="22.8" hidden="1">
       <c r="A192" s="192">
         <v>17</v>
       </c>
@@ -7251,7 +7517,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="23.25">
+    <row r="193" spans="1:7" ht="22.8" hidden="1">
       <c r="A193" s="192">
         <v>20</v>
       </c>
@@ -7274,7 +7540,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="23.25">
+    <row r="194" spans="1:7" ht="22.8" hidden="1">
       <c r="A194" s="192">
         <v>21</v>
       </c>
@@ -7297,7 +7563,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="23.25">
+    <row r="195" spans="1:7" ht="22.8" hidden="1">
       <c r="A195" s="192">
         <v>22</v>
       </c>
@@ -7320,7 +7586,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="23.25">
+    <row r="196" spans="1:7" ht="22.8" hidden="1">
       <c r="A196" s="192">
         <v>23</v>
       </c>
@@ -7343,7 +7609,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="46.5">
+    <row r="197" spans="1:7" ht="45.6" hidden="1">
       <c r="A197" s="192">
         <v>24</v>
       </c>
@@ -7366,7 +7632,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="23.25">
+    <row r="198" spans="1:7" ht="22.8" hidden="1">
       <c r="A198" s="188">
         <v>25</v>
       </c>
@@ -7389,7 +7655,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="23.25">
+    <row r="199" spans="1:7" ht="22.8" hidden="1">
       <c r="A199" s="192">
         <v>27</v>
       </c>
@@ -7412,7 +7678,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="23.25">
+    <row r="200" spans="1:7" ht="22.8" hidden="1">
       <c r="A200" s="192">
         <v>28</v>
       </c>
@@ -7435,7 +7701,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="23.25">
+    <row r="201" spans="1:7" ht="22.8" hidden="1">
       <c r="A201" s="192">
         <v>29</v>
       </c>
@@ -7458,7 +7724,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="23.25">
+    <row r="202" spans="1:7" ht="22.8" hidden="1">
       <c r="A202" s="192">
         <v>30</v>
       </c>
@@ -7481,7 +7747,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="23.25">
+    <row r="203" spans="1:7" ht="22.8" hidden="1">
       <c r="A203" s="192">
         <v>31</v>
       </c>
@@ -7504,7 +7770,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="23.25">
+    <row r="204" spans="1:7" ht="22.8" hidden="1">
       <c r="A204" s="203">
         <v>32</v>
       </c>
@@ -7525,7 +7791,7 @@
       </c>
       <c r="G204" s="275"/>
     </row>
-    <row r="205" spans="1:7" ht="23.25">
+    <row r="205" spans="1:7" ht="22.8" hidden="1">
       <c r="A205" s="192">
         <v>33</v>
       </c>
@@ -7548,7 +7814,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="23.25">
+    <row r="206" spans="1:7" ht="22.8" hidden="1">
       <c r="A206" s="192">
         <v>34</v>
       </c>
@@ -7571,7 +7837,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="23.25">
+    <row r="207" spans="1:7" ht="22.8" hidden="1">
       <c r="A207" s="188">
         <v>35</v>
       </c>
@@ -7594,7 +7860,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="23.25">
+    <row r="208" spans="1:7" ht="22.8" hidden="1">
       <c r="A208" s="192">
         <v>36</v>
       </c>
@@ -7617,7 +7883,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="23.25">
+    <row r="209" spans="1:7" ht="22.8" hidden="1">
       <c r="A209" s="192">
         <v>37</v>
       </c>
@@ -7640,7 +7906,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="23.25">
+    <row r="210" spans="1:7" ht="22.8" hidden="1">
       <c r="A210" s="192">
         <v>38</v>
       </c>
@@ -7663,7 +7929,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="23.25">
+    <row r="211" spans="1:7" ht="22.8" hidden="1">
       <c r="A211" s="192">
         <v>39</v>
       </c>
@@ -7686,7 +7952,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="23.25">
+    <row r="212" spans="1:7" ht="22.8" hidden="1">
       <c r="A212" s="192">
         <v>40</v>
       </c>
@@ -7709,7 +7975,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="23.25">
+    <row r="213" spans="1:7" ht="22.8" hidden="1">
       <c r="A213" s="192">
         <v>42</v>
       </c>
@@ -7732,7 +7998,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="23.25">
+    <row r="214" spans="1:7" ht="22.8" hidden="1">
       <c r="A214" s="203">
         <v>43</v>
       </c>
@@ -7755,7 +8021,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="23.25">
+    <row r="215" spans="1:7" ht="22.8" hidden="1">
       <c r="A215" s="203">
         <v>44</v>
       </c>
@@ -7778,7 +8044,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="23.25">
+    <row r="216" spans="1:7" ht="22.8" hidden="1">
       <c r="A216" s="188">
         <v>46</v>
       </c>
@@ -7801,7 +8067,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="23.25">
+    <row r="217" spans="1:7" ht="22.8" hidden="1">
       <c r="A217" s="192">
         <v>47</v>
       </c>
@@ -7824,7 +8090,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="23.25">
+    <row r="218" spans="1:7" ht="22.8" hidden="1">
       <c r="A218" s="192">
         <v>50</v>
       </c>
@@ -7847,7 +8113,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="23.25">
+    <row r="219" spans="1:7" ht="22.8" hidden="1">
       <c r="A219" s="192">
         <v>51</v>
       </c>
@@ -7870,7 +8136,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="23.25">
+    <row r="220" spans="1:7" ht="22.8" hidden="1">
       <c r="A220" s="192">
         <v>52</v>
       </c>
@@ -7893,7 +8159,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="23.25">
+    <row r="221" spans="1:7" ht="22.8" hidden="1">
       <c r="A221" s="192">
         <v>58</v>
       </c>
@@ -7916,7 +8182,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="23.25">
+    <row r="222" spans="1:7" ht="22.8" hidden="1">
       <c r="A222" s="192">
         <v>59</v>
       </c>
@@ -7939,7 +8205,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="23.25">
+    <row r="223" spans="1:7" ht="22.8" hidden="1">
       <c r="A223" s="192">
         <v>60</v>
       </c>
@@ -7962,7 +8228,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="23.25">
+    <row r="224" spans="1:7" ht="22.8" hidden="1">
       <c r="A224" s="192">
         <v>1</v>
       </c>
@@ -7985,7 +8251,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="23.25">
+    <row r="225" spans="1:7" ht="22.8" hidden="1">
       <c r="A225" s="217">
         <v>2</v>
       </c>
@@ -8008,7 +8274,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="23.25">
+    <row r="226" spans="1:7" ht="22.8" hidden="1">
       <c r="A226" s="192">
         <v>3</v>
       </c>
@@ -8031,7 +8297,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="23.25">
+    <row r="227" spans="1:7" ht="22.8" hidden="1">
       <c r="A227" s="217">
         <v>4</v>
       </c>
@@ -8052,7 +8318,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="23.25">
+    <row r="228" spans="1:7" ht="22.8" hidden="1">
       <c r="A228" s="217">
         <v>5</v>
       </c>
@@ -8075,7 +8341,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="23.25">
+    <row r="229" spans="1:7" ht="22.8" hidden="1">
       <c r="A229" s="208">
         <v>6</v>
       </c>
@@ -8098,7 +8364,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="23.25">
+    <row r="230" spans="1:7" ht="22.8" hidden="1">
       <c r="A230" s="192">
         <v>7</v>
       </c>
@@ -8121,7 +8387,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="23.25">
+    <row r="231" spans="1:7" ht="22.8" hidden="1">
       <c r="A231" s="192">
         <v>8</v>
       </c>
@@ -8144,7 +8410,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="23.25">
+    <row r="232" spans="1:7" ht="22.8" hidden="1">
       <c r="A232" s="192">
         <v>9</v>
       </c>
@@ -8167,7 +8433,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="23.25">
+    <row r="233" spans="1:7" ht="22.8" hidden="1">
       <c r="A233" s="192">
         <v>11</v>
       </c>
@@ -8190,7 +8456,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="23.25">
+    <row r="234" spans="1:7" ht="22.8" hidden="1">
       <c r="A234" s="192">
         <v>12</v>
       </c>
@@ -8213,7 +8479,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="23.25">
+    <row r="235" spans="1:7" ht="22.8" hidden="1">
       <c r="A235" s="192">
         <v>13</v>
       </c>
@@ -8236,7 +8502,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="23.25">
+    <row r="236" spans="1:7" ht="22.8" hidden="1">
       <c r="A236" s="192">
         <v>15</v>
       </c>
@@ -8259,7 +8525,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="23.25">
+    <row r="237" spans="1:7" ht="22.8" hidden="1">
       <c r="A237" s="192">
         <v>16</v>
       </c>
@@ -8282,7 +8548,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="23.25">
+    <row r="238" spans="1:7" ht="22.8" hidden="1">
       <c r="A238" s="188">
         <v>17</v>
       </c>
@@ -8305,7 +8571,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="23.25">
+    <row r="239" spans="1:7" ht="22.8" hidden="1">
       <c r="A239" s="192">
         <v>20</v>
       </c>
@@ -8328,7 +8594,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="23.25">
+    <row r="240" spans="1:7" ht="22.8" hidden="1">
       <c r="A240" s="192">
         <v>21</v>
       </c>
@@ -8351,7 +8617,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="23.25">
+    <row r="241" spans="1:7" ht="22.8" hidden="1">
       <c r="A241" s="192">
         <v>22</v>
       </c>
@@ -8374,7 +8640,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="23.25">
+    <row r="242" spans="1:7" ht="22.8" hidden="1">
       <c r="A242" s="192">
         <v>23</v>
       </c>
@@ -8397,7 +8663,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="46.5">
+    <row r="243" spans="1:7" ht="45.6" hidden="1">
       <c r="A243" s="192">
         <v>24</v>
       </c>
@@ -8420,7 +8686,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="23.25">
+    <row r="244" spans="1:7" ht="22.8" hidden="1">
       <c r="A244" s="192">
         <v>25</v>
       </c>
@@ -8443,7 +8709,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="23.25">
+    <row r="245" spans="1:7" ht="22.8" hidden="1">
       <c r="A245" s="192">
         <v>27</v>
       </c>
@@ -8466,7 +8732,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="23.25">
+    <row r="246" spans="1:7" ht="22.8" hidden="1">
       <c r="A246" s="188">
         <v>28</v>
       </c>
@@ -8489,7 +8755,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="23.25">
+    <row r="247" spans="1:7" ht="22.8" hidden="1">
       <c r="A247" s="192">
         <v>29</v>
       </c>
@@ -8512,7 +8778,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="23.25">
+    <row r="248" spans="1:7" ht="22.8" hidden="1">
       <c r="A248" s="192">
         <v>30</v>
       </c>
@@ -8535,7 +8801,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="23.25">
+    <row r="249" spans="1:7" ht="22.8" hidden="1">
       <c r="A249" s="192">
         <v>31</v>
       </c>
@@ -8558,7 +8824,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="23.25">
+    <row r="250" spans="1:7" ht="22.8" hidden="1">
       <c r="A250" s="203">
         <v>32</v>
       </c>
@@ -8581,7 +8847,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="23.25">
+    <row r="251" spans="1:7" ht="22.8" hidden="1">
       <c r="A251" s="192">
         <v>33</v>
       </c>
@@ -8604,7 +8870,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="23.25">
+    <row r="252" spans="1:7" ht="22.8" hidden="1">
       <c r="A252" s="192">
         <v>34</v>
       </c>
@@ -8627,7 +8893,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="23.25">
+    <row r="253" spans="1:7" ht="22.8" hidden="1">
       <c r="A253" s="192">
         <v>35</v>
       </c>
@@ -8650,7 +8916,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="23.25">
+    <row r="254" spans="1:7" ht="22.8" hidden="1">
       <c r="A254" s="192">
         <v>36</v>
       </c>
@@ -8673,7 +8939,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="23.25">
+    <row r="255" spans="1:7" ht="22.8" hidden="1">
       <c r="A255" s="188">
         <v>37</v>
       </c>
@@ -8696,7 +8962,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="23.25">
+    <row r="256" spans="1:7" ht="22.8" hidden="1">
       <c r="A256" s="192">
         <v>38</v>
       </c>
@@ -8719,7 +8985,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="23.25">
+    <row r="257" spans="1:7" ht="22.8" hidden="1">
       <c r="A257" s="192">
         <v>39</v>
       </c>
@@ -8742,7 +9008,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="23.25">
+    <row r="258" spans="1:7" ht="22.8" hidden="1">
       <c r="A258" s="192">
         <v>40</v>
       </c>
@@ -8765,7 +9031,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="23.25">
+    <row r="259" spans="1:7" ht="22.8" hidden="1">
       <c r="A259" s="192">
         <v>42</v>
       </c>
@@ -8788,7 +9054,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="23.25">
+    <row r="260" spans="1:7" ht="22.8" hidden="1">
       <c r="A260" s="203">
         <v>43</v>
       </c>
@@ -8811,7 +9077,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="23.25">
+    <row r="261" spans="1:7" ht="22.8" hidden="1">
       <c r="A261" s="203">
         <v>44</v>
       </c>
@@ -8834,7 +9100,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="23.25">
+    <row r="262" spans="1:7" ht="22.8" hidden="1">
       <c r="A262" s="192">
         <v>46</v>
       </c>
@@ -8857,7 +9123,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="23.25">
+    <row r="263" spans="1:7" ht="22.8" hidden="1">
       <c r="A263" s="192">
         <v>47</v>
       </c>
@@ -8880,7 +9146,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="23.25">
+    <row r="264" spans="1:7" ht="22.8" hidden="1">
       <c r="A264" s="188">
         <v>50</v>
       </c>
@@ -8903,7 +9169,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="23.25">
+    <row r="265" spans="1:7" ht="22.8" hidden="1">
       <c r="A265" s="192">
         <v>51</v>
       </c>
@@ -8926,7 +9192,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="23.25">
+    <row r="266" spans="1:7" ht="22.8" hidden="1">
       <c r="A266" s="192">
         <v>52</v>
       </c>
@@ -8949,7 +9215,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="23.25">
+    <row r="267" spans="1:7" ht="22.8" hidden="1">
       <c r="A267" s="192">
         <v>58</v>
       </c>
@@ -8972,7 +9238,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="23.25">
+    <row r="268" spans="1:7" ht="22.8" hidden="1">
       <c r="A268" s="192">
         <v>59</v>
       </c>
@@ -8995,7 +9261,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="23.25">
+    <row r="269" spans="1:7" ht="22.8" hidden="1">
       <c r="A269" s="192">
         <v>60</v>
       </c>
@@ -9018,7 +9284,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="23.25">
+    <row r="270" spans="1:7" ht="22.8" hidden="1">
       <c r="A270" s="192">
         <v>1</v>
       </c>
@@ -9041,7 +9307,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="23.25">
+    <row r="271" spans="1:7" ht="22.8" hidden="1">
       <c r="A271" s="192">
         <v>2</v>
       </c>
@@ -9064,7 +9330,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="23.25">
+    <row r="272" spans="1:7" ht="22.8" hidden="1">
       <c r="A272" s="188">
         <v>3</v>
       </c>
@@ -9087,7 +9353,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="23.25">
+    <row r="273" spans="1:7" ht="22.8" hidden="1">
       <c r="A273" s="192">
         <v>4</v>
       </c>
@@ -9108,7 +9374,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="23.25">
+    <row r="274" spans="1:7" ht="22.8" hidden="1">
       <c r="A274" s="192">
         <v>5</v>
       </c>
@@ -9131,7 +9397,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="23.25">
+    <row r="275" spans="1:7" ht="22.8" hidden="1">
       <c r="A275" s="192">
         <v>6</v>
       </c>
@@ -9155,7 +9421,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="23.25">
+    <row r="276" spans="1:7" ht="22.8" hidden="1">
       <c r="A276" s="192">
         <v>7</v>
       </c>
@@ -9178,7 +9444,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="23.25">
+    <row r="277" spans="1:7" ht="22.8" hidden="1">
       <c r="A277" s="192">
         <v>8</v>
       </c>
@@ -9202,7 +9468,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="23.25">
+    <row r="278" spans="1:7" ht="22.8" hidden="1">
       <c r="A278" s="192">
         <v>9</v>
       </c>
@@ -9225,7 +9491,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="23.25">
+    <row r="279" spans="1:7" ht="22.8" hidden="1">
       <c r="A279" s="192">
         <v>11</v>
       </c>
@@ -9248,7 +9514,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="23.25">
+    <row r="280" spans="1:7" ht="22.8" hidden="1">
       <c r="A280" s="192">
         <v>12</v>
       </c>
@@ -9271,7 +9537,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="23.25">
+    <row r="281" spans="1:7" ht="22.8" hidden="1">
       <c r="A281" s="188">
         <v>13</v>
       </c>
@@ -9294,7 +9560,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="23.25">
+    <row r="282" spans="1:7" ht="22.8" hidden="1">
       <c r="A282" s="192">
         <v>15</v>
       </c>
@@ -9317,7 +9583,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="23.25">
+    <row r="283" spans="1:7" ht="22.8" hidden="1">
       <c r="A283" s="192">
         <v>16</v>
       </c>
@@ -9340,7 +9606,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="23.25">
+    <row r="284" spans="1:7" ht="22.8" hidden="1">
       <c r="A284" s="192">
         <v>17</v>
       </c>
@@ -9363,7 +9629,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="23.25">
+    <row r="285" spans="1:7" ht="22.8" hidden="1">
       <c r="A285" s="192">
         <v>20</v>
       </c>
@@ -9386,7 +9652,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="23.25">
+    <row r="286" spans="1:7" ht="22.8" hidden="1">
       <c r="A286" s="192">
         <v>21</v>
       </c>
@@ -9409,7 +9675,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="23.25">
+    <row r="287" spans="1:7" ht="22.8" hidden="1">
       <c r="A287" s="192">
         <v>22</v>
       </c>
@@ -9432,7 +9698,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="23.25">
+    <row r="288" spans="1:7" ht="22.8" hidden="1">
       <c r="A288" s="192">
         <v>23</v>
       </c>
@@ -9455,7 +9721,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="46.5">
+    <row r="289" spans="1:7" ht="45.6" hidden="1">
       <c r="A289" s="192">
         <v>24</v>
       </c>
@@ -9478,7 +9744,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="23.25">
+    <row r="290" spans="1:7" ht="22.8" hidden="1">
       <c r="A290" s="188">
         <v>25</v>
       </c>
@@ -9501,7 +9767,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="23.25">
+    <row r="291" spans="1:7" ht="22.8" hidden="1">
       <c r="A291" s="192">
         <v>27</v>
       </c>
@@ -9524,7 +9790,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="23.25">
+    <row r="292" spans="1:7" ht="22.8" hidden="1">
       <c r="A292" s="192">
         <v>28</v>
       </c>
@@ -9547,7 +9813,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="23.25">
+    <row r="293" spans="1:7" ht="22.8" hidden="1">
       <c r="A293" s="192">
         <v>29</v>
       </c>
@@ -9570,7 +9836,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="23.25">
+    <row r="294" spans="1:7" ht="22.8" hidden="1">
       <c r="A294" s="192">
         <v>30</v>
       </c>
@@ -9593,7 +9859,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="23.25">
+    <row r="295" spans="1:7" ht="22.8" hidden="1">
       <c r="A295" s="192">
         <v>31</v>
       </c>
@@ -9616,7 +9882,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="23.25">
+    <row r="296" spans="1:7" ht="22.8" hidden="1">
       <c r="A296" s="203">
         <v>32</v>
       </c>
@@ -9639,7 +9905,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="23.25">
+    <row r="297" spans="1:7" ht="22.8" hidden="1">
       <c r="A297" s="192">
         <v>33</v>
       </c>
@@ -9662,7 +9928,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="23.25">
+    <row r="298" spans="1:7" ht="22.8" hidden="1">
       <c r="A298" s="192">
         <v>34</v>
       </c>
@@ -9685,7 +9951,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="23.25">
+    <row r="299" spans="1:7" ht="22.8" hidden="1">
       <c r="A299" s="217">
         <v>35</v>
       </c>
@@ -9708,7 +9974,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="23.25">
+    <row r="300" spans="1:7" ht="22.8" hidden="1">
       <c r="A300" s="192">
         <v>36</v>
       </c>
@@ -9731,7 +9997,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="23.25">
+    <row r="301" spans="1:7" ht="22.8" hidden="1">
       <c r="A301" s="217">
         <v>37</v>
       </c>
@@ -9754,7 +10020,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="23.25">
+    <row r="302" spans="1:7" ht="22.8" hidden="1">
       <c r="A302" s="217">
         <v>38</v>
       </c>
@@ -9777,7 +10043,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="23.25">
+    <row r="303" spans="1:7" ht="22.8" hidden="1">
       <c r="A303" s="208">
         <v>39</v>
       </c>
@@ -9800,7 +10066,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="23.25">
+    <row r="304" spans="1:7" ht="22.8" hidden="1">
       <c r="A304" s="192">
         <v>40</v>
       </c>
@@ -9823,7 +10089,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="23.25">
+    <row r="305" spans="1:7" ht="22.8" hidden="1">
       <c r="A305" s="192">
         <v>42</v>
       </c>
@@ -9846,7 +10112,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="23.25">
+    <row r="306" spans="1:7" ht="22.8" hidden="1">
       <c r="A306" s="203">
         <v>43</v>
       </c>
@@ -9869,7 +10135,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="23.25">
+    <row r="307" spans="1:7" ht="22.8" hidden="1">
       <c r="A307" s="203">
         <v>44</v>
       </c>
@@ -9892,7 +10158,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="23.25">
+    <row r="308" spans="1:7" ht="22.8" hidden="1">
       <c r="A308" s="192">
         <v>46</v>
       </c>
@@ -9915,7 +10181,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="23.25">
+    <row r="309" spans="1:7" ht="22.8" hidden="1">
       <c r="A309" s="192">
         <v>47</v>
       </c>
@@ -9938,7 +10204,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="23.25">
+    <row r="310" spans="1:7" ht="22.8" hidden="1">
       <c r="A310" s="203">
         <v>48</v>
       </c>
@@ -9959,7 +10225,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="23.25">
+    <row r="311" spans="1:7" ht="22.8" hidden="1">
       <c r="A311" s="192">
         <v>50</v>
       </c>
@@ -9982,7 +10248,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="23.25">
+    <row r="312" spans="1:7" ht="22.8" hidden="1">
       <c r="A312" s="188">
         <v>51</v>
       </c>
@@ -10005,7 +10271,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="23.25">
+    <row r="313" spans="1:7" ht="22.8" hidden="1">
       <c r="A313" s="192">
         <v>52</v>
       </c>
@@ -10028,7 +10294,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="23.25">
+    <row r="314" spans="1:7" ht="22.8" hidden="1">
       <c r="A314" s="192">
         <v>58</v>
       </c>
@@ -10051,7 +10317,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="23.25">
+    <row r="315" spans="1:7" ht="22.8" hidden="1">
       <c r="A315" s="192">
         <v>59</v>
       </c>
@@ -10074,7 +10340,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="23.25">
+    <row r="316" spans="1:7" ht="22.8" hidden="1">
       <c r="A316" s="192">
         <v>60</v>
       </c>
@@ -10097,7 +10363,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="23.25">
+    <row r="317" spans="1:7" ht="22.8" hidden="1">
       <c r="A317" s="203">
         <v>62</v>
       </c>
@@ -10114,7 +10380,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="23.25">
+    <row r="318" spans="1:7" ht="22.8" hidden="1">
       <c r="A318" s="203">
         <v>64</v>
       </c>
@@ -10131,7 +10397,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="23.25">
+    <row r="319" spans="1:7" ht="22.8" hidden="1">
       <c r="A319" s="192">
         <v>1</v>
       </c>
@@ -10154,7 +10420,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="23.25">
+    <row r="320" spans="1:7" ht="22.8" hidden="1">
       <c r="A320" s="188">
         <v>2</v>
       </c>
@@ -10177,7 +10443,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="23.25">
+    <row r="321" spans="1:7" ht="22.8" hidden="1">
       <c r="A321" s="192">
         <v>3</v>
       </c>
@@ -10200,7 +10466,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="23.25">
+    <row r="322" spans="1:7" ht="22.8" hidden="1">
       <c r="A322" s="192">
         <v>4</v>
       </c>
@@ -10221,7 +10487,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="23.25">
+    <row r="323" spans="1:7" ht="22.8" hidden="1">
       <c r="A323" s="192">
         <v>5</v>
       </c>
@@ -10244,7 +10510,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="23.25">
+    <row r="324" spans="1:7" ht="22.8" hidden="1">
       <c r="A324" s="192">
         <v>6</v>
       </c>
@@ -10268,7 +10534,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="23.25">
+    <row r="325" spans="1:7" ht="22.8" hidden="1">
       <c r="A325" s="192">
         <v>7</v>
       </c>
@@ -10291,7 +10557,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="23.25">
+    <row r="326" spans="1:7" ht="22.8" hidden="1">
       <c r="A326" s="192">
         <v>8</v>
       </c>
@@ -10315,7 +10581,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="23.25">
+    <row r="327" spans="1:7" ht="22.8" hidden="1">
       <c r="A327" s="192">
         <v>9</v>
       </c>
@@ -10338,7 +10604,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="23.25">
+    <row r="328" spans="1:7" ht="22.8" hidden="1">
       <c r="A328" s="192">
         <v>11</v>
       </c>
@@ -10361,7 +10627,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="23.25">
+    <row r="329" spans="1:7" ht="22.8" hidden="1">
       <c r="A329" s="188">
         <v>12</v>
       </c>
@@ -10384,7 +10650,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="23.25">
+    <row r="330" spans="1:7" ht="22.8" hidden="1">
       <c r="A330" s="192">
         <v>13</v>
       </c>
@@ -10407,7 +10673,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="23.25">
+    <row r="331" spans="1:7" ht="22.8" hidden="1">
       <c r="A331" s="192">
         <v>15</v>
       </c>
@@ -10430,7 +10696,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="23.25">
+    <row r="332" spans="1:7" ht="22.8" hidden="1">
       <c r="A332" s="192">
         <v>16</v>
       </c>
@@ -10453,7 +10719,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="23.25">
+    <row r="333" spans="1:7" ht="22.8" hidden="1">
       <c r="A333" s="192">
         <v>17</v>
       </c>
@@ -10476,7 +10742,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="23.25">
+    <row r="334" spans="1:7" ht="22.8" hidden="1">
       <c r="A334" s="192">
         <v>20</v>
       </c>
@@ -10499,7 +10765,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="23.25">
+    <row r="335" spans="1:7" ht="22.8" hidden="1">
       <c r="A335" s="192">
         <v>21</v>
       </c>
@@ -10522,7 +10788,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="23.25">
+    <row r="336" spans="1:7" ht="22.8" hidden="1">
       <c r="A336" s="192">
         <v>22</v>
       </c>
@@ -10545,7 +10811,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="23.25">
+    <row r="337" spans="1:7" ht="22.8" hidden="1">
       <c r="A337" s="192">
         <v>23</v>
       </c>
@@ -10568,7 +10834,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="46.5">
+    <row r="338" spans="1:7" ht="45.6" hidden="1">
       <c r="A338" s="188">
         <v>24</v>
       </c>
@@ -10591,7 +10857,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="23.25">
+    <row r="339" spans="1:7" ht="22.8" hidden="1">
       <c r="A339" s="192">
         <v>25</v>
       </c>
@@ -10614,7 +10880,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="23.25">
+    <row r="340" spans="1:7" ht="22.8" hidden="1">
       <c r="A340" s="192">
         <v>27</v>
       </c>
@@ -10637,7 +10903,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="23.25">
+    <row r="341" spans="1:7" ht="22.8" hidden="1">
       <c r="A341" s="192">
         <v>28</v>
       </c>
@@ -10660,7 +10926,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="23.25">
+    <row r="342" spans="1:7" ht="22.8" hidden="1">
       <c r="A342" s="192">
         <v>29</v>
       </c>
@@ -10683,7 +10949,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="23.25">
+    <row r="343" spans="1:7" ht="22.8" hidden="1">
       <c r="A343" s="192">
         <v>30</v>
       </c>
@@ -10706,7 +10972,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="23.25">
+    <row r="344" spans="1:7" ht="22.8" hidden="1">
       <c r="A344" s="192">
         <v>31</v>
       </c>
@@ -10729,7 +10995,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="23.25">
+    <row r="345" spans="1:7" ht="22.8" hidden="1">
       <c r="A345" s="203">
         <v>32</v>
       </c>
@@ -10752,7 +11018,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="23.25">
+    <row r="346" spans="1:7" ht="22.8" hidden="1">
       <c r="A346" s="188">
         <v>33</v>
       </c>
@@ -10775,7 +11041,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="23.25">
+    <row r="347" spans="1:7" ht="22.8" hidden="1">
       <c r="A347" s="192">
         <v>34</v>
       </c>
@@ -10798,7 +11064,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="23.25">
+    <row r="348" spans="1:7" ht="22.8" hidden="1">
       <c r="A348" s="192">
         <v>35</v>
       </c>
@@ -10821,7 +11087,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="23.25">
+    <row r="349" spans="1:7" ht="22.8" hidden="1">
       <c r="A349" s="192">
         <v>36</v>
       </c>
@@ -10844,7 +11110,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="23.25">
+    <row r="350" spans="1:7" ht="22.8" hidden="1">
       <c r="A350" s="192">
         <v>37</v>
       </c>
@@ -10867,7 +11133,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="23.25">
+    <row r="351" spans="1:7" ht="22.8" hidden="1">
       <c r="A351" s="192">
         <v>38</v>
       </c>
@@ -10890,7 +11156,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="23.25">
+    <row r="352" spans="1:7" ht="22.8" hidden="1">
       <c r="A352" s="192">
         <v>39</v>
       </c>
@@ -10913,7 +11179,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="23.25">
+    <row r="353" spans="1:7" ht="22.8" hidden="1">
       <c r="A353" s="192">
         <v>40</v>
       </c>
@@ -10936,7 +11202,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="23.25">
+    <row r="354" spans="1:7" ht="22.8" hidden="1">
       <c r="A354" s="192">
         <v>42</v>
       </c>
@@ -10959,7 +11225,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="23.25">
+    <row r="355" spans="1:7" ht="22.8" hidden="1">
       <c r="A355" s="225">
         <v>43</v>
       </c>
@@ -10982,7 +11248,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="23.25">
+    <row r="356" spans="1:7" ht="22.8" hidden="1">
       <c r="A356" s="203">
         <v>44</v>
       </c>
@@ -11005,7 +11271,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="23.25">
+    <row r="357" spans="1:7" ht="22.8" hidden="1">
       <c r="A357" s="192">
         <v>46</v>
       </c>
@@ -11028,7 +11294,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="23.25">
+    <row r="358" spans="1:7" ht="22.8" hidden="1">
       <c r="A358" s="192">
         <v>47</v>
       </c>
@@ -11051,7 +11317,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="23.25">
+    <row r="359" spans="1:7" ht="22.8" hidden="1">
       <c r="A359" s="203">
         <v>48</v>
       </c>
@@ -11072,7 +11338,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="23.25">
+    <row r="360" spans="1:7" ht="22.8" hidden="1">
       <c r="A360" s="192">
         <v>50</v>
       </c>
@@ -11095,7 +11361,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="23.25">
+    <row r="361" spans="1:7" ht="22.8" hidden="1">
       <c r="A361" s="192">
         <v>51</v>
       </c>
@@ -11118,7 +11384,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="23.25">
+    <row r="362" spans="1:7" ht="22.8" hidden="1">
       <c r="A362" s="192">
         <v>52</v>
       </c>
@@ -11141,7 +11407,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="23.25">
+    <row r="363" spans="1:7" ht="22.8" hidden="1">
       <c r="A363" s="192">
         <v>58</v>
       </c>
@@ -11164,7 +11430,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="23.25">
+    <row r="364" spans="1:7" ht="22.8" hidden="1">
       <c r="A364" s="188">
         <v>59</v>
       </c>
@@ -11187,7 +11453,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="23.25">
+    <row r="365" spans="1:7" ht="22.8" hidden="1">
       <c r="A365" s="192">
         <v>60</v>
       </c>
@@ -11210,7 +11476,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="23.25">
+    <row r="366" spans="1:7" ht="22.8" hidden="1">
       <c r="A366" s="192">
         <v>1</v>
       </c>
@@ -11233,7 +11499,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="23.25">
+    <row r="367" spans="1:7" ht="22.8" hidden="1">
       <c r="A367" s="192">
         <v>2</v>
       </c>
@@ -11256,7 +11522,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="23.25">
+    <row r="368" spans="1:7" ht="22.8" hidden="1">
       <c r="A368" s="192">
         <v>3</v>
       </c>
@@ -11279,7 +11545,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="23.25">
+    <row r="369" spans="1:7" ht="22.8" hidden="1">
       <c r="A369" s="192">
         <v>4</v>
       </c>
@@ -11300,7 +11566,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="23.25">
+    <row r="370" spans="1:7" ht="22.8" hidden="1">
       <c r="A370" s="192">
         <v>5</v>
       </c>
@@ -11323,7 +11589,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="23.25">
+    <row r="371" spans="1:7" ht="22.8" hidden="1">
       <c r="A371" s="192">
         <v>6</v>
       </c>
@@ -11347,7 +11613,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="23.25">
+    <row r="372" spans="1:7" ht="22.8" hidden="1">
       <c r="A372" s="192">
         <v>7</v>
       </c>
@@ -11370,7 +11636,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="23.25">
+    <row r="373" spans="1:7" ht="22.8" hidden="1">
       <c r="A373" s="217">
         <v>8</v>
       </c>
@@ -11394,7 +11660,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="23.25">
+    <row r="374" spans="1:7" ht="22.8" hidden="1">
       <c r="A374" s="192">
         <v>9</v>
       </c>
@@ -11417,7 +11683,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="23.25">
+    <row r="375" spans="1:7" ht="22.8" hidden="1">
       <c r="A375" s="217">
         <v>11</v>
       </c>
@@ -11440,7 +11706,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="23.25">
+    <row r="376" spans="1:7" ht="22.8" hidden="1">
       <c r="A376" s="217">
         <v>12</v>
       </c>
@@ -11463,7 +11729,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="23.25">
+    <row r="377" spans="1:7" ht="22.8" hidden="1">
       <c r="A377" s="208">
         <v>13</v>
       </c>
@@ -11486,7 +11752,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="23.25">
+    <row r="378" spans="1:7" ht="22.8" hidden="1">
       <c r="A378" s="192">
         <v>15</v>
       </c>
@@ -11509,7 +11775,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="23.25">
+    <row r="379" spans="1:7" ht="22.8" hidden="1">
       <c r="A379" s="192">
         <v>16</v>
       </c>
@@ -11532,7 +11798,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="23.25">
+    <row r="380" spans="1:7" ht="22.8" hidden="1">
       <c r="A380" s="192">
         <v>17</v>
       </c>
@@ -11555,7 +11821,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="23.25">
+    <row r="381" spans="1:7" ht="22.8" hidden="1">
       <c r="A381" s="192">
         <v>20</v>
       </c>
@@ -11578,7 +11844,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="23.25">
+    <row r="382" spans="1:7" ht="22.8" hidden="1">
       <c r="A382" s="192">
         <v>21</v>
       </c>
@@ -11601,7 +11867,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="23.25">
+    <row r="383" spans="1:7" ht="22.8" hidden="1">
       <c r="A383" s="192">
         <v>22</v>
       </c>
@@ -11624,7 +11890,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="23.25">
+    <row r="384" spans="1:7" ht="22.8" hidden="1">
       <c r="A384" s="192">
         <v>23</v>
       </c>
@@ -11647,7 +11913,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="46.5">
+    <row r="385" spans="1:7" ht="45.6" hidden="1">
       <c r="A385" s="192">
         <v>24</v>
       </c>
@@ -11670,7 +11936,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="23.25">
+    <row r="386" spans="1:7" ht="22.8" hidden="1">
       <c r="A386" s="188">
         <v>25</v>
       </c>
@@ -11693,7 +11959,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="23.25">
+    <row r="387" spans="1:7" ht="22.8" hidden="1">
       <c r="A387" s="192">
         <v>27</v>
       </c>
@@ -11716,7 +11982,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="23.25">
+    <row r="388" spans="1:7" ht="22.8" hidden="1">
       <c r="A388" s="192">
         <v>28</v>
       </c>
@@ -11739,7 +12005,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="23.25">
+    <row r="389" spans="1:7" ht="22.8" hidden="1">
       <c r="A389" s="192">
         <v>29</v>
       </c>
@@ -11762,7 +12028,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="23.25">
+    <row r="390" spans="1:7" ht="22.8" hidden="1">
       <c r="A390" s="192">
         <v>30</v>
       </c>
@@ -11785,7 +12051,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="23.25">
+    <row r="391" spans="1:7" ht="22.8" hidden="1">
       <c r="A391" s="192">
         <v>31</v>
       </c>
@@ -11808,7 +12074,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="23.25">
+    <row r="392" spans="1:7" ht="22.8" hidden="1">
       <c r="A392" s="203">
         <v>32</v>
       </c>
@@ -11831,7 +12097,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="23.25">
+    <row r="393" spans="1:7" ht="22.8" hidden="1">
       <c r="A393" s="192">
         <v>33</v>
       </c>
@@ -11854,7 +12120,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="23.25">
+    <row r="394" spans="1:7" ht="22.8" hidden="1">
       <c r="A394" s="188">
         <v>34</v>
       </c>
@@ -11877,7 +12143,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="23.25">
+    <row r="395" spans="1:7" ht="22.8" hidden="1">
       <c r="A395" s="192">
         <v>35</v>
       </c>
@@ -11900,7 +12166,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="23.25">
+    <row r="396" spans="1:7" ht="22.8" hidden="1">
       <c r="A396" s="192">
         <v>36</v>
       </c>
@@ -11923,7 +12189,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="23.25">
+    <row r="397" spans="1:7" ht="22.8" hidden="1">
       <c r="A397" s="192">
         <v>37</v>
       </c>
@@ -11946,7 +12212,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="23.25">
+    <row r="398" spans="1:7" ht="22.8" hidden="1">
       <c r="A398" s="192">
         <v>38</v>
       </c>
@@ -11969,7 +12235,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="23.25">
+    <row r="399" spans="1:7" ht="22.8" hidden="1">
       <c r="A399" s="192">
         <v>39</v>
       </c>
@@ -11992,7 +12258,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="23.25">
+    <row r="400" spans="1:7" ht="22.8" hidden="1">
       <c r="A400" s="192">
         <v>40</v>
       </c>
@@ -12015,7 +12281,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="23.25">
+    <row r="401" spans="1:7" ht="22.8" hidden="1">
       <c r="A401" s="192">
         <v>42</v>
       </c>
@@ -12038,7 +12304,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="23.25">
+    <row r="402" spans="1:7" ht="22.8" hidden="1">
       <c r="A402" s="203">
         <v>43</v>
       </c>
@@ -12061,7 +12327,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="23.25">
+    <row r="403" spans="1:7" ht="22.8" hidden="1">
       <c r="A403" s="225">
         <v>44</v>
       </c>
@@ -12084,7 +12350,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="23.25">
+    <row r="404" spans="1:7" ht="22.8" hidden="1">
       <c r="A404" s="192">
         <v>46</v>
       </c>
@@ -12107,7 +12373,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="23.25">
+    <row r="405" spans="1:7" ht="22.8" hidden="1">
       <c r="A405" s="203">
         <v>48</v>
       </c>
@@ -12128,7 +12394,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="23.25">
+    <row r="406" spans="1:7" ht="22.8" hidden="1">
       <c r="A406" s="192">
         <v>50</v>
       </c>
@@ -12151,7 +12417,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="23.25">
+    <row r="407" spans="1:7" ht="22.8" hidden="1">
       <c r="A407" s="192">
         <v>51</v>
       </c>
@@ -12174,7 +12440,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="23.25">
+    <row r="408" spans="1:7" ht="22.8" hidden="1">
       <c r="A408" s="192">
         <v>52</v>
       </c>
@@ -12197,7 +12463,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="23.25">
+    <row r="409" spans="1:7" ht="22.8" hidden="1">
       <c r="A409" s="192">
         <v>58</v>
       </c>
@@ -12220,7 +12486,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="23.25">
+    <row r="410" spans="1:7" ht="22.8" hidden="1">
       <c r="A410" s="192">
         <v>59</v>
       </c>
@@ -12243,7 +12509,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="23.25">
+    <row r="411" spans="1:7" ht="22.8" hidden="1">
       <c r="A411" s="192">
         <v>60</v>
       </c>
@@ -12266,7 +12532,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="23.25">
+    <row r="412" spans="1:7" ht="22.8" hidden="1">
       <c r="A412" s="225">
         <v>64</v>
       </c>
@@ -12283,7 +12549,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="23.25">
+    <row r="413" spans="1:7" ht="22.8" hidden="1">
       <c r="A413" s="192">
         <v>1</v>
       </c>
@@ -12306,7 +12572,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="23.25">
+    <row r="414" spans="1:7" ht="22.8" hidden="1">
       <c r="A414" s="192">
         <v>2</v>
       </c>
@@ -12329,7 +12595,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="23.25">
+    <row r="415" spans="1:7" ht="22.8" hidden="1">
       <c r="A415" s="192">
         <v>3</v>
       </c>
@@ -12352,7 +12618,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="23.25">
+    <row r="416" spans="1:7" ht="22.8" hidden="1">
       <c r="A416" s="192">
         <v>5</v>
       </c>
@@ -12375,7 +12641,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="23.25">
+    <row r="417" spans="1:7" ht="22.8" hidden="1">
       <c r="A417" s="192">
         <v>6</v>
       </c>
@@ -12399,7 +12665,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="23.25">
+    <row r="418" spans="1:7" ht="22.8" hidden="1">
       <c r="A418" s="192">
         <v>7</v>
       </c>
@@ -12422,7 +12688,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="23.25">
+    <row r="419" spans="1:7" ht="22.8" hidden="1">
       <c r="A419" s="192">
         <v>8</v>
       </c>
@@ -12446,7 +12712,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="23.25">
+    <row r="420" spans="1:7" ht="22.8" hidden="1">
       <c r="A420" s="188">
         <v>9</v>
       </c>
@@ -12469,7 +12735,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="23.25">
+    <row r="421" spans="1:7" ht="22.8" hidden="1">
       <c r="A421" s="192">
         <v>11</v>
       </c>
@@ -12492,7 +12758,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="23.25">
+    <row r="422" spans="1:7" ht="22.8" hidden="1">
       <c r="A422" s="192">
         <v>12</v>
       </c>
@@ -12515,7 +12781,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="23.25">
+    <row r="423" spans="1:7" ht="22.8" hidden="1">
       <c r="A423" s="192">
         <v>13</v>
       </c>
@@ -12538,7 +12804,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="23.25">
+    <row r="424" spans="1:7" ht="22.8" hidden="1">
       <c r="A424" s="192">
         <v>15</v>
       </c>
@@ -12561,7 +12827,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="23.25">
+    <row r="425" spans="1:7" ht="22.8" hidden="1">
       <c r="A425" s="192">
         <v>16</v>
       </c>
@@ -12584,7 +12850,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="23.25">
+    <row r="426" spans="1:7" ht="22.8" hidden="1">
       <c r="A426" s="192">
         <v>17</v>
       </c>
@@ -12607,7 +12873,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="23.25">
+    <row r="427" spans="1:7" ht="22.8" hidden="1">
       <c r="A427" s="192">
         <v>20</v>
       </c>
@@ -12630,7 +12896,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="23.25">
+    <row r="428" spans="1:7" ht="22.8" hidden="1">
       <c r="A428" s="192">
         <v>21</v>
       </c>
@@ -12653,7 +12919,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="23.25">
+    <row r="429" spans="1:7" ht="22.8" hidden="1">
       <c r="A429" s="188">
         <v>22</v>
       </c>
@@ -12676,7 +12942,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="23.25">
+    <row r="430" spans="1:7" ht="22.8" hidden="1">
       <c r="A430" s="192">
         <v>23</v>
       </c>
@@ -12699,7 +12965,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="46.5">
+    <row r="431" spans="1:7" ht="45.6" hidden="1">
       <c r="A431" s="192">
         <v>24</v>
       </c>
@@ -12722,7 +12988,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="23.25">
+    <row r="432" spans="1:7" ht="22.8" hidden="1">
       <c r="A432" s="192">
         <v>25</v>
       </c>
@@ -12745,7 +13011,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="23.25">
+    <row r="433" spans="1:7" ht="22.8" hidden="1">
       <c r="A433" s="192">
         <v>27</v>
       </c>
@@ -12768,7 +13034,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="23.25">
+    <row r="434" spans="1:7" ht="22.8" hidden="1">
       <c r="A434" s="192">
         <v>28</v>
       </c>
@@ -12791,7 +13057,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="23.25">
+    <row r="435" spans="1:7" ht="22.8" hidden="1">
       <c r="A435" s="192">
         <v>29</v>
       </c>
@@ -12814,7 +13080,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="23.25">
+    <row r="436" spans="1:7" ht="22.8" hidden="1">
       <c r="A436" s="192">
         <v>30</v>
       </c>
@@ -12837,7 +13103,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="23.25">
+    <row r="437" spans="1:7" ht="22.8" hidden="1">
       <c r="A437" s="192">
         <v>31</v>
       </c>
@@ -12860,7 +13126,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="23.25">
+    <row r="438" spans="1:7" ht="22.8" hidden="1">
       <c r="A438" s="225">
         <v>32</v>
       </c>
@@ -12883,7 +13149,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="23.25">
+    <row r="439" spans="1:7" ht="22.8" hidden="1">
       <c r="A439" s="192">
         <v>33</v>
       </c>
@@ -12906,7 +13172,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="23.25">
+    <row r="440" spans="1:7" ht="22.8" hidden="1">
       <c r="A440" s="192">
         <v>34</v>
       </c>
@@ -12929,7 +13195,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="23.25">
+    <row r="441" spans="1:7" ht="22.8" hidden="1">
       <c r="A441" s="192">
         <v>35</v>
       </c>
@@ -12952,7 +13218,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="23.25">
+    <row r="442" spans="1:7" ht="22.8" hidden="1">
       <c r="A442" s="192">
         <v>36</v>
       </c>
@@ -12975,7 +13241,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="23.25">
+    <row r="443" spans="1:7" ht="22.8" hidden="1">
       <c r="A443" s="192">
         <v>37</v>
       </c>
@@ -12998,7 +13264,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="23.25">
+    <row r="444" spans="1:7" ht="22.8" hidden="1">
       <c r="A444" s="192">
         <v>38</v>
       </c>
@@ -13021,7 +13287,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="23.25">
+    <row r="445" spans="1:7" ht="22.8" hidden="1">
       <c r="A445" s="192">
         <v>39</v>
       </c>
@@ -13044,7 +13310,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="23.25">
+    <row r="446" spans="1:7" ht="22.8" hidden="1">
       <c r="A446" s="192">
         <v>40</v>
       </c>
@@ -13067,7 +13333,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="23.25">
+    <row r="447" spans="1:7" ht="22.8" hidden="1">
       <c r="A447" s="217">
         <v>42</v>
       </c>
@@ -13090,7 +13356,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="23.25">
+    <row r="448" spans="1:7" ht="22.8" hidden="1">
       <c r="A448" s="203">
         <v>43</v>
       </c>
@@ -13113,7 +13379,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="23.25">
+    <row r="449" spans="1:7" ht="22.8" hidden="1">
       <c r="A449" s="237">
         <v>44</v>
       </c>
@@ -13136,7 +13402,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="23.25">
+    <row r="450" spans="1:7" ht="22.8" hidden="1">
       <c r="A450" s="217">
         <v>46</v>
       </c>
@@ -13159,7 +13425,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="23.25">
+    <row r="451" spans="1:7" ht="22.8" hidden="1">
       <c r="A451" s="232">
         <v>48</v>
       </c>
@@ -13180,7 +13446,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="23.25">
+    <row r="452" spans="1:7" ht="22.8" hidden="1">
       <c r="A452" s="192">
         <v>50</v>
       </c>
@@ -13203,7 +13469,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="23.25">
+    <row r="453" spans="1:7" ht="22.8" hidden="1">
       <c r="A453" s="192">
         <v>51</v>
       </c>
@@ -13226,7 +13492,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="23.25">
+    <row r="454" spans="1:7" ht="22.8" hidden="1">
       <c r="A454" s="192">
         <v>52</v>
       </c>
@@ -13249,7 +13515,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="23.25">
+    <row r="455" spans="1:7" ht="22.8" hidden="1">
       <c r="A455" s="192">
         <v>58</v>
       </c>
@@ -13272,7 +13538,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="23.25">
+    <row r="456" spans="1:7" ht="22.8" hidden="1">
       <c r="A456" s="192">
         <v>59</v>
       </c>
@@ -13295,7 +13561,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="23.25">
+    <row r="457" spans="1:7" ht="22.8" hidden="1">
       <c r="A457" s="192">
         <v>60</v>
       </c>
@@ -13318,7 +13584,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="23.25">
+    <row r="458" spans="1:7" ht="22.8" hidden="1">
       <c r="A458" s="192">
         <v>1</v>
       </c>
@@ -13341,7 +13607,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="23.25">
+    <row r="459" spans="1:7" ht="22.8" hidden="1">
       <c r="A459" s="192">
         <v>2</v>
       </c>
@@ -13364,7 +13630,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="23.25">
+    <row r="460" spans="1:7" ht="22.8" hidden="1">
       <c r="A460" s="188">
         <v>3</v>
       </c>
@@ -13387,7 +13653,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="23.25">
+    <row r="461" spans="1:7" ht="22.8" hidden="1">
       <c r="A461" s="192">
         <v>5</v>
       </c>
@@ -13410,7 +13676,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="23.25">
+    <row r="462" spans="1:7" ht="22.8" hidden="1">
       <c r="A462" s="192">
         <v>6</v>
       </c>
@@ -13434,7 +13700,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="23.25">
+    <row r="463" spans="1:7" ht="22.8" hidden="1">
       <c r="A463" s="192">
         <v>7</v>
       </c>
@@ -13457,7 +13723,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="23.25">
+    <row r="464" spans="1:7" ht="22.8" hidden="1">
       <c r="A464" s="192">
         <v>8</v>
       </c>
@@ -13481,7 +13747,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="23.25">
+    <row r="465" spans="1:7" ht="22.8" hidden="1">
       <c r="A465" s="192">
         <v>9</v>
       </c>
@@ -13504,7 +13770,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="23.25">
+    <row r="466" spans="1:7" ht="22.8" hidden="1">
       <c r="A466" s="192">
         <v>11</v>
       </c>
@@ -13527,7 +13793,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="23.25">
+    <row r="467" spans="1:7" ht="22.8" hidden="1">
       <c r="A467" s="192">
         <v>12</v>
       </c>
@@ -13550,7 +13816,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="23.25">
+    <row r="468" spans="1:7" ht="22.8" hidden="1">
       <c r="A468" s="188">
         <v>13</v>
       </c>
@@ -13573,7 +13839,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="23.25">
+    <row r="469" spans="1:7" ht="22.8" hidden="1">
       <c r="A469" s="192">
         <v>15</v>
       </c>
@@ -13596,7 +13862,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="23.25">
+    <row r="470" spans="1:7" ht="22.8" hidden="1">
       <c r="A470" s="192">
         <v>16</v>
       </c>
@@ -13619,7 +13885,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="23.25">
+    <row r="471" spans="1:7" ht="22.8" hidden="1">
       <c r="A471" s="192">
         <v>17</v>
       </c>
@@ -13642,7 +13908,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="23.25">
+    <row r="472" spans="1:7" ht="22.8" hidden="1">
       <c r="A472" s="192">
         <v>20</v>
       </c>
@@ -13665,7 +13931,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="23.25">
+    <row r="473" spans="1:7" ht="22.8" hidden="1">
       <c r="A473" s="192">
         <v>21</v>
       </c>
@@ -13688,7 +13954,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="23.25">
+    <row r="474" spans="1:7" ht="22.8" hidden="1">
       <c r="A474" s="192">
         <v>22</v>
       </c>
@@ -13711,7 +13977,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="23.25">
+    <row r="475" spans="1:7" ht="22.8" hidden="1">
       <c r="A475" s="192">
         <v>23</v>
       </c>
@@ -13734,7 +14000,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="46.5">
+    <row r="476" spans="1:7" ht="45.6" hidden="1">
       <c r="A476" s="192">
         <v>24</v>
       </c>
@@ -13757,7 +14023,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="23.25">
+    <row r="477" spans="1:7" ht="22.8" hidden="1">
       <c r="A477" s="188">
         <v>25</v>
       </c>
@@ -13780,7 +14046,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="23.25">
+    <row r="478" spans="1:7" ht="22.8" hidden="1">
       <c r="A478" s="192">
         <v>27</v>
       </c>
@@ -13803,7 +14069,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="23.25">
+    <row r="479" spans="1:7" ht="22.8" hidden="1">
       <c r="A479" s="192">
         <v>28</v>
       </c>
@@ -13826,7 +14092,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="23.25">
+    <row r="480" spans="1:7" ht="22.8" hidden="1">
       <c r="A480" s="192">
         <v>29</v>
       </c>
@@ -13849,7 +14115,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="23.25">
+    <row r="481" spans="1:7" ht="22.8" hidden="1">
       <c r="A481" s="192">
         <v>30</v>
       </c>
@@ -13872,7 +14138,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="23.25">
+    <row r="482" spans="1:7" ht="22.8" hidden="1">
       <c r="A482" s="192">
         <v>31</v>
       </c>
@@ -13895,7 +14161,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="23.25">
+    <row r="483" spans="1:7" ht="22.8" hidden="1">
       <c r="A483" s="203">
         <v>32</v>
       </c>
@@ -13918,7 +14184,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="23.25">
+    <row r="484" spans="1:7" ht="22.8" hidden="1">
       <c r="A484" s="192">
         <v>33</v>
       </c>
@@ -13941,7 +14207,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="23.25">
+    <row r="485" spans="1:7" ht="22.8" hidden="1">
       <c r="A485" s="192">
         <v>34</v>
       </c>
@@ -13964,7 +14230,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="23.25">
+    <row r="486" spans="1:7" ht="22.8" hidden="1">
       <c r="A486" s="188">
         <v>35</v>
       </c>
@@ -13987,7 +14253,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="23.25">
+    <row r="487" spans="1:7" ht="22.8" hidden="1">
       <c r="A487" s="192">
         <v>36</v>
       </c>
@@ -14010,7 +14276,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="23.25">
+    <row r="488" spans="1:7" ht="22.8" hidden="1">
       <c r="A488" s="192">
         <v>37</v>
       </c>
@@ -14033,7 +14299,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="23.25">
+    <row r="489" spans="1:7" ht="22.8" hidden="1">
       <c r="A489" s="192">
         <v>38</v>
       </c>
@@ -14056,7 +14322,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="23.25">
+    <row r="490" spans="1:7" ht="22.8" hidden="1">
       <c r="A490" s="192">
         <v>39</v>
       </c>
@@ -14079,7 +14345,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="23.25">
+    <row r="491" spans="1:7" ht="22.8" hidden="1">
       <c r="A491" s="192">
         <v>40</v>
       </c>
@@ -14102,7 +14368,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="23.25">
+    <row r="492" spans="1:7" ht="22.8" hidden="1">
       <c r="A492" s="192">
         <v>42</v>
       </c>
@@ -14125,7 +14391,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="23.25">
+    <row r="493" spans="1:7" ht="22.8" hidden="1">
       <c r="A493" s="203">
         <v>43</v>
       </c>
@@ -14148,7 +14414,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="23.25">
+    <row r="494" spans="1:7" ht="22.8" hidden="1">
       <c r="A494" s="225">
         <v>44</v>
       </c>
@@ -14171,7 +14437,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="23.25">
+    <row r="495" spans="1:7" ht="22.8" hidden="1">
       <c r="A495" s="192">
         <v>46</v>
       </c>
@@ -14194,7 +14460,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="23.25">
+    <row r="496" spans="1:7" ht="22.8" hidden="1">
       <c r="A496" s="203">
         <v>48</v>
       </c>
@@ -14215,7 +14481,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="23.25">
+    <row r="497" spans="1:7" ht="22.8" hidden="1">
       <c r="A497" s="192">
         <v>50</v>
       </c>
@@ -14238,7 +14504,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="23.25">
+    <row r="498" spans="1:7" ht="22.8" hidden="1">
       <c r="A498" s="192">
         <v>51</v>
       </c>
@@ -14261,7 +14527,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="23.25">
+    <row r="499" spans="1:7" ht="22.8" hidden="1">
       <c r="A499" s="192">
         <v>52</v>
       </c>
@@ -14284,7 +14550,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="23.25">
+    <row r="500" spans="1:7" ht="22.8" hidden="1">
       <c r="A500" s="192">
         <v>58</v>
       </c>
@@ -14307,7 +14573,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="23.25">
+    <row r="501" spans="1:7" ht="22.8" hidden="1">
       <c r="A501" s="192">
         <v>59</v>
       </c>
@@ -14330,7 +14596,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="23.25">
+    <row r="502" spans="1:7" ht="22.8" hidden="1">
       <c r="A502" s="192">
         <v>60</v>
       </c>
@@ -14353,7 +14619,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="23.25">
+    <row r="503" spans="1:7" ht="22.8" hidden="1">
       <c r="A503" s="188">
         <v>1</v>
       </c>
@@ -14376,7 +14642,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="23.25">
+    <row r="504" spans="1:7" ht="22.8" hidden="1">
       <c r="A504" s="192">
         <v>2</v>
       </c>
@@ -14399,7 +14665,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="23.25">
+    <row r="505" spans="1:7" ht="22.8" hidden="1">
       <c r="A505" s="192">
         <v>3</v>
       </c>
@@ -14422,7 +14688,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="23.25">
+    <row r="506" spans="1:7" ht="22.8" hidden="1">
       <c r="A506" s="192">
         <v>5</v>
       </c>
@@ -14445,7 +14711,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="23.25">
+    <row r="507" spans="1:7" ht="22.8" hidden="1">
       <c r="A507" s="192">
         <v>6</v>
       </c>
@@ -14469,7 +14735,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="23.25">
+    <row r="508" spans="1:7" ht="22.8" hidden="1">
       <c r="A508" s="192">
         <v>7</v>
       </c>
@@ -14492,7 +14758,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="23.25">
+    <row r="509" spans="1:7" ht="22.8" hidden="1">
       <c r="A509" s="192">
         <v>8</v>
       </c>
@@ -14516,7 +14782,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="23.25">
+    <row r="510" spans="1:7" ht="22.8" hidden="1">
       <c r="A510" s="192">
         <v>9</v>
       </c>
@@ -14539,7 +14805,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="23.25">
+    <row r="511" spans="1:7" ht="22.8" hidden="1">
       <c r="A511" s="192">
         <v>11</v>
       </c>
@@ -14562,7 +14828,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="23.25">
+    <row r="512" spans="1:7" ht="22.8" hidden="1">
       <c r="A512" s="188">
         <v>12</v>
       </c>
@@ -14585,7 +14851,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="23.25">
+    <row r="513" spans="1:7" ht="22.8" hidden="1">
       <c r="A513" s="192">
         <v>13</v>
       </c>
@@ -14608,7 +14874,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="23.25">
+    <row r="514" spans="1:7" ht="22.8" hidden="1">
       <c r="A514" s="192">
         <v>15</v>
       </c>
@@ -14631,7 +14897,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="23.25">
+    <row r="515" spans="1:7" ht="22.8" hidden="1">
       <c r="A515" s="192">
         <v>16</v>
       </c>
@@ -14654,7 +14920,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="23.25">
+    <row r="516" spans="1:7" ht="22.8" hidden="1">
       <c r="A516" s="192">
         <v>17</v>
       </c>
@@ -14677,7 +14943,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="23.25">
+    <row r="517" spans="1:7" ht="22.8" hidden="1">
       <c r="A517" s="192">
         <v>20</v>
       </c>
@@ -14700,7 +14966,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="23.25">
+    <row r="518" spans="1:7" ht="22.8" hidden="1">
       <c r="A518" s="192">
         <v>21</v>
       </c>
@@ -14723,7 +14989,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="23.25">
+    <row r="519" spans="1:7" ht="22.8" hidden="1">
       <c r="A519" s="192">
         <v>22</v>
       </c>
@@ -14746,7 +15012,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="23.25">
+    <row r="520" spans="1:7" ht="22.8" hidden="1">
       <c r="A520" s="192">
         <v>23</v>
       </c>
@@ -14769,7 +15035,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="46.5">
+    <row r="521" spans="1:7" ht="45.6" hidden="1">
       <c r="A521" s="217">
         <v>24</v>
       </c>
@@ -14792,7 +15058,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="23.25">
+    <row r="522" spans="1:7" ht="22.8" hidden="1">
       <c r="A522" s="192">
         <v>25</v>
       </c>
@@ -14815,7 +15081,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="23.25">
+    <row r="523" spans="1:7" ht="22.8" hidden="1">
       <c r="A523" s="217">
         <v>27</v>
       </c>
@@ -14838,7 +15104,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="23.25">
+    <row r="524" spans="1:7" ht="22.8" hidden="1">
       <c r="A524" s="217">
         <v>28</v>
       </c>
@@ -14861,7 +15127,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="23.25">
+    <row r="525" spans="1:7" ht="22.8" hidden="1">
       <c r="A525" s="208">
         <v>29</v>
       </c>
@@ -14884,7 +15150,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="23.25">
+    <row r="526" spans="1:7" ht="22.8" hidden="1">
       <c r="A526" s="192">
         <v>30</v>
       </c>
@@ -14907,7 +15173,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="23.25">
+    <row r="527" spans="1:7" ht="22.8" hidden="1">
       <c r="A527" s="192">
         <v>31</v>
       </c>
@@ -14930,7 +15196,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="23.25">
+    <row r="528" spans="1:7" ht="22.8" hidden="1">
       <c r="A528" s="203">
         <v>32</v>
       </c>
@@ -14953,7 +15219,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="23.25">
+    <row r="529" spans="1:7" ht="22.8" hidden="1">
       <c r="A529" s="192">
         <v>33</v>
       </c>
@@ -14976,7 +15242,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="23.25">
+    <row r="530" spans="1:7" ht="22.8" hidden="1">
       <c r="A530" s="192">
         <v>34</v>
       </c>
@@ -14999,7 +15265,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="23.25">
+    <row r="531" spans="1:7" ht="22.8" hidden="1">
       <c r="A531" s="192">
         <v>35</v>
       </c>
@@ -15022,7 +15288,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="23.25">
+    <row r="532" spans="1:7" ht="22.8" hidden="1">
       <c r="A532" s="192">
         <v>36</v>
       </c>
@@ -15045,7 +15311,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="23.25">
+    <row r="533" spans="1:7" ht="22.8" hidden="1">
       <c r="A533" s="192">
         <v>37</v>
       </c>
@@ -15068,7 +15334,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="23.25">
+    <row r="534" spans="1:7" ht="22.8" hidden="1">
       <c r="A534" s="188">
         <v>38</v>
       </c>
@@ -15091,7 +15357,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="23.25">
+    <row r="535" spans="1:7" ht="22.8" hidden="1">
       <c r="A535" s="192">
         <v>39</v>
       </c>
@@ -15114,7 +15380,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="23.25">
+    <row r="536" spans="1:7" ht="22.8" hidden="1">
       <c r="A536" s="192">
         <v>40</v>
       </c>
@@ -15137,7 +15403,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="23.25">
+    <row r="537" spans="1:7" ht="22.8" hidden="1">
       <c r="A537" s="192">
         <v>42</v>
       </c>
@@ -15160,7 +15426,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="23.25">
+    <row r="538" spans="1:7" ht="22.8" hidden="1">
       <c r="A538" s="203">
         <v>43</v>
       </c>
@@ -15183,7 +15449,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="23.25">
+    <row r="539" spans="1:7" ht="22.8" hidden="1">
       <c r="A539" s="203">
         <v>44</v>
       </c>
@@ -15206,7 +15472,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="23.25">
+    <row r="540" spans="1:7" ht="22.8" hidden="1">
       <c r="A540" s="192">
         <v>46</v>
       </c>
@@ -15229,7 +15495,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="541" spans="1:7" ht="23.25">
+    <row r="541" spans="1:7" ht="22.8" hidden="1">
       <c r="A541" s="203">
         <v>48</v>
       </c>
@@ -15250,7 +15516,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="23.25">
+    <row r="542" spans="1:7" ht="22.8" hidden="1">
       <c r="A542" s="188">
         <v>50</v>
       </c>
@@ -15273,7 +15539,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="23.25">
+    <row r="543" spans="1:7" ht="22.8" hidden="1">
       <c r="A543" s="192">
         <v>51</v>
       </c>
@@ -15296,7 +15562,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="23.25">
+    <row r="544" spans="1:7" ht="22.8" hidden="1">
       <c r="A544" s="192">
         <v>52</v>
       </c>
@@ -15319,7 +15585,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="23.25">
+    <row r="545" spans="1:7" ht="22.8" hidden="1">
       <c r="A545" s="192">
         <v>58</v>
       </c>
@@ -15342,7 +15608,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="23.25">
+    <row r="546" spans="1:7" ht="22.8" hidden="1">
       <c r="A546" s="192">
         <v>59</v>
       </c>
@@ -15365,7 +15631,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="23.25">
+    <row r="547" spans="1:7" ht="22.8" hidden="1">
       <c r="A547" s="192">
         <v>60</v>
       </c>
@@ -15388,7 +15654,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="548" spans="1:7" ht="23.25">
+    <row r="548" spans="1:7" ht="22.8" hidden="1">
       <c r="A548" s="192">
         <v>1</v>
       </c>
@@ -15411,7 +15677,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="23.25">
+    <row r="549" spans="1:7" ht="22.8" hidden="1">
       <c r="A549" s="192">
         <v>2</v>
       </c>
@@ -15434,7 +15700,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="23.25">
+    <row r="550" spans="1:7" ht="22.8" hidden="1">
       <c r="A550" s="192">
         <v>3</v>
       </c>
@@ -15457,7 +15723,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="23.25">
+    <row r="551" spans="1:7" ht="22.8" hidden="1">
       <c r="A551" s="188">
         <v>5</v>
       </c>
@@ -15480,7 +15746,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="552" spans="1:7" ht="23.25">
+    <row r="552" spans="1:7" ht="22.8" hidden="1">
       <c r="A552" s="192">
         <v>6</v>
       </c>
@@ -15504,7 +15770,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="553" spans="1:7" ht="23.25">
+    <row r="553" spans="1:7" ht="22.8" hidden="1">
       <c r="A553" s="192">
         <v>7</v>
       </c>
@@ -15527,7 +15793,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="554" spans="1:7" ht="23.25">
+    <row r="554" spans="1:7" ht="22.8" hidden="1">
       <c r="A554" s="192">
         <v>8</v>
       </c>
@@ -15551,7 +15817,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="555" spans="1:7" ht="23.25">
+    <row r="555" spans="1:7" ht="22.8" hidden="1">
       <c r="A555" s="192">
         <v>9</v>
       </c>
@@ -15574,7 +15840,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="556" spans="1:7" ht="23.25">
+    <row r="556" spans="1:7" ht="22.8" hidden="1">
       <c r="A556" s="192">
         <v>11</v>
       </c>
@@ -15597,7 +15863,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="557" spans="1:7" ht="23.25">
+    <row r="557" spans="1:7" ht="22.8" hidden="1">
       <c r="A557" s="192">
         <v>12</v>
       </c>
@@ -15620,7 +15886,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="558" spans="1:7" ht="23.25">
+    <row r="558" spans="1:7" ht="22.8" hidden="1">
       <c r="A558" s="192">
         <v>13</v>
       </c>
@@ -15643,7 +15909,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="559" spans="1:7" ht="23.25">
+    <row r="559" spans="1:7" ht="22.8" hidden="1">
       <c r="A559" s="192">
         <v>15</v>
       </c>
@@ -15666,7 +15932,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="23.25">
+    <row r="560" spans="1:7" ht="22.8" hidden="1">
       <c r="A560" s="188">
         <v>16</v>
       </c>
@@ -15689,7 +15955,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="561" spans="1:7" ht="23.25">
+    <row r="561" spans="1:7" ht="22.8" hidden="1">
       <c r="A561" s="192">
         <v>17</v>
       </c>
@@ -15712,7 +15978,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="562" spans="1:7" ht="23.25">
+    <row r="562" spans="1:7" ht="22.8" hidden="1">
       <c r="A562" s="192">
         <v>20</v>
       </c>
@@ -15735,7 +16001,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="563" spans="1:7" ht="23.25">
+    <row r="563" spans="1:7" ht="22.8" hidden="1">
       <c r="A563" s="192">
         <v>21</v>
       </c>
@@ -15758,7 +16024,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="564" spans="1:7" ht="23.25">
+    <row r="564" spans="1:7" ht="22.8" hidden="1">
       <c r="A564" s="192">
         <v>22</v>
       </c>
@@ -15781,7 +16047,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="565" spans="1:7" ht="23.25">
+    <row r="565" spans="1:7" ht="22.8" hidden="1">
       <c r="A565" s="192">
         <v>23</v>
       </c>
@@ -15804,7 +16070,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="566" spans="1:7" ht="46.5">
+    <row r="566" spans="1:7" ht="45.6" hidden="1">
       <c r="A566" s="192">
         <v>24</v>
       </c>
@@ -15827,7 +16093,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="567" spans="1:7" ht="23.25">
+    <row r="567" spans="1:7" ht="22.8" hidden="1">
       <c r="A567" s="192">
         <v>25</v>
       </c>
@@ -15850,7 +16116,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="568" spans="1:7" ht="23.25">
+    <row r="568" spans="1:7" ht="22.8" hidden="1">
       <c r="A568" s="188">
         <v>27</v>
       </c>
@@ -15873,7 +16139,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="569" spans="1:7" ht="23.25">
+    <row r="569" spans="1:7" ht="22.8" hidden="1">
       <c r="A569" s="192">
         <v>28</v>
       </c>
@@ -15896,7 +16162,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="570" spans="1:7" ht="23.25">
+    <row r="570" spans="1:7" ht="22.8" hidden="1">
       <c r="A570" s="192">
         <v>29</v>
       </c>
@@ -15919,7 +16185,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="571" spans="1:7" ht="23.25">
+    <row r="571" spans="1:7" ht="22.8" hidden="1">
       <c r="A571" s="192">
         <v>30</v>
       </c>
@@ -15942,7 +16208,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="572" spans="1:7" ht="23.25">
+    <row r="572" spans="1:7" ht="22.8" hidden="1">
       <c r="A572" s="192">
         <v>31</v>
       </c>
@@ -15965,7 +16231,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="573" spans="1:7" ht="23.25">
+    <row r="573" spans="1:7" ht="22.8" hidden="1">
       <c r="A573" s="203">
         <v>32</v>
       </c>
@@ -15988,7 +16254,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="574" spans="1:7" ht="23.25">
+    <row r="574" spans="1:7" ht="22.8" hidden="1">
       <c r="A574" s="192">
         <v>33</v>
       </c>
@@ -16011,7 +16277,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="575" spans="1:7" ht="23.25">
+    <row r="575" spans="1:7" ht="22.8" hidden="1">
       <c r="A575" s="192">
         <v>34</v>
       </c>
@@ -16034,7 +16300,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="576" spans="1:7" ht="23.25">
+    <row r="576" spans="1:7" ht="22.8" hidden="1">
       <c r="A576" s="192">
         <v>35</v>
       </c>
@@ -16057,7 +16323,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="577" spans="1:7" ht="23.25">
+    <row r="577" spans="1:7" ht="22.8" hidden="1">
       <c r="A577" s="188">
         <v>36</v>
       </c>
@@ -16080,7 +16346,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="578" spans="1:7" ht="23.25">
+    <row r="578" spans="1:7" ht="22.8" hidden="1">
       <c r="A578" s="192">
         <v>37</v>
       </c>
@@ -16103,7 +16369,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="579" spans="1:7" ht="23.25">
+    <row r="579" spans="1:7" ht="22.8" hidden="1">
       <c r="A579" s="192">
         <v>38</v>
       </c>
@@ -16126,7 +16392,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="580" spans="1:7" ht="23.25">
+    <row r="580" spans="1:7" ht="22.8" hidden="1">
       <c r="A580" s="192">
         <v>39</v>
       </c>
@@ -16149,7 +16415,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="581" spans="1:7" ht="23.25">
+    <row r="581" spans="1:7" ht="22.8" hidden="1">
       <c r="A581" s="192">
         <v>40</v>
       </c>
@@ -16172,7 +16438,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="23.25">
+    <row r="582" spans="1:7" ht="22.8" hidden="1">
       <c r="A582" s="192">
         <v>42</v>
       </c>
@@ -16195,7 +16461,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="583" spans="1:7" ht="23.25">
+    <row r="583" spans="1:7" ht="22.8" hidden="1">
       <c r="A583" s="203">
         <v>43</v>
       </c>
@@ -16218,7 +16484,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="584" spans="1:7" ht="23.25">
+    <row r="584" spans="1:7" ht="22.8" hidden="1">
       <c r="A584" s="203">
         <v>44</v>
       </c>
@@ -16241,7 +16507,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="585" spans="1:7" ht="23.25">
+    <row r="585" spans="1:7" ht="22.8" hidden="1">
       <c r="A585" s="192">
         <v>46</v>
       </c>
@@ -16264,7 +16530,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="586" spans="1:7" ht="23.25">
+    <row r="586" spans="1:7" ht="22.8" hidden="1">
       <c r="A586" s="225">
         <v>48</v>
       </c>
@@ -16285,7 +16551,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="23.25">
+    <row r="587" spans="1:7" ht="22.8" hidden="1">
       <c r="A587" s="192">
         <v>50</v>
       </c>
@@ -16308,7 +16574,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="588" spans="1:7" ht="23.25">
+    <row r="588" spans="1:7" ht="22.8" hidden="1">
       <c r="A588" s="192">
         <v>51</v>
       </c>
@@ -16331,7 +16597,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="589" spans="1:7" ht="23.25">
+    <row r="589" spans="1:7" ht="22.8" hidden="1">
       <c r="A589" s="192">
         <v>52</v>
       </c>
@@ -16354,7 +16620,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="590" spans="1:7" ht="23.25">
+    <row r="590" spans="1:7" ht="22.8" hidden="1">
       <c r="A590" s="192">
         <v>58</v>
       </c>
@@ -16377,7 +16643,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="591" spans="1:7" ht="23.25">
+    <row r="591" spans="1:7" ht="22.8" hidden="1">
       <c r="A591" s="192">
         <v>59</v>
       </c>
@@ -16400,7 +16666,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="592" spans="1:7" ht="23.25">
+    <row r="592" spans="1:7" ht="22.8" hidden="1">
       <c r="A592" s="192">
         <v>60</v>
       </c>
@@ -16423,7 +16689,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="23.25">
+    <row r="593" spans="1:7" ht="22.8" hidden="1">
       <c r="A593" s="192">
         <v>1</v>
       </c>
@@ -16446,7 +16712,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="594" spans="1:7" ht="23.25">
+    <row r="594" spans="1:7" ht="22.8" hidden="1">
       <c r="A594" s="192">
         <v>2</v>
       </c>
@@ -16469,7 +16735,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="595" spans="1:7" ht="23.25">
+    <row r="595" spans="1:7" ht="22.8" hidden="1">
       <c r="A595" s="217">
         <v>5</v>
       </c>
@@ -16492,7 +16758,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="596" spans="1:7" ht="23.25">
+    <row r="596" spans="1:7" ht="22.8" hidden="1">
       <c r="A596" s="192">
         <v>6</v>
       </c>
@@ -16516,7 +16782,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="597" spans="1:7" ht="23.25">
+    <row r="597" spans="1:7" ht="22.8" hidden="1">
       <c r="A597" s="217">
         <v>7</v>
       </c>
@@ -16539,7 +16805,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="598" spans="1:7" ht="23.25">
+    <row r="598" spans="1:7" ht="22.8" hidden="1">
       <c r="A598" s="217">
         <v>8</v>
       </c>
@@ -16563,7 +16829,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="23.25">
+    <row r="599" spans="1:7" ht="22.8" hidden="1">
       <c r="A599" s="208">
         <v>9</v>
       </c>
@@ -16586,7 +16852,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="600" spans="1:7" ht="23.25">
+    <row r="600" spans="1:7" ht="22.8" hidden="1">
       <c r="A600" s="192">
         <v>11</v>
       </c>
@@ -16609,7 +16875,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="601" spans="1:7" ht="23.25">
+    <row r="601" spans="1:7" ht="22.8" hidden="1">
       <c r="A601" s="192">
         <v>12</v>
       </c>
@@ -16632,7 +16898,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="602" spans="1:7" ht="23.25">
+    <row r="602" spans="1:7" ht="22.8" hidden="1">
       <c r="A602" s="192">
         <v>13</v>
       </c>
@@ -16655,7 +16921,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="603" spans="1:7" ht="23.25">
+    <row r="603" spans="1:7" ht="22.8" hidden="1">
       <c r="A603" s="192">
         <v>15</v>
       </c>
@@ -16678,7 +16944,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="23.25">
+    <row r="604" spans="1:7" ht="22.8" hidden="1">
       <c r="A604" s="192">
         <v>16</v>
       </c>
@@ -16701,7 +16967,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="23.25">
+    <row r="605" spans="1:7" ht="22.8" hidden="1">
       <c r="A605" s="192">
         <v>17</v>
       </c>
@@ -16724,7 +16990,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="23.25">
+    <row r="606" spans="1:7" ht="22.8" hidden="1">
       <c r="A606" s="192">
         <v>20</v>
       </c>
@@ -16747,7 +17013,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="23.25">
+    <row r="607" spans="1:7" ht="22.8" hidden="1">
       <c r="A607" s="192">
         <v>21</v>
       </c>
@@ -16770,7 +17036,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="608" spans="1:7" ht="23.25">
+    <row r="608" spans="1:7" ht="22.8" hidden="1">
       <c r="A608" s="188">
         <v>22</v>
       </c>
@@ -16793,7 +17059,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="609" spans="1:7" ht="23.25">
+    <row r="609" spans="1:7" ht="22.8" hidden="1">
       <c r="A609" s="192">
         <v>23</v>
       </c>
@@ -16816,7 +17082,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="610" spans="1:7" ht="46.5">
+    <row r="610" spans="1:7" ht="45.6" hidden="1">
       <c r="A610" s="192">
         <v>24</v>
       </c>
@@ -16839,7 +17105,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="611" spans="1:7" ht="23.25">
+    <row r="611" spans="1:7" ht="22.8" hidden="1">
       <c r="A611" s="192">
         <v>25</v>
       </c>
@@ -16862,7 +17128,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="612" spans="1:7" ht="23.25">
+    <row r="612" spans="1:7" ht="22.8" hidden="1">
       <c r="A612" s="192">
         <v>27</v>
       </c>
@@ -16885,7 +17151,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="613" spans="1:7" ht="23.25">
+    <row r="613" spans="1:7" ht="22.8" hidden="1">
       <c r="A613" s="192">
         <v>28</v>
       </c>
@@ -16908,7 +17174,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="614" spans="1:7" ht="23.25">
+    <row r="614" spans="1:7" ht="22.8" hidden="1">
       <c r="A614" s="192">
         <v>29</v>
       </c>
@@ -16931,7 +17197,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="615" spans="1:7" ht="23.25">
+    <row r="615" spans="1:7" ht="22.8" hidden="1">
       <c r="A615" s="192">
         <v>30</v>
       </c>
@@ -16954,7 +17220,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="616" spans="1:7" ht="23.25">
+    <row r="616" spans="1:7" ht="22.8" hidden="1">
       <c r="A616" s="188">
         <v>31</v>
       </c>
@@ -16977,7 +17243,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="617" spans="1:7" ht="23.25">
+    <row r="617" spans="1:7" ht="22.8" hidden="1">
       <c r="A617" s="203">
         <v>32</v>
       </c>
@@ -17000,7 +17266,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="23.25">
+    <row r="618" spans="1:7" ht="22.8" hidden="1">
       <c r="A618" s="192">
         <v>33</v>
       </c>
@@ -17023,7 +17289,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="619" spans="1:7" ht="23.25">
+    <row r="619" spans="1:7" ht="22.8" hidden="1">
       <c r="A619" s="192">
         <v>34</v>
       </c>
@@ -17046,7 +17312,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="620" spans="1:7" ht="23.25">
+    <row r="620" spans="1:7" ht="22.8" hidden="1">
       <c r="A620" s="192">
         <v>35</v>
       </c>
@@ -17069,7 +17335,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="621" spans="1:7" ht="23.25">
+    <row r="621" spans="1:7" ht="22.8" hidden="1">
       <c r="A621" s="192">
         <v>36</v>
       </c>
@@ -17092,7 +17358,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="622" spans="1:7" ht="23.25">
+    <row r="622" spans="1:7" ht="22.8" hidden="1">
       <c r="A622" s="192">
         <v>37</v>
       </c>
@@ -17115,7 +17381,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="623" spans="1:7" ht="23.25">
+    <row r="623" spans="1:7" ht="22.8" hidden="1">
       <c r="A623" s="192">
         <v>38</v>
       </c>
@@ -17138,7 +17404,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="624" spans="1:7" ht="23.25">
+    <row r="624" spans="1:7" ht="22.8" hidden="1">
       <c r="A624" s="192">
         <v>39</v>
       </c>
@@ -17161,7 +17427,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="625" spans="1:7" ht="23.25">
+    <row r="625" spans="1:7" ht="22.8" hidden="1">
       <c r="A625" s="188">
         <v>40</v>
       </c>
@@ -17184,7 +17450,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="626" spans="1:7" ht="23.25">
+    <row r="626" spans="1:7" ht="22.8" hidden="1">
       <c r="A626" s="192">
         <v>42</v>
       </c>
@@ -17207,7 +17473,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="627" spans="1:7" ht="23.25">
+    <row r="627" spans="1:7" ht="22.8" hidden="1">
       <c r="A627" s="203">
         <v>43</v>
       </c>
@@ -17230,7 +17496,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="628" spans="1:7" ht="23.25">
+    <row r="628" spans="1:7" ht="22.8" hidden="1">
       <c r="A628" s="203">
         <v>44</v>
       </c>
@@ -17253,7 +17519,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="629" spans="1:7" ht="23.25">
+    <row r="629" spans="1:7" ht="22.8" hidden="1">
       <c r="A629" s="192">
         <v>46</v>
       </c>
@@ -17276,7 +17542,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="630" spans="1:7" ht="23.25">
+    <row r="630" spans="1:7" ht="22.8" hidden="1">
       <c r="A630" s="203">
         <v>48</v>
       </c>
@@ -17297,7 +17563,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="631" spans="1:7" ht="23.25">
+    <row r="631" spans="1:7" ht="22.8" hidden="1">
       <c r="A631" s="192">
         <v>50</v>
       </c>
@@ -17320,7 +17586,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="632" spans="1:7" ht="23.25">
+    <row r="632" spans="1:7" ht="22.8" hidden="1">
       <c r="A632" s="192">
         <v>51</v>
       </c>
@@ -17343,7 +17609,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="633" spans="1:7" ht="23.25">
+    <row r="633" spans="1:7" ht="22.8" hidden="1">
       <c r="A633" s="192">
         <v>52</v>
       </c>
@@ -17366,7 +17632,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="634" spans="1:7" ht="23.25">
+    <row r="634" spans="1:7" ht="22.8" hidden="1">
       <c r="A634" s="188">
         <v>58</v>
       </c>
@@ -17389,7 +17655,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="635" spans="1:7" ht="23.25">
+    <row r="635" spans="1:7" ht="22.8" hidden="1">
       <c r="A635" s="192">
         <v>59</v>
       </c>
@@ -17412,7 +17678,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="636" spans="1:7" ht="23.25">
+    <row r="636" spans="1:7" ht="22.8" hidden="1">
       <c r="A636" s="192">
         <v>60</v>
       </c>
@@ -17435,8 +17701,22 @@
         <v>46143</v>
       </c>
     </row>
+    <row r="637" spans="1:7" ht="46.2" customHeight="1">
+      <c r="F637" s="319">
+        <f>SUBTOTAL(9,F6:F636)</f>
+        <v>49200</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" ht="46.2" customHeight="1"/>
+    <row r="639" spans="1:7" ht="46.2" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A5:G636" xr:uid="{51717A2D-38D8-4ABE-BD5F-98B6647922FB}"/>
+  <autoFilter ref="A5:G636" xr:uid="{51717A2D-38D8-4ABE-BD5F-98B6647922FB}">
+    <filterColumn colId="6">
+      <filters>
+        <dateGroupItem year="2025" month="7" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -17448,33 +17728,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AM81"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="3" customWidth="1"/>
-    <col min="8" max="9" width="17.83203125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="17.77734375" style="3" customWidth="1"/>
     <col min="10" max="10" width="18" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.1640625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.77734375" style="3" customWidth="1"/>
     <col min="14" max="14" width="21.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" style="3" customWidth="1"/>
     <col min="16" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="17.6640625" customWidth="1"/>
     <col min="19" max="19" width="21.33203125" customWidth="1"/>
-    <col min="20" max="21" width="16.83203125" customWidth="1"/>
+    <col min="20" max="21" width="16.77734375" customWidth="1"/>
     <col min="22" max="23" width="17.33203125" customWidth="1"/>
-    <col min="24" max="33" width="18.5" customWidth="1"/>
-    <col min="34" max="34" width="91.83203125" customWidth="1"/>
-    <col min="35" max="35" width="18.5" customWidth="1"/>
-    <col min="36" max="36" width="19.1640625" customWidth="1"/>
+    <col min="24" max="33" width="18.44140625" customWidth="1"/>
+    <col min="34" max="34" width="91.77734375" customWidth="1"/>
+    <col min="35" max="35" width="18.44140625" customWidth="1"/>
+    <col min="36" max="36" width="19.109375" customWidth="1"/>
     <col min="37" max="38" width="18.6640625" customWidth="1"/>
-    <col min="39" max="39" width="18.83203125" customWidth="1"/>
+    <col min="39" max="39" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="20.100000000000001" customHeight="1">
@@ -17579,7 +17859,7 @@
       <c r="AL3" s="6"/>
       <c r="AM3" s="7"/>
     </row>
-    <row r="4" spans="1:39" ht="44.45" customHeight="1">
+    <row r="4" spans="1:39" ht="44.4" customHeight="1">
       <c r="A4" s="161" t="s">
         <v>5</v>
       </c>
@@ -18037,7 +18317,7 @@
       <c r="K9" s="32">
         <v>45853</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="115">
         <f>1000+17200</f>
         <v>18200</v>
       </c>
@@ -21532,16 +21812,16 @@
       <c r="I57" s="32">
         <v>45823</v>
       </c>
-      <c r="J57" s="73">
+      <c r="J57" s="115">
         <v>1300</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="320">
         <v>45938</v>
       </c>
-      <c r="L57" s="73">
+      <c r="L57" s="115">
         <v>1300</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="320">
         <v>45938</v>
       </c>
       <c r="N57" s="74">
@@ -22686,7 +22966,7 @@
       <c r="AG76" s="70"/>
       <c r="AH76" s="41"/>
     </row>
-    <row r="77" spans="1:34" ht="26.45" customHeight="1">
+    <row r="77" spans="1:34" ht="26.4" customHeight="1">
       <c r="A77" s="22"/>
       <c r="B77" s="177" t="s">
         <v>3</v>
@@ -22819,7 +23099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="25.5">
+    <row r="80" spans="1:34" ht="24.6">
       <c r="F80" s="169">
         <v>45748</v>
       </c>
@@ -22877,7 +23157,7 @@
       </c>
       <c r="AG80" s="159"/>
     </row>
-    <row r="81" spans="1:17" ht="32.450000000000003" customHeight="1">
+    <row r="81" spans="1:17" ht="32.4" customHeight="1">
       <c r="A81" s="176" t="s">
         <v>22</v>
       </c>
@@ -22915,10 +23195,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388B0986-349B-4B1A-860F-2315B64A4EE8}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22929,7 +23209,7 @@
       <c r="B1" s="304"/>
       <c r="C1" s="304"/>
     </row>
-    <row r="3" spans="1:4" ht="26.45" customHeight="1">
+    <row r="3" spans="1:4" ht="26.4" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>129</v>
       </c>
@@ -23051,7 +23331,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75">
+    <row r="13" spans="1:4" ht="15.6">
       <c r="A13" s="48">
         <v>10</v>
       </c>
@@ -23063,7 +23343,7 @@
         <v>65800</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75">
+    <row r="14" spans="1:4" ht="15.6">
       <c r="A14" s="48">
         <v>11</v>
       </c>
@@ -23075,7 +23355,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75">
+    <row r="15" spans="1:4" ht="15.6">
       <c r="A15" s="129">
         <v>12</v>
       </c>
@@ -23087,7 +23367,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75">
+    <row r="16" spans="1:4" ht="15.6">
       <c r="A16" s="129">
         <v>13</v>
       </c>
@@ -23099,7 +23379,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75">
+    <row r="17" spans="1:3" ht="15.6">
       <c r="A17" s="129">
         <v>14</v>
       </c>
@@ -23123,145 +23403,145 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810C1D33-6CDF-4F26-B97B-E4FC71263824}">
   <dimension ref="A1:BA137"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" customWidth="1"/>
-    <col min="2" max="2" width="58.1640625" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" customWidth="1"/>
-    <col min="5" max="16" width="14.5" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="20" width="14.5" customWidth="1"/>
-    <col min="21" max="21" width="18.83203125" customWidth="1"/>
-    <col min="22" max="24" width="14.5" customWidth="1"/>
-    <col min="25" max="25" width="18.83203125" customWidth="1"/>
-    <col min="26" max="28" width="14.5" customWidth="1"/>
-    <col min="29" max="29" width="18.83203125" customWidth="1"/>
-    <col min="30" max="32" width="14.5" customWidth="1"/>
-    <col min="33" max="33" width="18.83203125" customWidth="1"/>
-    <col min="34" max="36" width="14.5" customWidth="1"/>
-    <col min="37" max="37" width="18.83203125" customWidth="1"/>
-    <col min="38" max="40" width="14.5" customWidth="1"/>
-    <col min="41" max="41" width="18.83203125" customWidth="1"/>
-    <col min="42" max="44" width="14.5" customWidth="1"/>
-    <col min="45" max="45" width="18.83203125" customWidth="1"/>
-    <col min="46" max="48" width="14.5" customWidth="1"/>
-    <col min="49" max="49" width="18.83203125" customWidth="1"/>
-    <col min="50" max="52" width="14.5" customWidth="1"/>
-    <col min="53" max="53" width="22.1640625" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="58.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="16" width="14.44140625" customWidth="1"/>
+    <col min="17" max="17" width="18.77734375" customWidth="1"/>
+    <col min="18" max="20" width="14.44140625" customWidth="1"/>
+    <col min="21" max="21" width="18.77734375" customWidth="1"/>
+    <col min="22" max="24" width="14.44140625" customWidth="1"/>
+    <col min="25" max="25" width="18.77734375" customWidth="1"/>
+    <col min="26" max="28" width="14.44140625" customWidth="1"/>
+    <col min="29" max="29" width="18.77734375" customWidth="1"/>
+    <col min="30" max="32" width="14.44140625" customWidth="1"/>
+    <col min="33" max="33" width="18.77734375" customWidth="1"/>
+    <col min="34" max="36" width="14.44140625" customWidth="1"/>
+    <col min="37" max="37" width="18.77734375" customWidth="1"/>
+    <col min="38" max="40" width="14.44140625" customWidth="1"/>
+    <col min="41" max="41" width="18.77734375" customWidth="1"/>
+    <col min="42" max="44" width="14.44140625" customWidth="1"/>
+    <col min="45" max="45" width="18.77734375" customWidth="1"/>
+    <col min="46" max="48" width="14.44140625" customWidth="1"/>
+    <col min="49" max="49" width="18.77734375" customWidth="1"/>
+    <col min="50" max="52" width="14.44140625" customWidth="1"/>
+    <col min="53" max="53" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="29.1" customHeight="1">
-      <c r="A1" s="307" t="s">
+      <c r="A1" s="313" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="308"/>
-      <c r="C1" s="308"/>
-      <c r="D1" s="308"/>
-      <c r="E1" s="308"/>
-      <c r="F1" s="308"/>
-      <c r="G1" s="308"/>
-      <c r="H1" s="308"/>
-      <c r="I1" s="308"/>
-      <c r="J1" s="308"/>
-      <c r="K1" s="308"/>
-      <c r="L1" s="308"/>
-      <c r="M1" s="308"/>
-      <c r="N1" s="308"/>
-      <c r="O1" s="308"/>
-      <c r="P1" s="308"/>
-      <c r="Q1" s="308"/>
+      <c r="B1" s="314"/>
+      <c r="C1" s="314"/>
+      <c r="D1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="314"/>
+      <c r="G1" s="314"/>
+      <c r="H1" s="314"/>
+      <c r="I1" s="314"/>
+      <c r="J1" s="314"/>
+      <c r="K1" s="314"/>
+      <c r="L1" s="314"/>
+      <c r="M1" s="314"/>
+      <c r="N1" s="314"/>
+      <c r="O1" s="314"/>
+      <c r="P1" s="314"/>
+      <c r="Q1" s="314"/>
     </row>
     <row r="2" spans="1:53" ht="31.5" customHeight="1">
-      <c r="A2" s="309" t="s">
+      <c r="A2" s="315" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="311" t="s">
+      <c r="B2" s="317" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="312" t="s">
+      <c r="C2" s="307" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="313"/>
-      <c r="E2" s="314" t="s">
+      <c r="D2" s="308"/>
+      <c r="E2" s="305" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="315"/>
-      <c r="G2" s="316"/>
-      <c r="H2" s="312" t="s">
+      <c r="F2" s="306"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="307" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="313"/>
-      <c r="J2" s="317"/>
-      <c r="K2" s="314" t="s">
+      <c r="I2" s="308"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="305" t="s">
         <v>146</v>
       </c>
-      <c r="L2" s="315"/>
-      <c r="M2" s="316"/>
-      <c r="N2" s="312" t="s">
+      <c r="L2" s="306"/>
+      <c r="M2" s="312"/>
+      <c r="N2" s="307" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="313"/>
-      <c r="P2" s="313"/>
-      <c r="Q2" s="317"/>
-      <c r="R2" s="314" t="s">
+      <c r="O2" s="308"/>
+      <c r="P2" s="308"/>
+      <c r="Q2" s="309"/>
+      <c r="R2" s="305" t="s">
         <v>168</v>
       </c>
-      <c r="S2" s="315"/>
-      <c r="T2" s="315"/>
-      <c r="U2" s="315"/>
-      <c r="V2" s="305" t="s">
+      <c r="S2" s="306"/>
+      <c r="T2" s="306"/>
+      <c r="U2" s="306"/>
+      <c r="V2" s="310" t="s">
         <v>182</v>
       </c>
-      <c r="W2" s="306"/>
-      <c r="X2" s="306"/>
-      <c r="Y2" s="306"/>
-      <c r="Z2" s="305" t="s">
+      <c r="W2" s="311"/>
+      <c r="X2" s="311"/>
+      <c r="Y2" s="311"/>
+      <c r="Z2" s="310" t="s">
         <v>187</v>
       </c>
-      <c r="AA2" s="306"/>
-      <c r="AB2" s="306"/>
-      <c r="AC2" s="306"/>
-      <c r="AD2" s="305" t="s">
+      <c r="AA2" s="311"/>
+      <c r="AB2" s="311"/>
+      <c r="AC2" s="311"/>
+      <c r="AD2" s="310" t="s">
         <v>188</v>
       </c>
-      <c r="AE2" s="306"/>
-      <c r="AF2" s="306"/>
-      <c r="AG2" s="306"/>
-      <c r="AH2" s="305" t="s">
+      <c r="AE2" s="311"/>
+      <c r="AF2" s="311"/>
+      <c r="AG2" s="311"/>
+      <c r="AH2" s="310" t="s">
         <v>190</v>
       </c>
-      <c r="AI2" s="306"/>
-      <c r="AJ2" s="306"/>
-      <c r="AK2" s="306"/>
-      <c r="AL2" s="305" t="s">
+      <c r="AI2" s="311"/>
+      <c r="AJ2" s="311"/>
+      <c r="AK2" s="311"/>
+      <c r="AL2" s="310" t="s">
         <v>215</v>
       </c>
-      <c r="AM2" s="306"/>
-      <c r="AN2" s="306"/>
-      <c r="AO2" s="306"/>
-      <c r="AP2" s="305" t="s">
+      <c r="AM2" s="311"/>
+      <c r="AN2" s="311"/>
+      <c r="AO2" s="311"/>
+      <c r="AP2" s="310" t="s">
         <v>216</v>
       </c>
-      <c r="AQ2" s="306"/>
-      <c r="AR2" s="306"/>
-      <c r="AS2" s="306"/>
-      <c r="AT2" s="305" t="s">
+      <c r="AQ2" s="311"/>
+      <c r="AR2" s="311"/>
+      <c r="AS2" s="311"/>
+      <c r="AT2" s="310" t="s">
         <v>226</v>
       </c>
-      <c r="AU2" s="306"/>
-      <c r="AV2" s="306"/>
-      <c r="AW2" s="306"/>
-      <c r="AX2" s="305" t="s">
+      <c r="AU2" s="311"/>
+      <c r="AV2" s="311"/>
+      <c r="AW2" s="311"/>
+      <c r="AX2" s="310" t="s">
         <v>227</v>
       </c>
-      <c r="AY2" s="306"/>
-      <c r="AZ2" s="306"/>
-      <c r="BA2" s="306"/>
+      <c r="AY2" s="311"/>
+      <c r="AZ2" s="311"/>
+      <c r="BA2" s="311"/>
     </row>
     <row r="3" spans="1:53" ht="45.75" customHeight="1">
-      <c r="A3" s="310"/>
-      <c r="B3" s="311"/>
+      <c r="A3" s="316"/>
+      <c r="B3" s="317"/>
       <c r="C3" s="76" t="s">
         <v>149</v>
       </c>
@@ -23416,7 +23696,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="44.45" customHeight="1">
+    <row r="4" spans="1:53" ht="44.4" customHeight="1">
       <c r="A4" s="78">
         <v>1</v>
       </c>
@@ -23521,7 +23801,7 @@
       <c r="AZ4" s="104"/>
       <c r="BA4" s="85"/>
     </row>
-    <row r="5" spans="1:53" ht="44.45" customHeight="1">
+    <row r="5" spans="1:53" ht="44.4" customHeight="1">
       <c r="A5" s="86">
         <v>2</v>
       </c>
@@ -23630,7 +23910,7 @@
       <c r="AZ5" s="104"/>
       <c r="BA5" s="85"/>
     </row>
-    <row r="6" spans="1:53" ht="44.45" customHeight="1">
+    <row r="6" spans="1:53" ht="44.4" customHeight="1">
       <c r="A6" s="86">
         <v>3</v>
       </c>
@@ -23858,7 +24138,7 @@
       <c r="AZ7" s="104"/>
       <c r="BA7" s="90"/>
     </row>
-    <row r="8" spans="1:53" ht="44.45" customHeight="1">
+    <row r="8" spans="1:53" ht="44.4" customHeight="1">
       <c r="A8" s="86">
         <v>5</v>
       </c>
@@ -24230,7 +24510,7 @@
       <c r="AZ11" s="104"/>
       <c r="BA11" s="114"/>
     </row>
-    <row r="12" spans="1:53" ht="44.45" customHeight="1">
+    <row r="12" spans="1:53" ht="44.4" customHeight="1">
       <c r="A12" s="139"/>
       <c r="B12" s="136" t="s">
         <v>156</v>
@@ -24362,7 +24642,7 @@
       <c r="AZ13" s="104"/>
       <c r="BA13" s="90"/>
     </row>
-    <row r="14" spans="1:53" ht="44.45" customHeight="1">
+    <row r="14" spans="1:53" ht="44.4" customHeight="1">
       <c r="A14" s="94">
         <v>8</v>
       </c>
@@ -24435,7 +24715,7 @@
       <c r="AZ14" s="104"/>
       <c r="BA14" s="90"/>
     </row>
-    <row r="15" spans="1:53" ht="44.45" customHeight="1">
+    <row r="15" spans="1:53" ht="44.4" customHeight="1">
       <c r="A15" s="94">
         <v>9</v>
       </c>
@@ -24498,7 +24778,7 @@
       <c r="AZ15" s="104"/>
       <c r="BA15" s="85"/>
     </row>
-    <row r="16" spans="1:53" ht="44.45" customHeight="1">
+    <row r="16" spans="1:53" ht="44.4" customHeight="1">
       <c r="A16" s="96">
         <v>10</v>
       </c>
@@ -24567,7 +24847,7 @@
       <c r="AZ16" s="104"/>
       <c r="BA16" s="85"/>
     </row>
-    <row r="17" spans="1:53" ht="44.45" customHeight="1">
+    <row r="17" spans="1:53" ht="44.4" customHeight="1">
       <c r="A17" s="121">
         <v>11</v>
       </c>
@@ -24914,7 +25194,7 @@
     <row r="28" spans="1:53" ht="28.5" customHeight="1"/>
     <row r="29" spans="1:53" ht="31.5" customHeight="1"/>
     <row r="30" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="31" spans="1:53" ht="32.450000000000003" customHeight="1"/>
+    <row r="31" spans="1:53" ht="32.4" customHeight="1"/>
     <row r="32" spans="1:53" ht="21" customHeight="1"/>
     <row r="33" ht="21" customHeight="1"/>
     <row r="34" ht="21" customHeight="1"/>
@@ -24924,27 +25204,17 @@
     <row r="38" ht="21" customHeight="1"/>
     <row r="39" ht="18" customHeight="1"/>
     <row r="40" ht="30.6" customHeight="1"/>
-    <row r="52" ht="30.95" customHeight="1"/>
-    <row r="64" ht="27.95" customHeight="1"/>
+    <row r="52" ht="30.9" customHeight="1"/>
+    <row r="64" ht="27.9" customHeight="1"/>
     <row r="76" ht="30" customHeight="1"/>
     <row r="88" ht="31.5" customHeight="1"/>
-    <row r="100" ht="27.95" customHeight="1"/>
+    <row r="100" ht="27.9" customHeight="1"/>
     <row r="112" ht="31.5" customHeight="1"/>
-    <row r="124" ht="32.450000000000003" customHeight="1"/>
-    <row r="136" ht="27.95" customHeight="1"/>
+    <row r="124" ht="32.4" customHeight="1"/>
+    <row r="136" ht="27.9" customHeight="1"/>
     <row r="137" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="K2:M2"/>
     <mergeCell ref="AT2:AW2"/>
     <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="Z2:AC2"/>
@@ -24952,6 +25222,16 @@
     <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AP2:AS2"/>
     <mergeCell ref="AL2:AO2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
@@ -24961,20 +25241,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65A7D1A-A130-4CF2-8F53-8DE497F18C35}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25">
+    <row r="1" spans="1:6" ht="22.8">
       <c r="A1" s="97" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="38.25">
+    <row r="3" spans="1:6" ht="39.6">
       <c r="A3" s="45" t="s">
         <v>164</v>
       </c>
@@ -25330,7 +25610,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="12.95" customHeight="1">
+    <row r="18" spans="1:6" ht="12.9" customHeight="1">
       <c r="A18" s="318" t="s">
         <v>3</v>
       </c>

--- a/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
+++ b/maintainance & expenditure/Maintanance Charge Collection Sheet_2025-26 up to may.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\developer\MaintApp\maintainance &amp; expenditure\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\deepshikha2\maintainance &amp; expenditure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E13494E-9ED8-412A-86F8-319BB186B64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C1C128-B4D7-4F2A-A789-CF52B1B96F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Details MC" sheetId="5" r:id="rId1"/>
@@ -1598,7 +1598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="321">
+  <cellXfs count="333">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2509,55 +2509,91 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="16" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="16" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2907,16 +2943,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51717A2D-38D8-4ABE-BD5F-98B6647922FB}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:K639"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="185" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" style="185" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" style="185" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" style="185" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" style="185" customWidth="1"/>
     <col min="4" max="4" width="20" style="185" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="184" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="184" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="184" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="184" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="184" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="183"/>
+    <col min="8" max="16384" width="8.83203125" style="183"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30">
@@ -2939,11 +2975,11 @@
       <c r="F2" s="303"/>
       <c r="G2" s="303"/>
     </row>
-    <row r="3" spans="1:7" ht="17.399999999999999">
+    <row r="3" spans="1:7" ht="18.75">
       <c r="F3" s="302"/>
       <c r="G3" s="302"/>
     </row>
-    <row r="4" spans="1:7" ht="24.6">
+    <row r="4" spans="1:7" ht="40.5">
       <c r="A4" s="301" t="s">
         <v>5</v>
       </c>
@@ -2956,7 +2992,7 @@
       </c>
       <c r="G4" s="297"/>
     </row>
-    <row r="5" spans="1:7" ht="20.399999999999999">
+    <row r="5" spans="1:7" ht="20.25">
       <c r="A5" s="295" t="s">
         <v>12</v>
       </c>
@@ -2979,7 +3015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="22.8" hidden="1">
+    <row r="6" spans="1:7" ht="23.25" hidden="1">
       <c r="A6" s="192">
         <v>1</v>
       </c>
@@ -3002,7 +3038,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="22.8" hidden="1">
+    <row r="7" spans="1:7" ht="23.25" hidden="1">
       <c r="A7" s="192">
         <v>2</v>
       </c>
@@ -3025,7 +3061,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="22.8" hidden="1">
+    <row r="8" spans="1:7" ht="23.25" hidden="1">
       <c r="A8" s="192">
         <v>3</v>
       </c>
@@ -3048,7 +3084,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="22.8" hidden="1">
+    <row r="9" spans="1:7" ht="23.25" hidden="1">
       <c r="A9" s="192">
         <v>4</v>
       </c>
@@ -3069,7 +3105,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="22.8" hidden="1">
+    <row r="10" spans="1:7" ht="23.25" hidden="1">
       <c r="A10" s="192">
         <v>5</v>
       </c>
@@ -3092,7 +3128,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="22.8" hidden="1">
+    <row r="11" spans="1:7" ht="23.25" hidden="1">
       <c r="A11" s="192">
         <v>6</v>
       </c>
@@ -3115,7 +3151,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="22.8" hidden="1">
+    <row r="12" spans="1:7" ht="23.25" hidden="1">
       <c r="A12" s="192">
         <v>7</v>
       </c>
@@ -3138,7 +3174,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="22.8" hidden="1">
+    <row r="13" spans="1:7" ht="23.25" hidden="1">
       <c r="A13" s="188">
         <v>8</v>
       </c>
@@ -3161,7 +3197,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="22.8" hidden="1">
+    <row r="14" spans="1:7" ht="23.25" hidden="1">
       <c r="A14" s="192">
         <v>9</v>
       </c>
@@ -3184,7 +3220,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="22.8" hidden="1">
+    <row r="15" spans="1:7" ht="23.25" hidden="1">
       <c r="A15" s="192">
         <v>11</v>
       </c>
@@ -3207,7 +3243,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="22.8" hidden="1">
+    <row r="16" spans="1:7" ht="23.25" hidden="1">
       <c r="A16" s="192">
         <v>12</v>
       </c>
@@ -3230,7 +3266,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="22.8" hidden="1">
+    <row r="17" spans="1:7" ht="23.25" hidden="1">
       <c r="A17" s="192">
         <v>13</v>
       </c>
@@ -3253,7 +3289,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="22.8" hidden="1">
+    <row r="18" spans="1:7" ht="23.25" hidden="1">
       <c r="A18" s="192">
         <v>15</v>
       </c>
@@ -3276,7 +3312,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="22.8" hidden="1">
+    <row r="19" spans="1:7" ht="23.25" hidden="1">
       <c r="A19" s="192">
         <v>16</v>
       </c>
@@ -3299,7 +3335,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="22.8" hidden="1">
+    <row r="20" spans="1:7" ht="23.25" hidden="1">
       <c r="A20" s="192">
         <v>17</v>
       </c>
@@ -3322,7 +3358,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="22.8" hidden="1">
+    <row r="21" spans="1:7" ht="23.25" hidden="1">
       <c r="A21" s="188">
         <v>20</v>
       </c>
@@ -3345,7 +3381,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="22.8" hidden="1">
+    <row r="22" spans="1:7" ht="23.25" hidden="1">
       <c r="A22" s="192">
         <v>21</v>
       </c>
@@ -3368,7 +3404,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="22.8" hidden="1">
+    <row r="23" spans="1:7" ht="23.25" hidden="1">
       <c r="A23" s="192">
         <v>22</v>
       </c>
@@ -3391,7 +3427,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="22.8" hidden="1">
+    <row r="24" spans="1:7" ht="23.25" hidden="1">
       <c r="A24" s="192">
         <v>23</v>
       </c>
@@ -3414,7 +3450,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="45.6" hidden="1">
+    <row r="25" spans="1:7" ht="46.5" hidden="1">
       <c r="A25" s="192">
         <v>24</v>
       </c>
@@ -3437,7 +3473,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="22.8" hidden="1">
+    <row r="26" spans="1:7" ht="23.25" hidden="1">
       <c r="A26" s="192">
         <v>25</v>
       </c>
@@ -3460,7 +3496,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="22.8" hidden="1">
+    <row r="27" spans="1:7" ht="23.25" hidden="1">
       <c r="A27" s="192">
         <v>27</v>
       </c>
@@ -3483,7 +3519,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="22.8" hidden="1">
+    <row r="28" spans="1:7" ht="23.25" hidden="1">
       <c r="A28" s="192">
         <v>28</v>
       </c>
@@ -3506,7 +3542,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="22.8" hidden="1">
+    <row r="29" spans="1:7" ht="23.25" hidden="1">
       <c r="A29" s="192">
         <v>29</v>
       </c>
@@ -3529,7 +3565,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="22.8" hidden="1">
+    <row r="30" spans="1:7" ht="23.25" hidden="1">
       <c r="A30" s="188">
         <v>30</v>
       </c>
@@ -3552,7 +3588,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="22.8" hidden="1">
+    <row r="31" spans="1:7" ht="23.25" hidden="1">
       <c r="A31" s="192">
         <v>31</v>
       </c>
@@ -3575,7 +3611,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="22.8" hidden="1">
+    <row r="32" spans="1:7" ht="23.25" hidden="1">
       <c r="A32" s="192">
         <v>33</v>
       </c>
@@ -3598,7 +3634,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="22.8" hidden="1">
+    <row r="33" spans="1:7" ht="23.25" hidden="1">
       <c r="A33" s="192">
         <v>34</v>
       </c>
@@ -3621,7 +3657,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="22.8" hidden="1">
+    <row r="34" spans="1:7" ht="23.25" hidden="1">
       <c r="A34" s="192">
         <v>35</v>
       </c>
@@ -3644,7 +3680,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="22.8" hidden="1">
+    <row r="35" spans="1:7" ht="23.25" hidden="1">
       <c r="A35" s="192">
         <v>36</v>
       </c>
@@ -3667,7 +3703,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="22.8" hidden="1">
+    <row r="36" spans="1:7" ht="23.25" hidden="1">
       <c r="A36" s="192">
         <v>37</v>
       </c>
@@ -3690,7 +3726,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="22.8" hidden="1">
+    <row r="37" spans="1:7" ht="23.25" hidden="1">
       <c r="A37" s="192">
         <v>38</v>
       </c>
@@ -3713,7 +3749,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="22.8" hidden="1">
+    <row r="38" spans="1:7" ht="23.25" hidden="1">
       <c r="A38" s="192">
         <v>39</v>
       </c>
@@ -3736,7 +3772,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="22.8" hidden="1">
+    <row r="39" spans="1:7" ht="23.25" hidden="1">
       <c r="A39" s="188">
         <v>40</v>
       </c>
@@ -3759,7 +3795,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="22.8" hidden="1">
+    <row r="40" spans="1:7" ht="23.25" hidden="1">
       <c r="A40" s="192">
         <v>42</v>
       </c>
@@ -3782,7 +3818,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="22.8" hidden="1">
+    <row r="41" spans="1:7" ht="23.25" hidden="1">
       <c r="A41" s="192">
         <v>46</v>
       </c>
@@ -3805,7 +3841,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="22.8" hidden="1">
+    <row r="42" spans="1:7" ht="23.25" hidden="1">
       <c r="A42" s="192">
         <v>47</v>
       </c>
@@ -3828,7 +3864,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="22.8" hidden="1">
+    <row r="43" spans="1:7" ht="23.25" hidden="1">
       <c r="A43" s="192">
         <v>50</v>
       </c>
@@ -3851,7 +3887,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="22.8" hidden="1">
+    <row r="44" spans="1:7" ht="23.25" hidden="1">
       <c r="A44" s="192">
         <v>51</v>
       </c>
@@ -3874,7 +3910,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="22.8" hidden="1">
+    <row r="45" spans="1:7" ht="23.25" hidden="1">
       <c r="A45" s="192">
         <v>52</v>
       </c>
@@ -3897,7 +3933,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="22.8" hidden="1">
+    <row r="46" spans="1:7" ht="23.25" hidden="1">
       <c r="A46" s="192">
         <v>58</v>
       </c>
@@ -3920,7 +3956,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="22.8" hidden="1">
+    <row r="47" spans="1:7" ht="23.25" hidden="1">
       <c r="A47" s="188">
         <v>59</v>
       </c>
@@ -3943,7 +3979,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="22.8" hidden="1">
+    <row r="48" spans="1:7" ht="23.25" hidden="1">
       <c r="A48" s="192">
         <v>60</v>
       </c>
@@ -3966,7 +4002,7 @@
         <v>45792</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="22.8" hidden="1">
+    <row r="49" spans="1:7" ht="23.25" hidden="1">
       <c r="A49" s="192">
         <v>1</v>
       </c>
@@ -3989,7 +4025,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="22.8" hidden="1">
+    <row r="50" spans="1:7" ht="23.25" hidden="1">
       <c r="A50" s="192">
         <v>2</v>
       </c>
@@ -4012,7 +4048,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="22.8" hidden="1">
+    <row r="51" spans="1:7" ht="23.25" hidden="1">
       <c r="A51" s="192">
         <v>3</v>
       </c>
@@ -4035,7 +4071,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="22.8" hidden="1">
+    <row r="52" spans="1:7" ht="23.25" hidden="1">
       <c r="A52" s="192">
         <v>4</v>
       </c>
@@ -4056,7 +4092,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="22.8" hidden="1">
+    <row r="53" spans="1:7" ht="23.25" hidden="1">
       <c r="A53" s="192">
         <v>5</v>
       </c>
@@ -4079,7 +4115,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="22.8" hidden="1">
+    <row r="54" spans="1:7" ht="23.25" hidden="1">
       <c r="A54" s="192">
         <v>6</v>
       </c>
@@ -4102,7 +4138,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="22.8" hidden="1">
+    <row r="55" spans="1:7" ht="23.25" hidden="1">
       <c r="A55" s="192">
         <v>7</v>
       </c>
@@ -4125,7 +4161,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="22.8" hidden="1">
+    <row r="56" spans="1:7" ht="23.25" hidden="1">
       <c r="A56" s="188">
         <v>8</v>
       </c>
@@ -4148,7 +4184,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="22.8" hidden="1">
+    <row r="57" spans="1:7" ht="23.25" hidden="1">
       <c r="A57" s="192">
         <v>9</v>
       </c>
@@ -4171,7 +4207,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="22.8" hidden="1">
+    <row r="58" spans="1:7" ht="23.25" hidden="1">
       <c r="A58" s="192">
         <v>11</v>
       </c>
@@ -4194,7 +4230,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="22.8" hidden="1">
+    <row r="59" spans="1:7" ht="23.25" hidden="1">
       <c r="A59" s="192">
         <v>12</v>
       </c>
@@ -4217,7 +4253,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="22.8" hidden="1">
+    <row r="60" spans="1:7" ht="23.25" hidden="1">
       <c r="A60" s="192">
         <v>13</v>
       </c>
@@ -4240,7 +4276,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="22.8" hidden="1">
+    <row r="61" spans="1:7" ht="23.25" hidden="1">
       <c r="A61" s="192">
         <v>15</v>
       </c>
@@ -4263,7 +4299,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="22.8" hidden="1">
+    <row r="62" spans="1:7" ht="23.25" hidden="1">
       <c r="A62" s="192">
         <v>16</v>
       </c>
@@ -4286,7 +4322,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="22.8" hidden="1">
+    <row r="63" spans="1:7" ht="23.25" hidden="1">
       <c r="A63" s="192">
         <v>17</v>
       </c>
@@ -4309,7 +4345,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="22.8" hidden="1">
+    <row r="64" spans="1:7" ht="23.25" hidden="1">
       <c r="A64" s="192">
         <v>20</v>
       </c>
@@ -4332,7 +4368,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="22.8" hidden="1">
+    <row r="65" spans="1:7" ht="23.25" hidden="1">
       <c r="A65" s="188">
         <v>21</v>
       </c>
@@ -4355,7 +4391,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="22.8" hidden="1">
+    <row r="66" spans="1:7" ht="23.25" hidden="1">
       <c r="A66" s="192">
         <v>22</v>
       </c>
@@ -4378,7 +4414,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="22.8" hidden="1">
+    <row r="67" spans="1:7" ht="23.25" hidden="1">
       <c r="A67" s="192">
         <v>23</v>
       </c>
@@ -4401,7 +4437,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="45.6" hidden="1">
+    <row r="68" spans="1:7" ht="46.5" hidden="1">
       <c r="A68" s="192">
         <v>24</v>
       </c>
@@ -4424,7 +4460,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="22.8" hidden="1">
+    <row r="69" spans="1:7" ht="23.25" hidden="1">
       <c r="A69" s="192">
         <v>25</v>
       </c>
@@ -4447,7 +4483,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="22.8" hidden="1">
+    <row r="70" spans="1:7" ht="23.25" hidden="1">
       <c r="A70" s="192">
         <v>27</v>
       </c>
@@ -4470,7 +4506,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="22.8" hidden="1">
+    <row r="71" spans="1:7" ht="23.25" hidden="1">
       <c r="A71" s="192">
         <v>28</v>
       </c>
@@ -4493,7 +4529,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="22.8" hidden="1">
+    <row r="72" spans="1:7" ht="23.25" hidden="1">
       <c r="A72" s="192">
         <v>29</v>
       </c>
@@ -4516,7 +4552,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="22.8" hidden="1">
+    <row r="73" spans="1:7" ht="23.25" hidden="1">
       <c r="A73" s="192">
         <v>30</v>
       </c>
@@ -4539,7 +4575,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="22.8" hidden="1">
+    <row r="74" spans="1:7" ht="23.25" hidden="1">
       <c r="A74" s="217">
         <v>31</v>
       </c>
@@ -4562,7 +4598,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="22.8" hidden="1">
+    <row r="75" spans="1:7" ht="23.25" hidden="1">
       <c r="A75" s="192">
         <v>33</v>
       </c>
@@ -4585,7 +4621,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="22.8" hidden="1">
+    <row r="76" spans="1:7" ht="23.25" hidden="1">
       <c r="A76" s="217">
         <v>34</v>
       </c>
@@ -4608,7 +4644,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="22.8" hidden="1">
+    <row r="77" spans="1:7" ht="23.25" hidden="1">
       <c r="A77" s="217">
         <v>35</v>
       </c>
@@ -4631,7 +4667,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="22.8" hidden="1">
+    <row r="78" spans="1:7" ht="23.25" hidden="1">
       <c r="A78" s="208">
         <v>36</v>
       </c>
@@ -4654,7 +4690,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="22.8" hidden="1">
+    <row r="79" spans="1:7" ht="23.25" hidden="1">
       <c r="A79" s="285">
         <v>37</v>
       </c>
@@ -4677,7 +4713,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="22.8" hidden="1">
+    <row r="80" spans="1:7" ht="23.25" hidden="1">
       <c r="A80" s="285">
         <v>38</v>
       </c>
@@ -4700,7 +4736,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="22.8" hidden="1">
+    <row r="81" spans="1:11" ht="23.25" hidden="1">
       <c r="A81" s="283">
         <v>39</v>
       </c>
@@ -4723,7 +4759,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="22.8" hidden="1">
+    <row r="82" spans="1:11" ht="23.25" hidden="1">
       <c r="A82" s="192">
         <v>40</v>
       </c>
@@ -4746,7 +4782,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="22.8" hidden="1">
+    <row r="83" spans="1:11" ht="23.25" hidden="1">
       <c r="A83" s="192">
         <v>42</v>
       </c>
@@ -4769,7 +4805,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="22.8" hidden="1">
+    <row r="84" spans="1:11" ht="23.25" hidden="1">
       <c r="A84" s="192">
         <v>46</v>
       </c>
@@ -4792,7 +4828,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="22.8" hidden="1">
+    <row r="85" spans="1:11" ht="23.25" hidden="1">
       <c r="A85" s="192">
         <v>47</v>
       </c>
@@ -4815,7 +4851,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="22.8" hidden="1">
+    <row r="86" spans="1:11" ht="23.25" hidden="1">
       <c r="A86" s="192">
         <v>50</v>
       </c>
@@ -4838,7 +4874,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="22.8" hidden="1">
+    <row r="87" spans="1:11" ht="23.25" hidden="1">
       <c r="A87" s="192">
         <v>51</v>
       </c>
@@ -4861,7 +4897,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="22.8" hidden="1">
+    <row r="88" spans="1:11" ht="23.25" hidden="1">
       <c r="A88" s="192">
         <v>52</v>
       </c>
@@ -4884,7 +4920,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="22.8" hidden="1">
+    <row r="89" spans="1:11" ht="23.25" hidden="1">
       <c r="A89" s="192">
         <v>58</v>
       </c>
@@ -4907,7 +4943,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="22.8" hidden="1">
+    <row r="90" spans="1:11" ht="23.25" hidden="1">
       <c r="A90" s="188">
         <v>59</v>
       </c>
@@ -4930,7 +4966,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="22.8" hidden="1">
+    <row r="91" spans="1:11" ht="23.25" hidden="1">
       <c r="A91" s="192">
         <v>60</v>
       </c>
@@ -4953,7 +4989,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="22.8">
+    <row r="92" spans="1:11" ht="23.25">
       <c r="A92" s="192">
         <v>1</v>
       </c>
@@ -4982,7 +5018,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="22.8">
+    <row r="93" spans="1:11" ht="23.25">
       <c r="A93" s="192">
         <v>2</v>
       </c>
@@ -5011,7 +5047,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="22.8">
+    <row r="94" spans="1:11" ht="23.25">
       <c r="A94" s="192">
         <v>3</v>
       </c>
@@ -5040,7 +5076,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="22.8">
+    <row r="95" spans="1:11" ht="23.25">
       <c r="A95" s="192">
         <v>4</v>
       </c>
@@ -5067,7 +5103,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="22.8">
+    <row r="96" spans="1:11" ht="23.25">
       <c r="A96" s="192">
         <v>5</v>
       </c>
@@ -5096,7 +5132,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="22.8">
+    <row r="97" spans="1:11" ht="23.25">
       <c r="A97" s="192">
         <v>6</v>
       </c>
@@ -5125,7 +5161,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="22.8">
+    <row r="98" spans="1:11" ht="23.25">
       <c r="A98" s="188">
         <v>7</v>
       </c>
@@ -5154,7 +5190,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="22.8">
+    <row r="99" spans="1:11" ht="23.25">
       <c r="A99" s="192">
         <v>8</v>
       </c>
@@ -5183,7 +5219,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="22.8">
+    <row r="100" spans="1:11" ht="23.25">
       <c r="A100" s="192">
         <v>9</v>
       </c>
@@ -5212,7 +5248,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="22.8">
+    <row r="101" spans="1:11" ht="23.25">
       <c r="A101" s="192">
         <v>11</v>
       </c>
@@ -5241,7 +5277,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="22.8">
+    <row r="102" spans="1:11" ht="23.25">
       <c r="A102" s="192">
         <v>12</v>
       </c>
@@ -5270,7 +5306,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="22.8">
+    <row r="103" spans="1:11" ht="23.25">
       <c r="A103" s="192">
         <v>13</v>
       </c>
@@ -5299,7 +5335,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="22.8">
+    <row r="104" spans="1:11" ht="23.25">
       <c r="A104" s="192">
         <v>15</v>
       </c>
@@ -5328,7 +5364,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="22.8">
+    <row r="105" spans="1:11" ht="23.25">
       <c r="A105" s="192">
         <v>16</v>
       </c>
@@ -5357,7 +5393,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="22.8">
+    <row r="106" spans="1:11" ht="23.25">
       <c r="A106" s="192">
         <v>17</v>
       </c>
@@ -5386,7 +5422,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="22.8">
+    <row r="107" spans="1:11" ht="23.25">
       <c r="A107" s="188">
         <v>20</v>
       </c>
@@ -5415,7 +5451,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="22.8">
+    <row r="108" spans="1:11" ht="23.25">
       <c r="A108" s="192">
         <v>21</v>
       </c>
@@ -5444,7 +5480,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="22.8">
+    <row r="109" spans="1:11" ht="23.25">
       <c r="A109" s="192">
         <v>22</v>
       </c>
@@ -5473,7 +5509,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="22.8">
+    <row r="110" spans="1:11" ht="23.25">
       <c r="A110" s="192">
         <v>23</v>
       </c>
@@ -5502,7 +5538,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="45.6">
+    <row r="111" spans="1:11" ht="46.5">
       <c r="A111" s="192">
         <v>24</v>
       </c>
@@ -5531,7 +5567,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="22.8">
+    <row r="112" spans="1:11" ht="23.25">
       <c r="A112" s="192">
         <v>25</v>
       </c>
@@ -5560,7 +5596,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="22.8">
+    <row r="113" spans="1:11" ht="23.25">
       <c r="A113" s="192">
         <v>27</v>
       </c>
@@ -5589,7 +5625,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="22.8">
+    <row r="114" spans="1:11" ht="23.25">
       <c r="A114" s="192">
         <v>28</v>
       </c>
@@ -5618,7 +5654,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="22.8">
+    <row r="115" spans="1:11" ht="23.25">
       <c r="A115" s="192">
         <v>29</v>
       </c>
@@ -5647,7 +5683,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="22.8">
+    <row r="116" spans="1:11" ht="23.25">
       <c r="A116" s="188">
         <v>30</v>
       </c>
@@ -5676,7 +5712,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="22.8">
+    <row r="117" spans="1:11" ht="23.25">
       <c r="A117" s="192">
         <v>31</v>
       </c>
@@ -5705,7 +5741,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="22.8">
+    <row r="118" spans="1:11" ht="23.25">
       <c r="A118" s="192">
         <v>33</v>
       </c>
@@ -5734,7 +5770,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="22.8">
+    <row r="119" spans="1:11" ht="23.25">
       <c r="A119" s="192">
         <v>34</v>
       </c>
@@ -5763,7 +5799,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="22.8">
+    <row r="120" spans="1:11" ht="23.25">
       <c r="A120" s="192">
         <v>35</v>
       </c>
@@ -5792,7 +5828,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="22.8">
+    <row r="121" spans="1:11" ht="23.25">
       <c r="A121" s="192">
         <v>36</v>
       </c>
@@ -5821,7 +5857,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="22.8">
+    <row r="122" spans="1:11" ht="23.25">
       <c r="A122" s="192">
         <v>37</v>
       </c>
@@ -5850,7 +5886,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="22.8">
+    <row r="123" spans="1:11" ht="23.25">
       <c r="A123" s="192">
         <v>38</v>
       </c>
@@ -5879,7 +5915,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="22.8">
+    <row r="124" spans="1:11" ht="23.25">
       <c r="A124" s="188">
         <v>39</v>
       </c>
@@ -5908,7 +5944,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="22.8">
+    <row r="125" spans="1:11" ht="23.25">
       <c r="A125" s="192">
         <v>40</v>
       </c>
@@ -5937,7 +5973,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="22.8">
+    <row r="126" spans="1:11" ht="23.25">
       <c r="A126" s="192">
         <v>42</v>
       </c>
@@ -5966,7 +6002,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="22.8" hidden="1">
+    <row r="127" spans="1:11" ht="23.25" hidden="1">
       <c r="A127" s="192">
         <v>46</v>
       </c>
@@ -5995,7 +6031,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="22.8">
+    <row r="128" spans="1:11" ht="23.25">
       <c r="A128" s="192">
         <v>47</v>
       </c>
@@ -6024,7 +6060,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="22.8">
+    <row r="129" spans="1:11" ht="23.25">
       <c r="A129" s="192">
         <v>50</v>
       </c>
@@ -6053,7 +6089,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="22.8">
+    <row r="130" spans="1:11" ht="23.25">
       <c r="A130" s="192">
         <v>51</v>
       </c>
@@ -6082,7 +6118,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="22.8">
+    <row r="131" spans="1:11" ht="23.25">
       <c r="A131" s="192">
         <v>52</v>
       </c>
@@ -6111,7 +6147,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="22.8" hidden="1">
+    <row r="132" spans="1:11" ht="23.25" hidden="1">
       <c r="A132" s="192">
         <v>58</v>
       </c>
@@ -6138,7 +6174,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="22.8" hidden="1">
+    <row r="133" spans="1:11" ht="23.25" hidden="1">
       <c r="A133" s="188">
         <v>59</v>
       </c>
@@ -6165,7 +6201,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="22.8" hidden="1">
+    <row r="134" spans="1:11" ht="23.25" hidden="1">
       <c r="A134" s="192">
         <v>60</v>
       </c>
@@ -6186,7 +6222,7 @@
       </c>
       <c r="G134" s="277"/>
     </row>
-    <row r="135" spans="1:11" ht="22.8" hidden="1">
+    <row r="135" spans="1:11" ht="23.25" hidden="1">
       <c r="A135" s="192">
         <v>1</v>
       </c>
@@ -6209,7 +6245,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="22.8" hidden="1">
+    <row r="136" spans="1:11" ht="23.25" hidden="1">
       <c r="A136" s="192">
         <v>2</v>
       </c>
@@ -6232,7 +6268,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="22.8" hidden="1">
+    <row r="137" spans="1:11" ht="23.25" hidden="1">
       <c r="A137" s="192">
         <v>3</v>
       </c>
@@ -6255,7 +6291,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="22.8" hidden="1">
+    <row r="138" spans="1:11" ht="23.25" hidden="1">
       <c r="A138" s="192">
         <v>4</v>
       </c>
@@ -6277,7 +6313,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="22.8" hidden="1">
+    <row r="139" spans="1:11" ht="23.25" hidden="1">
       <c r="A139" s="192">
         <v>5</v>
       </c>
@@ -6300,7 +6336,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="22.8" hidden="1">
+    <row r="140" spans="1:11" ht="23.25" hidden="1">
       <c r="A140" s="192">
         <v>6</v>
       </c>
@@ -6323,7 +6359,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="22.8" hidden="1">
+    <row r="141" spans="1:11" ht="23.25" hidden="1">
       <c r="A141" s="192">
         <v>7</v>
       </c>
@@ -6346,7 +6382,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="22.8" hidden="1">
+    <row r="142" spans="1:11" ht="23.25" hidden="1">
       <c r="A142" s="188">
         <v>8</v>
       </c>
@@ -6369,7 +6405,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="22.8" hidden="1">
+    <row r="143" spans="1:11" ht="23.25" hidden="1">
       <c r="A143" s="192">
         <v>9</v>
       </c>
@@ -6392,7 +6428,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="22.8" hidden="1">
+    <row r="144" spans="1:11" ht="23.25" hidden="1">
       <c r="A144" s="192">
         <v>11</v>
       </c>
@@ -6415,7 +6451,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="22.8" hidden="1">
+    <row r="145" spans="1:7" ht="23.25" hidden="1">
       <c r="A145" s="192">
         <v>12</v>
       </c>
@@ -6438,7 +6474,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="22.8" hidden="1">
+    <row r="146" spans="1:7" ht="23.25" hidden="1">
       <c r="A146" s="192">
         <v>13</v>
       </c>
@@ -6461,7 +6497,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="22.8" hidden="1">
+    <row r="147" spans="1:7" ht="23.25" hidden="1">
       <c r="A147" s="192">
         <v>15</v>
       </c>
@@ -6484,7 +6520,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="22.8" hidden="1">
+    <row r="148" spans="1:7" ht="23.25" hidden="1">
       <c r="A148" s="192">
         <v>16</v>
       </c>
@@ -6507,7 +6543,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="22.8" hidden="1">
+    <row r="149" spans="1:7" ht="23.25" hidden="1">
       <c r="A149" s="192">
         <v>17</v>
       </c>
@@ -6530,7 +6566,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="22.8" hidden="1">
+    <row r="150" spans="1:7" ht="23.25" hidden="1">
       <c r="A150" s="192">
         <v>20</v>
       </c>
@@ -6553,7 +6589,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="22.8" hidden="1">
+    <row r="151" spans="1:7" ht="23.25" hidden="1">
       <c r="A151" s="217">
         <v>21</v>
       </c>
@@ -6576,7 +6612,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="22.8" hidden="1">
+    <row r="152" spans="1:7" ht="23.25" hidden="1">
       <c r="A152" s="192">
         <v>22</v>
       </c>
@@ -6599,7 +6635,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="22.8" hidden="1">
+    <row r="153" spans="1:7" ht="23.25" hidden="1">
       <c r="A153" s="217">
         <v>23</v>
       </c>
@@ -6622,7 +6658,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="45.6" hidden="1">
+    <row r="154" spans="1:7" ht="46.5" hidden="1">
       <c r="A154" s="217">
         <v>24</v>
       </c>
@@ -6645,7 +6681,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="22.8" hidden="1">
+    <row r="155" spans="1:7" ht="23.25" hidden="1">
       <c r="A155" s="208">
         <v>25</v>
       </c>
@@ -6668,7 +6704,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="22.8" hidden="1">
+    <row r="156" spans="1:7" ht="23.25" hidden="1">
       <c r="A156" s="192">
         <v>27</v>
       </c>
@@ -6691,7 +6727,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="22.8" hidden="1">
+    <row r="157" spans="1:7" ht="23.25" hidden="1">
       <c r="A157" s="192">
         <v>28</v>
       </c>
@@ -6714,7 +6750,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="22.8" hidden="1">
+    <row r="158" spans="1:7" ht="23.25" hidden="1">
       <c r="A158" s="192">
         <v>29</v>
       </c>
@@ -6737,7 +6773,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="22.8" hidden="1">
+    <row r="159" spans="1:7" ht="23.25" hidden="1">
       <c r="A159" s="192">
         <v>30</v>
       </c>
@@ -6760,7 +6796,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="22.8" hidden="1">
+    <row r="160" spans="1:7" ht="23.25" hidden="1">
       <c r="A160" s="192">
         <v>31</v>
       </c>
@@ -6783,7 +6819,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="22.8" hidden="1">
+    <row r="161" spans="1:7" ht="23.25" hidden="1">
       <c r="A161" s="192">
         <v>33</v>
       </c>
@@ -6806,7 +6842,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="22.8" hidden="1">
+    <row r="162" spans="1:7" ht="23.25" hidden="1">
       <c r="A162" s="192">
         <v>34</v>
       </c>
@@ -6829,7 +6865,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="22.8" hidden="1">
+    <row r="163" spans="1:7" ht="23.25" hidden="1">
       <c r="A163" s="192">
         <v>35</v>
       </c>
@@ -6852,7 +6888,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="22.8" hidden="1">
+    <row r="164" spans="1:7" ht="23.25" hidden="1">
       <c r="A164" s="188">
         <v>36</v>
       </c>
@@ -6875,7 +6911,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="22.8" hidden="1">
+    <row r="165" spans="1:7" ht="23.25" hidden="1">
       <c r="A165" s="192">
         <v>37</v>
       </c>
@@ -6898,7 +6934,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="22.8" hidden="1">
+    <row r="166" spans="1:7" ht="23.25" hidden="1">
       <c r="A166" s="192">
         <v>38</v>
       </c>
@@ -6921,7 +6957,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="22.8" hidden="1">
+    <row r="167" spans="1:7" ht="23.25" hidden="1">
       <c r="A167" s="192">
         <v>39</v>
       </c>
@@ -6944,7 +6980,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="22.8" hidden="1">
+    <row r="168" spans="1:7" ht="23.25" hidden="1">
       <c r="A168" s="192">
         <v>40</v>
       </c>
@@ -6967,7 +7003,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="22.8" hidden="1">
+    <row r="169" spans="1:7" ht="23.25" hidden="1">
       <c r="A169" s="192">
         <v>42</v>
       </c>
@@ -6990,7 +7026,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="22.8" hidden="1">
+    <row r="170" spans="1:7" ht="23.25" hidden="1">
       <c r="A170" s="192">
         <v>46</v>
       </c>
@@ -7013,7 +7049,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="22.8" hidden="1">
+    <row r="171" spans="1:7" ht="23.25" hidden="1">
       <c r="A171" s="192">
         <v>47</v>
       </c>
@@ -7036,7 +7072,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="22.8" hidden="1">
+    <row r="172" spans="1:7" ht="23.25" hidden="1">
       <c r="A172" s="188">
         <v>50</v>
       </c>
@@ -7059,7 +7095,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="22.8" hidden="1">
+    <row r="173" spans="1:7" ht="23.25" hidden="1">
       <c r="A173" s="192">
         <v>51</v>
       </c>
@@ -7082,7 +7118,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="22.8" hidden="1">
+    <row r="174" spans="1:7" ht="23.25" hidden="1">
       <c r="A174" s="192">
         <v>52</v>
       </c>
@@ -7105,7 +7141,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="22.8" hidden="1">
+    <row r="175" spans="1:7" ht="23.25" hidden="1">
       <c r="A175" s="192">
         <v>58</v>
       </c>
@@ -7128,7 +7164,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="22.8" hidden="1">
+    <row r="176" spans="1:7" ht="23.25" hidden="1">
       <c r="A176" s="192">
         <v>59</v>
       </c>
@@ -7151,7 +7187,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="22.8" hidden="1">
+    <row r="177" spans="1:7" ht="23.25" hidden="1">
       <c r="A177" s="192">
         <v>60</v>
       </c>
@@ -7174,7 +7210,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="22.8" hidden="1">
+    <row r="178" spans="1:7" ht="23.25" hidden="1">
       <c r="A178" s="192">
         <v>1</v>
       </c>
@@ -7197,7 +7233,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="22.8" hidden="1">
+    <row r="179" spans="1:7" ht="23.25" hidden="1">
       <c r="A179" s="192">
         <v>2</v>
       </c>
@@ -7220,7 +7256,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="22.8" hidden="1">
+    <row r="180" spans="1:7" ht="23.25" hidden="1">
       <c r="A180" s="192">
         <v>3</v>
       </c>
@@ -7243,7 +7279,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="22.8" hidden="1">
+    <row r="181" spans="1:7" ht="23.25" hidden="1">
       <c r="A181" s="188">
         <v>4</v>
       </c>
@@ -7264,7 +7300,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="22.8" hidden="1">
+    <row r="182" spans="1:7" ht="23.25" hidden="1">
       <c r="A182" s="192">
         <v>5</v>
       </c>
@@ -7287,7 +7323,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="22.8" hidden="1">
+    <row r="183" spans="1:7" ht="23.25" hidden="1">
       <c r="A183" s="192">
         <v>6</v>
       </c>
@@ -7310,7 +7346,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="22.8" hidden="1">
+    <row r="184" spans="1:7" ht="23.25" hidden="1">
       <c r="A184" s="192">
         <v>7</v>
       </c>
@@ -7333,7 +7369,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="22.8" hidden="1">
+    <row r="185" spans="1:7" ht="23.25" hidden="1">
       <c r="A185" s="192">
         <v>8</v>
       </c>
@@ -7356,7 +7392,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="22.8" hidden="1">
+    <row r="186" spans="1:7" ht="23.25" hidden="1">
       <c r="A186" s="192">
         <v>9</v>
       </c>
@@ -7379,7 +7415,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="22.8" hidden="1">
+    <row r="187" spans="1:7" ht="23.25" hidden="1">
       <c r="A187" s="192">
         <v>11</v>
       </c>
@@ -7402,7 +7438,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="22.8" hidden="1">
+    <row r="188" spans="1:7" ht="23.25" hidden="1">
       <c r="A188" s="192">
         <v>12</v>
       </c>
@@ -7425,7 +7461,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="22.8" hidden="1">
+    <row r="189" spans="1:7" ht="23.25" hidden="1">
       <c r="A189" s="192">
         <v>13</v>
       </c>
@@ -7448,7 +7484,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="22.8" hidden="1">
+    <row r="190" spans="1:7" ht="23.25" hidden="1">
       <c r="A190" s="188">
         <v>15</v>
       </c>
@@ -7471,7 +7507,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="22.8" hidden="1">
+    <row r="191" spans="1:7" ht="23.25" hidden="1">
       <c r="A191" s="192">
         <v>16</v>
       </c>
@@ -7494,7 +7530,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="22.8" hidden="1">
+    <row r="192" spans="1:7" ht="23.25" hidden="1">
       <c r="A192" s="192">
         <v>17</v>
       </c>
@@ -7517,7 +7553,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="22.8" hidden="1">
+    <row r="193" spans="1:7" ht="23.25" hidden="1">
       <c r="A193" s="192">
         <v>20</v>
       </c>
@@ -7540,7 +7576,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="22.8" hidden="1">
+    <row r="194" spans="1:7" ht="23.25" hidden="1">
       <c r="A194" s="192">
         <v>21</v>
       </c>
@@ -7563,7 +7599,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="22.8" hidden="1">
+    <row r="195" spans="1:7" ht="23.25" hidden="1">
       <c r="A195" s="192">
         <v>22</v>
       </c>
@@ -7586,7 +7622,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="22.8" hidden="1">
+    <row r="196" spans="1:7" ht="23.25" hidden="1">
       <c r="A196" s="192">
         <v>23</v>
       </c>
@@ -7609,7 +7645,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="45.6" hidden="1">
+    <row r="197" spans="1:7" ht="46.5" hidden="1">
       <c r="A197" s="192">
         <v>24</v>
       </c>
@@ -7632,7 +7668,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="22.8" hidden="1">
+    <row r="198" spans="1:7" ht="23.25" hidden="1">
       <c r="A198" s="188">
         <v>25</v>
       </c>
@@ -7655,7 +7691,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="22.8" hidden="1">
+    <row r="199" spans="1:7" ht="23.25" hidden="1">
       <c r="A199" s="192">
         <v>27</v>
       </c>
@@ -7678,7 +7714,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="22.8" hidden="1">
+    <row r="200" spans="1:7" ht="23.25" hidden="1">
       <c r="A200" s="192">
         <v>28</v>
       </c>
@@ -7701,7 +7737,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="22.8" hidden="1">
+    <row r="201" spans="1:7" ht="23.25" hidden="1">
       <c r="A201" s="192">
         <v>29</v>
       </c>
@@ -7724,7 +7760,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="22.8" hidden="1">
+    <row r="202" spans="1:7" ht="23.25" hidden="1">
       <c r="A202" s="192">
         <v>30</v>
       </c>
@@ -7747,7 +7783,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="22.8" hidden="1">
+    <row r="203" spans="1:7" ht="23.25" hidden="1">
       <c r="A203" s="192">
         <v>31</v>
       </c>
@@ -7770,7 +7806,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="22.8" hidden="1">
+    <row r="204" spans="1:7" ht="23.25" hidden="1">
       <c r="A204" s="203">
         <v>32</v>
       </c>
@@ -7791,7 +7827,7 @@
       </c>
       <c r="G204" s="275"/>
     </row>
-    <row r="205" spans="1:7" ht="22.8" hidden="1">
+    <row r="205" spans="1:7" ht="23.25" hidden="1">
       <c r="A205" s="192">
         <v>33</v>
       </c>
@@ -7814,7 +7850,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="22.8" hidden="1">
+    <row r="206" spans="1:7" ht="23.25" hidden="1">
       <c r="A206" s="192">
         <v>34</v>
       </c>
@@ -7837,7 +7873,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="22.8" hidden="1">
+    <row r="207" spans="1:7" ht="23.25" hidden="1">
       <c r="A207" s="188">
         <v>35</v>
       </c>
@@ -7860,7 +7896,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="22.8" hidden="1">
+    <row r="208" spans="1:7" ht="23.25" hidden="1">
       <c r="A208" s="192">
         <v>36</v>
       </c>
@@ -7883,7 +7919,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="22.8" hidden="1">
+    <row r="209" spans="1:7" ht="23.25" hidden="1">
       <c r="A209" s="192">
         <v>37</v>
       </c>
@@ -7906,7 +7942,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="22.8" hidden="1">
+    <row r="210" spans="1:7" ht="23.25" hidden="1">
       <c r="A210" s="192">
         <v>38</v>
       </c>
@@ -7929,7 +7965,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="22.8" hidden="1">
+    <row r="211" spans="1:7" ht="23.25" hidden="1">
       <c r="A211" s="192">
         <v>39</v>
       </c>
@@ -7952,7 +7988,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="22.8" hidden="1">
+    <row r="212" spans="1:7" ht="23.25" hidden="1">
       <c r="A212" s="192">
         <v>40</v>
       </c>
@@ -7975,7 +8011,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="22.8" hidden="1">
+    <row r="213" spans="1:7" ht="23.25" hidden="1">
       <c r="A213" s="192">
         <v>42</v>
       </c>
@@ -7998,7 +8034,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="22.8" hidden="1">
+    <row r="214" spans="1:7" ht="23.25" hidden="1">
       <c r="A214" s="203">
         <v>43</v>
       </c>
@@ -8021,7 +8057,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="22.8" hidden="1">
+    <row r="215" spans="1:7" ht="23.25" hidden="1">
       <c r="A215" s="203">
         <v>44</v>
       </c>
@@ -8044,7 +8080,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="22.8" hidden="1">
+    <row r="216" spans="1:7" ht="23.25" hidden="1">
       <c r="A216" s="188">
         <v>46</v>
       </c>
@@ -8067,7 +8103,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="22.8" hidden="1">
+    <row r="217" spans="1:7" ht="23.25" hidden="1">
       <c r="A217" s="192">
         <v>47</v>
       </c>
@@ -8090,7 +8126,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="22.8" hidden="1">
+    <row r="218" spans="1:7" ht="23.25" hidden="1">
       <c r="A218" s="192">
         <v>50</v>
       </c>
@@ -8113,7 +8149,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="22.8" hidden="1">
+    <row r="219" spans="1:7" ht="23.25" hidden="1">
       <c r="A219" s="192">
         <v>51</v>
       </c>
@@ -8136,7 +8172,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="22.8" hidden="1">
+    <row r="220" spans="1:7" ht="23.25" hidden="1">
       <c r="A220" s="192">
         <v>52</v>
       </c>
@@ -8159,7 +8195,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="22.8" hidden="1">
+    <row r="221" spans="1:7" ht="23.25" hidden="1">
       <c r="A221" s="192">
         <v>58</v>
       </c>
@@ -8182,7 +8218,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="22.8" hidden="1">
+    <row r="222" spans="1:7" ht="23.25" hidden="1">
       <c r="A222" s="192">
         <v>59</v>
       </c>
@@ -8205,7 +8241,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="22.8" hidden="1">
+    <row r="223" spans="1:7" ht="23.25" hidden="1">
       <c r="A223" s="192">
         <v>60</v>
       </c>
@@ -8228,7 +8264,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="22.8" hidden="1">
+    <row r="224" spans="1:7" ht="23.25" hidden="1">
       <c r="A224" s="192">
         <v>1</v>
       </c>
@@ -8251,7 +8287,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="22.8" hidden="1">
+    <row r="225" spans="1:7" ht="23.25" hidden="1">
       <c r="A225" s="217">
         <v>2</v>
       </c>
@@ -8274,7 +8310,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="22.8" hidden="1">
+    <row r="226" spans="1:7" ht="23.25" hidden="1">
       <c r="A226" s="192">
         <v>3</v>
       </c>
@@ -8297,7 +8333,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="22.8" hidden="1">
+    <row r="227" spans="1:7" ht="23.25" hidden="1">
       <c r="A227" s="217">
         <v>4</v>
       </c>
@@ -8318,7 +8354,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="22.8" hidden="1">
+    <row r="228" spans="1:7" ht="23.25" hidden="1">
       <c r="A228" s="217">
         <v>5</v>
       </c>
@@ -8341,7 +8377,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="22.8" hidden="1">
+    <row r="229" spans="1:7" ht="23.25" hidden="1">
       <c r="A229" s="208">
         <v>6</v>
       </c>
@@ -8364,7 +8400,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="22.8" hidden="1">
+    <row r="230" spans="1:7" ht="23.25" hidden="1">
       <c r="A230" s="192">
         <v>7</v>
       </c>
@@ -8387,7 +8423,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="22.8" hidden="1">
+    <row r="231" spans="1:7" ht="23.25" hidden="1">
       <c r="A231" s="192">
         <v>8</v>
       </c>
@@ -8410,7 +8446,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="22.8" hidden="1">
+    <row r="232" spans="1:7" ht="23.25" hidden="1">
       <c r="A232" s="192">
         <v>9</v>
       </c>
@@ -8433,7 +8469,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="22.8" hidden="1">
+    <row r="233" spans="1:7" ht="23.25" hidden="1">
       <c r="A233" s="192">
         <v>11</v>
       </c>
@@ -8456,7 +8492,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="22.8" hidden="1">
+    <row r="234" spans="1:7" ht="23.25" hidden="1">
       <c r="A234" s="192">
         <v>12</v>
       </c>
@@ -8479,7 +8515,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="22.8" hidden="1">
+    <row r="235" spans="1:7" ht="23.25" hidden="1">
       <c r="A235" s="192">
         <v>13</v>
       </c>
@@ -8502,7 +8538,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="22.8" hidden="1">
+    <row r="236" spans="1:7" ht="23.25" hidden="1">
       <c r="A236" s="192">
         <v>15</v>
       </c>
@@ -8525,7 +8561,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="22.8" hidden="1">
+    <row r="237" spans="1:7" ht="23.25" hidden="1">
       <c r="A237" s="192">
         <v>16</v>
       </c>
@@ -8548,7 +8584,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="22.8" hidden="1">
+    <row r="238" spans="1:7" ht="23.25" hidden="1">
       <c r="A238" s="188">
         <v>17</v>
       </c>
@@ -8571,7 +8607,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="22.8" hidden="1">
+    <row r="239" spans="1:7" ht="23.25" hidden="1">
       <c r="A239" s="192">
         <v>20</v>
       </c>
@@ -8594,7 +8630,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="22.8" hidden="1">
+    <row r="240" spans="1:7" ht="23.25" hidden="1">
       <c r="A240" s="192">
         <v>21</v>
       </c>
@@ -8617,7 +8653,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="22.8" hidden="1">
+    <row r="241" spans="1:7" ht="23.25" hidden="1">
       <c r="A241" s="192">
         <v>22</v>
       </c>
@@ -8640,7 +8676,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="22.8" hidden="1">
+    <row r="242" spans="1:7" ht="23.25" hidden="1">
       <c r="A242" s="192">
         <v>23</v>
       </c>
@@ -8663,7 +8699,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="45.6" hidden="1">
+    <row r="243" spans="1:7" ht="46.5" hidden="1">
       <c r="A243" s="192">
         <v>24</v>
       </c>
@@ -8686,7 +8722,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="22.8" hidden="1">
+    <row r="244" spans="1:7" ht="23.25" hidden="1">
       <c r="A244" s="192">
         <v>25</v>
       </c>
@@ -8709,7 +8745,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="22.8" hidden="1">
+    <row r="245" spans="1:7" ht="23.25" hidden="1">
       <c r="A245" s="192">
         <v>27</v>
       </c>
@@ -8732,7 +8768,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="22.8" hidden="1">
+    <row r="246" spans="1:7" ht="23.25" hidden="1">
       <c r="A246" s="188">
         <v>28</v>
       </c>
@@ -8755,7 +8791,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="22.8" hidden="1">
+    <row r="247" spans="1:7" ht="23.25" hidden="1">
       <c r="A247" s="192">
         <v>29</v>
       </c>
@@ -8778,7 +8814,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="22.8" hidden="1">
+    <row r="248" spans="1:7" ht="23.25" hidden="1">
       <c r="A248" s="192">
         <v>30</v>
       </c>
@@ -8801,7 +8837,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="22.8" hidden="1">
+    <row r="249" spans="1:7" ht="23.25" hidden="1">
       <c r="A249" s="192">
         <v>31</v>
       </c>
@@ -8824,7 +8860,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="22.8" hidden="1">
+    <row r="250" spans="1:7" ht="23.25" hidden="1">
       <c r="A250" s="203">
         <v>32</v>
       </c>
@@ -8847,7 +8883,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="22.8" hidden="1">
+    <row r="251" spans="1:7" ht="23.25" hidden="1">
       <c r="A251" s="192">
         <v>33</v>
       </c>
@@ -8870,7 +8906,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="22.8" hidden="1">
+    <row r="252" spans="1:7" ht="23.25" hidden="1">
       <c r="A252" s="192">
         <v>34</v>
       </c>
@@ -8893,7 +8929,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="22.8" hidden="1">
+    <row r="253" spans="1:7" ht="23.25" hidden="1">
       <c r="A253" s="192">
         <v>35</v>
       </c>
@@ -8916,7 +8952,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="22.8" hidden="1">
+    <row r="254" spans="1:7" ht="23.25" hidden="1">
       <c r="A254" s="192">
         <v>36</v>
       </c>
@@ -8939,7 +8975,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="22.8" hidden="1">
+    <row r="255" spans="1:7" ht="23.25" hidden="1">
       <c r="A255" s="188">
         <v>37</v>
       </c>
@@ -8962,7 +8998,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="22.8" hidden="1">
+    <row r="256" spans="1:7" ht="23.25" hidden="1">
       <c r="A256" s="192">
         <v>38</v>
       </c>
@@ -8985,7 +9021,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="22.8" hidden="1">
+    <row r="257" spans="1:7" ht="23.25" hidden="1">
       <c r="A257" s="192">
         <v>39</v>
       </c>
@@ -9008,7 +9044,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="22.8" hidden="1">
+    <row r="258" spans="1:7" ht="23.25" hidden="1">
       <c r="A258" s="192">
         <v>40</v>
       </c>
@@ -9031,7 +9067,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="22.8" hidden="1">
+    <row r="259" spans="1:7" ht="23.25" hidden="1">
       <c r="A259" s="192">
         <v>42</v>
       </c>
@@ -9054,7 +9090,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="22.8" hidden="1">
+    <row r="260" spans="1:7" ht="23.25" hidden="1">
       <c r="A260" s="203">
         <v>43</v>
       </c>
@@ -9077,7 +9113,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="22.8" hidden="1">
+    <row r="261" spans="1:7" ht="23.25" hidden="1">
       <c r="A261" s="203">
         <v>44</v>
       </c>
@@ -9100,7 +9136,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="22.8" hidden="1">
+    <row r="262" spans="1:7" ht="23.25" hidden="1">
       <c r="A262" s="192">
         <v>46</v>
       </c>
@@ -9123,7 +9159,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="22.8" hidden="1">
+    <row r="263" spans="1:7" ht="23.25" hidden="1">
       <c r="A263" s="192">
         <v>47</v>
       </c>
@@ -9146,7 +9182,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="22.8" hidden="1">
+    <row r="264" spans="1:7" ht="23.25" hidden="1">
       <c r="A264" s="188">
         <v>50</v>
       </c>
@@ -9169,7 +9205,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="22.8" hidden="1">
+    <row r="265" spans="1:7" ht="23.25" hidden="1">
       <c r="A265" s="192">
         <v>51</v>
       </c>
@@ -9192,7 +9228,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="22.8" hidden="1">
+    <row r="266" spans="1:7" ht="23.25" hidden="1">
       <c r="A266" s="192">
         <v>52</v>
       </c>
@@ -9215,7 +9251,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="22.8" hidden="1">
+    <row r="267" spans="1:7" ht="23.25" hidden="1">
       <c r="A267" s="192">
         <v>58</v>
       </c>
@@ -9238,7 +9274,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="22.8" hidden="1">
+    <row r="268" spans="1:7" ht="23.25" hidden="1">
       <c r="A268" s="192">
         <v>59</v>
       </c>
@@ -9261,7 +9297,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="22.8" hidden="1">
+    <row r="269" spans="1:7" ht="23.25" hidden="1">
       <c r="A269" s="192">
         <v>60</v>
       </c>
@@ -9284,7 +9320,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="22.8" hidden="1">
+    <row r="270" spans="1:7" ht="23.25" hidden="1">
       <c r="A270" s="192">
         <v>1</v>
       </c>
@@ -9307,7 +9343,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="22.8" hidden="1">
+    <row r="271" spans="1:7" ht="23.25" hidden="1">
       <c r="A271" s="192">
         <v>2</v>
       </c>
@@ -9330,7 +9366,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="22.8" hidden="1">
+    <row r="272" spans="1:7" ht="23.25" hidden="1">
       <c r="A272" s="188">
         <v>3</v>
       </c>
@@ -9353,7 +9389,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="22.8" hidden="1">
+    <row r="273" spans="1:7" ht="23.25" hidden="1">
       <c r="A273" s="192">
         <v>4</v>
       </c>
@@ -9374,7 +9410,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="274" spans="1:7" ht="22.8" hidden="1">
+    <row r="274" spans="1:7" ht="23.25" hidden="1">
       <c r="A274" s="192">
         <v>5</v>
       </c>
@@ -9397,7 +9433,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="22.8" hidden="1">
+    <row r="275" spans="1:7" ht="23.25" hidden="1">
       <c r="A275" s="192">
         <v>6</v>
       </c>
@@ -9421,7 +9457,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="22.8" hidden="1">
+    <row r="276" spans="1:7" ht="23.25" hidden="1">
       <c r="A276" s="192">
         <v>7</v>
       </c>
@@ -9444,7 +9480,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="22.8" hidden="1">
+    <row r="277" spans="1:7" ht="23.25" hidden="1">
       <c r="A277" s="192">
         <v>8</v>
       </c>
@@ -9468,7 +9504,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="22.8" hidden="1">
+    <row r="278" spans="1:7" ht="23.25" hidden="1">
       <c r="A278" s="192">
         <v>9</v>
       </c>
@@ -9491,7 +9527,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="22.8" hidden="1">
+    <row r="279" spans="1:7" ht="23.25" hidden="1">
       <c r="A279" s="192">
         <v>11</v>
       </c>
@@ -9514,7 +9550,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="22.8" hidden="1">
+    <row r="280" spans="1:7" ht="23.25" hidden="1">
       <c r="A280" s="192">
         <v>12</v>
       </c>
@@ -9537,7 +9573,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="22.8" hidden="1">
+    <row r="281" spans="1:7" ht="23.25" hidden="1">
       <c r="A281" s="188">
         <v>13</v>
       </c>
@@ -9560,7 +9596,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="22.8" hidden="1">
+    <row r="282" spans="1:7" ht="23.25" hidden="1">
       <c r="A282" s="192">
         <v>15</v>
       </c>
@@ -9583,7 +9619,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="22.8" hidden="1">
+    <row r="283" spans="1:7" ht="23.25" hidden="1">
       <c r="A283" s="192">
         <v>16</v>
       </c>
@@ -9606,7 +9642,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="22.8" hidden="1">
+    <row r="284" spans="1:7" ht="23.25" hidden="1">
       <c r="A284" s="192">
         <v>17</v>
       </c>
@@ -9629,7 +9665,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="22.8" hidden="1">
+    <row r="285" spans="1:7" ht="23.25" hidden="1">
       <c r="A285" s="192">
         <v>20</v>
       </c>
@@ -9652,7 +9688,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="22.8" hidden="1">
+    <row r="286" spans="1:7" ht="23.25" hidden="1">
       <c r="A286" s="192">
         <v>21</v>
       </c>
@@ -9675,7 +9711,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="22.8" hidden="1">
+    <row r="287" spans="1:7" ht="23.25" hidden="1">
       <c r="A287" s="192">
         <v>22</v>
       </c>
@@ -9698,7 +9734,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="22.8" hidden="1">
+    <row r="288" spans="1:7" ht="23.25" hidden="1">
       <c r="A288" s="192">
         <v>23</v>
       </c>
@@ -9721,7 +9757,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="45.6" hidden="1">
+    <row r="289" spans="1:7" ht="46.5" hidden="1">
       <c r="A289" s="192">
         <v>24</v>
       </c>
@@ -9744,7 +9780,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="22.8" hidden="1">
+    <row r="290" spans="1:7" ht="23.25" hidden="1">
       <c r="A290" s="188">
         <v>25</v>
       </c>
@@ -9767,7 +9803,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="22.8" hidden="1">
+    <row r="291" spans="1:7" ht="23.25" hidden="1">
       <c r="A291" s="192">
         <v>27</v>
       </c>
@@ -9790,7 +9826,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="22.8" hidden="1">
+    <row r="292" spans="1:7" ht="23.25" hidden="1">
       <c r="A292" s="192">
         <v>28</v>
       </c>
@@ -9813,7 +9849,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="22.8" hidden="1">
+    <row r="293" spans="1:7" ht="23.25" hidden="1">
       <c r="A293" s="192">
         <v>29</v>
       </c>
@@ -9836,7 +9872,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="22.8" hidden="1">
+    <row r="294" spans="1:7" ht="23.25" hidden="1">
       <c r="A294" s="192">
         <v>30</v>
       </c>
@@ -9859,7 +9895,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="22.8" hidden="1">
+    <row r="295" spans="1:7" ht="23.25" hidden="1">
       <c r="A295" s="192">
         <v>31</v>
       </c>
@@ -9882,7 +9918,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="22.8" hidden="1">
+    <row r="296" spans="1:7" ht="23.25" hidden="1">
       <c r="A296" s="203">
         <v>32</v>
       </c>
@@ -9905,7 +9941,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="22.8" hidden="1">
+    <row r="297" spans="1:7" ht="23.25" hidden="1">
       <c r="A297" s="192">
         <v>33</v>
       </c>
@@ -9928,7 +9964,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="22.8" hidden="1">
+    <row r="298" spans="1:7" ht="23.25" hidden="1">
       <c r="A298" s="192">
         <v>34</v>
       </c>
@@ -9951,7 +9987,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="22.8" hidden="1">
+    <row r="299" spans="1:7" ht="23.25" hidden="1">
       <c r="A299" s="217">
         <v>35</v>
       </c>
@@ -9974,7 +10010,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="22.8" hidden="1">
+    <row r="300" spans="1:7" ht="23.25" hidden="1">
       <c r="A300" s="192">
         <v>36</v>
       </c>
@@ -9997,7 +10033,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="22.8" hidden="1">
+    <row r="301" spans="1:7" ht="23.25" hidden="1">
       <c r="A301" s="217">
         <v>37</v>
       </c>
@@ -10020,7 +10056,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="22.8" hidden="1">
+    <row r="302" spans="1:7" ht="23.25" hidden="1">
       <c r="A302" s="217">
         <v>38</v>
       </c>
@@ -10043,7 +10079,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="22.8" hidden="1">
+    <row r="303" spans="1:7" ht="23.25" hidden="1">
       <c r="A303" s="208">
         <v>39</v>
       </c>
@@ -10066,7 +10102,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="22.8" hidden="1">
+    <row r="304" spans="1:7" ht="23.25" hidden="1">
       <c r="A304" s="192">
         <v>40</v>
       </c>
@@ -10089,7 +10125,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="22.8" hidden="1">
+    <row r="305" spans="1:7" ht="23.25" hidden="1">
       <c r="A305" s="192">
         <v>42</v>
       </c>
@@ -10112,7 +10148,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="22.8" hidden="1">
+    <row r="306" spans="1:7" ht="23.25" hidden="1">
       <c r="A306" s="203">
         <v>43</v>
       </c>
@@ -10135,7 +10171,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="22.8" hidden="1">
+    <row r="307" spans="1:7" ht="23.25" hidden="1">
       <c r="A307" s="203">
         <v>44</v>
       </c>
@@ -10158,7 +10194,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="22.8" hidden="1">
+    <row r="308" spans="1:7" ht="23.25" hidden="1">
       <c r="A308" s="192">
         <v>46</v>
       </c>
@@ -10181,7 +10217,7 @@
         <v>45938</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="22.8" hidden="1">
+    <row r="309" spans="1:7" ht="23.25" hidden="1">
       <c r="A309" s="192">
         <v>47</v>
       </c>
@@ -10204,7 +10240,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="22.8" hidden="1">
+    <row r="310" spans="1:7" ht="23.25" hidden="1">
       <c r="A310" s="203">
         <v>48</v>
       </c>
@@ -10225,7 +10261,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="22.8" hidden="1">
+    <row r="311" spans="1:7" ht="23.25" hidden="1">
       <c r="A311" s="192">
         <v>50</v>
       </c>
@@ -10248,7 +10284,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="22.8" hidden="1">
+    <row r="312" spans="1:7" ht="23.25" hidden="1">
       <c r="A312" s="188">
         <v>51</v>
       </c>
@@ -10271,7 +10307,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="22.8" hidden="1">
+    <row r="313" spans="1:7" ht="23.25" hidden="1">
       <c r="A313" s="192">
         <v>52</v>
       </c>
@@ -10294,7 +10330,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="22.8" hidden="1">
+    <row r="314" spans="1:7" ht="23.25" hidden="1">
       <c r="A314" s="192">
         <v>58</v>
       </c>
@@ -10317,7 +10353,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="22.8" hidden="1">
+    <row r="315" spans="1:7" ht="23.25" hidden="1">
       <c r="A315" s="192">
         <v>59</v>
       </c>
@@ -10340,7 +10376,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="22.8" hidden="1">
+    <row r="316" spans="1:7" ht="23.25" hidden="1">
       <c r="A316" s="192">
         <v>60</v>
       </c>
@@ -10363,7 +10399,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="22.8" hidden="1">
+    <row r="317" spans="1:7" ht="23.25" hidden="1">
       <c r="A317" s="203">
         <v>62</v>
       </c>
@@ -10380,7 +10416,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="22.8" hidden="1">
+    <row r="318" spans="1:7" ht="23.25" hidden="1">
       <c r="A318" s="203">
         <v>64</v>
       </c>
@@ -10397,7 +10433,7 @@
         <v>45940</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="22.8" hidden="1">
+    <row r="319" spans="1:7" ht="23.25" hidden="1">
       <c r="A319" s="192">
         <v>1</v>
       </c>
@@ -10420,7 +10456,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="22.8" hidden="1">
+    <row r="320" spans="1:7" ht="23.25" hidden="1">
       <c r="A320" s="188">
         <v>2</v>
       </c>
@@ -10443,7 +10479,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="22.8" hidden="1">
+    <row r="321" spans="1:7" ht="23.25" hidden="1">
       <c r="A321" s="192">
         <v>3</v>
       </c>
@@ -10466,7 +10502,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="22.8" hidden="1">
+    <row r="322" spans="1:7" ht="23.25" hidden="1">
       <c r="A322" s="192">
         <v>4</v>
       </c>
@@ -10487,7 +10523,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="22.8" hidden="1">
+    <row r="323" spans="1:7" ht="23.25" hidden="1">
       <c r="A323" s="192">
         <v>5</v>
       </c>
@@ -10510,7 +10546,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="22.8" hidden="1">
+    <row r="324" spans="1:7" ht="23.25" hidden="1">
       <c r="A324" s="192">
         <v>6</v>
       </c>
@@ -10534,7 +10570,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="22.8" hidden="1">
+    <row r="325" spans="1:7" ht="23.25" hidden="1">
       <c r="A325" s="192">
         <v>7</v>
       </c>
@@ -10557,7 +10593,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="22.8" hidden="1">
+    <row r="326" spans="1:7" ht="23.25" hidden="1">
       <c r="A326" s="192">
         <v>8</v>
       </c>
@@ -10581,7 +10617,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="22.8" hidden="1">
+    <row r="327" spans="1:7" ht="23.25" hidden="1">
       <c r="A327" s="192">
         <v>9</v>
       </c>
@@ -10604,7 +10640,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="22.8" hidden="1">
+    <row r="328" spans="1:7" ht="23.25" hidden="1">
       <c r="A328" s="192">
         <v>11</v>
       </c>
@@ -10627,7 +10663,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="22.8" hidden="1">
+    <row r="329" spans="1:7" ht="23.25" hidden="1">
       <c r="A329" s="188">
         <v>12</v>
       </c>
@@ -10650,7 +10686,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="22.8" hidden="1">
+    <row r="330" spans="1:7" ht="23.25" hidden="1">
       <c r="A330" s="192">
         <v>13</v>
       </c>
@@ -10673,7 +10709,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="22.8" hidden="1">
+    <row r="331" spans="1:7" ht="23.25" hidden="1">
       <c r="A331" s="192">
         <v>15</v>
       </c>
@@ -10696,7 +10732,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="22.8" hidden="1">
+    <row r="332" spans="1:7" ht="23.25" hidden="1">
       <c r="A332" s="192">
         <v>16</v>
       </c>
@@ -10719,7 +10755,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="22.8" hidden="1">
+    <row r="333" spans="1:7" ht="23.25" hidden="1">
       <c r="A333" s="192">
         <v>17</v>
       </c>
@@ -10742,7 +10778,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="22.8" hidden="1">
+    <row r="334" spans="1:7" ht="23.25" hidden="1">
       <c r="A334" s="192">
         <v>20</v>
       </c>
@@ -10765,7 +10801,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="22.8" hidden="1">
+    <row r="335" spans="1:7" ht="23.25" hidden="1">
       <c r="A335" s="192">
         <v>21</v>
       </c>
@@ -10788,7 +10824,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="22.8" hidden="1">
+    <row r="336" spans="1:7" ht="23.25" hidden="1">
       <c r="A336" s="192">
         <v>22</v>
       </c>
@@ -10811,7 +10847,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="22.8" hidden="1">
+    <row r="337" spans="1:7" ht="23.25" hidden="1">
       <c r="A337" s="192">
         <v>23</v>
       </c>
@@ -10834,7 +10870,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="45.6" hidden="1">
+    <row r="338" spans="1:7" ht="46.5" hidden="1">
       <c r="A338" s="188">
         <v>24</v>
       </c>
@@ -10857,7 +10893,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="22.8" hidden="1">
+    <row r="339" spans="1:7" ht="23.25" hidden="1">
       <c r="A339" s="192">
         <v>25</v>
       </c>
@@ -10880,7 +10916,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="22.8" hidden="1">
+    <row r="340" spans="1:7" ht="23.25" hidden="1">
       <c r="A340" s="192">
         <v>27</v>
       </c>
@@ -10903,7 +10939,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="22.8" hidden="1">
+    <row r="341" spans="1:7" ht="23.25" hidden="1">
       <c r="A341" s="192">
         <v>28</v>
       </c>
@@ -10926,7 +10962,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="22.8" hidden="1">
+    <row r="342" spans="1:7" ht="23.25" hidden="1">
       <c r="A342" s="192">
         <v>29</v>
       </c>
@@ -10949,7 +10985,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="22.8" hidden="1">
+    <row r="343" spans="1:7" ht="23.25" hidden="1">
       <c r="A343" s="192">
         <v>30</v>
       </c>
@@ -10972,7 +11008,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="22.8" hidden="1">
+    <row r="344" spans="1:7" ht="23.25" hidden="1">
       <c r="A344" s="192">
         <v>31</v>
       </c>
@@ -10995,7 +11031,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="22.8" hidden="1">
+    <row r="345" spans="1:7" ht="23.25" hidden="1">
       <c r="A345" s="203">
         <v>32</v>
       </c>
@@ -11018,7 +11054,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="22.8" hidden="1">
+    <row r="346" spans="1:7" ht="23.25" hidden="1">
       <c r="A346" s="188">
         <v>33</v>
       </c>
@@ -11041,7 +11077,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="22.8" hidden="1">
+    <row r="347" spans="1:7" ht="23.25" hidden="1">
       <c r="A347" s="192">
         <v>34</v>
       </c>
@@ -11064,7 +11100,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="22.8" hidden="1">
+    <row r="348" spans="1:7" ht="23.25" hidden="1">
       <c r="A348" s="192">
         <v>35</v>
       </c>
@@ -11087,7 +11123,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="22.8" hidden="1">
+    <row r="349" spans="1:7" ht="23.25" hidden="1">
       <c r="A349" s="192">
         <v>36</v>
       </c>
@@ -11110,7 +11146,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="22.8" hidden="1">
+    <row r="350" spans="1:7" ht="23.25" hidden="1">
       <c r="A350" s="192">
         <v>37</v>
       </c>
@@ -11133,7 +11169,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="22.8" hidden="1">
+    <row r="351" spans="1:7" ht="23.25" hidden="1">
       <c r="A351" s="192">
         <v>38</v>
       </c>
@@ -11156,7 +11192,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="22.8" hidden="1">
+    <row r="352" spans="1:7" ht="23.25" hidden="1">
       <c r="A352" s="192">
         <v>39</v>
       </c>
@@ -11179,7 +11215,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="22.8" hidden="1">
+    <row r="353" spans="1:7" ht="23.25" hidden="1">
       <c r="A353" s="192">
         <v>40</v>
       </c>
@@ -11202,7 +11238,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="22.8" hidden="1">
+    <row r="354" spans="1:7" ht="23.25" hidden="1">
       <c r="A354" s="192">
         <v>42</v>
       </c>
@@ -11225,7 +11261,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="22.8" hidden="1">
+    <row r="355" spans="1:7" ht="23.25" hidden="1">
       <c r="A355" s="225">
         <v>43</v>
       </c>
@@ -11248,7 +11284,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="22.8" hidden="1">
+    <row r="356" spans="1:7" ht="23.25" hidden="1">
       <c r="A356" s="203">
         <v>44</v>
       </c>
@@ -11271,7 +11307,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="22.8" hidden="1">
+    <row r="357" spans="1:7" ht="23.25" hidden="1">
       <c r="A357" s="192">
         <v>46</v>
       </c>
@@ -11294,7 +11330,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="22.8" hidden="1">
+    <row r="358" spans="1:7" ht="23.25" hidden="1">
       <c r="A358" s="192">
         <v>47</v>
       </c>
@@ -11317,7 +11353,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="22.8" hidden="1">
+    <row r="359" spans="1:7" ht="23.25" hidden="1">
       <c r="A359" s="203">
         <v>48</v>
       </c>
@@ -11338,7 +11374,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="22.8" hidden="1">
+    <row r="360" spans="1:7" ht="23.25" hidden="1">
       <c r="A360" s="192">
         <v>50</v>
       </c>
@@ -11361,7 +11397,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="22.8" hidden="1">
+    <row r="361" spans="1:7" ht="23.25" hidden="1">
       <c r="A361" s="192">
         <v>51</v>
       </c>
@@ -11384,7 +11420,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="22.8" hidden="1">
+    <row r="362" spans="1:7" ht="23.25" hidden="1">
       <c r="A362" s="192">
         <v>52</v>
       </c>
@@ -11407,7 +11443,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="22.8" hidden="1">
+    <row r="363" spans="1:7" ht="23.25" hidden="1">
       <c r="A363" s="192">
         <v>58</v>
       </c>
@@ -11430,7 +11466,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="22.8" hidden="1">
+    <row r="364" spans="1:7" ht="23.25" hidden="1">
       <c r="A364" s="188">
         <v>59</v>
       </c>
@@ -11453,7 +11489,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="22.8" hidden="1">
+    <row r="365" spans="1:7" ht="23.25" hidden="1">
       <c r="A365" s="192">
         <v>60</v>
       </c>
@@ -11476,7 +11512,7 @@
         <v>45992</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="22.8" hidden="1">
+    <row r="366" spans="1:7" ht="23.25" hidden="1">
       <c r="A366" s="192">
         <v>1</v>
       </c>
@@ -11499,7 +11535,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="22.8" hidden="1">
+    <row r="367" spans="1:7" ht="23.25" hidden="1">
       <c r="A367" s="192">
         <v>2</v>
       </c>
@@ -11522,7 +11558,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="22.8" hidden="1">
+    <row r="368" spans="1:7" ht="23.25" hidden="1">
       <c r="A368" s="192">
         <v>3</v>
       </c>
@@ -11545,7 +11581,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="22.8" hidden="1">
+    <row r="369" spans="1:7" ht="23.25" hidden="1">
       <c r="A369" s="192">
         <v>4</v>
       </c>
@@ -11566,7 +11602,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="22.8" hidden="1">
+    <row r="370" spans="1:7" ht="23.25" hidden="1">
       <c r="A370" s="192">
         <v>5</v>
       </c>
@@ -11589,7 +11625,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="22.8" hidden="1">
+    <row r="371" spans="1:7" ht="23.25" hidden="1">
       <c r="A371" s="192">
         <v>6</v>
       </c>
@@ -11613,7 +11649,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="22.8" hidden="1">
+    <row r="372" spans="1:7" ht="23.25" hidden="1">
       <c r="A372" s="192">
         <v>7</v>
       </c>
@@ -11636,7 +11672,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="22.8" hidden="1">
+    <row r="373" spans="1:7" ht="23.25" hidden="1">
       <c r="A373" s="217">
         <v>8</v>
       </c>
@@ -11660,7 +11696,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="22.8" hidden="1">
+    <row r="374" spans="1:7" ht="23.25" hidden="1">
       <c r="A374" s="192">
         <v>9</v>
       </c>
@@ -11683,7 +11719,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="22.8" hidden="1">
+    <row r="375" spans="1:7" ht="23.25" hidden="1">
       <c r="A375" s="217">
         <v>11</v>
       </c>
@@ -11706,7 +11742,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="22.8" hidden="1">
+    <row r="376" spans="1:7" ht="23.25" hidden="1">
       <c r="A376" s="217">
         <v>12</v>
       </c>
@@ -11729,7 +11765,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="22.8" hidden="1">
+    <row r="377" spans="1:7" ht="23.25" hidden="1">
       <c r="A377" s="208">
         <v>13</v>
       </c>
@@ -11752,7 +11788,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="22.8" hidden="1">
+    <row r="378" spans="1:7" ht="23.25" hidden="1">
       <c r="A378" s="192">
         <v>15</v>
       </c>
@@ -11775,7 +11811,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="22.8" hidden="1">
+    <row r="379" spans="1:7" ht="23.25" hidden="1">
       <c r="A379" s="192">
         <v>16</v>
       </c>
@@ -11798,7 +11834,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="22.8" hidden="1">
+    <row r="380" spans="1:7" ht="23.25" hidden="1">
       <c r="A380" s="192">
         <v>17</v>
       </c>
@@ -11821,7 +11857,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="22.8" hidden="1">
+    <row r="381" spans="1:7" ht="23.25" hidden="1">
       <c r="A381" s="192">
         <v>20</v>
       </c>
@@ -11844,7 +11880,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="22.8" hidden="1">
+    <row r="382" spans="1:7" ht="23.25" hidden="1">
       <c r="A382" s="192">
         <v>21</v>
       </c>
@@ -11867,7 +11903,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="22.8" hidden="1">
+    <row r="383" spans="1:7" ht="23.25" hidden="1">
       <c r="A383" s="192">
         <v>22</v>
       </c>
@@ -11890,7 +11926,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="22.8" hidden="1">
+    <row r="384" spans="1:7" ht="23.25" hidden="1">
       <c r="A384" s="192">
         <v>23</v>
       </c>
@@ -11913,7 +11949,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="45.6" hidden="1">
+    <row r="385" spans="1:7" ht="46.5" hidden="1">
       <c r="A385" s="192">
         <v>24</v>
       </c>
@@ -11936,7 +11972,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="22.8" hidden="1">
+    <row r="386" spans="1:7" ht="23.25" hidden="1">
       <c r="A386" s="188">
         <v>25</v>
       </c>
@@ -11959,7 +11995,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="22.8" hidden="1">
+    <row r="387" spans="1:7" ht="23.25" hidden="1">
       <c r="A387" s="192">
         <v>27</v>
       </c>
@@ -11982,7 +12018,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="22.8" hidden="1">
+    <row r="388" spans="1:7" ht="23.25" hidden="1">
       <c r="A388" s="192">
         <v>28</v>
       </c>
@@ -12005,7 +12041,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="22.8" hidden="1">
+    <row r="389" spans="1:7" ht="23.25" hidden="1">
       <c r="A389" s="192">
         <v>29</v>
       </c>
@@ -12028,7 +12064,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="22.8" hidden="1">
+    <row r="390" spans="1:7" ht="23.25" hidden="1">
       <c r="A390" s="192">
         <v>30</v>
       </c>
@@ -12051,7 +12087,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="22.8" hidden="1">
+    <row r="391" spans="1:7" ht="23.25" hidden="1">
       <c r="A391" s="192">
         <v>31</v>
       </c>
@@ -12074,7 +12110,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="22.8" hidden="1">
+    <row r="392" spans="1:7" ht="23.25" hidden="1">
       <c r="A392" s="203">
         <v>32</v>
       </c>
@@ -12097,7 +12133,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="22.8" hidden="1">
+    <row r="393" spans="1:7" ht="23.25" hidden="1">
       <c r="A393" s="192">
         <v>33</v>
       </c>
@@ -12120,7 +12156,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="22.8" hidden="1">
+    <row r="394" spans="1:7" ht="23.25" hidden="1">
       <c r="A394" s="188">
         <v>34</v>
       </c>
@@ -12143,7 +12179,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="22.8" hidden="1">
+    <row r="395" spans="1:7" ht="23.25" hidden="1">
       <c r="A395" s="192">
         <v>35</v>
       </c>
@@ -12166,7 +12202,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="22.8" hidden="1">
+    <row r="396" spans="1:7" ht="23.25" hidden="1">
       <c r="A396" s="192">
         <v>36</v>
       </c>
@@ -12189,7 +12225,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="22.8" hidden="1">
+    <row r="397" spans="1:7" ht="23.25" hidden="1">
       <c r="A397" s="192">
         <v>37</v>
       </c>
@@ -12212,7 +12248,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="22.8" hidden="1">
+    <row r="398" spans="1:7" ht="23.25" hidden="1">
       <c r="A398" s="192">
         <v>38</v>
       </c>
@@ -12235,7 +12271,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="22.8" hidden="1">
+    <row r="399" spans="1:7" ht="23.25" hidden="1">
       <c r="A399" s="192">
         <v>39</v>
       </c>
@@ -12258,7 +12294,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="22.8" hidden="1">
+    <row r="400" spans="1:7" ht="23.25" hidden="1">
       <c r="A400" s="192">
         <v>40</v>
       </c>
@@ -12281,7 +12317,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="22.8" hidden="1">
+    <row r="401" spans="1:7" ht="23.25" hidden="1">
       <c r="A401" s="192">
         <v>42</v>
       </c>
@@ -12304,7 +12340,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="22.8" hidden="1">
+    <row r="402" spans="1:7" ht="23.25" hidden="1">
       <c r="A402" s="203">
         <v>43</v>
       </c>
@@ -12327,7 +12363,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="22.8" hidden="1">
+    <row r="403" spans="1:7" ht="23.25" hidden="1">
       <c r="A403" s="225">
         <v>44</v>
       </c>
@@ -12350,7 +12386,7 @@
         <v>45996</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="22.8" hidden="1">
+    <row r="404" spans="1:7" ht="23.25" hidden="1">
       <c r="A404" s="192">
         <v>46</v>
       </c>
@@ -12373,7 +12409,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="22.8" hidden="1">
+    <row r="405" spans="1:7" ht="23.25" hidden="1">
       <c r="A405" s="203">
         <v>48</v>
       </c>
@@ -12394,7 +12430,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="22.8" hidden="1">
+    <row r="406" spans="1:7" ht="23.25" hidden="1">
       <c r="A406" s="192">
         <v>50</v>
       </c>
@@ -12417,7 +12453,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="22.8" hidden="1">
+    <row r="407" spans="1:7" ht="23.25" hidden="1">
       <c r="A407" s="192">
         <v>51</v>
       </c>
@@ -12440,7 +12476,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="22.8" hidden="1">
+    <row r="408" spans="1:7" ht="23.25" hidden="1">
       <c r="A408" s="192">
         <v>52</v>
       </c>
@@ -12463,7 +12499,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="22.8" hidden="1">
+    <row r="409" spans="1:7" ht="23.25" hidden="1">
       <c r="A409" s="192">
         <v>58</v>
       </c>
@@ -12486,7 +12522,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="22.8" hidden="1">
+    <row r="410" spans="1:7" ht="23.25" hidden="1">
       <c r="A410" s="192">
         <v>59</v>
       </c>
@@ -12509,7 +12545,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="22.8" hidden="1">
+    <row r="411" spans="1:7" ht="23.25" hidden="1">
       <c r="A411" s="192">
         <v>60</v>
       </c>
@@ -12532,7 +12568,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="22.8" hidden="1">
+    <row r="412" spans="1:7" ht="23.25" hidden="1">
       <c r="A412" s="225">
         <v>64</v>
       </c>
@@ -12549,7 +12585,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="22.8" hidden="1">
+    <row r="413" spans="1:7" ht="23.25" hidden="1">
       <c r="A413" s="192">
         <v>1</v>
       </c>
@@ -12572,7 +12608,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="22.8" hidden="1">
+    <row r="414" spans="1:7" ht="23.25" hidden="1">
       <c r="A414" s="192">
         <v>2</v>
       </c>
@@ -12595,7 +12631,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="22.8" hidden="1">
+    <row r="415" spans="1:7" ht="23.25" hidden="1">
       <c r="A415" s="192">
         <v>3</v>
       </c>
@@ -12618,7 +12654,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="22.8" hidden="1">
+    <row r="416" spans="1:7" ht="23.25" hidden="1">
       <c r="A416" s="192">
         <v>5</v>
       </c>
@@ -12641,7 +12677,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="22.8" hidden="1">
+    <row r="417" spans="1:7" ht="23.25" hidden="1">
       <c r="A417" s="192">
         <v>6</v>
       </c>
@@ -12665,7 +12701,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="22.8" hidden="1">
+    <row r="418" spans="1:7" ht="23.25" hidden="1">
       <c r="A418" s="192">
         <v>7</v>
       </c>
@@ -12688,7 +12724,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="22.8" hidden="1">
+    <row r="419" spans="1:7" ht="23.25" hidden="1">
       <c r="A419" s="192">
         <v>8</v>
       </c>
@@ -12712,7 +12748,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="22.8" hidden="1">
+    <row r="420" spans="1:7" ht="23.25" hidden="1">
       <c r="A420" s="188">
         <v>9</v>
       </c>
@@ -12735,7 +12771,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="22.8" hidden="1">
+    <row r="421" spans="1:7" ht="23.25" hidden="1">
       <c r="A421" s="192">
         <v>11</v>
       </c>
@@ -12758,7 +12794,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="22.8" hidden="1">
+    <row r="422" spans="1:7" ht="23.25" hidden="1">
       <c r="A422" s="192">
         <v>12</v>
       </c>
@@ -12781,7 +12817,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="22.8" hidden="1">
+    <row r="423" spans="1:7" ht="23.25" hidden="1">
       <c r="A423" s="192">
         <v>13</v>
       </c>
@@ -12804,7 +12840,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="22.8" hidden="1">
+    <row r="424" spans="1:7" ht="23.25" hidden="1">
       <c r="A424" s="192">
         <v>15</v>
       </c>
@@ -12827,7 +12863,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="22.8" hidden="1">
+    <row r="425" spans="1:7" ht="23.25" hidden="1">
       <c r="A425" s="192">
         <v>16</v>
       </c>
@@ -12850,7 +12886,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="22.8" hidden="1">
+    <row r="426" spans="1:7" ht="23.25" hidden="1">
       <c r="A426" s="192">
         <v>17</v>
       </c>
@@ -12873,7 +12909,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="22.8" hidden="1">
+    <row r="427" spans="1:7" ht="23.25" hidden="1">
       <c r="A427" s="192">
         <v>20</v>
       </c>
@@ -12896,7 +12932,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="22.8" hidden="1">
+    <row r="428" spans="1:7" ht="23.25" hidden="1">
       <c r="A428" s="192">
         <v>21</v>
       </c>
@@ -12919,7 +12955,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="22.8" hidden="1">
+    <row r="429" spans="1:7" ht="23.25" hidden="1">
       <c r="A429" s="188">
         <v>22</v>
       </c>
@@ -12942,7 +12978,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="22.8" hidden="1">
+    <row r="430" spans="1:7" ht="23.25" hidden="1">
       <c r="A430" s="192">
         <v>23</v>
       </c>
@@ -12965,7 +13001,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="45.6" hidden="1">
+    <row r="431" spans="1:7" ht="46.5" hidden="1">
       <c r="A431" s="192">
         <v>24</v>
       </c>
@@ -12988,7 +13024,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="22.8" hidden="1">
+    <row r="432" spans="1:7" ht="23.25" hidden="1">
       <c r="A432" s="192">
         <v>25</v>
       </c>
@@ -13011,7 +13047,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="22.8" hidden="1">
+    <row r="433" spans="1:7" ht="23.25" hidden="1">
       <c r="A433" s="192">
         <v>27</v>
       </c>
@@ -13034,7 +13070,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="22.8" hidden="1">
+    <row r="434" spans="1:7" ht="23.25" hidden="1">
       <c r="A434" s="192">
         <v>28</v>
       </c>
@@ -13057,7 +13093,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="22.8" hidden="1">
+    <row r="435" spans="1:7" ht="23.25" hidden="1">
       <c r="A435" s="192">
         <v>29</v>
       </c>
@@ -13080,7 +13116,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="22.8" hidden="1">
+    <row r="436" spans="1:7" ht="23.25" hidden="1">
       <c r="A436" s="192">
         <v>30</v>
       </c>
@@ -13103,7 +13139,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="22.8" hidden="1">
+    <row r="437" spans="1:7" ht="23.25" hidden="1">
       <c r="A437" s="192">
         <v>31</v>
       </c>
@@ -13126,7 +13162,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="22.8" hidden="1">
+    <row r="438" spans="1:7" ht="23.25" hidden="1">
       <c r="A438" s="225">
         <v>32</v>
       </c>
@@ -13149,7 +13185,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="22.8" hidden="1">
+    <row r="439" spans="1:7" ht="23.25" hidden="1">
       <c r="A439" s="192">
         <v>33</v>
       </c>
@@ -13172,7 +13208,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="22.8" hidden="1">
+    <row r="440" spans="1:7" ht="23.25" hidden="1">
       <c r="A440" s="192">
         <v>34</v>
       </c>
@@ -13195,7 +13231,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="22.8" hidden="1">
+    <row r="441" spans="1:7" ht="23.25" hidden="1">
       <c r="A441" s="192">
         <v>35</v>
       </c>
@@ -13218,7 +13254,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="22.8" hidden="1">
+    <row r="442" spans="1:7" ht="23.25" hidden="1">
       <c r="A442" s="192">
         <v>36</v>
       </c>
@@ -13241,7 +13277,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="22.8" hidden="1">
+    <row r="443" spans="1:7" ht="23.25" hidden="1">
       <c r="A443" s="192">
         <v>37</v>
       </c>
@@ -13264,7 +13300,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="22.8" hidden="1">
+    <row r="444" spans="1:7" ht="23.25" hidden="1">
       <c r="A444" s="192">
         <v>38</v>
       </c>
@@ -13287,7 +13323,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="22.8" hidden="1">
+    <row r="445" spans="1:7" ht="23.25" hidden="1">
       <c r="A445" s="192">
         <v>39</v>
       </c>
@@ -13310,7 +13346,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="22.8" hidden="1">
+    <row r="446" spans="1:7" ht="23.25" hidden="1">
       <c r="A446" s="192">
         <v>40</v>
       </c>
@@ -13333,7 +13369,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="22.8" hidden="1">
+    <row r="447" spans="1:7" ht="23.25" hidden="1">
       <c r="A447" s="217">
         <v>42</v>
       </c>
@@ -13356,7 +13392,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="22.8" hidden="1">
+    <row r="448" spans="1:7" ht="23.25" hidden="1">
       <c r="A448" s="203">
         <v>43</v>
       </c>
@@ -13379,7 +13415,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="22.8" hidden="1">
+    <row r="449" spans="1:7" ht="23.25" hidden="1">
       <c r="A449" s="237">
         <v>44</v>
       </c>
@@ -13402,7 +13438,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="22.8" hidden="1">
+    <row r="450" spans="1:7" ht="23.25" hidden="1">
       <c r="A450" s="217">
         <v>46</v>
       </c>
@@ -13425,7 +13461,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="22.8" hidden="1">
+    <row r="451" spans="1:7" ht="23.25" hidden="1">
       <c r="A451" s="232">
         <v>48</v>
       </c>
@@ -13446,7 +13482,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="22.8" hidden="1">
+    <row r="452" spans="1:7" ht="23.25" hidden="1">
       <c r="A452" s="192">
         <v>50</v>
       </c>
@@ -13469,7 +13505,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="22.8" hidden="1">
+    <row r="453" spans="1:7" ht="23.25" hidden="1">
       <c r="A453" s="192">
         <v>51</v>
       </c>
@@ -13492,7 +13528,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="22.8" hidden="1">
+    <row r="454" spans="1:7" ht="23.25" hidden="1">
       <c r="A454" s="192">
         <v>52</v>
       </c>
@@ -13515,7 +13551,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="22.8" hidden="1">
+    <row r="455" spans="1:7" ht="23.25" hidden="1">
       <c r="A455" s="192">
         <v>58</v>
       </c>
@@ -13538,7 +13574,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="22.8" hidden="1">
+    <row r="456" spans="1:7" ht="23.25" hidden="1">
       <c r="A456" s="192">
         <v>59</v>
       </c>
@@ -13561,7 +13597,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="22.8" hidden="1">
+    <row r="457" spans="1:7" ht="23.25" hidden="1">
       <c r="A457" s="192">
         <v>60</v>
       </c>
@@ -13584,7 +13620,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="22.8" hidden="1">
+    <row r="458" spans="1:7" ht="23.25" hidden="1">
       <c r="A458" s="192">
         <v>1</v>
       </c>
@@ -13607,7 +13643,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="22.8" hidden="1">
+    <row r="459" spans="1:7" ht="23.25" hidden="1">
       <c r="A459" s="192">
         <v>2</v>
       </c>
@@ -13630,7 +13666,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="22.8" hidden="1">
+    <row r="460" spans="1:7" ht="23.25" hidden="1">
       <c r="A460" s="188">
         <v>3</v>
       </c>
@@ -13653,7 +13689,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="22.8" hidden="1">
+    <row r="461" spans="1:7" ht="23.25" hidden="1">
       <c r="A461" s="192">
         <v>5</v>
       </c>
@@ -13676,7 +13712,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="22.8" hidden="1">
+    <row r="462" spans="1:7" ht="23.25" hidden="1">
       <c r="A462" s="192">
         <v>6</v>
       </c>
@@ -13700,7 +13736,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="22.8" hidden="1">
+    <row r="463" spans="1:7" ht="23.25" hidden="1">
       <c r="A463" s="192">
         <v>7</v>
       </c>
@@ -13723,7 +13759,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="22.8" hidden="1">
+    <row r="464" spans="1:7" ht="23.25" hidden="1">
       <c r="A464" s="192">
         <v>8</v>
       </c>
@@ -13747,7 +13783,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="22.8" hidden="1">
+    <row r="465" spans="1:7" ht="23.25" hidden="1">
       <c r="A465" s="192">
         <v>9</v>
       </c>
@@ -13770,7 +13806,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="22.8" hidden="1">
+    <row r="466" spans="1:7" ht="23.25" hidden="1">
       <c r="A466" s="192">
         <v>11</v>
       </c>
@@ -13793,7 +13829,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="22.8" hidden="1">
+    <row r="467" spans="1:7" ht="23.25" hidden="1">
       <c r="A467" s="192">
         <v>12</v>
       </c>
@@ -13816,7 +13852,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="22.8" hidden="1">
+    <row r="468" spans="1:7" ht="23.25" hidden="1">
       <c r="A468" s="188">
         <v>13</v>
       </c>
@@ -13839,7 +13875,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="22.8" hidden="1">
+    <row r="469" spans="1:7" ht="23.25" hidden="1">
       <c r="A469" s="192">
         <v>15</v>
       </c>
@@ -13862,7 +13898,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="22.8" hidden="1">
+    <row r="470" spans="1:7" ht="23.25" hidden="1">
       <c r="A470" s="192">
         <v>16</v>
       </c>
@@ -13885,7 +13921,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="22.8" hidden="1">
+    <row r="471" spans="1:7" ht="23.25" hidden="1">
       <c r="A471" s="192">
         <v>17</v>
       </c>
@@ -13908,7 +13944,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="22.8" hidden="1">
+    <row r="472" spans="1:7" ht="23.25" hidden="1">
       <c r="A472" s="192">
         <v>20</v>
       </c>
@@ -13931,7 +13967,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="22.8" hidden="1">
+    <row r="473" spans="1:7" ht="23.25" hidden="1">
       <c r="A473" s="192">
         <v>21</v>
       </c>
@@ -13954,7 +13990,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="22.8" hidden="1">
+    <row r="474" spans="1:7" ht="23.25" hidden="1">
       <c r="A474" s="192">
         <v>22</v>
       </c>
@@ -13977,7 +14013,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="22.8" hidden="1">
+    <row r="475" spans="1:7" ht="23.25" hidden="1">
       <c r="A475" s="192">
         <v>23</v>
       </c>
@@ -14000,7 +14036,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="45.6" hidden="1">
+    <row r="476" spans="1:7" ht="46.5" hidden="1">
       <c r="A476" s="192">
         <v>24</v>
       </c>
@@ -14023,7 +14059,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="22.8" hidden="1">
+    <row r="477" spans="1:7" ht="23.25" hidden="1">
       <c r="A477" s="188">
         <v>25</v>
       </c>
@@ -14046,7 +14082,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="22.8" hidden="1">
+    <row r="478" spans="1:7" ht="23.25" hidden="1">
       <c r="A478" s="192">
         <v>27</v>
       </c>
@@ -14069,7 +14105,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="22.8" hidden="1">
+    <row r="479" spans="1:7" ht="23.25" hidden="1">
       <c r="A479" s="192">
         <v>28</v>
       </c>
@@ -14092,7 +14128,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="22.8" hidden="1">
+    <row r="480" spans="1:7" ht="23.25" hidden="1">
       <c r="A480" s="192">
         <v>29</v>
       </c>
@@ -14115,7 +14151,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="22.8" hidden="1">
+    <row r="481" spans="1:7" ht="23.25" hidden="1">
       <c r="A481" s="192">
         <v>30</v>
       </c>
@@ -14138,7 +14174,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="22.8" hidden="1">
+    <row r="482" spans="1:7" ht="23.25" hidden="1">
       <c r="A482" s="192">
         <v>31</v>
       </c>
@@ -14161,7 +14197,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="22.8" hidden="1">
+    <row r="483" spans="1:7" ht="23.25" hidden="1">
       <c r="A483" s="203">
         <v>32</v>
       </c>
@@ -14184,7 +14220,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="22.8" hidden="1">
+    <row r="484" spans="1:7" ht="23.25" hidden="1">
       <c r="A484" s="192">
         <v>33</v>
       </c>
@@ -14207,7 +14243,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="22.8" hidden="1">
+    <row r="485" spans="1:7" ht="23.25" hidden="1">
       <c r="A485" s="192">
         <v>34</v>
       </c>
@@ -14230,7 +14266,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="22.8" hidden="1">
+    <row r="486" spans="1:7" ht="23.25" hidden="1">
       <c r="A486" s="188">
         <v>35</v>
       </c>
@@ -14253,7 +14289,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="22.8" hidden="1">
+    <row r="487" spans="1:7" ht="23.25" hidden="1">
       <c r="A487" s="192">
         <v>36</v>
       </c>
@@ -14276,7 +14312,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="22.8" hidden="1">
+    <row r="488" spans="1:7" ht="23.25" hidden="1">
       <c r="A488" s="192">
         <v>37</v>
       </c>
@@ -14299,7 +14335,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="22.8" hidden="1">
+    <row r="489" spans="1:7" ht="23.25" hidden="1">
       <c r="A489" s="192">
         <v>38</v>
       </c>
@@ -14322,7 +14358,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="22.8" hidden="1">
+    <row r="490" spans="1:7" ht="23.25" hidden="1">
       <c r="A490" s="192">
         <v>39</v>
       </c>
@@ -14345,7 +14381,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="22.8" hidden="1">
+    <row r="491" spans="1:7" ht="23.25" hidden="1">
       <c r="A491" s="192">
         <v>40</v>
       </c>
@@ -14368,7 +14404,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="22.8" hidden="1">
+    <row r="492" spans="1:7" ht="23.25" hidden="1">
       <c r="A492" s="192">
         <v>42</v>
       </c>
@@ -14391,7 +14427,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="22.8" hidden="1">
+    <row r="493" spans="1:7" ht="23.25" hidden="1">
       <c r="A493" s="203">
         <v>43</v>
       </c>
@@ -14414,7 +14450,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="22.8" hidden="1">
+    <row r="494" spans="1:7" ht="23.25" hidden="1">
       <c r="A494" s="225">
         <v>44</v>
       </c>
@@ -14437,7 +14473,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="22.8" hidden="1">
+    <row r="495" spans="1:7" ht="23.25" hidden="1">
       <c r="A495" s="192">
         <v>46</v>
       </c>
@@ -14460,7 +14496,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="22.8" hidden="1">
+    <row r="496" spans="1:7" ht="23.25" hidden="1">
       <c r="A496" s="203">
         <v>48</v>
       </c>
@@ -14481,7 +14517,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="22.8" hidden="1">
+    <row r="497" spans="1:7" ht="23.25" hidden="1">
       <c r="A497" s="192">
         <v>50</v>
       </c>
@@ -14504,7 +14540,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="22.8" hidden="1">
+    <row r="498" spans="1:7" ht="23.25" hidden="1">
       <c r="A498" s="192">
         <v>51</v>
       </c>
@@ -14527,7 +14563,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="22.8" hidden="1">
+    <row r="499" spans="1:7" ht="23.25" hidden="1">
       <c r="A499" s="192">
         <v>52</v>
       </c>
@@ -14550,7 +14586,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="22.8" hidden="1">
+    <row r="500" spans="1:7" ht="23.25" hidden="1">
       <c r="A500" s="192">
         <v>58</v>
       </c>
@@ -14573,7 +14609,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="22.8" hidden="1">
+    <row r="501" spans="1:7" ht="23.25" hidden="1">
       <c r="A501" s="192">
         <v>59</v>
       </c>
@@ -14596,7 +14632,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="22.8" hidden="1">
+    <row r="502" spans="1:7" ht="23.25" hidden="1">
       <c r="A502" s="192">
         <v>60</v>
       </c>
@@ -14619,7 +14655,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="22.8" hidden="1">
+    <row r="503" spans="1:7" ht="23.25" hidden="1">
       <c r="A503" s="188">
         <v>1</v>
       </c>
@@ -14642,7 +14678,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="22.8" hidden="1">
+    <row r="504" spans="1:7" ht="23.25" hidden="1">
       <c r="A504" s="192">
         <v>2</v>
       </c>
@@ -14665,7 +14701,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="22.8" hidden="1">
+    <row r="505" spans="1:7" ht="23.25" hidden="1">
       <c r="A505" s="192">
         <v>3</v>
       </c>
@@ -14688,7 +14724,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="22.8" hidden="1">
+    <row r="506" spans="1:7" ht="23.25" hidden="1">
       <c r="A506" s="192">
         <v>5</v>
       </c>
@@ -14711,7 +14747,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="22.8" hidden="1">
+    <row r="507" spans="1:7" ht="23.25" hidden="1">
       <c r="A507" s="192">
         <v>6</v>
       </c>
@@ -14735,7 +14771,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="22.8" hidden="1">
+    <row r="508" spans="1:7" ht="23.25" hidden="1">
       <c r="A508" s="192">
         <v>7</v>
       </c>
@@ -14758,7 +14794,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="22.8" hidden="1">
+    <row r="509" spans="1:7" ht="23.25" hidden="1">
       <c r="A509" s="192">
         <v>8</v>
       </c>
@@ -14782,7 +14818,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="22.8" hidden="1">
+    <row r="510" spans="1:7" ht="23.25" hidden="1">
       <c r="A510" s="192">
         <v>9</v>
       </c>
@@ -14805,7 +14841,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="22.8" hidden="1">
+    <row r="511" spans="1:7" ht="23.25" hidden="1">
       <c r="A511" s="192">
         <v>11</v>
       </c>
@@ -14828,7 +14864,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="22.8" hidden="1">
+    <row r="512" spans="1:7" ht="23.25" hidden="1">
       <c r="A512" s="188">
         <v>12</v>
       </c>
@@ -14851,7 +14887,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="22.8" hidden="1">
+    <row r="513" spans="1:7" ht="23.25" hidden="1">
       <c r="A513" s="192">
         <v>13</v>
       </c>
@@ -14874,7 +14910,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="22.8" hidden="1">
+    <row r="514" spans="1:7" ht="23.25" hidden="1">
       <c r="A514" s="192">
         <v>15</v>
       </c>
@@ -14897,7 +14933,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="22.8" hidden="1">
+    <row r="515" spans="1:7" ht="23.25" hidden="1">
       <c r="A515" s="192">
         <v>16</v>
       </c>
@@ -14920,7 +14956,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="22.8" hidden="1">
+    <row r="516" spans="1:7" ht="23.25" hidden="1">
       <c r="A516" s="192">
         <v>17</v>
       </c>
@@ -14943,7 +14979,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="22.8" hidden="1">
+    <row r="517" spans="1:7" ht="23.25" hidden="1">
       <c r="A517" s="192">
         <v>20</v>
       </c>
@@ -14966,7 +15002,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="22.8" hidden="1">
+    <row r="518" spans="1:7" ht="23.25" hidden="1">
       <c r="A518" s="192">
         <v>21</v>
       </c>
@@ -14989,7 +15025,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="22.8" hidden="1">
+    <row r="519" spans="1:7" ht="23.25" hidden="1">
       <c r="A519" s="192">
         <v>22</v>
       </c>
@@ -15012,7 +15048,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="22.8" hidden="1">
+    <row r="520" spans="1:7" ht="23.25" hidden="1">
       <c r="A520" s="192">
         <v>23</v>
       </c>
@@ -15035,7 +15071,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="45.6" hidden="1">
+    <row r="521" spans="1:7" ht="46.5" hidden="1">
       <c r="A521" s="217">
         <v>24</v>
       </c>
@@ -15058,7 +15094,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="22.8" hidden="1">
+    <row r="522" spans="1:7" ht="23.25" hidden="1">
       <c r="A522" s="192">
         <v>25</v>
       </c>
@@ -15081,7 +15117,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="22.8" hidden="1">
+    <row r="523" spans="1:7" ht="23.25" hidden="1">
       <c r="A523" s="217">
         <v>27</v>
       </c>
@@ -15104,7 +15140,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="22.8" hidden="1">
+    <row r="524" spans="1:7" ht="23.25" hidden="1">
       <c r="A524" s="217">
         <v>28</v>
       </c>
@@ -15127,7 +15163,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="22.8" hidden="1">
+    <row r="525" spans="1:7" ht="23.25" hidden="1">
       <c r="A525" s="208">
         <v>29</v>
       </c>
@@ -15150,7 +15186,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="22.8" hidden="1">
+    <row r="526" spans="1:7" ht="23.25" hidden="1">
       <c r="A526" s="192">
         <v>30</v>
       </c>
@@ -15173,7 +15209,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="22.8" hidden="1">
+    <row r="527" spans="1:7" ht="23.25" hidden="1">
       <c r="A527" s="192">
         <v>31</v>
       </c>
@@ -15196,7 +15232,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="22.8" hidden="1">
+    <row r="528" spans="1:7" ht="23.25" hidden="1">
       <c r="A528" s="203">
         <v>32</v>
       </c>
@@ -15219,7 +15255,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="22.8" hidden="1">
+    <row r="529" spans="1:7" ht="23.25" hidden="1">
       <c r="A529" s="192">
         <v>33</v>
       </c>
@@ -15242,7 +15278,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="22.8" hidden="1">
+    <row r="530" spans="1:7" ht="23.25" hidden="1">
       <c r="A530" s="192">
         <v>34</v>
       </c>
@@ -15265,7 +15301,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="22.8" hidden="1">
+    <row r="531" spans="1:7" ht="23.25" hidden="1">
       <c r="A531" s="192">
         <v>35</v>
       </c>
@@ -15288,7 +15324,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="22.8" hidden="1">
+    <row r="532" spans="1:7" ht="23.25" hidden="1">
       <c r="A532" s="192">
         <v>36</v>
       </c>
@@ -15311,7 +15347,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="22.8" hidden="1">
+    <row r="533" spans="1:7" ht="23.25" hidden="1">
       <c r="A533" s="192">
         <v>37</v>
       </c>
@@ -15334,7 +15370,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="22.8" hidden="1">
+    <row r="534" spans="1:7" ht="23.25" hidden="1">
       <c r="A534" s="188">
         <v>38</v>
       </c>
@@ -15357,7 +15393,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="22.8" hidden="1">
+    <row r="535" spans="1:7" ht="23.25" hidden="1">
       <c r="A535" s="192">
         <v>39</v>
       </c>
@@ -15380,7 +15416,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="22.8" hidden="1">
+    <row r="536" spans="1:7" ht="23.25" hidden="1">
       <c r="A536" s="192">
         <v>40</v>
       </c>
@@ -15403,7 +15439,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="22.8" hidden="1">
+    <row r="537" spans="1:7" ht="23.25" hidden="1">
       <c r="A537" s="192">
         <v>42</v>
       </c>
@@ -15426,7 +15462,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="22.8" hidden="1">
+    <row r="538" spans="1:7" ht="23.25" hidden="1">
       <c r="A538" s="203">
         <v>43</v>
       </c>
@@ -15449,7 +15485,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="22.8" hidden="1">
+    <row r="539" spans="1:7" ht="23.25" hidden="1">
       <c r="A539" s="203">
         <v>44</v>
       </c>
@@ -15472,7 +15508,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="22.8" hidden="1">
+    <row r="540" spans="1:7" ht="23.25" hidden="1">
       <c r="A540" s="192">
         <v>46</v>
       </c>
@@ -15495,7 +15531,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="541" spans="1:7" ht="22.8" hidden="1">
+    <row r="541" spans="1:7" ht="23.25" hidden="1">
       <c r="A541" s="203">
         <v>48</v>
       </c>
@@ -15516,7 +15552,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="22.8" hidden="1">
+    <row r="542" spans="1:7" ht="23.25" hidden="1">
       <c r="A542" s="188">
         <v>50</v>
       </c>
@@ -15539,7 +15575,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="22.8" hidden="1">
+    <row r="543" spans="1:7" ht="23.25" hidden="1">
       <c r="A543" s="192">
         <v>51</v>
       </c>
@@ -15562,7 +15598,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="22.8" hidden="1">
+    <row r="544" spans="1:7" ht="23.25" hidden="1">
       <c r="A544" s="192">
         <v>52</v>
       </c>
@@ -15585,7 +15621,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="22.8" hidden="1">
+    <row r="545" spans="1:7" ht="23.25" hidden="1">
       <c r="A545" s="192">
         <v>58</v>
       </c>
@@ -15608,7 +15644,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="22.8" hidden="1">
+    <row r="546" spans="1:7" ht="23.25" hidden="1">
       <c r="A546" s="192">
         <v>59</v>
       </c>
@@ -15631,7 +15667,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="22.8" hidden="1">
+    <row r="547" spans="1:7" ht="23.25" hidden="1">
       <c r="A547" s="192">
         <v>60</v>
       </c>
@@ -15654,7 +15690,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="548" spans="1:7" ht="22.8" hidden="1">
+    <row r="548" spans="1:7" ht="23.25" hidden="1">
       <c r="A548" s="192">
         <v>1</v>
       </c>
@@ -15677,7 +15713,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="22.8" hidden="1">
+    <row r="549" spans="1:7" ht="23.25" hidden="1">
       <c r="A549" s="192">
         <v>2</v>
       </c>
@@ -15700,7 +15736,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="22.8" hidden="1">
+    <row r="550" spans="1:7" ht="23.25" hidden="1">
       <c r="A550" s="192">
         <v>3</v>
       </c>
@@ -15723,7 +15759,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="22.8" hidden="1">
+    <row r="551" spans="1:7" ht="23.25" hidden="1">
       <c r="A551" s="188">
         <v>5</v>
       </c>
@@ -15746,7 +15782,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="552" spans="1:7" ht="22.8" hidden="1">
+    <row r="552" spans="1:7" ht="23.25" hidden="1">
       <c r="A552" s="192">
         <v>6</v>
       </c>
@@ -15770,7 +15806,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="553" spans="1:7" ht="22.8" hidden="1">
+    <row r="553" spans="1:7" ht="23.25" hidden="1">
       <c r="A553" s="192">
         <v>7</v>
       </c>
@@ -15793,7 +15829,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="554" spans="1:7" ht="22.8" hidden="1">
+    <row r="554" spans="1:7" ht="23.25" hidden="1">
       <c r="A554" s="192">
         <v>8</v>
       </c>
@@ -15817,7 +15853,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="555" spans="1:7" ht="22.8" hidden="1">
+    <row r="555" spans="1:7" ht="23.25" hidden="1">
       <c r="A555" s="192">
         <v>9</v>
       </c>
@@ -15840,7 +15876,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="556" spans="1:7" ht="22.8" hidden="1">
+    <row r="556" spans="1:7" ht="23.25" hidden="1">
       <c r="A556" s="192">
         <v>11</v>
       </c>
@@ -15863,7 +15899,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="557" spans="1:7" ht="22.8" hidden="1">
+    <row r="557" spans="1:7" ht="23.25" hidden="1">
       <c r="A557" s="192">
         <v>12</v>
       </c>
@@ -15886,7 +15922,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="558" spans="1:7" ht="22.8" hidden="1">
+    <row r="558" spans="1:7" ht="23.25" hidden="1">
       <c r="A558" s="192">
         <v>13</v>
       </c>
@@ -15909,7 +15945,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="559" spans="1:7" ht="22.8" hidden="1">
+    <row r="559" spans="1:7" ht="23.25" hidden="1">
       <c r="A559" s="192">
         <v>15</v>
       </c>
@@ -15932,7 +15968,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="22.8" hidden="1">
+    <row r="560" spans="1:7" ht="23.25" hidden="1">
       <c r="A560" s="188">
         <v>16</v>
       </c>
@@ -15955,7 +15991,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="561" spans="1:7" ht="22.8" hidden="1">
+    <row r="561" spans="1:7" ht="23.25" hidden="1">
       <c r="A561" s="192">
         <v>17</v>
       </c>
@@ -15978,7 +16014,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="562" spans="1:7" ht="22.8" hidden="1">
+    <row r="562" spans="1:7" ht="23.25" hidden="1">
       <c r="A562" s="192">
         <v>20</v>
       </c>
@@ -16001,7 +16037,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="563" spans="1:7" ht="22.8" hidden="1">
+    <row r="563" spans="1:7" ht="23.25" hidden="1">
       <c r="A563" s="192">
         <v>21</v>
       </c>
@@ -16024,7 +16060,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="564" spans="1:7" ht="22.8" hidden="1">
+    <row r="564" spans="1:7" ht="23.25" hidden="1">
       <c r="A564" s="192">
         <v>22</v>
       </c>
@@ -16047,7 +16083,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="565" spans="1:7" ht="22.8" hidden="1">
+    <row r="565" spans="1:7" ht="23.25" hidden="1">
       <c r="A565" s="192">
         <v>23</v>
       </c>
@@ -16070,7 +16106,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="566" spans="1:7" ht="45.6" hidden="1">
+    <row r="566" spans="1:7" ht="46.5" hidden="1">
       <c r="A566" s="192">
         <v>24</v>
       </c>
@@ -16093,7 +16129,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="567" spans="1:7" ht="22.8" hidden="1">
+    <row r="567" spans="1:7" ht="23.25" hidden="1">
       <c r="A567" s="192">
         <v>25</v>
       </c>
@@ -16116,7 +16152,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="568" spans="1:7" ht="22.8" hidden="1">
+    <row r="568" spans="1:7" ht="23.25" hidden="1">
       <c r="A568" s="188">
         <v>27</v>
       </c>
@@ -16139,7 +16175,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="569" spans="1:7" ht="22.8" hidden="1">
+    <row r="569" spans="1:7" ht="23.25" hidden="1">
       <c r="A569" s="192">
         <v>28</v>
       </c>
@@ -16162,7 +16198,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="570" spans="1:7" ht="22.8" hidden="1">
+    <row r="570" spans="1:7" ht="23.25" hidden="1">
       <c r="A570" s="192">
         <v>29</v>
       </c>
@@ -16185,7 +16221,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="571" spans="1:7" ht="22.8" hidden="1">
+    <row r="571" spans="1:7" ht="23.25" hidden="1">
       <c r="A571" s="192">
         <v>30</v>
       </c>
@@ -16208,7 +16244,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="572" spans="1:7" ht="22.8" hidden="1">
+    <row r="572" spans="1:7" ht="23.25" hidden="1">
       <c r="A572" s="192">
         <v>31</v>
       </c>
@@ -16231,7 +16267,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="573" spans="1:7" ht="22.8" hidden="1">
+    <row r="573" spans="1:7" ht="23.25" hidden="1">
       <c r="A573" s="203">
         <v>32</v>
       </c>
@@ -16254,7 +16290,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="574" spans="1:7" ht="22.8" hidden="1">
+    <row r="574" spans="1:7" ht="23.25" hidden="1">
       <c r="A574" s="192">
         <v>33</v>
       </c>
@@ -16277,7 +16313,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="575" spans="1:7" ht="22.8" hidden="1">
+    <row r="575" spans="1:7" ht="23.25" hidden="1">
       <c r="A575" s="192">
         <v>34</v>
       </c>
@@ -16300,7 +16336,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="576" spans="1:7" ht="22.8" hidden="1">
+    <row r="576" spans="1:7" ht="23.25" hidden="1">
       <c r="A576" s="192">
         <v>35</v>
       </c>
@@ -16323,7 +16359,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="577" spans="1:7" ht="22.8" hidden="1">
+    <row r="577" spans="1:7" ht="23.25" hidden="1">
       <c r="A577" s="188">
         <v>36</v>
       </c>
@@ -16346,7 +16382,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="578" spans="1:7" ht="22.8" hidden="1">
+    <row r="578" spans="1:7" ht="23.25" hidden="1">
       <c r="A578" s="192">
         <v>37</v>
       </c>
@@ -16369,7 +16405,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="579" spans="1:7" ht="22.8" hidden="1">
+    <row r="579" spans="1:7" ht="23.25" hidden="1">
       <c r="A579" s="192">
         <v>38</v>
       </c>
@@ -16392,7 +16428,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="580" spans="1:7" ht="22.8" hidden="1">
+    <row r="580" spans="1:7" ht="23.25" hidden="1">
       <c r="A580" s="192">
         <v>39</v>
       </c>
@@ -16415,7 +16451,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="581" spans="1:7" ht="22.8" hidden="1">
+    <row r="581" spans="1:7" ht="23.25" hidden="1">
       <c r="A581" s="192">
         <v>40</v>
       </c>
@@ -16438,7 +16474,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="22.8" hidden="1">
+    <row r="582" spans="1:7" ht="23.25" hidden="1">
       <c r="A582" s="192">
         <v>42</v>
       </c>
@@ -16461,7 +16497,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="583" spans="1:7" ht="22.8" hidden="1">
+    <row r="583" spans="1:7" ht="23.25" hidden="1">
       <c r="A583" s="203">
         <v>43</v>
       </c>
@@ -16484,7 +16520,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="584" spans="1:7" ht="22.8" hidden="1">
+    <row r="584" spans="1:7" ht="23.25" hidden="1">
       <c r="A584" s="203">
         <v>44</v>
       </c>
@@ -16507,7 +16543,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="585" spans="1:7" ht="22.8" hidden="1">
+    <row r="585" spans="1:7" ht="23.25" hidden="1">
       <c r="A585" s="192">
         <v>46</v>
       </c>
@@ -16530,7 +16566,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="586" spans="1:7" ht="22.8" hidden="1">
+    <row r="586" spans="1:7" ht="23.25" hidden="1">
       <c r="A586" s="225">
         <v>48</v>
       </c>
@@ -16551,7 +16587,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="22.8" hidden="1">
+    <row r="587" spans="1:7" ht="23.25" hidden="1">
       <c r="A587" s="192">
         <v>50</v>
       </c>
@@ -16574,7 +16610,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="588" spans="1:7" ht="22.8" hidden="1">
+    <row r="588" spans="1:7" ht="23.25" hidden="1">
       <c r="A588" s="192">
         <v>51</v>
       </c>
@@ -16597,7 +16633,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="589" spans="1:7" ht="22.8" hidden="1">
+    <row r="589" spans="1:7" ht="23.25" hidden="1">
       <c r="A589" s="192">
         <v>52</v>
       </c>
@@ -16620,7 +16656,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="590" spans="1:7" ht="22.8" hidden="1">
+    <row r="590" spans="1:7" ht="23.25" hidden="1">
       <c r="A590" s="192">
         <v>58</v>
       </c>
@@ -16643,7 +16679,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="591" spans="1:7" ht="22.8" hidden="1">
+    <row r="591" spans="1:7" ht="23.25" hidden="1">
       <c r="A591" s="192">
         <v>59</v>
       </c>
@@ -16666,7 +16702,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="592" spans="1:7" ht="22.8" hidden="1">
+    <row r="592" spans="1:7" ht="23.25" hidden="1">
       <c r="A592" s="192">
         <v>60</v>
       </c>
@@ -16689,7 +16725,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="22.8" hidden="1">
+    <row r="593" spans="1:7" ht="23.25" hidden="1">
       <c r="A593" s="192">
         <v>1</v>
       </c>
@@ -16712,7 +16748,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="594" spans="1:7" ht="22.8" hidden="1">
+    <row r="594" spans="1:7" ht="23.25" hidden="1">
       <c r="A594" s="192">
         <v>2</v>
       </c>
@@ -16735,7 +16771,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="595" spans="1:7" ht="22.8" hidden="1">
+    <row r="595" spans="1:7" ht="23.25" hidden="1">
       <c r="A595" s="217">
         <v>5</v>
       </c>
@@ -16758,7 +16794,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="596" spans="1:7" ht="22.8" hidden="1">
+    <row r="596" spans="1:7" ht="23.25" hidden="1">
       <c r="A596" s="192">
         <v>6</v>
       </c>
@@ -16782,7 +16818,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="597" spans="1:7" ht="22.8" hidden="1">
+    <row r="597" spans="1:7" ht="23.25" hidden="1">
       <c r="A597" s="217">
         <v>7</v>
       </c>
@@ -16805,7 +16841,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="598" spans="1:7" ht="22.8" hidden="1">
+    <row r="598" spans="1:7" ht="23.25" hidden="1">
       <c r="A598" s="217">
         <v>8</v>
       </c>
@@ -16829,7 +16865,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="22.8" hidden="1">
+    <row r="599" spans="1:7" ht="23.25" hidden="1">
       <c r="A599" s="208">
         <v>9</v>
       </c>
@@ -16852,7 +16888,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="600" spans="1:7" ht="22.8" hidden="1">
+    <row r="600" spans="1:7" ht="23.25" hidden="1">
       <c r="A600" s="192">
         <v>11</v>
       </c>
@@ -16875,7 +16911,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="601" spans="1:7" ht="22.8" hidden="1">
+    <row r="601" spans="1:7" ht="23.25" hidden="1">
       <c r="A601" s="192">
         <v>12</v>
       </c>
@@ -16898,7 +16934,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="602" spans="1:7" ht="22.8" hidden="1">
+    <row r="602" spans="1:7" ht="23.25" hidden="1">
       <c r="A602" s="192">
         <v>13</v>
       </c>
@@ -16921,7 +16957,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="603" spans="1:7" ht="22.8" hidden="1">
+    <row r="603" spans="1:7" ht="23.25" hidden="1">
       <c r="A603" s="192">
         <v>15</v>
       </c>
@@ -16944,7 +16980,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="22.8" hidden="1">
+    <row r="604" spans="1:7" ht="23.25" hidden="1">
       <c r="A604" s="192">
         <v>16</v>
       </c>
@@ -16967,7 +17003,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="22.8" hidden="1">
+    <row r="605" spans="1:7" ht="23.25" hidden="1">
       <c r="A605" s="192">
         <v>17</v>
       </c>
@@ -16990,7 +17026,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="22.8" hidden="1">
+    <row r="606" spans="1:7" ht="23.25" hidden="1">
       <c r="A606" s="192">
         <v>20</v>
       </c>
@@ -17013,7 +17049,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="22.8" hidden="1">
+    <row r="607" spans="1:7" ht="23.25" hidden="1">
       <c r="A607" s="192">
         <v>21</v>
       </c>
@@ -17036,7 +17072,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="608" spans="1:7" ht="22.8" hidden="1">
+    <row r="608" spans="1:7" ht="23.25" hidden="1">
       <c r="A608" s="188">
         <v>22</v>
       </c>
@@ -17059,7 +17095,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="609" spans="1:7" ht="22.8" hidden="1">
+    <row r="609" spans="1:7" ht="23.25" hidden="1">
       <c r="A609" s="192">
         <v>23</v>
       </c>
@@ -17082,7 +17118,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="610" spans="1:7" ht="45.6" hidden="1">
+    <row r="610" spans="1:7" ht="46.5" hidden="1">
       <c r="A610" s="192">
         <v>24</v>
       </c>
@@ -17105,7 +17141,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="611" spans="1:7" ht="22.8" hidden="1">
+    <row r="611" spans="1:7" ht="23.25" hidden="1">
       <c r="A611" s="192">
         <v>25</v>
       </c>
@@ -17128,7 +17164,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="612" spans="1:7" ht="22.8" hidden="1">
+    <row r="612" spans="1:7" ht="23.25" hidden="1">
       <c r="A612" s="192">
         <v>27</v>
       </c>
@@ -17151,7 +17187,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="613" spans="1:7" ht="22.8" hidden="1">
+    <row r="613" spans="1:7" ht="23.25" hidden="1">
       <c r="A613" s="192">
         <v>28</v>
       </c>
@@ -17174,7 +17210,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="614" spans="1:7" ht="22.8" hidden="1">
+    <row r="614" spans="1:7" ht="23.25" hidden="1">
       <c r="A614" s="192">
         <v>29</v>
       </c>
@@ -17197,7 +17233,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="615" spans="1:7" ht="22.8" hidden="1">
+    <row r="615" spans="1:7" ht="23.25" hidden="1">
       <c r="A615" s="192">
         <v>30</v>
       </c>
@@ -17220,7 +17256,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="616" spans="1:7" ht="22.8" hidden="1">
+    <row r="616" spans="1:7" ht="23.25" hidden="1">
       <c r="A616" s="188">
         <v>31</v>
       </c>
@@ -17243,7 +17279,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="617" spans="1:7" ht="22.8" hidden="1">
+    <row r="617" spans="1:7" ht="23.25" hidden="1">
       <c r="A617" s="203">
         <v>32</v>
       </c>
@@ -17266,7 +17302,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="22.8" hidden="1">
+    <row r="618" spans="1:7" ht="23.25" hidden="1">
       <c r="A618" s="192">
         <v>33</v>
       </c>
@@ -17289,7 +17325,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="619" spans="1:7" ht="22.8" hidden="1">
+    <row r="619" spans="1:7" ht="23.25" hidden="1">
       <c r="A619" s="192">
         <v>34</v>
       </c>
@@ -17312,7 +17348,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="620" spans="1:7" ht="22.8" hidden="1">
+    <row r="620" spans="1:7" ht="23.25" hidden="1">
       <c r="A620" s="192">
         <v>35</v>
       </c>
@@ -17335,7 +17371,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="621" spans="1:7" ht="22.8" hidden="1">
+    <row r="621" spans="1:7" ht="23.25" hidden="1">
       <c r="A621" s="192">
         <v>36</v>
       </c>
@@ -17358,7 +17394,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="622" spans="1:7" ht="22.8" hidden="1">
+    <row r="622" spans="1:7" ht="23.25" hidden="1">
       <c r="A622" s="192">
         <v>37</v>
       </c>
@@ -17381,7 +17417,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="623" spans="1:7" ht="22.8" hidden="1">
+    <row r="623" spans="1:7" ht="23.25" hidden="1">
       <c r="A623" s="192">
         <v>38</v>
       </c>
@@ -17404,7 +17440,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="624" spans="1:7" ht="22.8" hidden="1">
+    <row r="624" spans="1:7" ht="23.25" hidden="1">
       <c r="A624" s="192">
         <v>39</v>
       </c>
@@ -17427,7 +17463,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="625" spans="1:7" ht="22.8" hidden="1">
+    <row r="625" spans="1:7" ht="23.25" hidden="1">
       <c r="A625" s="188">
         <v>40</v>
       </c>
@@ -17450,7 +17486,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="626" spans="1:7" ht="22.8" hidden="1">
+    <row r="626" spans="1:7" ht="23.25" hidden="1">
       <c r="A626" s="192">
         <v>42</v>
       </c>
@@ -17473,7 +17509,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="627" spans="1:7" ht="22.8" hidden="1">
+    <row r="627" spans="1:7" ht="23.25" hidden="1">
       <c r="A627" s="203">
         <v>43</v>
       </c>
@@ -17496,7 +17532,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="628" spans="1:7" ht="22.8" hidden="1">
+    <row r="628" spans="1:7" ht="23.25" hidden="1">
       <c r="A628" s="203">
         <v>44</v>
       </c>
@@ -17519,7 +17555,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="629" spans="1:7" ht="22.8" hidden="1">
+    <row r="629" spans="1:7" ht="23.25" hidden="1">
       <c r="A629" s="192">
         <v>46</v>
       </c>
@@ -17542,7 +17578,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="630" spans="1:7" ht="22.8" hidden="1">
+    <row r="630" spans="1:7" ht="23.25" hidden="1">
       <c r="A630" s="203">
         <v>48</v>
       </c>
@@ -17563,7 +17599,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="631" spans="1:7" ht="22.8" hidden="1">
+    <row r="631" spans="1:7" ht="23.25" hidden="1">
       <c r="A631" s="192">
         <v>50</v>
       </c>
@@ -17586,7 +17622,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="632" spans="1:7" ht="22.8" hidden="1">
+    <row r="632" spans="1:7" ht="23.25" hidden="1">
       <c r="A632" s="192">
         <v>51</v>
       </c>
@@ -17609,7 +17645,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="633" spans="1:7" ht="22.8" hidden="1">
+    <row r="633" spans="1:7" ht="23.25" hidden="1">
       <c r="A633" s="192">
         <v>52</v>
       </c>
@@ -17632,7 +17668,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="634" spans="1:7" ht="22.8" hidden="1">
+    <row r="634" spans="1:7" ht="23.25" hidden="1">
       <c r="A634" s="188">
         <v>58</v>
       </c>
@@ -17655,7 +17691,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="635" spans="1:7" ht="22.8" hidden="1">
+    <row r="635" spans="1:7" ht="23.25" hidden="1">
       <c r="A635" s="192">
         <v>59</v>
       </c>
@@ -17678,7 +17714,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="636" spans="1:7" ht="22.8" hidden="1">
+    <row r="636" spans="1:7" ht="23.25" hidden="1">
       <c r="A636" s="192">
         <v>60</v>
       </c>
@@ -17701,14 +17737,14 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="637" spans="1:7" ht="46.2" customHeight="1">
-      <c r="F637" s="319">
+    <row r="637" spans="1:7" ht="46.15" customHeight="1">
+      <c r="F637" s="304">
         <f>SUBTOTAL(9,F6:F636)</f>
         <v>49200</v>
       </c>
     </row>
-    <row r="638" spans="1:7" ht="46.2" customHeight="1"/>
-    <row r="639" spans="1:7" ht="46.2" customHeight="1"/>
+    <row r="638" spans="1:7" ht="46.15" customHeight="1"/>
+    <row r="639" spans="1:7" ht="46.15" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A5:G636" xr:uid="{51717A2D-38D8-4ABE-BD5F-98B6647922FB}">
     <filterColumn colId="6">
@@ -17727,34 +17763,34 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AM81"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2"/>
+  <dimension ref="A1:AM90"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="22.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" style="3" customWidth="1"/>
-    <col min="8" max="9" width="17.77734375" style="3" customWidth="1"/>
+    <col min="8" max="9" width="17.83203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="18" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.6640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="20.109375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.77734375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" style="3" customWidth="1"/>
     <col min="14" max="14" width="21.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="18.44140625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.5" style="3" customWidth="1"/>
     <col min="16" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="17.6640625" customWidth="1"/>
     <col min="19" max="19" width="21.33203125" customWidth="1"/>
-    <col min="20" max="21" width="16.77734375" customWidth="1"/>
+    <col min="20" max="21" width="16.83203125" customWidth="1"/>
     <col min="22" max="23" width="17.33203125" customWidth="1"/>
-    <col min="24" max="33" width="18.44140625" customWidth="1"/>
-    <col min="34" max="34" width="91.77734375" customWidth="1"/>
-    <col min="35" max="35" width="18.44140625" customWidth="1"/>
-    <col min="36" max="36" width="19.109375" customWidth="1"/>
+    <col min="24" max="33" width="18.5" customWidth="1"/>
+    <col min="34" max="34" width="91.83203125" customWidth="1"/>
+    <col min="35" max="35" width="18.5" customWidth="1"/>
+    <col min="36" max="36" width="19.1640625" customWidth="1"/>
     <col min="37" max="38" width="18.6640625" customWidth="1"/>
-    <col min="39" max="39" width="18.77734375" customWidth="1"/>
+    <col min="39" max="39" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="20.100000000000001" customHeight="1">
@@ -17859,7 +17895,7 @@
       <c r="AL3" s="6"/>
       <c r="AM3" s="7"/>
     </row>
-    <row r="4" spans="1:39" ht="44.4" customHeight="1">
+    <row r="4" spans="1:39" ht="44.45" customHeight="1">
       <c r="A4" s="161" t="s">
         <v>5</v>
       </c>
@@ -21815,13 +21851,13 @@
       <c r="J57" s="115">
         <v>1300</v>
       </c>
-      <c r="K57" s="320">
+      <c r="K57" s="305">
         <v>45938</v>
       </c>
       <c r="L57" s="115">
         <v>1300</v>
       </c>
-      <c r="M57" s="320">
+      <c r="M57" s="305">
         <v>45938</v>
       </c>
       <c r="N57" s="74">
@@ -22966,7 +23002,7 @@
       <c r="AG76" s="70"/>
       <c r="AH76" s="41"/>
     </row>
-    <row r="77" spans="1:34" ht="26.4" customHeight="1">
+    <row r="77" spans="1:34" ht="26.45" customHeight="1">
       <c r="A77" s="22"/>
       <c r="B77" s="177" t="s">
         <v>3</v>
@@ -23012,57 +23048,57 @@
       <c r="C78" s="172"/>
       <c r="D78" s="172"/>
       <c r="E78" s="172"/>
-      <c r="F78" s="28">
+      <c r="F78" s="332">
         <f>SUM(F6:F77)</f>
         <v>55200</v>
       </c>
       <c r="G78" s="28"/>
-      <c r="H78" s="28">
+      <c r="H78" s="332">
         <f t="shared" ref="H78:AH78" si="0">SUM(H6:H77)</f>
         <v>55200</v>
       </c>
       <c r="I78" s="28"/>
-      <c r="J78" s="28">
+      <c r="J78" s="332">
         <f t="shared" si="0"/>
         <v>54100</v>
       </c>
       <c r="K78" s="28"/>
-      <c r="L78" s="28">
+      <c r="L78" s="332">
         <f t="shared" si="0"/>
         <v>71300</v>
       </c>
       <c r="M78" s="28"/>
-      <c r="N78" s="28">
+      <c r="N78" s="332">
         <f t="shared" si="0"/>
         <v>57700</v>
       </c>
       <c r="O78" s="28"/>
-      <c r="P78" s="28">
+      <c r="P78" s="332">
         <f t="shared" si="0"/>
         <v>57700</v>
       </c>
       <c r="Q78" s="13"/>
-      <c r="R78" s="28">
-        <f t="shared" si="0"/>
+      <c r="R78" s="332">
+        <f>SUM(R6:R77)</f>
         <v>78900</v>
       </c>
       <c r="S78" s="13"/>
-      <c r="T78" s="28">
+      <c r="T78" s="332">
         <f t="shared" si="0"/>
         <v>68500</v>
       </c>
       <c r="U78" s="13"/>
-      <c r="V78" s="28">
-        <f t="shared" si="0"/>
+      <c r="V78" s="332">
+        <f>SUM(V6:V77)</f>
         <v>71000</v>
       </c>
       <c r="W78" s="13"/>
-      <c r="X78" s="28">
+      <c r="X78" s="332">
         <f t="shared" si="0"/>
         <v>65800</v>
       </c>
       <c r="Y78" s="13"/>
-      <c r="Z78" s="28">
+      <c r="Z78" s="332">
         <f t="shared" si="0"/>
         <v>66000</v>
       </c>
@@ -23070,7 +23106,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB78" s="28">
+      <c r="AB78" s="332">
         <f t="shared" si="0"/>
         <v>66000</v>
       </c>
@@ -23078,7 +23114,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AD78" s="28">
+      <c r="AD78" s="332">
         <f t="shared" ref="AD78:AE78" si="1">SUM(AD6:AD77)</f>
         <v>66000</v>
       </c>
@@ -23095,11 +23131,11 @@
         <v>0</v>
       </c>
       <c r="AH78" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:34" ht="24.6">
+        <f>SUM(F78:AG78)</f>
+        <v>898200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:34" ht="25.5">
       <c r="F80" s="169">
         <v>45748</v>
       </c>
@@ -23157,7 +23193,7 @@
       </c>
       <c r="AG80" s="159"/>
     </row>
-    <row r="81" spans="1:17" ht="32.4" customHeight="1">
+    <row r="81" spans="1:22" ht="32.450000000000003" customHeight="1">
       <c r="A81" s="176" t="s">
         <v>22</v>
       </c>
@@ -23180,6 +23216,17 @@
       <c r="O81" s="182"/>
       <c r="P81" s="182"/>
       <c r="Q81" s="182"/>
+    </row>
+    <row r="83" spans="1:22">
+      <c r="V83">
+        <v>69500</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
+      <c r="R90">
+        <f>P78+R74+R76</f>
+        <v>68100</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -23195,21 +23242,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388B0986-349B-4B1A-860F-2315B64A4EE8}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="52.5" customHeight="1">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="306" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-    </row>
-    <row r="3" spans="1:4" ht="26.4" customHeight="1">
+      <c r="B1" s="306"/>
+      <c r="C1" s="306"/>
+    </row>
+    <row r="3" spans="1:4" ht="26.45" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>129</v>
       </c>
@@ -23227,7 +23274,7 @@
       <c r="B4" s="72">
         <v>45748</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="331">
         <f>'Details MC1 '!F78</f>
         <v>55200</v>
       </c>
@@ -23331,7 +23378,7 @@
         <v>71000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.6">
+    <row r="13" spans="1:4" ht="15.75">
       <c r="A13" s="48">
         <v>10</v>
       </c>
@@ -23343,7 +23390,7 @@
         <v>65800</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.6">
+    <row r="14" spans="1:4" ht="15.75">
       <c r="A14" s="48">
         <v>11</v>
       </c>
@@ -23355,7 +23402,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.6">
+    <row r="15" spans="1:4" ht="15.75">
       <c r="A15" s="129">
         <v>12</v>
       </c>
@@ -23367,7 +23414,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.6">
+    <row r="16" spans="1:4" ht="15.75">
       <c r="A16" s="129">
         <v>13</v>
       </c>
@@ -23379,7 +23426,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6">
+    <row r="17" spans="1:3" ht="15.75">
       <c r="A17" s="129">
         <v>14</v>
       </c>
@@ -23402,146 +23449,147 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810C1D33-6CDF-4F26-B97B-E4FC71263824}">
-  <dimension ref="A1:BA137"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <dimension ref="A1:BB137"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="58.109375" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
-    <col min="5" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="18.77734375" customWidth="1"/>
-    <col min="18" max="20" width="14.44140625" customWidth="1"/>
-    <col min="21" max="21" width="18.77734375" customWidth="1"/>
-    <col min="22" max="24" width="14.44140625" customWidth="1"/>
-    <col min="25" max="25" width="18.77734375" customWidth="1"/>
-    <col min="26" max="28" width="14.44140625" customWidth="1"/>
-    <col min="29" max="29" width="18.77734375" customWidth="1"/>
-    <col min="30" max="32" width="14.44140625" customWidth="1"/>
-    <col min="33" max="33" width="18.77734375" customWidth="1"/>
-    <col min="34" max="36" width="14.44140625" customWidth="1"/>
-    <col min="37" max="37" width="18.77734375" customWidth="1"/>
-    <col min="38" max="40" width="14.44140625" customWidth="1"/>
-    <col min="41" max="41" width="18.77734375" customWidth="1"/>
-    <col min="42" max="44" width="14.44140625" customWidth="1"/>
-    <col min="45" max="45" width="18.77734375" customWidth="1"/>
-    <col min="46" max="48" width="14.44140625" customWidth="1"/>
-    <col min="49" max="49" width="18.77734375" customWidth="1"/>
-    <col min="50" max="52" width="14.44140625" customWidth="1"/>
-    <col min="53" max="53" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="58.1640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="16" width="14.5" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="20" width="14.5" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="24" width="14.5" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="26" max="28" width="14.5" customWidth="1"/>
+    <col min="29" max="29" width="18.83203125" customWidth="1"/>
+    <col min="30" max="32" width="14.5" customWidth="1"/>
+    <col min="33" max="33" width="18.83203125" customWidth="1"/>
+    <col min="34" max="36" width="14.5" customWidth="1"/>
+    <col min="37" max="37" width="18.83203125" customWidth="1"/>
+    <col min="38" max="40" width="14.5" customWidth="1"/>
+    <col min="41" max="41" width="18.83203125" customWidth="1"/>
+    <col min="42" max="44" width="14.5" customWidth="1"/>
+    <col min="45" max="45" width="18.83203125" customWidth="1"/>
+    <col min="46" max="48" width="14.5" customWidth="1"/>
+    <col min="49" max="49" width="18.83203125" customWidth="1"/>
+    <col min="50" max="52" width="14.5" customWidth="1"/>
+    <col min="53" max="53" width="22.1640625" customWidth="1"/>
+    <col min="54" max="54" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="29.1" customHeight="1">
-      <c r="A1" s="313" t="s">
+      <c r="A1" s="309" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="314"/>
-      <c r="C1" s="314"/>
-      <c r="D1" s="314"/>
-      <c r="E1" s="314"/>
-      <c r="F1" s="314"/>
-      <c r="G1" s="314"/>
-      <c r="H1" s="314"/>
-      <c r="I1" s="314"/>
-      <c r="J1" s="314"/>
-      <c r="K1" s="314"/>
-      <c r="L1" s="314"/>
-      <c r="M1" s="314"/>
-      <c r="N1" s="314"/>
-      <c r="O1" s="314"/>
-      <c r="P1" s="314"/>
-      <c r="Q1" s="314"/>
+      <c r="B1" s="310"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
+      <c r="J1" s="310"/>
+      <c r="K1" s="310"/>
+      <c r="L1" s="310"/>
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
     </row>
     <row r="2" spans="1:53" ht="31.5" customHeight="1">
-      <c r="A2" s="315" t="s">
+      <c r="A2" s="311" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="317" t="s">
+      <c r="B2" s="313" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="307" t="s">
+      <c r="C2" s="314" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="308"/>
-      <c r="E2" s="305" t="s">
+      <c r="D2" s="315"/>
+      <c r="E2" s="316" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="306"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="307" t="s">
+      <c r="F2" s="317"/>
+      <c r="G2" s="318"/>
+      <c r="H2" s="314" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="308"/>
-      <c r="J2" s="309"/>
-      <c r="K2" s="305" t="s">
+      <c r="I2" s="315"/>
+      <c r="J2" s="319"/>
+      <c r="K2" s="316" t="s">
         <v>146</v>
       </c>
-      <c r="L2" s="306"/>
-      <c r="M2" s="312"/>
-      <c r="N2" s="307" t="s">
+      <c r="L2" s="317"/>
+      <c r="M2" s="318"/>
+      <c r="N2" s="314" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="308"/>
-      <c r="P2" s="308"/>
-      <c r="Q2" s="309"/>
-      <c r="R2" s="305" t="s">
+      <c r="O2" s="315"/>
+      <c r="P2" s="315"/>
+      <c r="Q2" s="319"/>
+      <c r="R2" s="316" t="s">
         <v>168</v>
       </c>
-      <c r="S2" s="306"/>
-      <c r="T2" s="306"/>
-      <c r="U2" s="306"/>
-      <c r="V2" s="310" t="s">
+      <c r="S2" s="317"/>
+      <c r="T2" s="317"/>
+      <c r="U2" s="317"/>
+      <c r="V2" s="307" t="s">
         <v>182</v>
       </c>
-      <c r="W2" s="311"/>
-      <c r="X2" s="311"/>
-      <c r="Y2" s="311"/>
-      <c r="Z2" s="310" t="s">
+      <c r="W2" s="308"/>
+      <c r="X2" s="308"/>
+      <c r="Y2" s="308"/>
+      <c r="Z2" s="307" t="s">
         <v>187</v>
       </c>
-      <c r="AA2" s="311"/>
-      <c r="AB2" s="311"/>
-      <c r="AC2" s="311"/>
-      <c r="AD2" s="310" t="s">
+      <c r="AA2" s="308"/>
+      <c r="AB2" s="308"/>
+      <c r="AC2" s="308"/>
+      <c r="AD2" s="307" t="s">
         <v>188</v>
       </c>
-      <c r="AE2" s="311"/>
-      <c r="AF2" s="311"/>
-      <c r="AG2" s="311"/>
-      <c r="AH2" s="310" t="s">
+      <c r="AE2" s="308"/>
+      <c r="AF2" s="308"/>
+      <c r="AG2" s="308"/>
+      <c r="AH2" s="307" t="s">
         <v>190</v>
       </c>
-      <c r="AI2" s="311"/>
-      <c r="AJ2" s="311"/>
-      <c r="AK2" s="311"/>
-      <c r="AL2" s="310" t="s">
+      <c r="AI2" s="308"/>
+      <c r="AJ2" s="308"/>
+      <c r="AK2" s="308"/>
+      <c r="AL2" s="307" t="s">
         <v>215</v>
       </c>
-      <c r="AM2" s="311"/>
-      <c r="AN2" s="311"/>
-      <c r="AO2" s="311"/>
-      <c r="AP2" s="310" t="s">
+      <c r="AM2" s="308"/>
+      <c r="AN2" s="308"/>
+      <c r="AO2" s="308"/>
+      <c r="AP2" s="307" t="s">
         <v>216</v>
       </c>
-      <c r="AQ2" s="311"/>
-      <c r="AR2" s="311"/>
-      <c r="AS2" s="311"/>
-      <c r="AT2" s="310" t="s">
+      <c r="AQ2" s="308"/>
+      <c r="AR2" s="308"/>
+      <c r="AS2" s="308"/>
+      <c r="AT2" s="307" t="s">
         <v>226</v>
       </c>
-      <c r="AU2" s="311"/>
-      <c r="AV2" s="311"/>
-      <c r="AW2" s="311"/>
-      <c r="AX2" s="310" t="s">
+      <c r="AU2" s="308"/>
+      <c r="AV2" s="308"/>
+      <c r="AW2" s="308"/>
+      <c r="AX2" s="307" t="s">
         <v>227</v>
       </c>
-      <c r="AY2" s="311"/>
-      <c r="AZ2" s="311"/>
-      <c r="BA2" s="311"/>
+      <c r="AY2" s="308"/>
+      <c r="AZ2" s="308"/>
+      <c r="BA2" s="308"/>
     </row>
     <row r="3" spans="1:53" ht="45.75" customHeight="1">
-      <c r="A3" s="316"/>
-      <c r="B3" s="317"/>
+      <c r="A3" s="312"/>
+      <c r="B3" s="313"/>
       <c r="C3" s="76" t="s">
         <v>149</v>
       </c>
@@ -23696,7 +23744,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="44.4" customHeight="1">
+    <row r="4" spans="1:53" ht="44.45" customHeight="1">
       <c r="A4" s="78">
         <v>1</v>
       </c>
@@ -23718,7 +23766,7 @@
         <v>45843</v>
       </c>
       <c r="M4" s="104"/>
-      <c r="N4" s="112">
+      <c r="N4" s="325">
         <v>5500</v>
       </c>
       <c r="O4" s="104">
@@ -23801,7 +23849,7 @@
       <c r="AZ4" s="104"/>
       <c r="BA4" s="85"/>
     </row>
-    <row r="5" spans="1:53" ht="44.4" customHeight="1">
+    <row r="5" spans="1:53" ht="44.45" customHeight="1">
       <c r="A5" s="86">
         <v>2</v>
       </c>
@@ -23823,7 +23871,7 @@
         <v>45843</v>
       </c>
       <c r="M5" s="104"/>
-      <c r="N5" s="112">
+      <c r="N5" s="325">
         <v>10000</v>
       </c>
       <c r="O5" s="104">
@@ -23893,7 +23941,7 @@
       <c r="AS5" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="AT5" s="112">
+      <c r="AT5" s="330">
         <v>15000</v>
       </c>
       <c r="AU5" s="104">
@@ -23910,7 +23958,7 @@
       <c r="AZ5" s="104"/>
       <c r="BA5" s="85"/>
     </row>
-    <row r="6" spans="1:53" ht="44.4" customHeight="1">
+    <row r="6" spans="1:53" ht="44.45" customHeight="1">
       <c r="A6" s="86">
         <v>3</v>
       </c>
@@ -23922,7 +23970,7 @@
       <c r="E6" s="82"/>
       <c r="F6" s="88"/>
       <c r="G6" s="88"/>
-      <c r="H6" s="82">
+      <c r="H6" s="322">
         <v>1500</v>
       </c>
       <c r="I6" s="104">
@@ -23936,7 +23984,7 @@
         <v>45842</v>
       </c>
       <c r="M6" s="104"/>
-      <c r="N6" s="112">
+      <c r="N6" s="325">
         <v>1500</v>
       </c>
       <c r="O6" s="104">
@@ -24002,7 +24050,7 @@
       <c r="AS6" s="90" t="s">
         <v>223</v>
       </c>
-      <c r="AT6" s="112">
+      <c r="AT6" s="330">
         <f>1500+1000</f>
         <v>2500</v>
       </c>
@@ -24040,7 +24088,7 @@
         <v>45790</v>
       </c>
       <c r="G7" s="104"/>
-      <c r="H7" s="82">
+      <c r="H7" s="323">
         <f>18393+226</f>
         <v>18619</v>
       </c>
@@ -24057,7 +24105,7 @@
         <v>45847</v>
       </c>
       <c r="M7" s="104"/>
-      <c r="N7" s="113">
+      <c r="N7" s="324">
         <v>10010</v>
       </c>
       <c r="O7" s="104">
@@ -24138,7 +24186,7 @@
       <c r="AZ7" s="104"/>
       <c r="BA7" s="90"/>
     </row>
-    <row r="8" spans="1:53" ht="44.4" customHeight="1">
+    <row r="8" spans="1:53" ht="44.45" customHeight="1">
       <c r="A8" s="86">
         <v>5</v>
       </c>
@@ -24254,7 +24302,7 @@
         <v>45857</v>
       </c>
       <c r="M9" s="152"/>
-      <c r="N9" s="146">
+      <c r="N9" s="326">
         <v>155</v>
       </c>
       <c r="O9" s="152">
@@ -24447,7 +24495,7 @@
       <c r="K11" s="147"/>
       <c r="L11" s="153"/>
       <c r="M11" s="153"/>
-      <c r="N11" s="82">
+      <c r="N11" s="322">
         <v>525</v>
       </c>
       <c r="O11" s="104">
@@ -24510,7 +24558,7 @@
       <c r="AZ11" s="104"/>
       <c r="BA11" s="114"/>
     </row>
-    <row r="12" spans="1:53" ht="44.4" customHeight="1">
+    <row r="12" spans="1:53" ht="44.45" customHeight="1">
       <c r="A12" s="139"/>
       <c r="B12" s="136" t="s">
         <v>156</v>
@@ -24526,7 +24574,7 @@
       <c r="K12" s="148"/>
       <c r="L12" s="154"/>
       <c r="M12" s="154"/>
-      <c r="N12" s="82">
+      <c r="N12" s="322">
         <v>376</v>
       </c>
       <c r="O12" s="104">
@@ -24642,7 +24690,7 @@
       <c r="AZ13" s="104"/>
       <c r="BA13" s="90"/>
     </row>
-    <row r="14" spans="1:53" ht="44.4" customHeight="1">
+    <row r="14" spans="1:53" ht="44.45" customHeight="1">
       <c r="A14" s="94">
         <v>8</v>
       </c>
@@ -24654,7 +24702,7 @@
       <c r="E14" s="82"/>
       <c r="F14" s="83"/>
       <c r="G14" s="83"/>
-      <c r="H14" s="82">
+      <c r="H14" s="322">
         <v>1000</v>
       </c>
       <c r="I14" s="89">
@@ -24664,7 +24712,7 @@
       <c r="K14" s="82"/>
       <c r="L14" s="104"/>
       <c r="M14" s="104"/>
-      <c r="N14" s="82">
+      <c r="N14" s="322">
         <v>50</v>
       </c>
       <c r="O14" s="104">
@@ -24715,7 +24763,7 @@
       <c r="AZ14" s="104"/>
       <c r="BA14" s="90"/>
     </row>
-    <row r="15" spans="1:53" ht="44.4" customHeight="1">
+    <row r="15" spans="1:53" ht="44.45" customHeight="1">
       <c r="A15" s="94">
         <v>9</v>
       </c>
@@ -24727,7 +24775,7 @@
       <c r="E15" s="82"/>
       <c r="F15" s="83"/>
       <c r="G15" s="83"/>
-      <c r="H15" s="82">
+      <c r="H15" s="322">
         <v>11500</v>
       </c>
       <c r="I15" s="89">
@@ -24778,7 +24826,7 @@
       <c r="AZ15" s="104"/>
       <c r="BA15" s="85"/>
     </row>
-    <row r="16" spans="1:53" ht="44.4" customHeight="1">
+    <row r="16" spans="1:53" ht="44.45" customHeight="1">
       <c r="A16" s="96">
         <v>10</v>
       </c>
@@ -24847,7 +24895,7 @@
       <c r="AZ16" s="104"/>
       <c r="BA16" s="85"/>
     </row>
-    <row r="17" spans="1:53" ht="44.4" customHeight="1">
+    <row r="17" spans="1:54" ht="44.45" customHeight="1">
       <c r="A17" s="121">
         <v>11</v>
       </c>
@@ -24859,7 +24907,7 @@
       <c r="E17" s="82"/>
       <c r="F17" s="83"/>
       <c r="G17" s="83"/>
-      <c r="H17" s="82">
+      <c r="H17" s="322">
         <v>95</v>
       </c>
       <c r="I17" s="89">
@@ -24916,7 +24964,7 @@
       <c r="AS17" s="130" t="s">
         <v>230</v>
       </c>
-      <c r="AT17" s="112">
+      <c r="AT17" s="330">
         <v>3300</v>
       </c>
       <c r="AU17" s="104">
@@ -24931,7 +24979,7 @@
       <c r="AZ17" s="104"/>
       <c r="BA17" s="127"/>
     </row>
-    <row r="18" spans="1:53" ht="55.5" customHeight="1">
+    <row r="18" spans="1:54" ht="55.5" customHeight="1">
       <c r="A18" s="123">
         <v>12</v>
       </c>
@@ -24949,7 +24997,7 @@
       <c r="K18" s="82"/>
       <c r="L18" s="104"/>
       <c r="M18" s="104"/>
-      <c r="N18" s="82">
+      <c r="N18" s="322">
         <v>1537</v>
       </c>
       <c r="O18" s="104"/>
@@ -25020,7 +25068,7 @@
       <c r="AS18" s="131" t="s">
         <v>231</v>
       </c>
-      <c r="AT18" s="112">
+      <c r="AT18" s="330">
         <f>3000+1055</f>
         <v>4055</v>
       </c>
@@ -25036,7 +25084,7 @@
       <c r="AZ18" s="104"/>
       <c r="BA18" s="127"/>
     </row>
-    <row r="19" spans="1:53" ht="55.5" customHeight="1">
+    <row r="19" spans="1:54" ht="55.5" customHeight="1">
       <c r="A19" s="123">
         <v>13</v>
       </c>
@@ -25107,7 +25155,7 @@
       <c r="AZ19" s="104"/>
       <c r="BA19" s="90"/>
     </row>
-    <row r="20" spans="1:53" ht="55.5" customHeight="1">
+    <row r="20" spans="1:54" ht="55.5" customHeight="1">
       <c r="A20" s="123">
         <v>14</v>
       </c>
@@ -25184,18 +25232,91 @@
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="22" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="23" spans="1:53" ht="29.85" customHeight="1"/>
-    <row r="24" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="25" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="26" spans="1:53" ht="19.5" customHeight="1"/>
-    <row r="27" spans="1:53" ht="18" customHeight="1"/>
-    <row r="28" spans="1:53" ht="28.5" customHeight="1"/>
-    <row r="29" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="30" spans="1:53" ht="31.5" customHeight="1"/>
-    <row r="31" spans="1:53" ht="32.4" customHeight="1"/>
-    <row r="32" spans="1:53" ht="21" customHeight="1"/>
+    <row r="21" spans="1:54" ht="31.5" customHeight="1">
+      <c r="E21" s="327">
+        <f>SUM(E4:E20)</f>
+        <v>23533</v>
+      </c>
+      <c r="H21" s="327">
+        <f>SUM(H4:H20)</f>
+        <v>32714</v>
+      </c>
+      <c r="K21" s="327">
+        <f>SUM(K4:K20)</f>
+        <v>32385</v>
+      </c>
+      <c r="N21" s="327">
+        <f>SUM(N4:N20)</f>
+        <v>29653</v>
+      </c>
+      <c r="R21" s="327">
+        <f>SUM(R4:R20)</f>
+        <v>45523</v>
+      </c>
+      <c r="V21" s="327">
+        <f>SUM(V4:V20)</f>
+        <v>41892</v>
+      </c>
+      <c r="Z21" s="327">
+        <f>SUM(Z4:Z20)</f>
+        <v>41396</v>
+      </c>
+      <c r="AD21" s="327">
+        <f>SUM(AD4:AD20)</f>
+        <v>56463</v>
+      </c>
+      <c r="AH21" s="327">
+        <f>SUM(AH4:AH20)</f>
+        <v>57882</v>
+      </c>
+      <c r="AL21" s="327">
+        <f>SUM(AL4:AL20)</f>
+        <v>76927</v>
+      </c>
+      <c r="AP21" s="327">
+        <f>SUM(AP4:AP20)</f>
+        <v>61966</v>
+      </c>
+      <c r="AT21" s="327">
+        <f>SUM(AT4:AT20)</f>
+        <v>48553</v>
+      </c>
+      <c r="AX21" s="327">
+        <f>SUM(AX4:AX20)</f>
+        <v>53967</v>
+      </c>
+      <c r="BB21" s="321">
+        <f>SUM(E21:BA21)</f>
+        <v>602854</v>
+      </c>
+    </row>
+    <row r="22" spans="1:54" ht="31.5" customHeight="1"/>
+    <row r="23" spans="1:54" ht="29.85" customHeight="1">
+      <c r="AP23" s="328">
+        <v>62416</v>
+      </c>
+      <c r="AT23" s="328">
+        <v>48103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:54" ht="19.5" customHeight="1">
+      <c r="AP24" s="328">
+        <f>AP23-AP21</f>
+        <v>450</v>
+      </c>
+      <c r="AT24" s="329">
+        <f>AT21-AT23</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="1:54" ht="19.5" customHeight="1"/>
+    <row r="26" spans="1:54" ht="19.5" customHeight="1"/>
+    <row r="27" spans="1:54" ht="18" customHeight="1"/>
+    <row r="28" spans="1:54" ht="28.5" customHeight="1"/>
+    <row r="29" spans="1:54" ht="31.5" customHeight="1"/>
+    <row r="30" spans="1:54" ht="31.5" customHeight="1"/>
+    <row r="31" spans="1:54" ht="32.450000000000003" customHeight="1"/>
+    <row r="32" spans="1:54" ht="21" customHeight="1"/>
     <row r="33" ht="21" customHeight="1"/>
     <row r="34" ht="21" customHeight="1"/>
     <row r="35" ht="21" customHeight="1"/>
@@ -25204,17 +25325,27 @@
     <row r="38" ht="21" customHeight="1"/>
     <row r="39" ht="18" customHeight="1"/>
     <row r="40" ht="30.6" customHeight="1"/>
-    <row r="52" ht="30.9" customHeight="1"/>
-    <row r="64" ht="27.9" customHeight="1"/>
+    <row r="52" ht="30.95" customHeight="1"/>
+    <row r="64" ht="27.95" customHeight="1"/>
     <row r="76" ht="30" customHeight="1"/>
     <row r="88" ht="31.5" customHeight="1"/>
-    <row r="100" ht="27.9" customHeight="1"/>
+    <row r="100" ht="27.95" customHeight="1"/>
     <row r="112" ht="31.5" customHeight="1"/>
-    <row r="124" ht="32.4" customHeight="1"/>
-    <row r="136" ht="27.9" customHeight="1"/>
+    <row r="124" ht="32.450000000000003" customHeight="1"/>
+    <row r="136" ht="27.95" customHeight="1"/>
     <row r="137" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="R2:U2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="V2:Y2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="AT2:AW2"/>
     <mergeCell ref="AX2:BA2"/>
     <mergeCell ref="Z2:AC2"/>
@@ -25222,16 +25353,6 @@
     <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AP2:AS2"/>
     <mergeCell ref="AL2:AO2"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="R2:U2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="V2:Y2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
@@ -25241,20 +25362,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D65A7D1A-A130-4CF2-8F53-8DE497F18C35}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="3" max="3" width="9.44140625" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.8">
+    <row r="1" spans="1:6" ht="23.25">
       <c r="A1" s="97" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="39.6">
+    <row r="3" spans="1:6" ht="38.25">
       <c r="A3" s="45" t="s">
         <v>164</v>
       </c>
@@ -25610,11 +25731,11 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="12.9" customHeight="1">
-      <c r="A18" s="318" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="318"/>
+    <row r="18" spans="1:6" ht="12.95" customHeight="1">
+      <c r="A18" s="320" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="320"/>
       <c r="C18" s="45">
         <f>SUM(C4:C13)</f>
         <v>635400</v>
